--- a/public/templates/BOOKENDS_Seed_Template.xlsx
+++ b/public/templates/BOOKENDS_Seed_Template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" r:id="R8953c87863a843e6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOMEs" sheetId="2" r:id="R4b63c393524f4da3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="3" r:id="Rb111639361314781"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="4" r:id="Raa52254e3f4e4473"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="5" r:id="Ra59c0114ee1b42a4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="6" r:id="R6e1b6c28c2f14a53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagement roles" sheetId="7" r:id="Rdbb1d9d8474747bb"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" r:id="R5e00576b954945e6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="9" r:id="R11143746300847ee"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" r:id="Rb270663088fe4ac0"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOMEs" sheetId="2" r:id="R763cce0d8d63448f"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="3" r:id="R6d15d8762c494235"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="4" r:id="R7771891d26674138"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="5" r:id="R8ff760d1f98f404e"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="6" r:id="R8557a19baef24cf6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagement roles" sheetId="7" r:id="R69c35f41658c4c22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" r:id="R64677503624e4ac5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="9" r:id="R78779d0338b74475"/>
   </sheets>
   <definedNames>
     <definedName name="BookendsHomeCodes">'HOMEs'!$A$5:$A$1004</definedName>
@@ -704,7 +704,7 @@
         <v>1. Set up the basics</v>
       </c>
       <c r="C6" s="18" t="str">
-        <v>Add HOMEs and Clients. Define Roles and Skills, then add People.</v>
+        <v>Add People and Clients. Define Roles and Skills; add HOMEs when useful.</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
@@ -767,10 +767,10 @@
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="7" t="str">
-        <v>Owner name</v>
+        <v>HOME / owner</v>
       </c>
       <c r="C12" s="18" t="str">
-        <v>Optional. Leave blank for the workspace owner, or match an existing owner name.</v>
+        <v>Optional for People. New people stay ungrouped and unowned when blank.</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -861,7 +861,7 @@
         <v>First required field</v>
       </c>
       <c r="D20" s="13" t="str">
-        <v>Second required field</v>
+        <v>Second field</v>
       </c>
       <c r="E20" s="13" t="str">
         <v>Meaning</v>
@@ -908,11 +908,9 @@
       <c r="C23" s="16" t="str">
         <v>Taylor Example</v>
       </c>
-      <c r="D23" s="16" t="str">
-        <v>DESIGN</v>
-      </c>
+      <c r="D23" s="16" t="str"/>
       <c r="E23" s="16" t="str">
-        <v>Person belongs to DESIGN</v>
+        <v>Add a person without a HOME</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -946,7 +944,7 @@
         <v>Ready to begin</v>
       </c>
       <c r="C26" s="18" t="str">
-        <v>Open HOMEs and enter your first record in row 5.</v>
+        <v>Open People or Clients and enter your first record in row 5.</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
@@ -985,10 +983,10 @@
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="7" t="str">
-        <v>Optional fields</v>
+        <v>People links</v>
       </c>
       <c r="C30" s="18" t="str">
-        <v>Blank optional cells clear saved values. Blank Owner name uses the workspace owner.</v>
+        <v>Blank HOME / owner keeps existing links. Clear or change a HOME in Admin.</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
@@ -1000,7 +998,7 @@
         <v>Names and roles</v>
       </c>
       <c r="C31" s="18" t="str">
-        <v>Rename in Admin. New names add records. Unlisted delivery roles are kept.</v>
+        <v>Blank HOME matches one unique person name. Duplicate names need a HOME code.</v>
       </c>
       <c r="D31" s="18"/>
       <c r="E31" s="18"/>
@@ -1174,7 +1172,7 @@
         <v>Optional columns</v>
       </c>
       <c r="C46" s="18" t="str">
-        <v>Remove an optional column to keep saved values. Present blank cells clear values.</v>
+        <v>Other optional blanks clear values. Omit columns to keep them. Rename in Admin.</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
@@ -6304,7 +6302,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb886e3b4ae3240b1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b7b1caf77ad434f"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13368,7 +13366,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6a0239d234a4467"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b4dff126a946ce"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13398,7 +13396,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="18" t="str">
-        <v>Name and HOME are required. Separate delivery roles and skills with semicolons. Owner is optional.</v>
+        <v>Only name is required. HOME and owner are optional. Separate delivery roles and skills with semicolons.</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -13416,7 +13414,7 @@
       <c r="A4" s="32" t="str">
         <v>Person name</v>
       </c>
-      <c r="B4" s="36" t="str">
+      <c r="B4" s="30" t="str">
         <v>HOME code</v>
       </c>
       <c r="C4" s="30" t="str">
@@ -13431,7000 +13429,7000 @@
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
       <c r="E7" s="24"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
       <c r="E8" s="24"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
       <c r="E9" s="24"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="24"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
       <c r="E11" s="24"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="24"/>
       <c r="D12" s="24"/>
       <c r="E12" s="24"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="24"/>
       <c r="D13" s="24"/>
       <c r="E13" s="24"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="24"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="24"/>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="24"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="34"/>
-      <c r="B25" s="34"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
+      <c r="B30" s="24"/>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
+      <c r="B31" s="24"/>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
+      <c r="B32" s="24"/>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="34"/>
-      <c r="B33" s="34"/>
+      <c r="B33" s="24"/>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
+      <c r="B34" s="24"/>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
+      <c r="B35" s="24"/>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
+      <c r="B36" s="24"/>
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
       <c r="E36" s="24"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
+      <c r="B37" s="24"/>
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
       <c r="E38" s="24"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
+      <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
+      <c r="B42" s="24"/>
       <c r="C42" s="24"/>
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="34"/>
-      <c r="B43" s="34"/>
+      <c r="B43" s="24"/>
       <c r="C43" s="24"/>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="34"/>
-      <c r="B44" s="34"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="24"/>
       <c r="D44" s="24"/>
       <c r="E44" s="24"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="34"/>
-      <c r="B45" s="34"/>
+      <c r="B45" s="24"/>
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="34"/>
-      <c r="B46" s="34"/>
+      <c r="B46" s="24"/>
       <c r="C46" s="24"/>
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="34"/>
-      <c r="B47" s="34"/>
+      <c r="B47" s="24"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="34"/>
-      <c r="B48" s="34"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="24"/>
       <c r="D48" s="24"/>
       <c r="E48" s="24"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="34"/>
-      <c r="B49" s="34"/>
+      <c r="B49" s="24"/>
       <c r="C49" s="24"/>
       <c r="D49" s="24"/>
       <c r="E49" s="24"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="34"/>
-      <c r="B50" s="34"/>
+      <c r="B50" s="24"/>
       <c r="C50" s="24"/>
       <c r="D50" s="24"/>
       <c r="E50" s="24"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="34"/>
-      <c r="B51" s="34"/>
+      <c r="B51" s="24"/>
       <c r="C51" s="24"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="34"/>
-      <c r="B52" s="34"/>
+      <c r="B52" s="24"/>
       <c r="C52" s="24"/>
       <c r="D52" s="24"/>
       <c r="E52" s="24"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="34"/>
-      <c r="B53" s="34"/>
+      <c r="B53" s="24"/>
       <c r="C53" s="24"/>
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="34"/>
-      <c r="B54" s="34"/>
+      <c r="B54" s="24"/>
       <c r="C54" s="24"/>
       <c r="D54" s="24"/>
       <c r="E54" s="24"/>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="34"/>
-      <c r="B55" s="34"/>
+      <c r="B55" s="24"/>
       <c r="C55" s="24"/>
       <c r="D55" s="24"/>
       <c r="E55" s="24"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="34"/>
-      <c r="B56" s="34"/>
+      <c r="B56" s="24"/>
       <c r="C56" s="24"/>
       <c r="D56" s="24"/>
       <c r="E56" s="24"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="34"/>
-      <c r="B57" s="34"/>
+      <c r="B57" s="24"/>
       <c r="C57" s="24"/>
       <c r="D57" s="24"/>
       <c r="E57" s="24"/>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="34"/>
-      <c r="B58" s="34"/>
+      <c r="B58" s="24"/>
       <c r="C58" s="24"/>
       <c r="D58" s="24"/>
       <c r="E58" s="24"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="34"/>
-      <c r="B59" s="34"/>
+      <c r="B59" s="24"/>
       <c r="C59" s="24"/>
       <c r="D59" s="24"/>
       <c r="E59" s="24"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="34"/>
-      <c r="B60" s="34"/>
+      <c r="B60" s="24"/>
       <c r="C60" s="24"/>
       <c r="D60" s="24"/>
       <c r="E60" s="24"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="34"/>
-      <c r="B61" s="34"/>
+      <c r="B61" s="24"/>
       <c r="C61" s="24"/>
       <c r="D61" s="24"/>
       <c r="E61" s="24"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="34"/>
-      <c r="B62" s="34"/>
+      <c r="B62" s="24"/>
       <c r="C62" s="24"/>
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="34"/>
-      <c r="B63" s="34"/>
+      <c r="B63" s="24"/>
       <c r="C63" s="24"/>
       <c r="D63" s="24"/>
       <c r="E63" s="24"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="34"/>
-      <c r="B64" s="34"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
       <c r="E64" s="24"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="34"/>
-      <c r="B65" s="34"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
       <c r="E65" s="24"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="34"/>
-      <c r="B66" s="34"/>
+      <c r="B66" s="24"/>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
       <c r="E66" s="24"/>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="34"/>
-      <c r="B67" s="34"/>
+      <c r="B67" s="24"/>
       <c r="C67" s="24"/>
       <c r="D67" s="24"/>
       <c r="E67" s="24"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="34"/>
-      <c r="B68" s="34"/>
+      <c r="B68" s="24"/>
       <c r="C68" s="24"/>
       <c r="D68" s="24"/>
       <c r="E68" s="24"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
+      <c r="B69" s="24"/>
       <c r="C69" s="24"/>
       <c r="D69" s="24"/>
       <c r="E69" s="24"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
+      <c r="B70" s="24"/>
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
       <c r="E70" s="24"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
+      <c r="B71" s="24"/>
       <c r="C71" s="24"/>
       <c r="D71" s="24"/>
       <c r="E71" s="24"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="34"/>
-      <c r="B72" s="34"/>
+      <c r="B72" s="24"/>
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
       <c r="E72" s="24"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="34"/>
-      <c r="B73" s="34"/>
+      <c r="B73" s="24"/>
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
       <c r="E73" s="24"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="34"/>
-      <c r="B74" s="34"/>
+      <c r="B74" s="24"/>
       <c r="C74" s="24"/>
       <c r="D74" s="24"/>
       <c r="E74" s="24"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="34"/>
-      <c r="B75" s="34"/>
+      <c r="B75" s="24"/>
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
       <c r="E75" s="24"/>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="34"/>
-      <c r="B76" s="34"/>
+      <c r="B76" s="24"/>
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
       <c r="E76" s="24"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="34"/>
-      <c r="B77" s="34"/>
+      <c r="B77" s="24"/>
       <c r="C77" s="24"/>
       <c r="D77" s="24"/>
       <c r="E77" s="24"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="34"/>
-      <c r="B78" s="34"/>
+      <c r="B78" s="24"/>
       <c r="C78" s="24"/>
       <c r="D78" s="24"/>
       <c r="E78" s="24"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="34"/>
-      <c r="B79" s="34"/>
+      <c r="B79" s="24"/>
       <c r="C79" s="24"/>
       <c r="D79" s="24"/>
       <c r="E79" s="24"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="34"/>
-      <c r="B80" s="34"/>
+      <c r="B80" s="24"/>
       <c r="C80" s="24"/>
       <c r="D80" s="24"/>
       <c r="E80" s="24"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="34"/>
-      <c r="B81" s="34"/>
+      <c r="B81" s="24"/>
       <c r="C81" s="24"/>
       <c r="D81" s="24"/>
       <c r="E81" s="24"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="34"/>
-      <c r="B82" s="34"/>
+      <c r="B82" s="24"/>
       <c r="C82" s="24"/>
       <c r="D82" s="24"/>
       <c r="E82" s="24"/>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="34"/>
-      <c r="B83" s="34"/>
+      <c r="B83" s="24"/>
       <c r="C83" s="24"/>
       <c r="D83" s="24"/>
       <c r="E83" s="24"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="34"/>
-      <c r="B84" s="34"/>
+      <c r="B84" s="24"/>
       <c r="C84" s="24"/>
       <c r="D84" s="24"/>
       <c r="E84" s="24"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="34"/>
-      <c r="B85" s="34"/>
+      <c r="B85" s="24"/>
       <c r="C85" s="24"/>
       <c r="D85" s="24"/>
       <c r="E85" s="24"/>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="34"/>
-      <c r="B86" s="34"/>
+      <c r="B86" s="24"/>
       <c r="C86" s="24"/>
       <c r="D86" s="24"/>
       <c r="E86" s="24"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="34"/>
-      <c r="B87" s="34"/>
+      <c r="B87" s="24"/>
       <c r="C87" s="24"/>
       <c r="D87" s="24"/>
       <c r="E87" s="24"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="34"/>
-      <c r="B88" s="34"/>
+      <c r="B88" s="24"/>
       <c r="C88" s="24"/>
       <c r="D88" s="24"/>
       <c r="E88" s="24"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="34"/>
-      <c r="B89" s="34"/>
+      <c r="B89" s="24"/>
       <c r="C89" s="24"/>
       <c r="D89" s="24"/>
       <c r="E89" s="24"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="34"/>
-      <c r="B90" s="34"/>
+      <c r="B90" s="24"/>
       <c r="C90" s="24"/>
       <c r="D90" s="24"/>
       <c r="E90" s="24"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="34"/>
-      <c r="B91" s="34"/>
+      <c r="B91" s="24"/>
       <c r="C91" s="24"/>
       <c r="D91" s="24"/>
       <c r="E91" s="24"/>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="34"/>
-      <c r="B92" s="34"/>
+      <c r="B92" s="24"/>
       <c r="C92" s="24"/>
       <c r="D92" s="24"/>
       <c r="E92" s="24"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="34"/>
-      <c r="B93" s="34"/>
+      <c r="B93" s="24"/>
       <c r="C93" s="24"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="34"/>
-      <c r="B94" s="34"/>
+      <c r="B94" s="24"/>
       <c r="C94" s="24"/>
       <c r="D94" s="24"/>
       <c r="E94" s="24"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="34"/>
-      <c r="B95" s="34"/>
+      <c r="B95" s="24"/>
       <c r="C95" s="24"/>
       <c r="D95" s="24"/>
       <c r="E95" s="24"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="34"/>
-      <c r="B96" s="34"/>
+      <c r="B96" s="24"/>
       <c r="C96" s="24"/>
       <c r="D96" s="24"/>
       <c r="E96" s="24"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="34"/>
-      <c r="B97" s="34"/>
+      <c r="B97" s="24"/>
       <c r="C97" s="24"/>
       <c r="D97" s="24"/>
       <c r="E97" s="24"/>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="34"/>
-      <c r="B98" s="34"/>
+      <c r="B98" s="24"/>
       <c r="C98" s="24"/>
       <c r="D98" s="24"/>
       <c r="E98" s="24"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
+      <c r="B99" s="24"/>
       <c r="C99" s="24"/>
       <c r="D99" s="24"/>
       <c r="E99" s="24"/>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
+      <c r="B100" s="24"/>
       <c r="C100" s="24"/>
       <c r="D100" s="24"/>
       <c r="E100" s="24"/>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
+      <c r="B101" s="24"/>
       <c r="C101" s="24"/>
       <c r="D101" s="24"/>
       <c r="E101" s="24"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="34"/>
-      <c r="B102" s="34"/>
+      <c r="B102" s="24"/>
       <c r="C102" s="24"/>
       <c r="D102" s="24"/>
       <c r="E102" s="24"/>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="34"/>
-      <c r="B103" s="34"/>
+      <c r="B103" s="24"/>
       <c r="C103" s="24"/>
       <c r="D103" s="24"/>
       <c r="E103" s="24"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="34"/>
-      <c r="B104" s="34"/>
+      <c r="B104" s="24"/>
       <c r="C104" s="24"/>
       <c r="D104" s="24"/>
       <c r="E104" s="24"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="34"/>
-      <c r="B105" s="34"/>
+      <c r="B105" s="24"/>
       <c r="C105" s="24"/>
       <c r="D105" s="24"/>
       <c r="E105" s="24"/>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="34"/>
-      <c r="B106" s="34"/>
+      <c r="B106" s="24"/>
       <c r="C106" s="24"/>
       <c r="D106" s="24"/>
       <c r="E106" s="24"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="34"/>
-      <c r="B107" s="34"/>
+      <c r="B107" s="24"/>
       <c r="C107" s="24"/>
       <c r="D107" s="24"/>
       <c r="E107" s="24"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="34"/>
-      <c r="B108" s="34"/>
+      <c r="B108" s="24"/>
       <c r="C108" s="24"/>
       <c r="D108" s="24"/>
       <c r="E108" s="24"/>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="34"/>
-      <c r="B109" s="34"/>
+      <c r="B109" s="24"/>
       <c r="C109" s="24"/>
       <c r="D109" s="24"/>
       <c r="E109" s="24"/>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="34"/>
-      <c r="B110" s="34"/>
+      <c r="B110" s="24"/>
       <c r="C110" s="24"/>
       <c r="D110" s="24"/>
       <c r="E110" s="24"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="34"/>
-      <c r="B111" s="34"/>
+      <c r="B111" s="24"/>
       <c r="C111" s="24"/>
       <c r="D111" s="24"/>
       <c r="E111" s="24"/>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="34"/>
-      <c r="B112" s="34"/>
+      <c r="B112" s="24"/>
       <c r="C112" s="24"/>
       <c r="D112" s="24"/>
       <c r="E112" s="24"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="34"/>
-      <c r="B113" s="34"/>
+      <c r="B113" s="24"/>
       <c r="C113" s="24"/>
       <c r="D113" s="24"/>
       <c r="E113" s="24"/>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="34"/>
-      <c r="B114" s="34"/>
+      <c r="B114" s="24"/>
       <c r="C114" s="24"/>
       <c r="D114" s="24"/>
       <c r="E114" s="24"/>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="34"/>
-      <c r="B115" s="34"/>
+      <c r="B115" s="24"/>
       <c r="C115" s="24"/>
       <c r="D115" s="24"/>
       <c r="E115" s="24"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="34"/>
-      <c r="B116" s="34"/>
+      <c r="B116" s="24"/>
       <c r="C116" s="24"/>
       <c r="D116" s="24"/>
       <c r="E116" s="24"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="34"/>
-      <c r="B117" s="34"/>
+      <c r="B117" s="24"/>
       <c r="C117" s="24"/>
       <c r="D117" s="24"/>
       <c r="E117" s="24"/>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="34"/>
-      <c r="B118" s="34"/>
+      <c r="B118" s="24"/>
       <c r="C118" s="24"/>
       <c r="D118" s="24"/>
       <c r="E118" s="24"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="34"/>
-      <c r="B119" s="34"/>
+      <c r="B119" s="24"/>
       <c r="C119" s="24"/>
       <c r="D119" s="24"/>
       <c r="E119" s="24"/>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="34"/>
-      <c r="B120" s="34"/>
+      <c r="B120" s="24"/>
       <c r="C120" s="24"/>
       <c r="D120" s="24"/>
       <c r="E120" s="24"/>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="34"/>
-      <c r="B121" s="34"/>
+      <c r="B121" s="24"/>
       <c r="C121" s="24"/>
       <c r="D121" s="24"/>
       <c r="E121" s="24"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="34"/>
-      <c r="B122" s="34"/>
+      <c r="B122" s="24"/>
       <c r="C122" s="24"/>
       <c r="D122" s="24"/>
       <c r="E122" s="24"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="34"/>
-      <c r="B123" s="34"/>
+      <c r="B123" s="24"/>
       <c r="C123" s="24"/>
       <c r="D123" s="24"/>
       <c r="E123" s="24"/>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="34"/>
-      <c r="B124" s="34"/>
+      <c r="B124" s="24"/>
       <c r="C124" s="24"/>
       <c r="D124" s="24"/>
       <c r="E124" s="24"/>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="34"/>
-      <c r="B125" s="34"/>
+      <c r="B125" s="24"/>
       <c r="C125" s="24"/>
       <c r="D125" s="24"/>
       <c r="E125" s="24"/>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="34"/>
-      <c r="B126" s="34"/>
+      <c r="B126" s="24"/>
       <c r="C126" s="24"/>
       <c r="D126" s="24"/>
       <c r="E126" s="24"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="34"/>
-      <c r="B127" s="34"/>
+      <c r="B127" s="24"/>
       <c r="C127" s="24"/>
       <c r="D127" s="24"/>
       <c r="E127" s="24"/>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="34"/>
-      <c r="B128" s="34"/>
+      <c r="B128" s="24"/>
       <c r="C128" s="24"/>
       <c r="D128" s="24"/>
       <c r="E128" s="24"/>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="34"/>
-      <c r="B129" s="34"/>
+      <c r="B129" s="24"/>
       <c r="C129" s="24"/>
       <c r="D129" s="24"/>
       <c r="E129" s="24"/>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="34"/>
-      <c r="B130" s="34"/>
+      <c r="B130" s="24"/>
       <c r="C130" s="24"/>
       <c r="D130" s="24"/>
       <c r="E130" s="24"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="34"/>
-      <c r="B131" s="34"/>
+      <c r="B131" s="24"/>
       <c r="C131" s="24"/>
       <c r="D131" s="24"/>
       <c r="E131" s="24"/>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="34"/>
-      <c r="B132" s="34"/>
+      <c r="B132" s="24"/>
       <c r="C132" s="24"/>
       <c r="D132" s="24"/>
       <c r="E132" s="24"/>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="34"/>
-      <c r="B133" s="34"/>
+      <c r="B133" s="24"/>
       <c r="C133" s="24"/>
       <c r="D133" s="24"/>
       <c r="E133" s="24"/>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="34"/>
-      <c r="B134" s="34"/>
+      <c r="B134" s="24"/>
       <c r="C134" s="24"/>
       <c r="D134" s="24"/>
       <c r="E134" s="24"/>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="34"/>
-      <c r="B135" s="34"/>
+      <c r="B135" s="24"/>
       <c r="C135" s="24"/>
       <c r="D135" s="24"/>
       <c r="E135" s="24"/>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="34"/>
-      <c r="B136" s="34"/>
+      <c r="B136" s="24"/>
       <c r="C136" s="24"/>
       <c r="D136" s="24"/>
       <c r="E136" s="24"/>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="34"/>
-      <c r="B137" s="34"/>
+      <c r="B137" s="24"/>
       <c r="C137" s="24"/>
       <c r="D137" s="24"/>
       <c r="E137" s="24"/>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="34"/>
-      <c r="B138" s="34"/>
+      <c r="B138" s="24"/>
       <c r="C138" s="24"/>
       <c r="D138" s="24"/>
       <c r="E138" s="24"/>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="34"/>
-      <c r="B139" s="34"/>
+      <c r="B139" s="24"/>
       <c r="C139" s="24"/>
       <c r="D139" s="24"/>
       <c r="E139" s="24"/>
     </row>
     <row r="140" ht="24" customHeight="1">
       <c r="A140" s="34"/>
-      <c r="B140" s="34"/>
+      <c r="B140" s="24"/>
       <c r="C140" s="24"/>
       <c r="D140" s="24"/>
       <c r="E140" s="24"/>
     </row>
     <row r="141" ht="24" customHeight="1">
       <c r="A141" s="34"/>
-      <c r="B141" s="34"/>
+      <c r="B141" s="24"/>
       <c r="C141" s="24"/>
       <c r="D141" s="24"/>
       <c r="E141" s="24"/>
     </row>
     <row r="142" ht="24" customHeight="1">
       <c r="A142" s="34"/>
-      <c r="B142" s="34"/>
+      <c r="B142" s="24"/>
       <c r="C142" s="24"/>
       <c r="D142" s="24"/>
       <c r="E142" s="24"/>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="34"/>
-      <c r="B143" s="34"/>
+      <c r="B143" s="24"/>
       <c r="C143" s="24"/>
       <c r="D143" s="24"/>
       <c r="E143" s="24"/>
     </row>
     <row r="144" ht="24" customHeight="1">
       <c r="A144" s="34"/>
-      <c r="B144" s="34"/>
+      <c r="B144" s="24"/>
       <c r="C144" s="24"/>
       <c r="D144" s="24"/>
       <c r="E144" s="24"/>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="34"/>
-      <c r="B145" s="34"/>
+      <c r="B145" s="24"/>
       <c r="C145" s="24"/>
       <c r="D145" s="24"/>
       <c r="E145" s="24"/>
     </row>
     <row r="146" ht="24" customHeight="1">
       <c r="A146" s="34"/>
-      <c r="B146" s="34"/>
+      <c r="B146" s="24"/>
       <c r="C146" s="24"/>
       <c r="D146" s="24"/>
       <c r="E146" s="24"/>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="34"/>
-      <c r="B147" s="34"/>
+      <c r="B147" s="24"/>
       <c r="C147" s="24"/>
       <c r="D147" s="24"/>
       <c r="E147" s="24"/>
     </row>
     <row r="148" ht="24" customHeight="1">
       <c r="A148" s="34"/>
-      <c r="B148" s="34"/>
+      <c r="B148" s="24"/>
       <c r="C148" s="24"/>
       <c r="D148" s="24"/>
       <c r="E148" s="24"/>
     </row>
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="34"/>
-      <c r="B149" s="34"/>
+      <c r="B149" s="24"/>
       <c r="C149" s="24"/>
       <c r="D149" s="24"/>
       <c r="E149" s="24"/>
     </row>
     <row r="150" ht="24" customHeight="1">
       <c r="A150" s="34"/>
-      <c r="B150" s="34"/>
+      <c r="B150" s="24"/>
       <c r="C150" s="24"/>
       <c r="D150" s="24"/>
       <c r="E150" s="24"/>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="34"/>
-      <c r="B151" s="34"/>
+      <c r="B151" s="24"/>
       <c r="C151" s="24"/>
       <c r="D151" s="24"/>
       <c r="E151" s="24"/>
     </row>
     <row r="152" ht="24" customHeight="1">
       <c r="A152" s="34"/>
-      <c r="B152" s="34"/>
+      <c r="B152" s="24"/>
       <c r="C152" s="24"/>
       <c r="D152" s="24"/>
       <c r="E152" s="24"/>
     </row>
     <row r="153" ht="24" customHeight="1">
       <c r="A153" s="34"/>
-      <c r="B153" s="34"/>
+      <c r="B153" s="24"/>
       <c r="C153" s="24"/>
       <c r="D153" s="24"/>
       <c r="E153" s="24"/>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="34"/>
-      <c r="B154" s="34"/>
+      <c r="B154" s="24"/>
       <c r="C154" s="24"/>
       <c r="D154" s="24"/>
       <c r="E154" s="24"/>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="34"/>
-      <c r="B155" s="34"/>
+      <c r="B155" s="24"/>
       <c r="C155" s="24"/>
       <c r="D155" s="24"/>
       <c r="E155" s="24"/>
     </row>
     <row r="156" ht="24" customHeight="1">
       <c r="A156" s="34"/>
-      <c r="B156" s="34"/>
+      <c r="B156" s="24"/>
       <c r="C156" s="24"/>
       <c r="D156" s="24"/>
       <c r="E156" s="24"/>
     </row>
     <row r="157" ht="24" customHeight="1">
       <c r="A157" s="34"/>
-      <c r="B157" s="34"/>
+      <c r="B157" s="24"/>
       <c r="C157" s="24"/>
       <c r="D157" s="24"/>
       <c r="E157" s="24"/>
     </row>
     <row r="158" ht="24" customHeight="1">
       <c r="A158" s="34"/>
-      <c r="B158" s="34"/>
+      <c r="B158" s="24"/>
       <c r="C158" s="24"/>
       <c r="D158" s="24"/>
       <c r="E158" s="24"/>
     </row>
     <row r="159" ht="24" customHeight="1">
       <c r="A159" s="34"/>
-      <c r="B159" s="34"/>
+      <c r="B159" s="24"/>
       <c r="C159" s="24"/>
       <c r="D159" s="24"/>
       <c r="E159" s="24"/>
     </row>
     <row r="160" ht="24" customHeight="1">
       <c r="A160" s="34"/>
-      <c r="B160" s="34"/>
+      <c r="B160" s="24"/>
       <c r="C160" s="24"/>
       <c r="D160" s="24"/>
       <c r="E160" s="24"/>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="34"/>
-      <c r="B161" s="34"/>
+      <c r="B161" s="24"/>
       <c r="C161" s="24"/>
       <c r="D161" s="24"/>
       <c r="E161" s="24"/>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="34"/>
-      <c r="B162" s="34"/>
+      <c r="B162" s="24"/>
       <c r="C162" s="24"/>
       <c r="D162" s="24"/>
       <c r="E162" s="24"/>
     </row>
     <row r="163" ht="24" customHeight="1">
       <c r="A163" s="34"/>
-      <c r="B163" s="34"/>
+      <c r="B163" s="24"/>
       <c r="C163" s="24"/>
       <c r="D163" s="24"/>
       <c r="E163" s="24"/>
     </row>
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="34"/>
-      <c r="B164" s="34"/>
+      <c r="B164" s="24"/>
       <c r="C164" s="24"/>
       <c r="D164" s="24"/>
       <c r="E164" s="24"/>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="34"/>
-      <c r="B165" s="34"/>
+      <c r="B165" s="24"/>
       <c r="C165" s="24"/>
       <c r="D165" s="24"/>
       <c r="E165" s="24"/>
     </row>
     <row r="166" ht="24" customHeight="1">
       <c r="A166" s="34"/>
-      <c r="B166" s="34"/>
+      <c r="B166" s="24"/>
       <c r="C166" s="24"/>
       <c r="D166" s="24"/>
       <c r="E166" s="24"/>
     </row>
     <row r="167" ht="24" customHeight="1">
       <c r="A167" s="34"/>
-      <c r="B167" s="34"/>
+      <c r="B167" s="24"/>
       <c r="C167" s="24"/>
       <c r="D167" s="24"/>
       <c r="E167" s="24"/>
     </row>
     <row r="168" ht="24" customHeight="1">
       <c r="A168" s="34"/>
-      <c r="B168" s="34"/>
+      <c r="B168" s="24"/>
       <c r="C168" s="24"/>
       <c r="D168" s="24"/>
       <c r="E168" s="24"/>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="34"/>
-      <c r="B169" s="34"/>
+      <c r="B169" s="24"/>
       <c r="C169" s="24"/>
       <c r="D169" s="24"/>
       <c r="E169" s="24"/>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="34"/>
-      <c r="B170" s="34"/>
+      <c r="B170" s="24"/>
       <c r="C170" s="24"/>
       <c r="D170" s="24"/>
       <c r="E170" s="24"/>
     </row>
     <row r="171" ht="24" customHeight="1">
       <c r="A171" s="34"/>
-      <c r="B171" s="34"/>
+      <c r="B171" s="24"/>
       <c r="C171" s="24"/>
       <c r="D171" s="24"/>
       <c r="E171" s="24"/>
     </row>
     <row r="172" ht="24" customHeight="1">
       <c r="A172" s="34"/>
-      <c r="B172" s="34"/>
+      <c r="B172" s="24"/>
       <c r="C172" s="24"/>
       <c r="D172" s="24"/>
       <c r="E172" s="24"/>
     </row>
     <row r="173" ht="24" customHeight="1">
       <c r="A173" s="34"/>
-      <c r="B173" s="34"/>
+      <c r="B173" s="24"/>
       <c r="C173" s="24"/>
       <c r="D173" s="24"/>
       <c r="E173" s="24"/>
     </row>
     <row r="174" ht="24" customHeight="1">
       <c r="A174" s="34"/>
-      <c r="B174" s="34"/>
+      <c r="B174" s="24"/>
       <c r="C174" s="24"/>
       <c r="D174" s="24"/>
       <c r="E174" s="24"/>
     </row>
     <row r="175" ht="24" customHeight="1">
       <c r="A175" s="34"/>
-      <c r="B175" s="34"/>
+      <c r="B175" s="24"/>
       <c r="C175" s="24"/>
       <c r="D175" s="24"/>
       <c r="E175" s="24"/>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="34"/>
-      <c r="B176" s="34"/>
+      <c r="B176" s="24"/>
       <c r="C176" s="24"/>
       <c r="D176" s="24"/>
       <c r="E176" s="24"/>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="34"/>
-      <c r="B177" s="34"/>
+      <c r="B177" s="24"/>
       <c r="C177" s="24"/>
       <c r="D177" s="24"/>
       <c r="E177" s="24"/>
     </row>
     <row r="178" ht="24" customHeight="1">
       <c r="A178" s="34"/>
-      <c r="B178" s="34"/>
+      <c r="B178" s="24"/>
       <c r="C178" s="24"/>
       <c r="D178" s="24"/>
       <c r="E178" s="24"/>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="34"/>
-      <c r="B179" s="34"/>
+      <c r="B179" s="24"/>
       <c r="C179" s="24"/>
       <c r="D179" s="24"/>
       <c r="E179" s="24"/>
     </row>
     <row r="180" ht="24" customHeight="1">
       <c r="A180" s="34"/>
-      <c r="B180" s="34"/>
+      <c r="B180" s="24"/>
       <c r="C180" s="24"/>
       <c r="D180" s="24"/>
       <c r="E180" s="24"/>
     </row>
     <row r="181" ht="24" customHeight="1">
       <c r="A181" s="34"/>
-      <c r="B181" s="34"/>
+      <c r="B181" s="24"/>
       <c r="C181" s="24"/>
       <c r="D181" s="24"/>
       <c r="E181" s="24"/>
     </row>
     <row r="182" ht="24" customHeight="1">
       <c r="A182" s="34"/>
-      <c r="B182" s="34"/>
+      <c r="B182" s="24"/>
       <c r="C182" s="24"/>
       <c r="D182" s="24"/>
       <c r="E182" s="24"/>
     </row>
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="34"/>
-      <c r="B183" s="34"/>
+      <c r="B183" s="24"/>
       <c r="C183" s="24"/>
       <c r="D183" s="24"/>
       <c r="E183" s="24"/>
     </row>
     <row r="184" ht="24" customHeight="1">
       <c r="A184" s="34"/>
-      <c r="B184" s="34"/>
+      <c r="B184" s="24"/>
       <c r="C184" s="24"/>
       <c r="D184" s="24"/>
       <c r="E184" s="24"/>
     </row>
     <row r="185" ht="24" customHeight="1">
       <c r="A185" s="34"/>
-      <c r="B185" s="34"/>
+      <c r="B185" s="24"/>
       <c r="C185" s="24"/>
       <c r="D185" s="24"/>
       <c r="E185" s="24"/>
     </row>
     <row r="186" ht="24" customHeight="1">
       <c r="A186" s="34"/>
-      <c r="B186" s="34"/>
+      <c r="B186" s="24"/>
       <c r="C186" s="24"/>
       <c r="D186" s="24"/>
       <c r="E186" s="24"/>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="34"/>
-      <c r="B187" s="34"/>
+      <c r="B187" s="24"/>
       <c r="C187" s="24"/>
       <c r="D187" s="24"/>
       <c r="E187" s="24"/>
     </row>
     <row r="188" ht="24" customHeight="1">
       <c r="A188" s="34"/>
-      <c r="B188" s="34"/>
+      <c r="B188" s="24"/>
       <c r="C188" s="24"/>
       <c r="D188" s="24"/>
       <c r="E188" s="24"/>
     </row>
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="34"/>
-      <c r="B189" s="34"/>
+      <c r="B189" s="24"/>
       <c r="C189" s="24"/>
       <c r="D189" s="24"/>
       <c r="E189" s="24"/>
     </row>
     <row r="190" ht="24" customHeight="1">
       <c r="A190" s="34"/>
-      <c r="B190" s="34"/>
+      <c r="B190" s="24"/>
       <c r="C190" s="24"/>
       <c r="D190" s="24"/>
       <c r="E190" s="24"/>
     </row>
     <row r="191" ht="24" customHeight="1">
       <c r="A191" s="34"/>
-      <c r="B191" s="34"/>
+      <c r="B191" s="24"/>
       <c r="C191" s="24"/>
       <c r="D191" s="24"/>
       <c r="E191" s="24"/>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="34"/>
-      <c r="B192" s="34"/>
+      <c r="B192" s="24"/>
       <c r="C192" s="24"/>
       <c r="D192" s="24"/>
       <c r="E192" s="24"/>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="34"/>
-      <c r="B193" s="34"/>
+      <c r="B193" s="24"/>
       <c r="C193" s="24"/>
       <c r="D193" s="24"/>
       <c r="E193" s="24"/>
     </row>
     <row r="194" ht="24" customHeight="1">
       <c r="A194" s="34"/>
-      <c r="B194" s="34"/>
+      <c r="B194" s="24"/>
       <c r="C194" s="24"/>
       <c r="D194" s="24"/>
       <c r="E194" s="24"/>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="34"/>
-      <c r="B195" s="34"/>
+      <c r="B195" s="24"/>
       <c r="C195" s="24"/>
       <c r="D195" s="24"/>
       <c r="E195" s="24"/>
     </row>
     <row r="196" ht="24" customHeight="1">
       <c r="A196" s="34"/>
-      <c r="B196" s="34"/>
+      <c r="B196" s="24"/>
       <c r="C196" s="24"/>
       <c r="D196" s="24"/>
       <c r="E196" s="24"/>
     </row>
     <row r="197" ht="24" customHeight="1">
       <c r="A197" s="34"/>
-      <c r="B197" s="34"/>
+      <c r="B197" s="24"/>
       <c r="C197" s="24"/>
       <c r="D197" s="24"/>
       <c r="E197" s="24"/>
     </row>
     <row r="198" ht="24" customHeight="1">
       <c r="A198" s="34"/>
-      <c r="B198" s="34"/>
+      <c r="B198" s="24"/>
       <c r="C198" s="24"/>
       <c r="D198" s="24"/>
       <c r="E198" s="24"/>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="34"/>
-      <c r="B199" s="34"/>
+      <c r="B199" s="24"/>
       <c r="C199" s="24"/>
       <c r="D199" s="24"/>
       <c r="E199" s="24"/>
     </row>
     <row r="200" ht="24" customHeight="1">
       <c r="A200" s="34"/>
-      <c r="B200" s="34"/>
+      <c r="B200" s="24"/>
       <c r="C200" s="24"/>
       <c r="D200" s="24"/>
       <c r="E200" s="24"/>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="34"/>
-      <c r="B201" s="34"/>
+      <c r="B201" s="24"/>
       <c r="C201" s="24"/>
       <c r="D201" s="24"/>
       <c r="E201" s="24"/>
     </row>
     <row r="202" ht="24" customHeight="1">
       <c r="A202" s="34"/>
-      <c r="B202" s="34"/>
+      <c r="B202" s="24"/>
       <c r="C202" s="24"/>
       <c r="D202" s="24"/>
       <c r="E202" s="24"/>
     </row>
     <row r="203" ht="24" customHeight="1">
       <c r="A203" s="34"/>
-      <c r="B203" s="34"/>
+      <c r="B203" s="24"/>
       <c r="C203" s="24"/>
       <c r="D203" s="24"/>
       <c r="E203" s="24"/>
     </row>
     <row r="204" ht="24" customHeight="1">
       <c r="A204" s="34"/>
-      <c r="B204" s="34"/>
+      <c r="B204" s="24"/>
       <c r="C204" s="24"/>
       <c r="D204" s="24"/>
       <c r="E204" s="24"/>
     </row>
     <row r="205" ht="24" customHeight="1">
       <c r="A205" s="34"/>
-      <c r="B205" s="34"/>
+      <c r="B205" s="24"/>
       <c r="C205" s="24"/>
       <c r="D205" s="24"/>
       <c r="E205" s="24"/>
     </row>
     <row r="206" ht="24" customHeight="1">
       <c r="A206" s="34"/>
-      <c r="B206" s="34"/>
+      <c r="B206" s="24"/>
       <c r="C206" s="24"/>
       <c r="D206" s="24"/>
       <c r="E206" s="24"/>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="34"/>
-      <c r="B207" s="34"/>
+      <c r="B207" s="24"/>
       <c r="C207" s="24"/>
       <c r="D207" s="24"/>
       <c r="E207" s="24"/>
     </row>
     <row r="208" ht="24" customHeight="1">
       <c r="A208" s="34"/>
-      <c r="B208" s="34"/>
+      <c r="B208" s="24"/>
       <c r="C208" s="24"/>
       <c r="D208" s="24"/>
       <c r="E208" s="24"/>
     </row>
     <row r="209" ht="24" customHeight="1">
       <c r="A209" s="34"/>
-      <c r="B209" s="34"/>
+      <c r="B209" s="24"/>
       <c r="C209" s="24"/>
       <c r="D209" s="24"/>
       <c r="E209" s="24"/>
     </row>
     <row r="210" ht="24" customHeight="1">
       <c r="A210" s="34"/>
-      <c r="B210" s="34"/>
+      <c r="B210" s="24"/>
       <c r="C210" s="24"/>
       <c r="D210" s="24"/>
       <c r="E210" s="24"/>
     </row>
     <row r="211" ht="24" customHeight="1">
       <c r="A211" s="34"/>
-      <c r="B211" s="34"/>
+      <c r="B211" s="24"/>
       <c r="C211" s="24"/>
       <c r="D211" s="24"/>
       <c r="E211" s="24"/>
     </row>
     <row r="212" ht="24" customHeight="1">
       <c r="A212" s="34"/>
-      <c r="B212" s="34"/>
+      <c r="B212" s="24"/>
       <c r="C212" s="24"/>
       <c r="D212" s="24"/>
       <c r="E212" s="24"/>
     </row>
     <row r="213" ht="24" customHeight="1">
       <c r="A213" s="34"/>
-      <c r="B213" s="34"/>
+      <c r="B213" s="24"/>
       <c r="C213" s="24"/>
       <c r="D213" s="24"/>
       <c r="E213" s="24"/>
     </row>
     <row r="214" ht="24" customHeight="1">
       <c r="A214" s="34"/>
-      <c r="B214" s="34"/>
+      <c r="B214" s="24"/>
       <c r="C214" s="24"/>
       <c r="D214" s="24"/>
       <c r="E214" s="24"/>
     </row>
     <row r="215" ht="24" customHeight="1">
       <c r="A215" s="34"/>
-      <c r="B215" s="34"/>
+      <c r="B215" s="24"/>
       <c r="C215" s="24"/>
       <c r="D215" s="24"/>
       <c r="E215" s="24"/>
     </row>
     <row r="216" ht="24" customHeight="1">
       <c r="A216" s="34"/>
-      <c r="B216" s="34"/>
+      <c r="B216" s="24"/>
       <c r="C216" s="24"/>
       <c r="D216" s="24"/>
       <c r="E216" s="24"/>
     </row>
     <row r="217" ht="24" customHeight="1">
       <c r="A217" s="34"/>
-      <c r="B217" s="34"/>
+      <c r="B217" s="24"/>
       <c r="C217" s="24"/>
       <c r="D217" s="24"/>
       <c r="E217" s="24"/>
     </row>
     <row r="218" ht="24" customHeight="1">
       <c r="A218" s="34"/>
-      <c r="B218" s="34"/>
+      <c r="B218" s="24"/>
       <c r="C218" s="24"/>
       <c r="D218" s="24"/>
       <c r="E218" s="24"/>
     </row>
     <row r="219" ht="24" customHeight="1">
       <c r="A219" s="34"/>
-      <c r="B219" s="34"/>
+      <c r="B219" s="24"/>
       <c r="C219" s="24"/>
       <c r="D219" s="24"/>
       <c r="E219" s="24"/>
     </row>
     <row r="220" ht="24" customHeight="1">
       <c r="A220" s="34"/>
-      <c r="B220" s="34"/>
+      <c r="B220" s="24"/>
       <c r="C220" s="24"/>
       <c r="D220" s="24"/>
       <c r="E220" s="24"/>
     </row>
     <row r="221" ht="24" customHeight="1">
       <c r="A221" s="34"/>
-      <c r="B221" s="34"/>
+      <c r="B221" s="24"/>
       <c r="C221" s="24"/>
       <c r="D221" s="24"/>
       <c r="E221" s="24"/>
     </row>
     <row r="222" ht="24" customHeight="1">
       <c r="A222" s="34"/>
-      <c r="B222" s="34"/>
+      <c r="B222" s="24"/>
       <c r="C222" s="24"/>
       <c r="D222" s="24"/>
       <c r="E222" s="24"/>
     </row>
     <row r="223" ht="24" customHeight="1">
       <c r="A223" s="34"/>
-      <c r="B223" s="34"/>
+      <c r="B223" s="24"/>
       <c r="C223" s="24"/>
       <c r="D223" s="24"/>
       <c r="E223" s="24"/>
     </row>
     <row r="224" ht="24" customHeight="1">
       <c r="A224" s="34"/>
-      <c r="B224" s="34"/>
+      <c r="B224" s="24"/>
       <c r="C224" s="24"/>
       <c r="D224" s="24"/>
       <c r="E224" s="24"/>
     </row>
     <row r="225" ht="24" customHeight="1">
       <c r="A225" s="34"/>
-      <c r="B225" s="34"/>
+      <c r="B225" s="24"/>
       <c r="C225" s="24"/>
       <c r="D225" s="24"/>
       <c r="E225" s="24"/>
     </row>
     <row r="226" ht="24" customHeight="1">
       <c r="A226" s="34"/>
-      <c r="B226" s="34"/>
+      <c r="B226" s="24"/>
       <c r="C226" s="24"/>
       <c r="D226" s="24"/>
       <c r="E226" s="24"/>
     </row>
     <row r="227" ht="24" customHeight="1">
       <c r="A227" s="34"/>
-      <c r="B227" s="34"/>
+      <c r="B227" s="24"/>
       <c r="C227" s="24"/>
       <c r="D227" s="24"/>
       <c r="E227" s="24"/>
     </row>
     <row r="228" ht="24" customHeight="1">
       <c r="A228" s="34"/>
-      <c r="B228" s="34"/>
+      <c r="B228" s="24"/>
       <c r="C228" s="24"/>
       <c r="D228" s="24"/>
       <c r="E228" s="24"/>
     </row>
     <row r="229" ht="24" customHeight="1">
       <c r="A229" s="34"/>
-      <c r="B229" s="34"/>
+      <c r="B229" s="24"/>
       <c r="C229" s="24"/>
       <c r="D229" s="24"/>
       <c r="E229" s="24"/>
     </row>
     <row r="230" ht="24" customHeight="1">
       <c r="A230" s="34"/>
-      <c r="B230" s="34"/>
+      <c r="B230" s="24"/>
       <c r="C230" s="24"/>
       <c r="D230" s="24"/>
       <c r="E230" s="24"/>
     </row>
     <row r="231" ht="24" customHeight="1">
       <c r="A231" s="34"/>
-      <c r="B231" s="34"/>
+      <c r="B231" s="24"/>
       <c r="C231" s="24"/>
       <c r="D231" s="24"/>
       <c r="E231" s="24"/>
     </row>
     <row r="232" ht="24" customHeight="1">
       <c r="A232" s="34"/>
-      <c r="B232" s="34"/>
+      <c r="B232" s="24"/>
       <c r="C232" s="24"/>
       <c r="D232" s="24"/>
       <c r="E232" s="24"/>
     </row>
     <row r="233" ht="24" customHeight="1">
       <c r="A233" s="34"/>
-      <c r="B233" s="34"/>
+      <c r="B233" s="24"/>
       <c r="C233" s="24"/>
       <c r="D233" s="24"/>
       <c r="E233" s="24"/>
     </row>
     <row r="234" ht="24" customHeight="1">
       <c r="A234" s="34"/>
-      <c r="B234" s="34"/>
+      <c r="B234" s="24"/>
       <c r="C234" s="24"/>
       <c r="D234" s="24"/>
       <c r="E234" s="24"/>
     </row>
     <row r="235" ht="24" customHeight="1">
       <c r="A235" s="34"/>
-      <c r="B235" s="34"/>
+      <c r="B235" s="24"/>
       <c r="C235" s="24"/>
       <c r="D235" s="24"/>
       <c r="E235" s="24"/>
     </row>
     <row r="236" ht="24" customHeight="1">
       <c r="A236" s="34"/>
-      <c r="B236" s="34"/>
+      <c r="B236" s="24"/>
       <c r="C236" s="24"/>
       <c r="D236" s="24"/>
       <c r="E236" s="24"/>
     </row>
     <row r="237" ht="24" customHeight="1">
       <c r="A237" s="34"/>
-      <c r="B237" s="34"/>
+      <c r="B237" s="24"/>
       <c r="C237" s="24"/>
       <c r="D237" s="24"/>
       <c r="E237" s="24"/>
     </row>
     <row r="238" ht="24" customHeight="1">
       <c r="A238" s="34"/>
-      <c r="B238" s="34"/>
+      <c r="B238" s="24"/>
       <c r="C238" s="24"/>
       <c r="D238" s="24"/>
       <c r="E238" s="24"/>
     </row>
     <row r="239" ht="24" customHeight="1">
       <c r="A239" s="34"/>
-      <c r="B239" s="34"/>
+      <c r="B239" s="24"/>
       <c r="C239" s="24"/>
       <c r="D239" s="24"/>
       <c r="E239" s="24"/>
     </row>
     <row r="240" ht="24" customHeight="1">
       <c r="A240" s="34"/>
-      <c r="B240" s="34"/>
+      <c r="B240" s="24"/>
       <c r="C240" s="24"/>
       <c r="D240" s="24"/>
       <c r="E240" s="24"/>
     </row>
     <row r="241" ht="24" customHeight="1">
       <c r="A241" s="34"/>
-      <c r="B241" s="34"/>
+      <c r="B241" s="24"/>
       <c r="C241" s="24"/>
       <c r="D241" s="24"/>
       <c r="E241" s="24"/>
     </row>
     <row r="242" ht="24" customHeight="1">
       <c r="A242" s="34"/>
-      <c r="B242" s="34"/>
+      <c r="B242" s="24"/>
       <c r="C242" s="24"/>
       <c r="D242" s="24"/>
       <c r="E242" s="24"/>
     </row>
     <row r="243" ht="24" customHeight="1">
       <c r="A243" s="34"/>
-      <c r="B243" s="34"/>
+      <c r="B243" s="24"/>
       <c r="C243" s="24"/>
       <c r="D243" s="24"/>
       <c r="E243" s="24"/>
     </row>
     <row r="244" ht="24" customHeight="1">
       <c r="A244" s="34"/>
-      <c r="B244" s="34"/>
+      <c r="B244" s="24"/>
       <c r="C244" s="24"/>
       <c r="D244" s="24"/>
       <c r="E244" s="24"/>
     </row>
     <row r="245" ht="24" customHeight="1">
       <c r="A245" s="34"/>
-      <c r="B245" s="34"/>
+      <c r="B245" s="24"/>
       <c r="C245" s="24"/>
       <c r="D245" s="24"/>
       <c r="E245" s="24"/>
     </row>
     <row r="246" ht="24" customHeight="1">
       <c r="A246" s="34"/>
-      <c r="B246" s="34"/>
+      <c r="B246" s="24"/>
       <c r="C246" s="24"/>
       <c r="D246" s="24"/>
       <c r="E246" s="24"/>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="34"/>
-      <c r="B247" s="34"/>
+      <c r="B247" s="24"/>
       <c r="C247" s="24"/>
       <c r="D247" s="24"/>
       <c r="E247" s="24"/>
     </row>
     <row r="248" ht="24" customHeight="1">
       <c r="A248" s="34"/>
-      <c r="B248" s="34"/>
+      <c r="B248" s="24"/>
       <c r="C248" s="24"/>
       <c r="D248" s="24"/>
       <c r="E248" s="24"/>
     </row>
     <row r="249" ht="24" customHeight="1">
       <c r="A249" s="34"/>
-      <c r="B249" s="34"/>
+      <c r="B249" s="24"/>
       <c r="C249" s="24"/>
       <c r="D249" s="24"/>
       <c r="E249" s="24"/>
     </row>
     <row r="250" ht="24" customHeight="1">
       <c r="A250" s="34"/>
-      <c r="B250" s="34"/>
+      <c r="B250" s="24"/>
       <c r="C250" s="24"/>
       <c r="D250" s="24"/>
       <c r="E250" s="24"/>
     </row>
     <row r="251" ht="24" customHeight="1">
       <c r="A251" s="34"/>
-      <c r="B251" s="34"/>
+      <c r="B251" s="24"/>
       <c r="C251" s="24"/>
       <c r="D251" s="24"/>
       <c r="E251" s="24"/>
     </row>
     <row r="252" ht="24" customHeight="1">
       <c r="A252" s="34"/>
-      <c r="B252" s="34"/>
+      <c r="B252" s="24"/>
       <c r="C252" s="24"/>
       <c r="D252" s="24"/>
       <c r="E252" s="24"/>
     </row>
     <row r="253" ht="24" customHeight="1">
       <c r="A253" s="34"/>
-      <c r="B253" s="34"/>
+      <c r="B253" s="24"/>
       <c r="C253" s="24"/>
       <c r="D253" s="24"/>
       <c r="E253" s="24"/>
     </row>
     <row r="254" ht="24" customHeight="1">
       <c r="A254" s="34"/>
-      <c r="B254" s="34"/>
+      <c r="B254" s="24"/>
       <c r="C254" s="24"/>
       <c r="D254" s="24"/>
       <c r="E254" s="24"/>
     </row>
     <row r="255" ht="24" customHeight="1">
       <c r="A255" s="34"/>
-      <c r="B255" s="34"/>
+      <c r="B255" s="24"/>
       <c r="C255" s="24"/>
       <c r="D255" s="24"/>
       <c r="E255" s="24"/>
     </row>
     <row r="256" ht="24" customHeight="1">
       <c r="A256" s="34"/>
-      <c r="B256" s="34"/>
+      <c r="B256" s="24"/>
       <c r="C256" s="24"/>
       <c r="D256" s="24"/>
       <c r="E256" s="24"/>
     </row>
     <row r="257" ht="24" customHeight="1">
       <c r="A257" s="34"/>
-      <c r="B257" s="34"/>
+      <c r="B257" s="24"/>
       <c r="C257" s="24"/>
       <c r="D257" s="24"/>
       <c r="E257" s="24"/>
     </row>
     <row r="258" ht="24" customHeight="1">
       <c r="A258" s="34"/>
-      <c r="B258" s="34"/>
+      <c r="B258" s="24"/>
       <c r="C258" s="24"/>
       <c r="D258" s="24"/>
       <c r="E258" s="24"/>
     </row>
     <row r="259" ht="24" customHeight="1">
       <c r="A259" s="34"/>
-      <c r="B259" s="34"/>
+      <c r="B259" s="24"/>
       <c r="C259" s="24"/>
       <c r="D259" s="24"/>
       <c r="E259" s="24"/>
     </row>
     <row r="260" ht="24" customHeight="1">
       <c r="A260" s="34"/>
-      <c r="B260" s="34"/>
+      <c r="B260" s="24"/>
       <c r="C260" s="24"/>
       <c r="D260" s="24"/>
       <c r="E260" s="24"/>
     </row>
     <row r="261" ht="24" customHeight="1">
       <c r="A261" s="34"/>
-      <c r="B261" s="34"/>
+      <c r="B261" s="24"/>
       <c r="C261" s="24"/>
       <c r="D261" s="24"/>
       <c r="E261" s="24"/>
     </row>
     <row r="262" ht="24" customHeight="1">
       <c r="A262" s="34"/>
-      <c r="B262" s="34"/>
+      <c r="B262" s="24"/>
       <c r="C262" s="24"/>
       <c r="D262" s="24"/>
       <c r="E262" s="24"/>
     </row>
     <row r="263" ht="24" customHeight="1">
       <c r="A263" s="34"/>
-      <c r="B263" s="34"/>
+      <c r="B263" s="24"/>
       <c r="C263" s="24"/>
       <c r="D263" s="24"/>
       <c r="E263" s="24"/>
     </row>
     <row r="264" ht="24" customHeight="1">
       <c r="A264" s="34"/>
-      <c r="B264" s="34"/>
+      <c r="B264" s="24"/>
       <c r="C264" s="24"/>
       <c r="D264" s="24"/>
       <c r="E264" s="24"/>
     </row>
     <row r="265" ht="24" customHeight="1">
       <c r="A265" s="34"/>
-      <c r="B265" s="34"/>
+      <c r="B265" s="24"/>
       <c r="C265" s="24"/>
       <c r="D265" s="24"/>
       <c r="E265" s="24"/>
     </row>
     <row r="266" ht="24" customHeight="1">
       <c r="A266" s="34"/>
-      <c r="B266" s="34"/>
+      <c r="B266" s="24"/>
       <c r="C266" s="24"/>
       <c r="D266" s="24"/>
       <c r="E266" s="24"/>
     </row>
     <row r="267" ht="24" customHeight="1">
       <c r="A267" s="34"/>
-      <c r="B267" s="34"/>
+      <c r="B267" s="24"/>
       <c r="C267" s="24"/>
       <c r="D267" s="24"/>
       <c r="E267" s="24"/>
     </row>
     <row r="268" ht="24" customHeight="1">
       <c r="A268" s="34"/>
-      <c r="B268" s="34"/>
+      <c r="B268" s="24"/>
       <c r="C268" s="24"/>
       <c r="D268" s="24"/>
       <c r="E268" s="24"/>
     </row>
     <row r="269" ht="24" customHeight="1">
       <c r="A269" s="34"/>
-      <c r="B269" s="34"/>
+      <c r="B269" s="24"/>
       <c r="C269" s="24"/>
       <c r="D269" s="24"/>
       <c r="E269" s="24"/>
     </row>
     <row r="270" ht="24" customHeight="1">
       <c r="A270" s="34"/>
-      <c r="B270" s="34"/>
+      <c r="B270" s="24"/>
       <c r="C270" s="24"/>
       <c r="D270" s="24"/>
       <c r="E270" s="24"/>
     </row>
     <row r="271" ht="24" customHeight="1">
       <c r="A271" s="34"/>
-      <c r="B271" s="34"/>
+      <c r="B271" s="24"/>
       <c r="C271" s="24"/>
       <c r="D271" s="24"/>
       <c r="E271" s="24"/>
     </row>
     <row r="272" ht="24" customHeight="1">
       <c r="A272" s="34"/>
-      <c r="B272" s="34"/>
+      <c r="B272" s="24"/>
       <c r="C272" s="24"/>
       <c r="D272" s="24"/>
       <c r="E272" s="24"/>
     </row>
     <row r="273" ht="24" customHeight="1">
       <c r="A273" s="34"/>
-      <c r="B273" s="34"/>
+      <c r="B273" s="24"/>
       <c r="C273" s="24"/>
       <c r="D273" s="24"/>
       <c r="E273" s="24"/>
     </row>
     <row r="274" ht="24" customHeight="1">
       <c r="A274" s="34"/>
-      <c r="B274" s="34"/>
+      <c r="B274" s="24"/>
       <c r="C274" s="24"/>
       <c r="D274" s="24"/>
       <c r="E274" s="24"/>
     </row>
     <row r="275" ht="24" customHeight="1">
       <c r="A275" s="34"/>
-      <c r="B275" s="34"/>
+      <c r="B275" s="24"/>
       <c r="C275" s="24"/>
       <c r="D275" s="24"/>
       <c r="E275" s="24"/>
     </row>
     <row r="276" ht="24" customHeight="1">
       <c r="A276" s="34"/>
-      <c r="B276" s="34"/>
+      <c r="B276" s="24"/>
       <c r="C276" s="24"/>
       <c r="D276" s="24"/>
       <c r="E276" s="24"/>
     </row>
     <row r="277" ht="24" customHeight="1">
       <c r="A277" s="34"/>
-      <c r="B277" s="34"/>
+      <c r="B277" s="24"/>
       <c r="C277" s="24"/>
       <c r="D277" s="24"/>
       <c r="E277" s="24"/>
     </row>
     <row r="278" ht="24" customHeight="1">
       <c r="A278" s="34"/>
-      <c r="B278" s="34"/>
+      <c r="B278" s="24"/>
       <c r="C278" s="24"/>
       <c r="D278" s="24"/>
       <c r="E278" s="24"/>
     </row>
     <row r="279" ht="24" customHeight="1">
       <c r="A279" s="34"/>
-      <c r="B279" s="34"/>
+      <c r="B279" s="24"/>
       <c r="C279" s="24"/>
       <c r="D279" s="24"/>
       <c r="E279" s="24"/>
     </row>
     <row r="280" ht="24" customHeight="1">
       <c r="A280" s="34"/>
-      <c r="B280" s="34"/>
+      <c r="B280" s="24"/>
       <c r="C280" s="24"/>
       <c r="D280" s="24"/>
       <c r="E280" s="24"/>
     </row>
     <row r="281" ht="24" customHeight="1">
       <c r="A281" s="34"/>
-      <c r="B281" s="34"/>
+      <c r="B281" s="24"/>
       <c r="C281" s="24"/>
       <c r="D281" s="24"/>
       <c r="E281" s="24"/>
     </row>
     <row r="282" ht="24" customHeight="1">
       <c r="A282" s="34"/>
-      <c r="B282" s="34"/>
+      <c r="B282" s="24"/>
       <c r="C282" s="24"/>
       <c r="D282" s="24"/>
       <c r="E282" s="24"/>
     </row>
     <row r="283" ht="24" customHeight="1">
       <c r="A283" s="34"/>
-      <c r="B283" s="34"/>
+      <c r="B283" s="24"/>
       <c r="C283" s="24"/>
       <c r="D283" s="24"/>
       <c r="E283" s="24"/>
     </row>
     <row r="284" ht="24" customHeight="1">
       <c r="A284" s="34"/>
-      <c r="B284" s="34"/>
+      <c r="B284" s="24"/>
       <c r="C284" s="24"/>
       <c r="D284" s="24"/>
       <c r="E284" s="24"/>
     </row>
     <row r="285" ht="24" customHeight="1">
       <c r="A285" s="34"/>
-      <c r="B285" s="34"/>
+      <c r="B285" s="24"/>
       <c r="C285" s="24"/>
       <c r="D285" s="24"/>
       <c r="E285" s="24"/>
     </row>
     <row r="286" ht="24" customHeight="1">
       <c r="A286" s="34"/>
-      <c r="B286" s="34"/>
+      <c r="B286" s="24"/>
       <c r="C286" s="24"/>
       <c r="D286" s="24"/>
       <c r="E286" s="24"/>
     </row>
     <row r="287" ht="24" customHeight="1">
       <c r="A287" s="34"/>
-      <c r="B287" s="34"/>
+      <c r="B287" s="24"/>
       <c r="C287" s="24"/>
       <c r="D287" s="24"/>
       <c r="E287" s="24"/>
     </row>
     <row r="288" ht="24" customHeight="1">
       <c r="A288" s="34"/>
-      <c r="B288" s="34"/>
+      <c r="B288" s="24"/>
       <c r="C288" s="24"/>
       <c r="D288" s="24"/>
       <c r="E288" s="24"/>
     </row>
     <row r="289" ht="24" customHeight="1">
       <c r="A289" s="34"/>
-      <c r="B289" s="34"/>
+      <c r="B289" s="24"/>
       <c r="C289" s="24"/>
       <c r="D289" s="24"/>
       <c r="E289" s="24"/>
     </row>
     <row r="290" ht="24" customHeight="1">
       <c r="A290" s="34"/>
-      <c r="B290" s="34"/>
+      <c r="B290" s="24"/>
       <c r="C290" s="24"/>
       <c r="D290" s="24"/>
       <c r="E290" s="24"/>
     </row>
     <row r="291" ht="24" customHeight="1">
       <c r="A291" s="34"/>
-      <c r="B291" s="34"/>
+      <c r="B291" s="24"/>
       <c r="C291" s="24"/>
       <c r="D291" s="24"/>
       <c r="E291" s="24"/>
     </row>
     <row r="292" ht="24" customHeight="1">
       <c r="A292" s="34"/>
-      <c r="B292" s="34"/>
+      <c r="B292" s="24"/>
       <c r="C292" s="24"/>
       <c r="D292" s="24"/>
       <c r="E292" s="24"/>
     </row>
     <row r="293" ht="24" customHeight="1">
       <c r="A293" s="34"/>
-      <c r="B293" s="34"/>
+      <c r="B293" s="24"/>
       <c r="C293" s="24"/>
       <c r="D293" s="24"/>
       <c r="E293" s="24"/>
     </row>
     <row r="294" ht="24" customHeight="1">
       <c r="A294" s="34"/>
-      <c r="B294" s="34"/>
+      <c r="B294" s="24"/>
       <c r="C294" s="24"/>
       <c r="D294" s="24"/>
       <c r="E294" s="24"/>
     </row>
     <row r="295" ht="24" customHeight="1">
       <c r="A295" s="34"/>
-      <c r="B295" s="34"/>
+      <c r="B295" s="24"/>
       <c r="C295" s="24"/>
       <c r="D295" s="24"/>
       <c r="E295" s="24"/>
     </row>
     <row r="296" ht="24" customHeight="1">
       <c r="A296" s="34"/>
-      <c r="B296" s="34"/>
+      <c r="B296" s="24"/>
       <c r="C296" s="24"/>
       <c r="D296" s="24"/>
       <c r="E296" s="24"/>
     </row>
     <row r="297" ht="24" customHeight="1">
       <c r="A297" s="34"/>
-      <c r="B297" s="34"/>
+      <c r="B297" s="24"/>
       <c r="C297" s="24"/>
       <c r="D297" s="24"/>
       <c r="E297" s="24"/>
     </row>
     <row r="298" ht="24" customHeight="1">
       <c r="A298" s="34"/>
-      <c r="B298" s="34"/>
+      <c r="B298" s="24"/>
       <c r="C298" s="24"/>
       <c r="D298" s="24"/>
       <c r="E298" s="24"/>
     </row>
     <row r="299" ht="24" customHeight="1">
       <c r="A299" s="34"/>
-      <c r="B299" s="34"/>
+      <c r="B299" s="24"/>
       <c r="C299" s="24"/>
       <c r="D299" s="24"/>
       <c r="E299" s="24"/>
     </row>
     <row r="300" ht="24" customHeight="1">
       <c r="A300" s="34"/>
-      <c r="B300" s="34"/>
+      <c r="B300" s="24"/>
       <c r="C300" s="24"/>
       <c r="D300" s="24"/>
       <c r="E300" s="24"/>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="34"/>
-      <c r="B301" s="34"/>
+      <c r="B301" s="24"/>
       <c r="C301" s="24"/>
       <c r="D301" s="24"/>
       <c r="E301" s="24"/>
     </row>
     <row r="302" ht="24" customHeight="1">
       <c r="A302" s="34"/>
-      <c r="B302" s="34"/>
+      <c r="B302" s="24"/>
       <c r="C302" s="24"/>
       <c r="D302" s="24"/>
       <c r="E302" s="24"/>
     </row>
     <row r="303" ht="24" customHeight="1">
       <c r="A303" s="34"/>
-      <c r="B303" s="34"/>
+      <c r="B303" s="24"/>
       <c r="C303" s="24"/>
       <c r="D303" s="24"/>
       <c r="E303" s="24"/>
     </row>
     <row r="304" ht="24" customHeight="1">
       <c r="A304" s="34"/>
-      <c r="B304" s="34"/>
+      <c r="B304" s="24"/>
       <c r="C304" s="24"/>
       <c r="D304" s="24"/>
       <c r="E304" s="24"/>
     </row>
     <row r="305" ht="24" customHeight="1">
       <c r="A305" s="34"/>
-      <c r="B305" s="34"/>
+      <c r="B305" s="24"/>
       <c r="C305" s="24"/>
       <c r="D305" s="24"/>
       <c r="E305" s="24"/>
     </row>
     <row r="306" ht="24" customHeight="1">
       <c r="A306" s="34"/>
-      <c r="B306" s="34"/>
+      <c r="B306" s="24"/>
       <c r="C306" s="24"/>
       <c r="D306" s="24"/>
       <c r="E306" s="24"/>
     </row>
     <row r="307" ht="24" customHeight="1">
       <c r="A307" s="34"/>
-      <c r="B307" s="34"/>
+      <c r="B307" s="24"/>
       <c r="C307" s="24"/>
       <c r="D307" s="24"/>
       <c r="E307" s="24"/>
     </row>
     <row r="308" ht="24" customHeight="1">
       <c r="A308" s="34"/>
-      <c r="B308" s="34"/>
+      <c r="B308" s="24"/>
       <c r="C308" s="24"/>
       <c r="D308" s="24"/>
       <c r="E308" s="24"/>
     </row>
     <row r="309" ht="24" customHeight="1">
       <c r="A309" s="34"/>
-      <c r="B309" s="34"/>
+      <c r="B309" s="24"/>
       <c r="C309" s="24"/>
       <c r="D309" s="24"/>
       <c r="E309" s="24"/>
     </row>
     <row r="310" ht="24" customHeight="1">
       <c r="A310" s="34"/>
-      <c r="B310" s="34"/>
+      <c r="B310" s="24"/>
       <c r="C310" s="24"/>
       <c r="D310" s="24"/>
       <c r="E310" s="24"/>
     </row>
     <row r="311" ht="24" customHeight="1">
       <c r="A311" s="34"/>
-      <c r="B311" s="34"/>
+      <c r="B311" s="24"/>
       <c r="C311" s="24"/>
       <c r="D311" s="24"/>
       <c r="E311" s="24"/>
     </row>
     <row r="312" ht="24" customHeight="1">
       <c r="A312" s="34"/>
-      <c r="B312" s="34"/>
+      <c r="B312" s="24"/>
       <c r="C312" s="24"/>
       <c r="D312" s="24"/>
       <c r="E312" s="24"/>
     </row>
     <row r="313" ht="24" customHeight="1">
       <c r="A313" s="34"/>
-      <c r="B313" s="34"/>
+      <c r="B313" s="24"/>
       <c r="C313" s="24"/>
       <c r="D313" s="24"/>
       <c r="E313" s="24"/>
     </row>
     <row r="314" ht="24" customHeight="1">
       <c r="A314" s="34"/>
-      <c r="B314" s="34"/>
+      <c r="B314" s="24"/>
       <c r="C314" s="24"/>
       <c r="D314" s="24"/>
       <c r="E314" s="24"/>
     </row>
     <row r="315" ht="24" customHeight="1">
       <c r="A315" s="34"/>
-      <c r="B315" s="34"/>
+      <c r="B315" s="24"/>
       <c r="C315" s="24"/>
       <c r="D315" s="24"/>
       <c r="E315" s="24"/>
     </row>
     <row r="316" ht="24" customHeight="1">
       <c r="A316" s="34"/>
-      <c r="B316" s="34"/>
+      <c r="B316" s="24"/>
       <c r="C316" s="24"/>
       <c r="D316" s="24"/>
       <c r="E316" s="24"/>
     </row>
     <row r="317" ht="24" customHeight="1">
       <c r="A317" s="34"/>
-      <c r="B317" s="34"/>
+      <c r="B317" s="24"/>
       <c r="C317" s="24"/>
       <c r="D317" s="24"/>
       <c r="E317" s="24"/>
     </row>
     <row r="318" ht="24" customHeight="1">
       <c r="A318" s="34"/>
-      <c r="B318" s="34"/>
+      <c r="B318" s="24"/>
       <c r="C318" s="24"/>
       <c r="D318" s="24"/>
       <c r="E318" s="24"/>
     </row>
     <row r="319" ht="24" customHeight="1">
       <c r="A319" s="34"/>
-      <c r="B319" s="34"/>
+      <c r="B319" s="24"/>
       <c r="C319" s="24"/>
       <c r="D319" s="24"/>
       <c r="E319" s="24"/>
     </row>
     <row r="320" ht="24" customHeight="1">
       <c r="A320" s="34"/>
-      <c r="B320" s="34"/>
+      <c r="B320" s="24"/>
       <c r="C320" s="24"/>
       <c r="D320" s="24"/>
       <c r="E320" s="24"/>
     </row>
     <row r="321" ht="24" customHeight="1">
       <c r="A321" s="34"/>
-      <c r="B321" s="34"/>
+      <c r="B321" s="24"/>
       <c r="C321" s="24"/>
       <c r="D321" s="24"/>
       <c r="E321" s="24"/>
     </row>
     <row r="322" ht="24" customHeight="1">
       <c r="A322" s="34"/>
-      <c r="B322" s="34"/>
+      <c r="B322" s="24"/>
       <c r="C322" s="24"/>
       <c r="D322" s="24"/>
       <c r="E322" s="24"/>
     </row>
     <row r="323" ht="24" customHeight="1">
       <c r="A323" s="34"/>
-      <c r="B323" s="34"/>
+      <c r="B323" s="24"/>
       <c r="C323" s="24"/>
       <c r="D323" s="24"/>
       <c r="E323" s="24"/>
     </row>
     <row r="324" ht="24" customHeight="1">
       <c r="A324" s="34"/>
-      <c r="B324" s="34"/>
+      <c r="B324" s="24"/>
       <c r="C324" s="24"/>
       <c r="D324" s="24"/>
       <c r="E324" s="24"/>
     </row>
     <row r="325" ht="24" customHeight="1">
       <c r="A325" s="34"/>
-      <c r="B325" s="34"/>
+      <c r="B325" s="24"/>
       <c r="C325" s="24"/>
       <c r="D325" s="24"/>
       <c r="E325" s="24"/>
     </row>
     <row r="326" ht="24" customHeight="1">
       <c r="A326" s="34"/>
-      <c r="B326" s="34"/>
+      <c r="B326" s="24"/>
       <c r="C326" s="24"/>
       <c r="D326" s="24"/>
       <c r="E326" s="24"/>
     </row>
     <row r="327" ht="24" customHeight="1">
       <c r="A327" s="34"/>
-      <c r="B327" s="34"/>
+      <c r="B327" s="24"/>
       <c r="C327" s="24"/>
       <c r="D327" s="24"/>
       <c r="E327" s="24"/>
     </row>
     <row r="328" ht="24" customHeight="1">
       <c r="A328" s="34"/>
-      <c r="B328" s="34"/>
+      <c r="B328" s="24"/>
       <c r="C328" s="24"/>
       <c r="D328" s="24"/>
       <c r="E328" s="24"/>
     </row>
     <row r="329" ht="24" customHeight="1">
       <c r="A329" s="34"/>
-      <c r="B329" s="34"/>
+      <c r="B329" s="24"/>
       <c r="C329" s="24"/>
       <c r="D329" s="24"/>
       <c r="E329" s="24"/>
     </row>
     <row r="330" ht="24" customHeight="1">
       <c r="A330" s="34"/>
-      <c r="B330" s="34"/>
+      <c r="B330" s="24"/>
       <c r="C330" s="24"/>
       <c r="D330" s="24"/>
       <c r="E330" s="24"/>
     </row>
     <row r="331" ht="24" customHeight="1">
       <c r="A331" s="34"/>
-      <c r="B331" s="34"/>
+      <c r="B331" s="24"/>
       <c r="C331" s="24"/>
       <c r="D331" s="24"/>
       <c r="E331" s="24"/>
     </row>
     <row r="332" ht="24" customHeight="1">
       <c r="A332" s="34"/>
-      <c r="B332" s="34"/>
+      <c r="B332" s="24"/>
       <c r="C332" s="24"/>
       <c r="D332" s="24"/>
       <c r="E332" s="24"/>
     </row>
     <row r="333" ht="24" customHeight="1">
       <c r="A333" s="34"/>
-      <c r="B333" s="34"/>
+      <c r="B333" s="24"/>
       <c r="C333" s="24"/>
       <c r="D333" s="24"/>
       <c r="E333" s="24"/>
     </row>
     <row r="334" ht="24" customHeight="1">
       <c r="A334" s="34"/>
-      <c r="B334" s="34"/>
+      <c r="B334" s="24"/>
       <c r="C334" s="24"/>
       <c r="D334" s="24"/>
       <c r="E334" s="24"/>
     </row>
     <row r="335" ht="24" customHeight="1">
       <c r="A335" s="34"/>
-      <c r="B335" s="34"/>
+      <c r="B335" s="24"/>
       <c r="C335" s="24"/>
       <c r="D335" s="24"/>
       <c r="E335" s="24"/>
     </row>
     <row r="336" ht="24" customHeight="1">
       <c r="A336" s="34"/>
-      <c r="B336" s="34"/>
+      <c r="B336" s="24"/>
       <c r="C336" s="24"/>
       <c r="D336" s="24"/>
       <c r="E336" s="24"/>
     </row>
     <row r="337" ht="24" customHeight="1">
       <c r="A337" s="34"/>
-      <c r="B337" s="34"/>
+      <c r="B337" s="24"/>
       <c r="C337" s="24"/>
       <c r="D337" s="24"/>
       <c r="E337" s="24"/>
     </row>
     <row r="338" ht="24" customHeight="1">
       <c r="A338" s="34"/>
-      <c r="B338" s="34"/>
+      <c r="B338" s="24"/>
       <c r="C338" s="24"/>
       <c r="D338" s="24"/>
       <c r="E338" s="24"/>
     </row>
     <row r="339" ht="24" customHeight="1">
       <c r="A339" s="34"/>
-      <c r="B339" s="34"/>
+      <c r="B339" s="24"/>
       <c r="C339" s="24"/>
       <c r="D339" s="24"/>
       <c r="E339" s="24"/>
     </row>
     <row r="340" ht="24" customHeight="1">
       <c r="A340" s="34"/>
-      <c r="B340" s="34"/>
+      <c r="B340" s="24"/>
       <c r="C340" s="24"/>
       <c r="D340" s="24"/>
       <c r="E340" s="24"/>
     </row>
     <row r="341" ht="24" customHeight="1">
       <c r="A341" s="34"/>
-      <c r="B341" s="34"/>
+      <c r="B341" s="24"/>
       <c r="C341" s="24"/>
       <c r="D341" s="24"/>
       <c r="E341" s="24"/>
     </row>
     <row r="342" ht="24" customHeight="1">
       <c r="A342" s="34"/>
-      <c r="B342" s="34"/>
+      <c r="B342" s="24"/>
       <c r="C342" s="24"/>
       <c r="D342" s="24"/>
       <c r="E342" s="24"/>
     </row>
     <row r="343" ht="24" customHeight="1">
       <c r="A343" s="34"/>
-      <c r="B343" s="34"/>
+      <c r="B343" s="24"/>
       <c r="C343" s="24"/>
       <c r="D343" s="24"/>
       <c r="E343" s="24"/>
     </row>
     <row r="344" ht="24" customHeight="1">
       <c r="A344" s="34"/>
-      <c r="B344" s="34"/>
+      <c r="B344" s="24"/>
       <c r="C344" s="24"/>
       <c r="D344" s="24"/>
       <c r="E344" s="24"/>
     </row>
     <row r="345" ht="24" customHeight="1">
       <c r="A345" s="34"/>
-      <c r="B345" s="34"/>
+      <c r="B345" s="24"/>
       <c r="C345" s="24"/>
       <c r="D345" s="24"/>
       <c r="E345" s="24"/>
     </row>
     <row r="346" ht="24" customHeight="1">
       <c r="A346" s="34"/>
-      <c r="B346" s="34"/>
+      <c r="B346" s="24"/>
       <c r="C346" s="24"/>
       <c r="D346" s="24"/>
       <c r="E346" s="24"/>
     </row>
     <row r="347" ht="24" customHeight="1">
       <c r="A347" s="34"/>
-      <c r="B347" s="34"/>
+      <c r="B347" s="24"/>
       <c r="C347" s="24"/>
       <c r="D347" s="24"/>
       <c r="E347" s="24"/>
     </row>
     <row r="348" ht="24" customHeight="1">
       <c r="A348" s="34"/>
-      <c r="B348" s="34"/>
+      <c r="B348" s="24"/>
       <c r="C348" s="24"/>
       <c r="D348" s="24"/>
       <c r="E348" s="24"/>
     </row>
     <row r="349" ht="24" customHeight="1">
       <c r="A349" s="34"/>
-      <c r="B349" s="34"/>
+      <c r="B349" s="24"/>
       <c r="C349" s="24"/>
       <c r="D349" s="24"/>
       <c r="E349" s="24"/>
     </row>
     <row r="350" ht="24" customHeight="1">
       <c r="A350" s="34"/>
-      <c r="B350" s="34"/>
+      <c r="B350" s="24"/>
       <c r="C350" s="24"/>
       <c r="D350" s="24"/>
       <c r="E350" s="24"/>
     </row>
     <row r="351" ht="24" customHeight="1">
       <c r="A351" s="34"/>
-      <c r="B351" s="34"/>
+      <c r="B351" s="24"/>
       <c r="C351" s="24"/>
       <c r="D351" s="24"/>
       <c r="E351" s="24"/>
     </row>
     <row r="352" ht="24" customHeight="1">
       <c r="A352" s="34"/>
-      <c r="B352" s="34"/>
+      <c r="B352" s="24"/>
       <c r="C352" s="24"/>
       <c r="D352" s="24"/>
       <c r="E352" s="24"/>
     </row>
     <row r="353" ht="24" customHeight="1">
       <c r="A353" s="34"/>
-      <c r="B353" s="34"/>
+      <c r="B353" s="24"/>
       <c r="C353" s="24"/>
       <c r="D353" s="24"/>
       <c r="E353" s="24"/>
     </row>
     <row r="354" ht="24" customHeight="1">
       <c r="A354" s="34"/>
-      <c r="B354" s="34"/>
+      <c r="B354" s="24"/>
       <c r="C354" s="24"/>
       <c r="D354" s="24"/>
       <c r="E354" s="24"/>
     </row>
     <row r="355" ht="24" customHeight="1">
       <c r="A355" s="34"/>
-      <c r="B355" s="34"/>
+      <c r="B355" s="24"/>
       <c r="C355" s="24"/>
       <c r="D355" s="24"/>
       <c r="E355" s="24"/>
     </row>
     <row r="356" ht="24" customHeight="1">
       <c r="A356" s="34"/>
-      <c r="B356" s="34"/>
+      <c r="B356" s="24"/>
       <c r="C356" s="24"/>
       <c r="D356" s="24"/>
       <c r="E356" s="24"/>
     </row>
     <row r="357" ht="24" customHeight="1">
       <c r="A357" s="34"/>
-      <c r="B357" s="34"/>
+      <c r="B357" s="24"/>
       <c r="C357" s="24"/>
       <c r="D357" s="24"/>
       <c r="E357" s="24"/>
     </row>
     <row r="358" ht="24" customHeight="1">
       <c r="A358" s="34"/>
-      <c r="B358" s="34"/>
+      <c r="B358" s="24"/>
       <c r="C358" s="24"/>
       <c r="D358" s="24"/>
       <c r="E358" s="24"/>
     </row>
     <row r="359" ht="24" customHeight="1">
       <c r="A359" s="34"/>
-      <c r="B359" s="34"/>
+      <c r="B359" s="24"/>
       <c r="C359" s="24"/>
       <c r="D359" s="24"/>
       <c r="E359" s="24"/>
     </row>
     <row r="360" ht="24" customHeight="1">
       <c r="A360" s="34"/>
-      <c r="B360" s="34"/>
+      <c r="B360" s="24"/>
       <c r="C360" s="24"/>
       <c r="D360" s="24"/>
       <c r="E360" s="24"/>
     </row>
     <row r="361" ht="24" customHeight="1">
       <c r="A361" s="34"/>
-      <c r="B361" s="34"/>
+      <c r="B361" s="24"/>
       <c r="C361" s="24"/>
       <c r="D361" s="24"/>
       <c r="E361" s="24"/>
     </row>
     <row r="362" ht="24" customHeight="1">
       <c r="A362" s="34"/>
-      <c r="B362" s="34"/>
+      <c r="B362" s="24"/>
       <c r="C362" s="24"/>
       <c r="D362" s="24"/>
       <c r="E362" s="24"/>
     </row>
     <row r="363" ht="24" customHeight="1">
       <c r="A363" s="34"/>
-      <c r="B363" s="34"/>
+      <c r="B363" s="24"/>
       <c r="C363" s="24"/>
       <c r="D363" s="24"/>
       <c r="E363" s="24"/>
     </row>
     <row r="364" ht="24" customHeight="1">
       <c r="A364" s="34"/>
-      <c r="B364" s="34"/>
+      <c r="B364" s="24"/>
       <c r="C364" s="24"/>
       <c r="D364" s="24"/>
       <c r="E364" s="24"/>
     </row>
     <row r="365" ht="24" customHeight="1">
       <c r="A365" s="34"/>
-      <c r="B365" s="34"/>
+      <c r="B365" s="24"/>
       <c r="C365" s="24"/>
       <c r="D365" s="24"/>
       <c r="E365" s="24"/>
     </row>
     <row r="366" ht="24" customHeight="1">
       <c r="A366" s="34"/>
-      <c r="B366" s="34"/>
+      <c r="B366" s="24"/>
       <c r="C366" s="24"/>
       <c r="D366" s="24"/>
       <c r="E366" s="24"/>
     </row>
     <row r="367" ht="24" customHeight="1">
       <c r="A367" s="34"/>
-      <c r="B367" s="34"/>
+      <c r="B367" s="24"/>
       <c r="C367" s="24"/>
       <c r="D367" s="24"/>
       <c r="E367" s="24"/>
     </row>
     <row r="368" ht="24" customHeight="1">
       <c r="A368" s="34"/>
-      <c r="B368" s="34"/>
+      <c r="B368" s="24"/>
       <c r="C368" s="24"/>
       <c r="D368" s="24"/>
       <c r="E368" s="24"/>
     </row>
     <row r="369" ht="24" customHeight="1">
       <c r="A369" s="34"/>
-      <c r="B369" s="34"/>
+      <c r="B369" s="24"/>
       <c r="C369" s="24"/>
       <c r="D369" s="24"/>
       <c r="E369" s="24"/>
     </row>
     <row r="370" ht="24" customHeight="1">
       <c r="A370" s="34"/>
-      <c r="B370" s="34"/>
+      <c r="B370" s="24"/>
       <c r="C370" s="24"/>
       <c r="D370" s="24"/>
       <c r="E370" s="24"/>
     </row>
     <row r="371" ht="24" customHeight="1">
       <c r="A371" s="34"/>
-      <c r="B371" s="34"/>
+      <c r="B371" s="24"/>
       <c r="C371" s="24"/>
       <c r="D371" s="24"/>
       <c r="E371" s="24"/>
     </row>
     <row r="372" ht="24" customHeight="1">
       <c r="A372" s="34"/>
-      <c r="B372" s="34"/>
+      <c r="B372" s="24"/>
       <c r="C372" s="24"/>
       <c r="D372" s="24"/>
       <c r="E372" s="24"/>
     </row>
     <row r="373" ht="24" customHeight="1">
       <c r="A373" s="34"/>
-      <c r="B373" s="34"/>
+      <c r="B373" s="24"/>
       <c r="C373" s="24"/>
       <c r="D373" s="24"/>
       <c r="E373" s="24"/>
     </row>
     <row r="374" ht="24" customHeight="1">
       <c r="A374" s="34"/>
-      <c r="B374" s="34"/>
+      <c r="B374" s="24"/>
       <c r="C374" s="24"/>
       <c r="D374" s="24"/>
       <c r="E374" s="24"/>
     </row>
     <row r="375" ht="24" customHeight="1">
       <c r="A375" s="34"/>
-      <c r="B375" s="34"/>
+      <c r="B375" s="24"/>
       <c r="C375" s="24"/>
       <c r="D375" s="24"/>
       <c r="E375" s="24"/>
     </row>
     <row r="376" ht="24" customHeight="1">
       <c r="A376" s="34"/>
-      <c r="B376" s="34"/>
+      <c r="B376" s="24"/>
       <c r="C376" s="24"/>
       <c r="D376" s="24"/>
       <c r="E376" s="24"/>
     </row>
     <row r="377" ht="24" customHeight="1">
       <c r="A377" s="34"/>
-      <c r="B377" s="34"/>
+      <c r="B377" s="24"/>
       <c r="C377" s="24"/>
       <c r="D377" s="24"/>
       <c r="E377" s="24"/>
     </row>
     <row r="378" ht="24" customHeight="1">
       <c r="A378" s="34"/>
-      <c r="B378" s="34"/>
+      <c r="B378" s="24"/>
       <c r="C378" s="24"/>
       <c r="D378" s="24"/>
       <c r="E378" s="24"/>
     </row>
     <row r="379" ht="24" customHeight="1">
       <c r="A379" s="34"/>
-      <c r="B379" s="34"/>
+      <c r="B379" s="24"/>
       <c r="C379" s="24"/>
       <c r="D379" s="24"/>
       <c r="E379" s="24"/>
     </row>
     <row r="380" ht="24" customHeight="1">
       <c r="A380" s="34"/>
-      <c r="B380" s="34"/>
+      <c r="B380" s="24"/>
       <c r="C380" s="24"/>
       <c r="D380" s="24"/>
       <c r="E380" s="24"/>
     </row>
     <row r="381" ht="24" customHeight="1">
       <c r="A381" s="34"/>
-      <c r="B381" s="34"/>
+      <c r="B381" s="24"/>
       <c r="C381" s="24"/>
       <c r="D381" s="24"/>
       <c r="E381" s="24"/>
     </row>
     <row r="382" ht="24" customHeight="1">
       <c r="A382" s="34"/>
-      <c r="B382" s="34"/>
+      <c r="B382" s="24"/>
       <c r="C382" s="24"/>
       <c r="D382" s="24"/>
       <c r="E382" s="24"/>
     </row>
     <row r="383" ht="24" customHeight="1">
       <c r="A383" s="34"/>
-      <c r="B383" s="34"/>
+      <c r="B383" s="24"/>
       <c r="C383" s="24"/>
       <c r="D383" s="24"/>
       <c r="E383" s="24"/>
     </row>
     <row r="384" ht="24" customHeight="1">
       <c r="A384" s="34"/>
-      <c r="B384" s="34"/>
+      <c r="B384" s="24"/>
       <c r="C384" s="24"/>
       <c r="D384" s="24"/>
       <c r="E384" s="24"/>
     </row>
     <row r="385" ht="24" customHeight="1">
       <c r="A385" s="34"/>
-      <c r="B385" s="34"/>
+      <c r="B385" s="24"/>
       <c r="C385" s="24"/>
       <c r="D385" s="24"/>
       <c r="E385" s="24"/>
     </row>
     <row r="386" ht="24" customHeight="1">
       <c r="A386" s="34"/>
-      <c r="B386" s="34"/>
+      <c r="B386" s="24"/>
       <c r="C386" s="24"/>
       <c r="D386" s="24"/>
       <c r="E386" s="24"/>
     </row>
     <row r="387" ht="24" customHeight="1">
       <c r="A387" s="34"/>
-      <c r="B387" s="34"/>
+      <c r="B387" s="24"/>
       <c r="C387" s="24"/>
       <c r="D387" s="24"/>
       <c r="E387" s="24"/>
     </row>
     <row r="388" ht="24" customHeight="1">
       <c r="A388" s="34"/>
-      <c r="B388" s="34"/>
+      <c r="B388" s="24"/>
       <c r="C388" s="24"/>
       <c r="D388" s="24"/>
       <c r="E388" s="24"/>
     </row>
     <row r="389" ht="24" customHeight="1">
       <c r="A389" s="34"/>
-      <c r="B389" s="34"/>
+      <c r="B389" s="24"/>
       <c r="C389" s="24"/>
       <c r="D389" s="24"/>
       <c r="E389" s="24"/>
     </row>
     <row r="390" ht="24" customHeight="1">
       <c r="A390" s="34"/>
-      <c r="B390" s="34"/>
+      <c r="B390" s="24"/>
       <c r="C390" s="24"/>
       <c r="D390" s="24"/>
       <c r="E390" s="24"/>
     </row>
     <row r="391" ht="24" customHeight="1">
       <c r="A391" s="34"/>
-      <c r="B391" s="34"/>
+      <c r="B391" s="24"/>
       <c r="C391" s="24"/>
       <c r="D391" s="24"/>
       <c r="E391" s="24"/>
     </row>
     <row r="392" ht="24" customHeight="1">
       <c r="A392" s="34"/>
-      <c r="B392" s="34"/>
+      <c r="B392" s="24"/>
       <c r="C392" s="24"/>
       <c r="D392" s="24"/>
       <c r="E392" s="24"/>
     </row>
     <row r="393" ht="24" customHeight="1">
       <c r="A393" s="34"/>
-      <c r="B393" s="34"/>
+      <c r="B393" s="24"/>
       <c r="C393" s="24"/>
       <c r="D393" s="24"/>
       <c r="E393" s="24"/>
     </row>
     <row r="394" ht="24" customHeight="1">
       <c r="A394" s="34"/>
-      <c r="B394" s="34"/>
+      <c r="B394" s="24"/>
       <c r="C394" s="24"/>
       <c r="D394" s="24"/>
       <c r="E394" s="24"/>
     </row>
     <row r="395" ht="24" customHeight="1">
       <c r="A395" s="34"/>
-      <c r="B395" s="34"/>
+      <c r="B395" s="24"/>
       <c r="C395" s="24"/>
       <c r="D395" s="24"/>
       <c r="E395" s="24"/>
     </row>
     <row r="396" ht="24" customHeight="1">
       <c r="A396" s="34"/>
-      <c r="B396" s="34"/>
+      <c r="B396" s="24"/>
       <c r="C396" s="24"/>
       <c r="D396" s="24"/>
       <c r="E396" s="24"/>
     </row>
     <row r="397" ht="24" customHeight="1">
       <c r="A397" s="34"/>
-      <c r="B397" s="34"/>
+      <c r="B397" s="24"/>
       <c r="C397" s="24"/>
       <c r="D397" s="24"/>
       <c r="E397" s="24"/>
     </row>
     <row r="398" ht="24" customHeight="1">
       <c r="A398" s="34"/>
-      <c r="B398" s="34"/>
+      <c r="B398" s="24"/>
       <c r="C398" s="24"/>
       <c r="D398" s="24"/>
       <c r="E398" s="24"/>
     </row>
     <row r="399" ht="24" customHeight="1">
       <c r="A399" s="34"/>
-      <c r="B399" s="34"/>
+      <c r="B399" s="24"/>
       <c r="C399" s="24"/>
       <c r="D399" s="24"/>
       <c r="E399" s="24"/>
     </row>
     <row r="400" ht="24" customHeight="1">
       <c r="A400" s="34"/>
-      <c r="B400" s="34"/>
+      <c r="B400" s="24"/>
       <c r="C400" s="24"/>
       <c r="D400" s="24"/>
       <c r="E400" s="24"/>
     </row>
     <row r="401" ht="24" customHeight="1">
       <c r="A401" s="34"/>
-      <c r="B401" s="34"/>
+      <c r="B401" s="24"/>
       <c r="C401" s="24"/>
       <c r="D401" s="24"/>
       <c r="E401" s="24"/>
     </row>
     <row r="402" ht="24" customHeight="1">
       <c r="A402" s="34"/>
-      <c r="B402" s="34"/>
+      <c r="B402" s="24"/>
       <c r="C402" s="24"/>
       <c r="D402" s="24"/>
       <c r="E402" s="24"/>
     </row>
     <row r="403" ht="24" customHeight="1">
       <c r="A403" s="34"/>
-      <c r="B403" s="34"/>
+      <c r="B403" s="24"/>
       <c r="C403" s="24"/>
       <c r="D403" s="24"/>
       <c r="E403" s="24"/>
     </row>
     <row r="404" ht="24" customHeight="1">
       <c r="A404" s="34"/>
-      <c r="B404" s="34"/>
+      <c r="B404" s="24"/>
       <c r="C404" s="24"/>
       <c r="D404" s="24"/>
       <c r="E404" s="24"/>
     </row>
     <row r="405" ht="24" customHeight="1">
       <c r="A405" s="34"/>
-      <c r="B405" s="34"/>
+      <c r="B405" s="24"/>
       <c r="C405" s="24"/>
       <c r="D405" s="24"/>
       <c r="E405" s="24"/>
     </row>
     <row r="406" ht="24" customHeight="1">
       <c r="A406" s="34"/>
-      <c r="B406" s="34"/>
+      <c r="B406" s="24"/>
       <c r="C406" s="24"/>
       <c r="D406" s="24"/>
       <c r="E406" s="24"/>
     </row>
     <row r="407" ht="24" customHeight="1">
       <c r="A407" s="34"/>
-      <c r="B407" s="34"/>
+      <c r="B407" s="24"/>
       <c r="C407" s="24"/>
       <c r="D407" s="24"/>
       <c r="E407" s="24"/>
     </row>
     <row r="408" ht="24" customHeight="1">
       <c r="A408" s="34"/>
-      <c r="B408" s="34"/>
+      <c r="B408" s="24"/>
       <c r="C408" s="24"/>
       <c r="D408" s="24"/>
       <c r="E408" s="24"/>
     </row>
     <row r="409" ht="24" customHeight="1">
       <c r="A409" s="34"/>
-      <c r="B409" s="34"/>
+      <c r="B409" s="24"/>
       <c r="C409" s="24"/>
       <c r="D409" s="24"/>
       <c r="E409" s="24"/>
     </row>
     <row r="410" ht="24" customHeight="1">
       <c r="A410" s="34"/>
-      <c r="B410" s="34"/>
+      <c r="B410" s="24"/>
       <c r="C410" s="24"/>
       <c r="D410" s="24"/>
       <c r="E410" s="24"/>
     </row>
     <row r="411" ht="24" customHeight="1">
       <c r="A411" s="34"/>
-      <c r="B411" s="34"/>
+      <c r="B411" s="24"/>
       <c r="C411" s="24"/>
       <c r="D411" s="24"/>
       <c r="E411" s="24"/>
     </row>
     <row r="412" ht="24" customHeight="1">
       <c r="A412" s="34"/>
-      <c r="B412" s="34"/>
+      <c r="B412" s="24"/>
       <c r="C412" s="24"/>
       <c r="D412" s="24"/>
       <c r="E412" s="24"/>
     </row>
     <row r="413" ht="24" customHeight="1">
       <c r="A413" s="34"/>
-      <c r="B413" s="34"/>
+      <c r="B413" s="24"/>
       <c r="C413" s="24"/>
       <c r="D413" s="24"/>
       <c r="E413" s="24"/>
     </row>
     <row r="414" ht="24" customHeight="1">
       <c r="A414" s="34"/>
-      <c r="B414" s="34"/>
+      <c r="B414" s="24"/>
       <c r="C414" s="24"/>
       <c r="D414" s="24"/>
       <c r="E414" s="24"/>
     </row>
     <row r="415" ht="24" customHeight="1">
       <c r="A415" s="34"/>
-      <c r="B415" s="34"/>
+      <c r="B415" s="24"/>
       <c r="C415" s="24"/>
       <c r="D415" s="24"/>
       <c r="E415" s="24"/>
     </row>
     <row r="416" ht="24" customHeight="1">
       <c r="A416" s="34"/>
-      <c r="B416" s="34"/>
+      <c r="B416" s="24"/>
       <c r="C416" s="24"/>
       <c r="D416" s="24"/>
       <c r="E416" s="24"/>
     </row>
     <row r="417" ht="24" customHeight="1">
       <c r="A417" s="34"/>
-      <c r="B417" s="34"/>
+      <c r="B417" s="24"/>
       <c r="C417" s="24"/>
       <c r="D417" s="24"/>
       <c r="E417" s="24"/>
     </row>
     <row r="418" ht="24" customHeight="1">
       <c r="A418" s="34"/>
-      <c r="B418" s="34"/>
+      <c r="B418" s="24"/>
       <c r="C418" s="24"/>
       <c r="D418" s="24"/>
       <c r="E418" s="24"/>
     </row>
     <row r="419" ht="24" customHeight="1">
       <c r="A419" s="34"/>
-      <c r="B419" s="34"/>
+      <c r="B419" s="24"/>
       <c r="C419" s="24"/>
       <c r="D419" s="24"/>
       <c r="E419" s="24"/>
     </row>
     <row r="420" ht="24" customHeight="1">
       <c r="A420" s="34"/>
-      <c r="B420" s="34"/>
+      <c r="B420" s="24"/>
       <c r="C420" s="24"/>
       <c r="D420" s="24"/>
       <c r="E420" s="24"/>
     </row>
     <row r="421" ht="24" customHeight="1">
       <c r="A421" s="34"/>
-      <c r="B421" s="34"/>
+      <c r="B421" s="24"/>
       <c r="C421" s="24"/>
       <c r="D421" s="24"/>
       <c r="E421" s="24"/>
     </row>
     <row r="422" ht="24" customHeight="1">
       <c r="A422" s="34"/>
-      <c r="B422" s="34"/>
+      <c r="B422" s="24"/>
       <c r="C422" s="24"/>
       <c r="D422" s="24"/>
       <c r="E422" s="24"/>
     </row>
     <row r="423" ht="24" customHeight="1">
       <c r="A423" s="34"/>
-      <c r="B423" s="34"/>
+      <c r="B423" s="24"/>
       <c r="C423" s="24"/>
       <c r="D423" s="24"/>
       <c r="E423" s="24"/>
     </row>
     <row r="424" ht="24" customHeight="1">
       <c r="A424" s="34"/>
-      <c r="B424" s="34"/>
+      <c r="B424" s="24"/>
       <c r="C424" s="24"/>
       <c r="D424" s="24"/>
       <c r="E424" s="24"/>
     </row>
     <row r="425" ht="24" customHeight="1">
       <c r="A425" s="34"/>
-      <c r="B425" s="34"/>
+      <c r="B425" s="24"/>
       <c r="C425" s="24"/>
       <c r="D425" s="24"/>
       <c r="E425" s="24"/>
     </row>
     <row r="426" ht="24" customHeight="1">
       <c r="A426" s="34"/>
-      <c r="B426" s="34"/>
+      <c r="B426" s="24"/>
       <c r="C426" s="24"/>
       <c r="D426" s="24"/>
       <c r="E426" s="24"/>
     </row>
     <row r="427" ht="24" customHeight="1">
       <c r="A427" s="34"/>
-      <c r="B427" s="34"/>
+      <c r="B427" s="24"/>
       <c r="C427" s="24"/>
       <c r="D427" s="24"/>
       <c r="E427" s="24"/>
     </row>
     <row r="428" ht="24" customHeight="1">
       <c r="A428" s="34"/>
-      <c r="B428" s="34"/>
+      <c r="B428" s="24"/>
       <c r="C428" s="24"/>
       <c r="D428" s="24"/>
       <c r="E428" s="24"/>
     </row>
     <row r="429" ht="24" customHeight="1">
       <c r="A429" s="34"/>
-      <c r="B429" s="34"/>
+      <c r="B429" s="24"/>
       <c r="C429" s="24"/>
       <c r="D429" s="24"/>
       <c r="E429" s="24"/>
     </row>
     <row r="430" ht="24" customHeight="1">
       <c r="A430" s="34"/>
-      <c r="B430" s="34"/>
+      <c r="B430" s="24"/>
       <c r="C430" s="24"/>
       <c r="D430" s="24"/>
       <c r="E430" s="24"/>
     </row>
     <row r="431" ht="24" customHeight="1">
       <c r="A431" s="34"/>
-      <c r="B431" s="34"/>
+      <c r="B431" s="24"/>
       <c r="C431" s="24"/>
       <c r="D431" s="24"/>
       <c r="E431" s="24"/>
     </row>
     <row r="432" ht="24" customHeight="1">
       <c r="A432" s="34"/>
-      <c r="B432" s="34"/>
+      <c r="B432" s="24"/>
       <c r="C432" s="24"/>
       <c r="D432" s="24"/>
       <c r="E432" s="24"/>
     </row>
     <row r="433" ht="24" customHeight="1">
       <c r="A433" s="34"/>
-      <c r="B433" s="34"/>
+      <c r="B433" s="24"/>
       <c r="C433" s="24"/>
       <c r="D433" s="24"/>
       <c r="E433" s="24"/>
     </row>
     <row r="434" ht="24" customHeight="1">
       <c r="A434" s="34"/>
-      <c r="B434" s="34"/>
+      <c r="B434" s="24"/>
       <c r="C434" s="24"/>
       <c r="D434" s="24"/>
       <c r="E434" s="24"/>
     </row>
     <row r="435" ht="24" customHeight="1">
       <c r="A435" s="34"/>
-      <c r="B435" s="34"/>
+      <c r="B435" s="24"/>
       <c r="C435" s="24"/>
       <c r="D435" s="24"/>
       <c r="E435" s="24"/>
     </row>
     <row r="436" ht="24" customHeight="1">
       <c r="A436" s="34"/>
-      <c r="B436" s="34"/>
+      <c r="B436" s="24"/>
       <c r="C436" s="24"/>
       <c r="D436" s="24"/>
       <c r="E436" s="24"/>
     </row>
     <row r="437" ht="24" customHeight="1">
       <c r="A437" s="34"/>
-      <c r="B437" s="34"/>
+      <c r="B437" s="24"/>
       <c r="C437" s="24"/>
       <c r="D437" s="24"/>
       <c r="E437" s="24"/>
     </row>
     <row r="438" ht="24" customHeight="1">
       <c r="A438" s="34"/>
-      <c r="B438" s="34"/>
+      <c r="B438" s="24"/>
       <c r="C438" s="24"/>
       <c r="D438" s="24"/>
       <c r="E438" s="24"/>
     </row>
     <row r="439" ht="24" customHeight="1">
       <c r="A439" s="34"/>
-      <c r="B439" s="34"/>
+      <c r="B439" s="24"/>
       <c r="C439" s="24"/>
       <c r="D439" s="24"/>
       <c r="E439" s="24"/>
     </row>
     <row r="440" ht="24" customHeight="1">
       <c r="A440" s="34"/>
-      <c r="B440" s="34"/>
+      <c r="B440" s="24"/>
       <c r="C440" s="24"/>
       <c r="D440" s="24"/>
       <c r="E440" s="24"/>
     </row>
     <row r="441" ht="24" customHeight="1">
       <c r="A441" s="34"/>
-      <c r="B441" s="34"/>
+      <c r="B441" s="24"/>
       <c r="C441" s="24"/>
       <c r="D441" s="24"/>
       <c r="E441" s="24"/>
     </row>
     <row r="442" ht="24" customHeight="1">
       <c r="A442" s="34"/>
-      <c r="B442" s="34"/>
+      <c r="B442" s="24"/>
       <c r="C442" s="24"/>
       <c r="D442" s="24"/>
       <c r="E442" s="24"/>
     </row>
     <row r="443" ht="24" customHeight="1">
       <c r="A443" s="34"/>
-      <c r="B443" s="34"/>
+      <c r="B443" s="24"/>
       <c r="C443" s="24"/>
       <c r="D443" s="24"/>
       <c r="E443" s="24"/>
     </row>
     <row r="444" ht="24" customHeight="1">
       <c r="A444" s="34"/>
-      <c r="B444" s="34"/>
+      <c r="B444" s="24"/>
       <c r="C444" s="24"/>
       <c r="D444" s="24"/>
       <c r="E444" s="24"/>
     </row>
     <row r="445" ht="24" customHeight="1">
       <c r="A445" s="34"/>
-      <c r="B445" s="34"/>
+      <c r="B445" s="24"/>
       <c r="C445" s="24"/>
       <c r="D445" s="24"/>
       <c r="E445" s="24"/>
     </row>
     <row r="446" ht="24" customHeight="1">
       <c r="A446" s="34"/>
-      <c r="B446" s="34"/>
+      <c r="B446" s="24"/>
       <c r="C446" s="24"/>
       <c r="D446" s="24"/>
       <c r="E446" s="24"/>
     </row>
     <row r="447" ht="24" customHeight="1">
       <c r="A447" s="34"/>
-      <c r="B447" s="34"/>
+      <c r="B447" s="24"/>
       <c r="C447" s="24"/>
       <c r="D447" s="24"/>
       <c r="E447" s="24"/>
     </row>
     <row r="448" ht="24" customHeight="1">
       <c r="A448" s="34"/>
-      <c r="B448" s="34"/>
+      <c r="B448" s="24"/>
       <c r="C448" s="24"/>
       <c r="D448" s="24"/>
       <c r="E448" s="24"/>
     </row>
     <row r="449" ht="24" customHeight="1">
       <c r="A449" s="34"/>
-      <c r="B449" s="34"/>
+      <c r="B449" s="24"/>
       <c r="C449" s="24"/>
       <c r="D449" s="24"/>
       <c r="E449" s="24"/>
     </row>
     <row r="450" ht="24" customHeight="1">
       <c r="A450" s="34"/>
-      <c r="B450" s="34"/>
+      <c r="B450" s="24"/>
       <c r="C450" s="24"/>
       <c r="D450" s="24"/>
       <c r="E450" s="24"/>
     </row>
     <row r="451" ht="24" customHeight="1">
       <c r="A451" s="34"/>
-      <c r="B451" s="34"/>
+      <c r="B451" s="24"/>
       <c r="C451" s="24"/>
       <c r="D451" s="24"/>
       <c r="E451" s="24"/>
     </row>
     <row r="452" ht="24" customHeight="1">
       <c r="A452" s="34"/>
-      <c r="B452" s="34"/>
+      <c r="B452" s="24"/>
       <c r="C452" s="24"/>
       <c r="D452" s="24"/>
       <c r="E452" s="24"/>
     </row>
     <row r="453" ht="24" customHeight="1">
       <c r="A453" s="34"/>
-      <c r="B453" s="34"/>
+      <c r="B453" s="24"/>
       <c r="C453" s="24"/>
       <c r="D453" s="24"/>
       <c r="E453" s="24"/>
     </row>
     <row r="454" ht="24" customHeight="1">
       <c r="A454" s="34"/>
-      <c r="B454" s="34"/>
+      <c r="B454" s="24"/>
       <c r="C454" s="24"/>
       <c r="D454" s="24"/>
       <c r="E454" s="24"/>
     </row>
     <row r="455" ht="24" customHeight="1">
       <c r="A455" s="34"/>
-      <c r="B455" s="34"/>
+      <c r="B455" s="24"/>
       <c r="C455" s="24"/>
       <c r="D455" s="24"/>
       <c r="E455" s="24"/>
     </row>
     <row r="456" ht="24" customHeight="1">
       <c r="A456" s="34"/>
-      <c r="B456" s="34"/>
+      <c r="B456" s="24"/>
       <c r="C456" s="24"/>
       <c r="D456" s="24"/>
       <c r="E456" s="24"/>
     </row>
     <row r="457" ht="24" customHeight="1">
       <c r="A457" s="34"/>
-      <c r="B457" s="34"/>
+      <c r="B457" s="24"/>
       <c r="C457" s="24"/>
       <c r="D457" s="24"/>
       <c r="E457" s="24"/>
     </row>
     <row r="458" ht="24" customHeight="1">
       <c r="A458" s="34"/>
-      <c r="B458" s="34"/>
+      <c r="B458" s="24"/>
       <c r="C458" s="24"/>
       <c r="D458" s="24"/>
       <c r="E458" s="24"/>
     </row>
     <row r="459" ht="24" customHeight="1">
       <c r="A459" s="34"/>
-      <c r="B459" s="34"/>
+      <c r="B459" s="24"/>
       <c r="C459" s="24"/>
       <c r="D459" s="24"/>
       <c r="E459" s="24"/>
     </row>
     <row r="460" ht="24" customHeight="1">
       <c r="A460" s="34"/>
-      <c r="B460" s="34"/>
+      <c r="B460" s="24"/>
       <c r="C460" s="24"/>
       <c r="D460" s="24"/>
       <c r="E460" s="24"/>
     </row>
     <row r="461" ht="24" customHeight="1">
       <c r="A461" s="34"/>
-      <c r="B461" s="34"/>
+      <c r="B461" s="24"/>
       <c r="C461" s="24"/>
       <c r="D461" s="24"/>
       <c r="E461" s="24"/>
     </row>
     <row r="462" ht="24" customHeight="1">
       <c r="A462" s="34"/>
-      <c r="B462" s="34"/>
+      <c r="B462" s="24"/>
       <c r="C462" s="24"/>
       <c r="D462" s="24"/>
       <c r="E462" s="24"/>
     </row>
     <row r="463" ht="24" customHeight="1">
       <c r="A463" s="34"/>
-      <c r="B463" s="34"/>
+      <c r="B463" s="24"/>
       <c r="C463" s="24"/>
       <c r="D463" s="24"/>
       <c r="E463" s="24"/>
     </row>
     <row r="464" ht="24" customHeight="1">
       <c r="A464" s="34"/>
-      <c r="B464" s="34"/>
+      <c r="B464" s="24"/>
       <c r="C464" s="24"/>
       <c r="D464" s="24"/>
       <c r="E464" s="24"/>
     </row>
     <row r="465" ht="24" customHeight="1">
       <c r="A465" s="34"/>
-      <c r="B465" s="34"/>
+      <c r="B465" s="24"/>
       <c r="C465" s="24"/>
       <c r="D465" s="24"/>
       <c r="E465" s="24"/>
     </row>
     <row r="466" ht="24" customHeight="1">
       <c r="A466" s="34"/>
-      <c r="B466" s="34"/>
+      <c r="B466" s="24"/>
       <c r="C466" s="24"/>
       <c r="D466" s="24"/>
       <c r="E466" s="24"/>
     </row>
     <row r="467" ht="24" customHeight="1">
       <c r="A467" s="34"/>
-      <c r="B467" s="34"/>
+      <c r="B467" s="24"/>
       <c r="C467" s="24"/>
       <c r="D467" s="24"/>
       <c r="E467" s="24"/>
     </row>
     <row r="468" ht="24" customHeight="1">
       <c r="A468" s="34"/>
-      <c r="B468" s="34"/>
+      <c r="B468" s="24"/>
       <c r="C468" s="24"/>
       <c r="D468" s="24"/>
       <c r="E468" s="24"/>
     </row>
     <row r="469" ht="24" customHeight="1">
       <c r="A469" s="34"/>
-      <c r="B469" s="34"/>
+      <c r="B469" s="24"/>
       <c r="C469" s="24"/>
       <c r="D469" s="24"/>
       <c r="E469" s="24"/>
     </row>
     <row r="470" ht="24" customHeight="1">
       <c r="A470" s="34"/>
-      <c r="B470" s="34"/>
+      <c r="B470" s="24"/>
       <c r="C470" s="24"/>
       <c r="D470" s="24"/>
       <c r="E470" s="24"/>
     </row>
     <row r="471" ht="24" customHeight="1">
       <c r="A471" s="34"/>
-      <c r="B471" s="34"/>
+      <c r="B471" s="24"/>
       <c r="C471" s="24"/>
       <c r="D471" s="24"/>
       <c r="E471" s="24"/>
     </row>
     <row r="472" ht="24" customHeight="1">
       <c r="A472" s="34"/>
-      <c r="B472" s="34"/>
+      <c r="B472" s="24"/>
       <c r="C472" s="24"/>
       <c r="D472" s="24"/>
       <c r="E472" s="24"/>
     </row>
     <row r="473" ht="24" customHeight="1">
       <c r="A473" s="34"/>
-      <c r="B473" s="34"/>
+      <c r="B473" s="24"/>
       <c r="C473" s="24"/>
       <c r="D473" s="24"/>
       <c r="E473" s="24"/>
     </row>
     <row r="474" ht="24" customHeight="1">
       <c r="A474" s="34"/>
-      <c r="B474" s="34"/>
+      <c r="B474" s="24"/>
       <c r="C474" s="24"/>
       <c r="D474" s="24"/>
       <c r="E474" s="24"/>
     </row>
     <row r="475" ht="24" customHeight="1">
       <c r="A475" s="34"/>
-      <c r="B475" s="34"/>
+      <c r="B475" s="24"/>
       <c r="C475" s="24"/>
       <c r="D475" s="24"/>
       <c r="E475" s="24"/>
     </row>
     <row r="476" ht="24" customHeight="1">
       <c r="A476" s="34"/>
-      <c r="B476" s="34"/>
+      <c r="B476" s="24"/>
       <c r="C476" s="24"/>
       <c r="D476" s="24"/>
       <c r="E476" s="24"/>
     </row>
     <row r="477" ht="24" customHeight="1">
       <c r="A477" s="34"/>
-      <c r="B477" s="34"/>
+      <c r="B477" s="24"/>
       <c r="C477" s="24"/>
       <c r="D477" s="24"/>
       <c r="E477" s="24"/>
     </row>
     <row r="478" ht="24" customHeight="1">
       <c r="A478" s="34"/>
-      <c r="B478" s="34"/>
+      <c r="B478" s="24"/>
       <c r="C478" s="24"/>
       <c r="D478" s="24"/>
       <c r="E478" s="24"/>
     </row>
     <row r="479" ht="24" customHeight="1">
       <c r="A479" s="34"/>
-      <c r="B479" s="34"/>
+      <c r="B479" s="24"/>
       <c r="C479" s="24"/>
       <c r="D479" s="24"/>
       <c r="E479" s="24"/>
     </row>
     <row r="480" ht="24" customHeight="1">
       <c r="A480" s="34"/>
-      <c r="B480" s="34"/>
+      <c r="B480" s="24"/>
       <c r="C480" s="24"/>
       <c r="D480" s="24"/>
       <c r="E480" s="24"/>
     </row>
     <row r="481" ht="24" customHeight="1">
       <c r="A481" s="34"/>
-      <c r="B481" s="34"/>
+      <c r="B481" s="24"/>
       <c r="C481" s="24"/>
       <c r="D481" s="24"/>
       <c r="E481" s="24"/>
     </row>
     <row r="482" ht="24" customHeight="1">
       <c r="A482" s="34"/>
-      <c r="B482" s="34"/>
+      <c r="B482" s="24"/>
       <c r="C482" s="24"/>
       <c r="D482" s="24"/>
       <c r="E482" s="24"/>
     </row>
     <row r="483" ht="24" customHeight="1">
       <c r="A483" s="34"/>
-      <c r="B483" s="34"/>
+      <c r="B483" s="24"/>
       <c r="C483" s="24"/>
       <c r="D483" s="24"/>
       <c r="E483" s="24"/>
     </row>
     <row r="484" ht="24" customHeight="1">
       <c r="A484" s="34"/>
-      <c r="B484" s="34"/>
+      <c r="B484" s="24"/>
       <c r="C484" s="24"/>
       <c r="D484" s="24"/>
       <c r="E484" s="24"/>
     </row>
     <row r="485" ht="24" customHeight="1">
       <c r="A485" s="34"/>
-      <c r="B485" s="34"/>
+      <c r="B485" s="24"/>
       <c r="C485" s="24"/>
       <c r="D485" s="24"/>
       <c r="E485" s="24"/>
     </row>
     <row r="486" ht="24" customHeight="1">
       <c r="A486" s="34"/>
-      <c r="B486" s="34"/>
+      <c r="B486" s="24"/>
       <c r="C486" s="24"/>
       <c r="D486" s="24"/>
       <c r="E486" s="24"/>
     </row>
     <row r="487" ht="24" customHeight="1">
       <c r="A487" s="34"/>
-      <c r="B487" s="34"/>
+      <c r="B487" s="24"/>
       <c r="C487" s="24"/>
       <c r="D487" s="24"/>
       <c r="E487" s="24"/>
     </row>
     <row r="488" ht="24" customHeight="1">
       <c r="A488" s="34"/>
-      <c r="B488" s="34"/>
+      <c r="B488" s="24"/>
       <c r="C488" s="24"/>
       <c r="D488" s="24"/>
       <c r="E488" s="24"/>
     </row>
     <row r="489" ht="24" customHeight="1">
       <c r="A489" s="34"/>
-      <c r="B489" s="34"/>
+      <c r="B489" s="24"/>
       <c r="C489" s="24"/>
       <c r="D489" s="24"/>
       <c r="E489" s="24"/>
     </row>
     <row r="490" ht="24" customHeight="1">
       <c r="A490" s="34"/>
-      <c r="B490" s="34"/>
+      <c r="B490" s="24"/>
       <c r="C490" s="24"/>
       <c r="D490" s="24"/>
       <c r="E490" s="24"/>
     </row>
     <row r="491" ht="24" customHeight="1">
       <c r="A491" s="34"/>
-      <c r="B491" s="34"/>
+      <c r="B491" s="24"/>
       <c r="C491" s="24"/>
       <c r="D491" s="24"/>
       <c r="E491" s="24"/>
     </row>
     <row r="492" ht="24" customHeight="1">
       <c r="A492" s="34"/>
-      <c r="B492" s="34"/>
+      <c r="B492" s="24"/>
       <c r="C492" s="24"/>
       <c r="D492" s="24"/>
       <c r="E492" s="24"/>
     </row>
     <row r="493" ht="24" customHeight="1">
       <c r="A493" s="34"/>
-      <c r="B493" s="34"/>
+      <c r="B493" s="24"/>
       <c r="C493" s="24"/>
       <c r="D493" s="24"/>
       <c r="E493" s="24"/>
     </row>
     <row r="494" ht="24" customHeight="1">
       <c r="A494" s="34"/>
-      <c r="B494" s="34"/>
+      <c r="B494" s="24"/>
       <c r="C494" s="24"/>
       <c r="D494" s="24"/>
       <c r="E494" s="24"/>
     </row>
     <row r="495" ht="24" customHeight="1">
       <c r="A495" s="34"/>
-      <c r="B495" s="34"/>
+      <c r="B495" s="24"/>
       <c r="C495" s="24"/>
       <c r="D495" s="24"/>
       <c r="E495" s="24"/>
     </row>
     <row r="496" ht="24" customHeight="1">
       <c r="A496" s="34"/>
-      <c r="B496" s="34"/>
+      <c r="B496" s="24"/>
       <c r="C496" s="24"/>
       <c r="D496" s="24"/>
       <c r="E496" s="24"/>
     </row>
     <row r="497" ht="24" customHeight="1">
       <c r="A497" s="34"/>
-      <c r="B497" s="34"/>
+      <c r="B497" s="24"/>
       <c r="C497" s="24"/>
       <c r="D497" s="24"/>
       <c r="E497" s="24"/>
     </row>
     <row r="498" ht="24" customHeight="1">
       <c r="A498" s="34"/>
-      <c r="B498" s="34"/>
+      <c r="B498" s="24"/>
       <c r="C498" s="24"/>
       <c r="D498" s="24"/>
       <c r="E498" s="24"/>
     </row>
     <row r="499" ht="24" customHeight="1">
       <c r="A499" s="34"/>
-      <c r="B499" s="34"/>
+      <c r="B499" s="24"/>
       <c r="C499" s="24"/>
       <c r="D499" s="24"/>
       <c r="E499" s="24"/>
     </row>
     <row r="500" ht="24" customHeight="1">
       <c r="A500" s="34"/>
-      <c r="B500" s="34"/>
+      <c r="B500" s="24"/>
       <c r="C500" s="24"/>
       <c r="D500" s="24"/>
       <c r="E500" s="24"/>
     </row>
     <row r="501" ht="24" customHeight="1">
       <c r="A501" s="34"/>
-      <c r="B501" s="34"/>
+      <c r="B501" s="24"/>
       <c r="C501" s="24"/>
       <c r="D501" s="24"/>
       <c r="E501" s="24"/>
     </row>
     <row r="502" ht="24" customHeight="1">
       <c r="A502" s="34"/>
-      <c r="B502" s="34"/>
+      <c r="B502" s="24"/>
       <c r="C502" s="24"/>
       <c r="D502" s="24"/>
       <c r="E502" s="24"/>
     </row>
     <row r="503" ht="24" customHeight="1">
       <c r="A503" s="34"/>
-      <c r="B503" s="34"/>
+      <c r="B503" s="24"/>
       <c r="C503" s="24"/>
       <c r="D503" s="24"/>
       <c r="E503" s="24"/>
     </row>
     <row r="504" ht="24" customHeight="1">
       <c r="A504" s="34"/>
-      <c r="B504" s="34"/>
+      <c r="B504" s="24"/>
       <c r="C504" s="24"/>
       <c r="D504" s="24"/>
       <c r="E504" s="24"/>
     </row>
     <row r="505" ht="24" customHeight="1">
       <c r="A505" s="34"/>
-      <c r="B505" s="34"/>
+      <c r="B505" s="24"/>
       <c r="C505" s="24"/>
       <c r="D505" s="24"/>
       <c r="E505" s="24"/>
     </row>
     <row r="506" ht="24" customHeight="1">
       <c r="A506" s="34"/>
-      <c r="B506" s="34"/>
+      <c r="B506" s="24"/>
       <c r="C506" s="24"/>
       <c r="D506" s="24"/>
       <c r="E506" s="24"/>
     </row>
     <row r="507" ht="24" customHeight="1">
       <c r="A507" s="34"/>
-      <c r="B507" s="34"/>
+      <c r="B507" s="24"/>
       <c r="C507" s="24"/>
       <c r="D507" s="24"/>
       <c r="E507" s="24"/>
     </row>
     <row r="508" ht="24" customHeight="1">
       <c r="A508" s="34"/>
-      <c r="B508" s="34"/>
+      <c r="B508" s="24"/>
       <c r="C508" s="24"/>
       <c r="D508" s="24"/>
       <c r="E508" s="24"/>
     </row>
     <row r="509" ht="24" customHeight="1">
       <c r="A509" s="34"/>
-      <c r="B509" s="34"/>
+      <c r="B509" s="24"/>
       <c r="C509" s="24"/>
       <c r="D509" s="24"/>
       <c r="E509" s="24"/>
     </row>
     <row r="510" ht="24" customHeight="1">
       <c r="A510" s="34"/>
-      <c r="B510" s="34"/>
+      <c r="B510" s="24"/>
       <c r="C510" s="24"/>
       <c r="D510" s="24"/>
       <c r="E510" s="24"/>
     </row>
     <row r="511" ht="24" customHeight="1">
       <c r="A511" s="34"/>
-      <c r="B511" s="34"/>
+      <c r="B511" s="24"/>
       <c r="C511" s="24"/>
       <c r="D511" s="24"/>
       <c r="E511" s="24"/>
     </row>
     <row r="512" ht="24" customHeight="1">
       <c r="A512" s="34"/>
-      <c r="B512" s="34"/>
+      <c r="B512" s="24"/>
       <c r="C512" s="24"/>
       <c r="D512" s="24"/>
       <c r="E512" s="24"/>
     </row>
     <row r="513" ht="24" customHeight="1">
       <c r="A513" s="34"/>
-      <c r="B513" s="34"/>
+      <c r="B513" s="24"/>
       <c r="C513" s="24"/>
       <c r="D513" s="24"/>
       <c r="E513" s="24"/>
     </row>
     <row r="514" ht="24" customHeight="1">
       <c r="A514" s="34"/>
-      <c r="B514" s="34"/>
+      <c r="B514" s="24"/>
       <c r="C514" s="24"/>
       <c r="D514" s="24"/>
       <c r="E514" s="24"/>
     </row>
     <row r="515" ht="24" customHeight="1">
       <c r="A515" s="34"/>
-      <c r="B515" s="34"/>
+      <c r="B515" s="24"/>
       <c r="C515" s="24"/>
       <c r="D515" s="24"/>
       <c r="E515" s="24"/>
     </row>
     <row r="516" ht="24" customHeight="1">
       <c r="A516" s="34"/>
-      <c r="B516" s="34"/>
+      <c r="B516" s="24"/>
       <c r="C516" s="24"/>
       <c r="D516" s="24"/>
       <c r="E516" s="24"/>
     </row>
     <row r="517" ht="24" customHeight="1">
       <c r="A517" s="34"/>
-      <c r="B517" s="34"/>
+      <c r="B517" s="24"/>
       <c r="C517" s="24"/>
       <c r="D517" s="24"/>
       <c r="E517" s="24"/>
     </row>
     <row r="518" ht="24" customHeight="1">
       <c r="A518" s="34"/>
-      <c r="B518" s="34"/>
+      <c r="B518" s="24"/>
       <c r="C518" s="24"/>
       <c r="D518" s="24"/>
       <c r="E518" s="24"/>
     </row>
     <row r="519" ht="24" customHeight="1">
       <c r="A519" s="34"/>
-      <c r="B519" s="34"/>
+      <c r="B519" s="24"/>
       <c r="C519" s="24"/>
       <c r="D519" s="24"/>
       <c r="E519" s="24"/>
     </row>
     <row r="520" ht="24" customHeight="1">
       <c r="A520" s="34"/>
-      <c r="B520" s="34"/>
+      <c r="B520" s="24"/>
       <c r="C520" s="24"/>
       <c r="D520" s="24"/>
       <c r="E520" s="24"/>
     </row>
     <row r="521" ht="24" customHeight="1">
       <c r="A521" s="34"/>
-      <c r="B521" s="34"/>
+      <c r="B521" s="24"/>
       <c r="C521" s="24"/>
       <c r="D521" s="24"/>
       <c r="E521" s="24"/>
     </row>
     <row r="522" ht="24" customHeight="1">
       <c r="A522" s="34"/>
-      <c r="B522" s="34"/>
+      <c r="B522" s="24"/>
       <c r="C522" s="24"/>
       <c r="D522" s="24"/>
       <c r="E522" s="24"/>
     </row>
     <row r="523" ht="24" customHeight="1">
       <c r="A523" s="34"/>
-      <c r="B523" s="34"/>
+      <c r="B523" s="24"/>
       <c r="C523" s="24"/>
       <c r="D523" s="24"/>
       <c r="E523" s="24"/>
     </row>
     <row r="524" ht="24" customHeight="1">
       <c r="A524" s="34"/>
-      <c r="B524" s="34"/>
+      <c r="B524" s="24"/>
       <c r="C524" s="24"/>
       <c r="D524" s="24"/>
       <c r="E524" s="24"/>
     </row>
     <row r="525" ht="24" customHeight="1">
       <c r="A525" s="34"/>
-      <c r="B525" s="34"/>
+      <c r="B525" s="24"/>
       <c r="C525" s="24"/>
       <c r="D525" s="24"/>
       <c r="E525" s="24"/>
     </row>
     <row r="526" ht="24" customHeight="1">
       <c r="A526" s="34"/>
-      <c r="B526" s="34"/>
+      <c r="B526" s="24"/>
       <c r="C526" s="24"/>
       <c r="D526" s="24"/>
       <c r="E526" s="24"/>
     </row>
     <row r="527" ht="24" customHeight="1">
       <c r="A527" s="34"/>
-      <c r="B527" s="34"/>
+      <c r="B527" s="24"/>
       <c r="C527" s="24"/>
       <c r="D527" s="24"/>
       <c r="E527" s="24"/>
     </row>
     <row r="528" ht="24" customHeight="1">
       <c r="A528" s="34"/>
-      <c r="B528" s="34"/>
+      <c r="B528" s="24"/>
       <c r="C528" s="24"/>
       <c r="D528" s="24"/>
       <c r="E528" s="24"/>
     </row>
     <row r="529" ht="24" customHeight="1">
       <c r="A529" s="34"/>
-      <c r="B529" s="34"/>
+      <c r="B529" s="24"/>
       <c r="C529" s="24"/>
       <c r="D529" s="24"/>
       <c r="E529" s="24"/>
     </row>
     <row r="530" ht="24" customHeight="1">
       <c r="A530" s="34"/>
-      <c r="B530" s="34"/>
+      <c r="B530" s="24"/>
       <c r="C530" s="24"/>
       <c r="D530" s="24"/>
       <c r="E530" s="24"/>
     </row>
     <row r="531" ht="24" customHeight="1">
       <c r="A531" s="34"/>
-      <c r="B531" s="34"/>
+      <c r="B531" s="24"/>
       <c r="C531" s="24"/>
       <c r="D531" s="24"/>
       <c r="E531" s="24"/>
     </row>
     <row r="532" ht="24" customHeight="1">
       <c r="A532" s="34"/>
-      <c r="B532" s="34"/>
+      <c r="B532" s="24"/>
       <c r="C532" s="24"/>
       <c r="D532" s="24"/>
       <c r="E532" s="24"/>
     </row>
     <row r="533" ht="24" customHeight="1">
       <c r="A533" s="34"/>
-      <c r="B533" s="34"/>
+      <c r="B533" s="24"/>
       <c r="C533" s="24"/>
       <c r="D533" s="24"/>
       <c r="E533" s="24"/>
     </row>
     <row r="534" ht="24" customHeight="1">
       <c r="A534" s="34"/>
-      <c r="B534" s="34"/>
+      <c r="B534" s="24"/>
       <c r="C534" s="24"/>
       <c r="D534" s="24"/>
       <c r="E534" s="24"/>
     </row>
     <row r="535" ht="24" customHeight="1">
       <c r="A535" s="34"/>
-      <c r="B535" s="34"/>
+      <c r="B535" s="24"/>
       <c r="C535" s="24"/>
       <c r="D535" s="24"/>
       <c r="E535" s="24"/>
     </row>
     <row r="536" ht="24" customHeight="1">
       <c r="A536" s="34"/>
-      <c r="B536" s="34"/>
+      <c r="B536" s="24"/>
       <c r="C536" s="24"/>
       <c r="D536" s="24"/>
       <c r="E536" s="24"/>
     </row>
     <row r="537" ht="24" customHeight="1">
       <c r="A537" s="34"/>
-      <c r="B537" s="34"/>
+      <c r="B537" s="24"/>
       <c r="C537" s="24"/>
       <c r="D537" s="24"/>
       <c r="E537" s="24"/>
     </row>
     <row r="538" ht="24" customHeight="1">
       <c r="A538" s="34"/>
-      <c r="B538" s="34"/>
+      <c r="B538" s="24"/>
       <c r="C538" s="24"/>
       <c r="D538" s="24"/>
       <c r="E538" s="24"/>
     </row>
     <row r="539" ht="24" customHeight="1">
       <c r="A539" s="34"/>
-      <c r="B539" s="34"/>
+      <c r="B539" s="24"/>
       <c r="C539" s="24"/>
       <c r="D539" s="24"/>
       <c r="E539" s="24"/>
     </row>
     <row r="540" ht="24" customHeight="1">
       <c r="A540" s="34"/>
-      <c r="B540" s="34"/>
+      <c r="B540" s="24"/>
       <c r="C540" s="24"/>
       <c r="D540" s="24"/>
       <c r="E540" s="24"/>
     </row>
     <row r="541" ht="24" customHeight="1">
       <c r="A541" s="34"/>
-      <c r="B541" s="34"/>
+      <c r="B541" s="24"/>
       <c r="C541" s="24"/>
       <c r="D541" s="24"/>
       <c r="E541" s="24"/>
     </row>
     <row r="542" ht="24" customHeight="1">
       <c r="A542" s="34"/>
-      <c r="B542" s="34"/>
+      <c r="B542" s="24"/>
       <c r="C542" s="24"/>
       <c r="D542" s="24"/>
       <c r="E542" s="24"/>
     </row>
     <row r="543" ht="24" customHeight="1">
       <c r="A543" s="34"/>
-      <c r="B543" s="34"/>
+      <c r="B543" s="24"/>
       <c r="C543" s="24"/>
       <c r="D543" s="24"/>
       <c r="E543" s="24"/>
     </row>
     <row r="544" ht="24" customHeight="1">
       <c r="A544" s="34"/>
-      <c r="B544" s="34"/>
+      <c r="B544" s="24"/>
       <c r="C544" s="24"/>
       <c r="D544" s="24"/>
       <c r="E544" s="24"/>
     </row>
     <row r="545" ht="24" customHeight="1">
       <c r="A545" s="34"/>
-      <c r="B545" s="34"/>
+      <c r="B545" s="24"/>
       <c r="C545" s="24"/>
       <c r="D545" s="24"/>
       <c r="E545" s="24"/>
     </row>
     <row r="546" ht="24" customHeight="1">
       <c r="A546" s="34"/>
-      <c r="B546" s="34"/>
+      <c r="B546" s="24"/>
       <c r="C546" s="24"/>
       <c r="D546" s="24"/>
       <c r="E546" s="24"/>
     </row>
     <row r="547" ht="24" customHeight="1">
       <c r="A547" s="34"/>
-      <c r="B547" s="34"/>
+      <c r="B547" s="24"/>
       <c r="C547" s="24"/>
       <c r="D547" s="24"/>
       <c r="E547" s="24"/>
     </row>
     <row r="548" ht="24" customHeight="1">
       <c r="A548" s="34"/>
-      <c r="B548" s="34"/>
+      <c r="B548" s="24"/>
       <c r="C548" s="24"/>
       <c r="D548" s="24"/>
       <c r="E548" s="24"/>
     </row>
     <row r="549" ht="24" customHeight="1">
       <c r="A549" s="34"/>
-      <c r="B549" s="34"/>
+      <c r="B549" s="24"/>
       <c r="C549" s="24"/>
       <c r="D549" s="24"/>
       <c r="E549" s="24"/>
     </row>
     <row r="550" ht="24" customHeight="1">
       <c r="A550" s="34"/>
-      <c r="B550" s="34"/>
+      <c r="B550" s="24"/>
       <c r="C550" s="24"/>
       <c r="D550" s="24"/>
       <c r="E550" s="24"/>
     </row>
     <row r="551" ht="24" customHeight="1">
       <c r="A551" s="34"/>
-      <c r="B551" s="34"/>
+      <c r="B551" s="24"/>
       <c r="C551" s="24"/>
       <c r="D551" s="24"/>
       <c r="E551" s="24"/>
     </row>
     <row r="552" ht="24" customHeight="1">
       <c r="A552" s="34"/>
-      <c r="B552" s="34"/>
+      <c r="B552" s="24"/>
       <c r="C552" s="24"/>
       <c r="D552" s="24"/>
       <c r="E552" s="24"/>
     </row>
     <row r="553" ht="24" customHeight="1">
       <c r="A553" s="34"/>
-      <c r="B553" s="34"/>
+      <c r="B553" s="24"/>
       <c r="C553" s="24"/>
       <c r="D553" s="24"/>
       <c r="E553" s="24"/>
     </row>
     <row r="554" ht="24" customHeight="1">
       <c r="A554" s="34"/>
-      <c r="B554" s="34"/>
+      <c r="B554" s="24"/>
       <c r="C554" s="24"/>
       <c r="D554" s="24"/>
       <c r="E554" s="24"/>
     </row>
     <row r="555" ht="24" customHeight="1">
       <c r="A555" s="34"/>
-      <c r="B555" s="34"/>
+      <c r="B555" s="24"/>
       <c r="C555" s="24"/>
       <c r="D555" s="24"/>
       <c r="E555" s="24"/>
     </row>
     <row r="556" ht="24" customHeight="1">
       <c r="A556" s="34"/>
-      <c r="B556" s="34"/>
+      <c r="B556" s="24"/>
       <c r="C556" s="24"/>
       <c r="D556" s="24"/>
       <c r="E556" s="24"/>
     </row>
     <row r="557" ht="24" customHeight="1">
       <c r="A557" s="34"/>
-      <c r="B557" s="34"/>
+      <c r="B557" s="24"/>
       <c r="C557" s="24"/>
       <c r="D557" s="24"/>
       <c r="E557" s="24"/>
     </row>
     <row r="558" ht="24" customHeight="1">
       <c r="A558" s="34"/>
-      <c r="B558" s="34"/>
+      <c r="B558" s="24"/>
       <c r="C558" s="24"/>
       <c r="D558" s="24"/>
       <c r="E558" s="24"/>
     </row>
     <row r="559" ht="24" customHeight="1">
       <c r="A559" s="34"/>
-      <c r="B559" s="34"/>
+      <c r="B559" s="24"/>
       <c r="C559" s="24"/>
       <c r="D559" s="24"/>
       <c r="E559" s="24"/>
     </row>
     <row r="560" ht="24" customHeight="1">
       <c r="A560" s="34"/>
-      <c r="B560" s="34"/>
+      <c r="B560" s="24"/>
       <c r="C560" s="24"/>
       <c r="D560" s="24"/>
       <c r="E560" s="24"/>
     </row>
     <row r="561" ht="24" customHeight="1">
       <c r="A561" s="34"/>
-      <c r="B561" s="34"/>
+      <c r="B561" s="24"/>
       <c r="C561" s="24"/>
       <c r="D561" s="24"/>
       <c r="E561" s="24"/>
     </row>
     <row r="562" ht="24" customHeight="1">
       <c r="A562" s="34"/>
-      <c r="B562" s="34"/>
+      <c r="B562" s="24"/>
       <c r="C562" s="24"/>
       <c r="D562" s="24"/>
       <c r="E562" s="24"/>
     </row>
     <row r="563" ht="24" customHeight="1">
       <c r="A563" s="34"/>
-      <c r="B563" s="34"/>
+      <c r="B563" s="24"/>
       <c r="C563" s="24"/>
       <c r="D563" s="24"/>
       <c r="E563" s="24"/>
     </row>
     <row r="564" ht="24" customHeight="1">
       <c r="A564" s="34"/>
-      <c r="B564" s="34"/>
+      <c r="B564" s="24"/>
       <c r="C564" s="24"/>
       <c r="D564" s="24"/>
       <c r="E564" s="24"/>
     </row>
     <row r="565" ht="24" customHeight="1">
       <c r="A565" s="34"/>
-      <c r="B565" s="34"/>
+      <c r="B565" s="24"/>
       <c r="C565" s="24"/>
       <c r="D565" s="24"/>
       <c r="E565" s="24"/>
     </row>
     <row r="566" ht="24" customHeight="1">
       <c r="A566" s="34"/>
-      <c r="B566" s="34"/>
+      <c r="B566" s="24"/>
       <c r="C566" s="24"/>
       <c r="D566" s="24"/>
       <c r="E566" s="24"/>
     </row>
     <row r="567" ht="24" customHeight="1">
       <c r="A567" s="34"/>
-      <c r="B567" s="34"/>
+      <c r="B567" s="24"/>
       <c r="C567" s="24"/>
       <c r="D567" s="24"/>
       <c r="E567" s="24"/>
     </row>
     <row r="568" ht="24" customHeight="1">
       <c r="A568" s="34"/>
-      <c r="B568" s="34"/>
+      <c r="B568" s="24"/>
       <c r="C568" s="24"/>
       <c r="D568" s="24"/>
       <c r="E568" s="24"/>
     </row>
     <row r="569" ht="24" customHeight="1">
       <c r="A569" s="34"/>
-      <c r="B569" s="34"/>
+      <c r="B569" s="24"/>
       <c r="C569" s="24"/>
       <c r="D569" s="24"/>
       <c r="E569" s="24"/>
     </row>
     <row r="570" ht="24" customHeight="1">
       <c r="A570" s="34"/>
-      <c r="B570" s="34"/>
+      <c r="B570" s="24"/>
       <c r="C570" s="24"/>
       <c r="D570" s="24"/>
       <c r="E570" s="24"/>
     </row>
     <row r="571" ht="24" customHeight="1">
       <c r="A571" s="34"/>
-      <c r="B571" s="34"/>
+      <c r="B571" s="24"/>
       <c r="C571" s="24"/>
       <c r="D571" s="24"/>
       <c r="E571" s="24"/>
     </row>
     <row r="572" ht="24" customHeight="1">
       <c r="A572" s="34"/>
-      <c r="B572" s="34"/>
+      <c r="B572" s="24"/>
       <c r="C572" s="24"/>
       <c r="D572" s="24"/>
       <c r="E572" s="24"/>
     </row>
     <row r="573" ht="24" customHeight="1">
       <c r="A573" s="34"/>
-      <c r="B573" s="34"/>
+      <c r="B573" s="24"/>
       <c r="C573" s="24"/>
       <c r="D573" s="24"/>
       <c r="E573" s="24"/>
     </row>
     <row r="574" ht="24" customHeight="1">
       <c r="A574" s="34"/>
-      <c r="B574" s="34"/>
+      <c r="B574" s="24"/>
       <c r="C574" s="24"/>
       <c r="D574" s="24"/>
       <c r="E574" s="24"/>
     </row>
     <row r="575" ht="24" customHeight="1">
       <c r="A575" s="34"/>
-      <c r="B575" s="34"/>
+      <c r="B575" s="24"/>
       <c r="C575" s="24"/>
       <c r="D575" s="24"/>
       <c r="E575" s="24"/>
     </row>
     <row r="576" ht="24" customHeight="1">
       <c r="A576" s="34"/>
-      <c r="B576" s="34"/>
+      <c r="B576" s="24"/>
       <c r="C576" s="24"/>
       <c r="D576" s="24"/>
       <c r="E576" s="24"/>
     </row>
     <row r="577" ht="24" customHeight="1">
       <c r="A577" s="34"/>
-      <c r="B577" s="34"/>
+      <c r="B577" s="24"/>
       <c r="C577" s="24"/>
       <c r="D577" s="24"/>
       <c r="E577" s="24"/>
     </row>
     <row r="578" ht="24" customHeight="1">
       <c r="A578" s="34"/>
-      <c r="B578" s="34"/>
+      <c r="B578" s="24"/>
       <c r="C578" s="24"/>
       <c r="D578" s="24"/>
       <c r="E578" s="24"/>
     </row>
     <row r="579" ht="24" customHeight="1">
       <c r="A579" s="34"/>
-      <c r="B579" s="34"/>
+      <c r="B579" s="24"/>
       <c r="C579" s="24"/>
       <c r="D579" s="24"/>
       <c r="E579" s="24"/>
     </row>
     <row r="580" ht="24" customHeight="1">
       <c r="A580" s="34"/>
-      <c r="B580" s="34"/>
+      <c r="B580" s="24"/>
       <c r="C580" s="24"/>
       <c r="D580" s="24"/>
       <c r="E580" s="24"/>
     </row>
     <row r="581" ht="24" customHeight="1">
       <c r="A581" s="34"/>
-      <c r="B581" s="34"/>
+      <c r="B581" s="24"/>
       <c r="C581" s="24"/>
       <c r="D581" s="24"/>
       <c r="E581" s="24"/>
     </row>
     <row r="582" ht="24" customHeight="1">
       <c r="A582" s="34"/>
-      <c r="B582" s="34"/>
+      <c r="B582" s="24"/>
       <c r="C582" s="24"/>
       <c r="D582" s="24"/>
       <c r="E582" s="24"/>
     </row>
     <row r="583" ht="24" customHeight="1">
       <c r="A583" s="34"/>
-      <c r="B583" s="34"/>
+      <c r="B583" s="24"/>
       <c r="C583" s="24"/>
       <c r="D583" s="24"/>
       <c r="E583" s="24"/>
     </row>
     <row r="584" ht="24" customHeight="1">
       <c r="A584" s="34"/>
-      <c r="B584" s="34"/>
+      <c r="B584" s="24"/>
       <c r="C584" s="24"/>
       <c r="D584" s="24"/>
       <c r="E584" s="24"/>
     </row>
     <row r="585" ht="24" customHeight="1">
       <c r="A585" s="34"/>
-      <c r="B585" s="34"/>
+      <c r="B585" s="24"/>
       <c r="C585" s="24"/>
       <c r="D585" s="24"/>
       <c r="E585" s="24"/>
     </row>
     <row r="586" ht="24" customHeight="1">
       <c r="A586" s="34"/>
-      <c r="B586" s="34"/>
+      <c r="B586" s="24"/>
       <c r="C586" s="24"/>
       <c r="D586" s="24"/>
       <c r="E586" s="24"/>
     </row>
     <row r="587" ht="24" customHeight="1">
       <c r="A587" s="34"/>
-      <c r="B587" s="34"/>
+      <c r="B587" s="24"/>
       <c r="C587" s="24"/>
       <c r="D587" s="24"/>
       <c r="E587" s="24"/>
     </row>
     <row r="588" ht="24" customHeight="1">
       <c r="A588" s="34"/>
-      <c r="B588" s="34"/>
+      <c r="B588" s="24"/>
       <c r="C588" s="24"/>
       <c r="D588" s="24"/>
       <c r="E588" s="24"/>
     </row>
     <row r="589" ht="24" customHeight="1">
       <c r="A589" s="34"/>
-      <c r="B589" s="34"/>
+      <c r="B589" s="24"/>
       <c r="C589" s="24"/>
       <c r="D589" s="24"/>
       <c r="E589" s="24"/>
     </row>
     <row r="590" ht="24" customHeight="1">
       <c r="A590" s="34"/>
-      <c r="B590" s="34"/>
+      <c r="B590" s="24"/>
       <c r="C590" s="24"/>
       <c r="D590" s="24"/>
       <c r="E590" s="24"/>
     </row>
     <row r="591" ht="24" customHeight="1">
       <c r="A591" s="34"/>
-      <c r="B591" s="34"/>
+      <c r="B591" s="24"/>
       <c r="C591" s="24"/>
       <c r="D591" s="24"/>
       <c r="E591" s="24"/>
     </row>
     <row r="592" ht="24" customHeight="1">
       <c r="A592" s="34"/>
-      <c r="B592" s="34"/>
+      <c r="B592" s="24"/>
       <c r="C592" s="24"/>
       <c r="D592" s="24"/>
       <c r="E592" s="24"/>
     </row>
     <row r="593" ht="24" customHeight="1">
       <c r="A593" s="34"/>
-      <c r="B593" s="34"/>
+      <c r="B593" s="24"/>
       <c r="C593" s="24"/>
       <c r="D593" s="24"/>
       <c r="E593" s="24"/>
     </row>
     <row r="594" ht="24" customHeight="1">
       <c r="A594" s="34"/>
-      <c r="B594" s="34"/>
+      <c r="B594" s="24"/>
       <c r="C594" s="24"/>
       <c r="D594" s="24"/>
       <c r="E594" s="24"/>
     </row>
     <row r="595" ht="24" customHeight="1">
       <c r="A595" s="34"/>
-      <c r="B595" s="34"/>
+      <c r="B595" s="24"/>
       <c r="C595" s="24"/>
       <c r="D595" s="24"/>
       <c r="E595" s="24"/>
     </row>
     <row r="596" ht="24" customHeight="1">
       <c r="A596" s="34"/>
-      <c r="B596" s="34"/>
+      <c r="B596" s="24"/>
       <c r="C596" s="24"/>
       <c r="D596" s="24"/>
       <c r="E596" s="24"/>
     </row>
     <row r="597" ht="24" customHeight="1">
       <c r="A597" s="34"/>
-      <c r="B597" s="34"/>
+      <c r="B597" s="24"/>
       <c r="C597" s="24"/>
       <c r="D597" s="24"/>
       <c r="E597" s="24"/>
     </row>
     <row r="598" ht="24" customHeight="1">
       <c r="A598" s="34"/>
-      <c r="B598" s="34"/>
+      <c r="B598" s="24"/>
       <c r="C598" s="24"/>
       <c r="D598" s="24"/>
       <c r="E598" s="24"/>
     </row>
     <row r="599" ht="24" customHeight="1">
       <c r="A599" s="34"/>
-      <c r="B599" s="34"/>
+      <c r="B599" s="24"/>
       <c r="C599" s="24"/>
       <c r="D599" s="24"/>
       <c r="E599" s="24"/>
     </row>
     <row r="600" ht="24" customHeight="1">
       <c r="A600" s="34"/>
-      <c r="B600" s="34"/>
+      <c r="B600" s="24"/>
       <c r="C600" s="24"/>
       <c r="D600" s="24"/>
       <c r="E600" s="24"/>
     </row>
     <row r="601" ht="24" customHeight="1">
       <c r="A601" s="34"/>
-      <c r="B601" s="34"/>
+      <c r="B601" s="24"/>
       <c r="C601" s="24"/>
       <c r="D601" s="24"/>
       <c r="E601" s="24"/>
     </row>
     <row r="602" ht="24" customHeight="1">
       <c r="A602" s="34"/>
-      <c r="B602" s="34"/>
+      <c r="B602" s="24"/>
       <c r="C602" s="24"/>
       <c r="D602" s="24"/>
       <c r="E602" s="24"/>
     </row>
     <row r="603" ht="24" customHeight="1">
       <c r="A603" s="34"/>
-      <c r="B603" s="34"/>
+      <c r="B603" s="24"/>
       <c r="C603" s="24"/>
       <c r="D603" s="24"/>
       <c r="E603" s="24"/>
     </row>
     <row r="604" ht="24" customHeight="1">
       <c r="A604" s="34"/>
-      <c r="B604" s="34"/>
+      <c r="B604" s="24"/>
       <c r="C604" s="24"/>
       <c r="D604" s="24"/>
       <c r="E604" s="24"/>
     </row>
     <row r="605" ht="24" customHeight="1">
       <c r="A605" s="34"/>
-      <c r="B605" s="34"/>
+      <c r="B605" s="24"/>
       <c r="C605" s="24"/>
       <c r="D605" s="24"/>
       <c r="E605" s="24"/>
     </row>
     <row r="606" ht="24" customHeight="1">
       <c r="A606" s="34"/>
-      <c r="B606" s="34"/>
+      <c r="B606" s="24"/>
       <c r="C606" s="24"/>
       <c r="D606" s="24"/>
       <c r="E606" s="24"/>
     </row>
     <row r="607" ht="24" customHeight="1">
       <c r="A607" s="34"/>
-      <c r="B607" s="34"/>
+      <c r="B607" s="24"/>
       <c r="C607" s="24"/>
       <c r="D607" s="24"/>
       <c r="E607" s="24"/>
     </row>
     <row r="608" ht="24" customHeight="1">
       <c r="A608" s="34"/>
-      <c r="B608" s="34"/>
+      <c r="B608" s="24"/>
       <c r="C608" s="24"/>
       <c r="D608" s="24"/>
       <c r="E608" s="24"/>
     </row>
     <row r="609" ht="24" customHeight="1">
       <c r="A609" s="34"/>
-      <c r="B609" s="34"/>
+      <c r="B609" s="24"/>
       <c r="C609" s="24"/>
       <c r="D609" s="24"/>
       <c r="E609" s="24"/>
     </row>
     <row r="610" ht="24" customHeight="1">
       <c r="A610" s="34"/>
-      <c r="B610" s="34"/>
+      <c r="B610" s="24"/>
       <c r="C610" s="24"/>
       <c r="D610" s="24"/>
       <c r="E610" s="24"/>
     </row>
     <row r="611" ht="24" customHeight="1">
       <c r="A611" s="34"/>
-      <c r="B611" s="34"/>
+      <c r="B611" s="24"/>
       <c r="C611" s="24"/>
       <c r="D611" s="24"/>
       <c r="E611" s="24"/>
     </row>
     <row r="612" ht="24" customHeight="1">
       <c r="A612" s="34"/>
-      <c r="B612" s="34"/>
+      <c r="B612" s="24"/>
       <c r="C612" s="24"/>
       <c r="D612" s="24"/>
       <c r="E612" s="24"/>
     </row>
     <row r="613" ht="24" customHeight="1">
       <c r="A613" s="34"/>
-      <c r="B613" s="34"/>
+      <c r="B613" s="24"/>
       <c r="C613" s="24"/>
       <c r="D613" s="24"/>
       <c r="E613" s="24"/>
     </row>
     <row r="614" ht="24" customHeight="1">
       <c r="A614" s="34"/>
-      <c r="B614" s="34"/>
+      <c r="B614" s="24"/>
       <c r="C614" s="24"/>
       <c r="D614" s="24"/>
       <c r="E614" s="24"/>
     </row>
     <row r="615" ht="24" customHeight="1">
       <c r="A615" s="34"/>
-      <c r="B615" s="34"/>
+      <c r="B615" s="24"/>
       <c r="C615" s="24"/>
       <c r="D615" s="24"/>
       <c r="E615" s="24"/>
     </row>
     <row r="616" ht="24" customHeight="1">
       <c r="A616" s="34"/>
-      <c r="B616" s="34"/>
+      <c r="B616" s="24"/>
       <c r="C616" s="24"/>
       <c r="D616" s="24"/>
       <c r="E616" s="24"/>
     </row>
     <row r="617" ht="24" customHeight="1">
       <c r="A617" s="34"/>
-      <c r="B617" s="34"/>
+      <c r="B617" s="24"/>
       <c r="C617" s="24"/>
       <c r="D617" s="24"/>
       <c r="E617" s="24"/>
     </row>
     <row r="618" ht="24" customHeight="1">
       <c r="A618" s="34"/>
-      <c r="B618" s="34"/>
+      <c r="B618" s="24"/>
       <c r="C618" s="24"/>
       <c r="D618" s="24"/>
       <c r="E618" s="24"/>
     </row>
     <row r="619" ht="24" customHeight="1">
       <c r="A619" s="34"/>
-      <c r="B619" s="34"/>
+      <c r="B619" s="24"/>
       <c r="C619" s="24"/>
       <c r="D619" s="24"/>
       <c r="E619" s="24"/>
     </row>
     <row r="620" ht="24" customHeight="1">
       <c r="A620" s="34"/>
-      <c r="B620" s="34"/>
+      <c r="B620" s="24"/>
       <c r="C620" s="24"/>
       <c r="D620" s="24"/>
       <c r="E620" s="24"/>
     </row>
     <row r="621" ht="24" customHeight="1">
       <c r="A621" s="34"/>
-      <c r="B621" s="34"/>
+      <c r="B621" s="24"/>
       <c r="C621" s="24"/>
       <c r="D621" s="24"/>
       <c r="E621" s="24"/>
     </row>
     <row r="622" ht="24" customHeight="1">
       <c r="A622" s="34"/>
-      <c r="B622" s="34"/>
+      <c r="B622" s="24"/>
       <c r="C622" s="24"/>
       <c r="D622" s="24"/>
       <c r="E622" s="24"/>
     </row>
     <row r="623" ht="24" customHeight="1">
       <c r="A623" s="34"/>
-      <c r="B623" s="34"/>
+      <c r="B623" s="24"/>
       <c r="C623" s="24"/>
       <c r="D623" s="24"/>
       <c r="E623" s="24"/>
     </row>
     <row r="624" ht="24" customHeight="1">
       <c r="A624" s="34"/>
-      <c r="B624" s="34"/>
+      <c r="B624" s="24"/>
       <c r="C624" s="24"/>
       <c r="D624" s="24"/>
       <c r="E624" s="24"/>
     </row>
     <row r="625" ht="24" customHeight="1">
       <c r="A625" s="34"/>
-      <c r="B625" s="34"/>
+      <c r="B625" s="24"/>
       <c r="C625" s="24"/>
       <c r="D625" s="24"/>
       <c r="E625" s="24"/>
     </row>
     <row r="626" ht="24" customHeight="1">
       <c r="A626" s="34"/>
-      <c r="B626" s="34"/>
+      <c r="B626" s="24"/>
       <c r="C626" s="24"/>
       <c r="D626" s="24"/>
       <c r="E626" s="24"/>
     </row>
     <row r="627" ht="24" customHeight="1">
       <c r="A627" s="34"/>
-      <c r="B627" s="34"/>
+      <c r="B627" s="24"/>
       <c r="C627" s="24"/>
       <c r="D627" s="24"/>
       <c r="E627" s="24"/>
     </row>
     <row r="628" ht="24" customHeight="1">
       <c r="A628" s="34"/>
-      <c r="B628" s="34"/>
+      <c r="B628" s="24"/>
       <c r="C628" s="24"/>
       <c r="D628" s="24"/>
       <c r="E628" s="24"/>
     </row>
     <row r="629" ht="24" customHeight="1">
       <c r="A629" s="34"/>
-      <c r="B629" s="34"/>
+      <c r="B629" s="24"/>
       <c r="C629" s="24"/>
       <c r="D629" s="24"/>
       <c r="E629" s="24"/>
     </row>
     <row r="630" ht="24" customHeight="1">
       <c r="A630" s="34"/>
-      <c r="B630" s="34"/>
+      <c r="B630" s="24"/>
       <c r="C630" s="24"/>
       <c r="D630" s="24"/>
       <c r="E630" s="24"/>
     </row>
     <row r="631" ht="24" customHeight="1">
       <c r="A631" s="34"/>
-      <c r="B631" s="34"/>
+      <c r="B631" s="24"/>
       <c r="C631" s="24"/>
       <c r="D631" s="24"/>
       <c r="E631" s="24"/>
     </row>
     <row r="632" ht="24" customHeight="1">
       <c r="A632" s="34"/>
-      <c r="B632" s="34"/>
+      <c r="B632" s="24"/>
       <c r="C632" s="24"/>
       <c r="D632" s="24"/>
       <c r="E632" s="24"/>
     </row>
     <row r="633" ht="24" customHeight="1">
       <c r="A633" s="34"/>
-      <c r="B633" s="34"/>
+      <c r="B633" s="24"/>
       <c r="C633" s="24"/>
       <c r="D633" s="24"/>
       <c r="E633" s="24"/>
     </row>
     <row r="634" ht="24" customHeight="1">
       <c r="A634" s="34"/>
-      <c r="B634" s="34"/>
+      <c r="B634" s="24"/>
       <c r="C634" s="24"/>
       <c r="D634" s="24"/>
       <c r="E634" s="24"/>
     </row>
     <row r="635" ht="24" customHeight="1">
       <c r="A635" s="34"/>
-      <c r="B635" s="34"/>
+      <c r="B635" s="24"/>
       <c r="C635" s="24"/>
       <c r="D635" s="24"/>
       <c r="E635" s="24"/>
     </row>
     <row r="636" ht="24" customHeight="1">
       <c r="A636" s="34"/>
-      <c r="B636" s="34"/>
+      <c r="B636" s="24"/>
       <c r="C636" s="24"/>
       <c r="D636" s="24"/>
       <c r="E636" s="24"/>
     </row>
     <row r="637" ht="24" customHeight="1">
       <c r="A637" s="34"/>
-      <c r="B637" s="34"/>
+      <c r="B637" s="24"/>
       <c r="C637" s="24"/>
       <c r="D637" s="24"/>
       <c r="E637" s="24"/>
     </row>
     <row r="638" ht="24" customHeight="1">
       <c r="A638" s="34"/>
-      <c r="B638" s="34"/>
+      <c r="B638" s="24"/>
       <c r="C638" s="24"/>
       <c r="D638" s="24"/>
       <c r="E638" s="24"/>
     </row>
     <row r="639" ht="24" customHeight="1">
       <c r="A639" s="34"/>
-      <c r="B639" s="34"/>
+      <c r="B639" s="24"/>
       <c r="C639" s="24"/>
       <c r="D639" s="24"/>
       <c r="E639" s="24"/>
     </row>
     <row r="640" ht="24" customHeight="1">
       <c r="A640" s="34"/>
-      <c r="B640" s="34"/>
+      <c r="B640" s="24"/>
       <c r="C640" s="24"/>
       <c r="D640" s="24"/>
       <c r="E640" s="24"/>
     </row>
     <row r="641" ht="24" customHeight="1">
       <c r="A641" s="34"/>
-      <c r="B641" s="34"/>
+      <c r="B641" s="24"/>
       <c r="C641" s="24"/>
       <c r="D641" s="24"/>
       <c r="E641" s="24"/>
     </row>
     <row r="642" ht="24" customHeight="1">
       <c r="A642" s="34"/>
-      <c r="B642" s="34"/>
+      <c r="B642" s="24"/>
       <c r="C642" s="24"/>
       <c r="D642" s="24"/>
       <c r="E642" s="24"/>
     </row>
     <row r="643" ht="24" customHeight="1">
       <c r="A643" s="34"/>
-      <c r="B643" s="34"/>
+      <c r="B643" s="24"/>
       <c r="C643" s="24"/>
       <c r="D643" s="24"/>
       <c r="E643" s="24"/>
     </row>
     <row r="644" ht="24" customHeight="1">
       <c r="A644" s="34"/>
-      <c r="B644" s="34"/>
+      <c r="B644" s="24"/>
       <c r="C644" s="24"/>
       <c r="D644" s="24"/>
       <c r="E644" s="24"/>
     </row>
     <row r="645" ht="24" customHeight="1">
       <c r="A645" s="34"/>
-      <c r="B645" s="34"/>
+      <c r="B645" s="24"/>
       <c r="C645" s="24"/>
       <c r="D645" s="24"/>
       <c r="E645" s="24"/>
     </row>
     <row r="646" ht="24" customHeight="1">
       <c r="A646" s="34"/>
-      <c r="B646" s="34"/>
+      <c r="B646" s="24"/>
       <c r="C646" s="24"/>
       <c r="D646" s="24"/>
       <c r="E646" s="24"/>
     </row>
     <row r="647" ht="24" customHeight="1">
       <c r="A647" s="34"/>
-      <c r="B647" s="34"/>
+      <c r="B647" s="24"/>
       <c r="C647" s="24"/>
       <c r="D647" s="24"/>
       <c r="E647" s="24"/>
     </row>
     <row r="648" ht="24" customHeight="1">
       <c r="A648" s="34"/>
-      <c r="B648" s="34"/>
+      <c r="B648" s="24"/>
       <c r="C648" s="24"/>
       <c r="D648" s="24"/>
       <c r="E648" s="24"/>
     </row>
     <row r="649" ht="24" customHeight="1">
       <c r="A649" s="34"/>
-      <c r="B649" s="34"/>
+      <c r="B649" s="24"/>
       <c r="C649" s="24"/>
       <c r="D649" s="24"/>
       <c r="E649" s="24"/>
     </row>
     <row r="650" ht="24" customHeight="1">
       <c r="A650" s="34"/>
-      <c r="B650" s="34"/>
+      <c r="B650" s="24"/>
       <c r="C650" s="24"/>
       <c r="D650" s="24"/>
       <c r="E650" s="24"/>
     </row>
     <row r="651" ht="24" customHeight="1">
       <c r="A651" s="34"/>
-      <c r="B651" s="34"/>
+      <c r="B651" s="24"/>
       <c r="C651" s="24"/>
       <c r="D651" s="24"/>
       <c r="E651" s="24"/>
     </row>
     <row r="652" ht="24" customHeight="1">
       <c r="A652" s="34"/>
-      <c r="B652" s="34"/>
+      <c r="B652" s="24"/>
       <c r="C652" s="24"/>
       <c r="D652" s="24"/>
       <c r="E652" s="24"/>
     </row>
     <row r="653" ht="24" customHeight="1">
       <c r="A653" s="34"/>
-      <c r="B653" s="34"/>
+      <c r="B653" s="24"/>
       <c r="C653" s="24"/>
       <c r="D653" s="24"/>
       <c r="E653" s="24"/>
     </row>
     <row r="654" ht="24" customHeight="1">
       <c r="A654" s="34"/>
-      <c r="B654" s="34"/>
+      <c r="B654" s="24"/>
       <c r="C654" s="24"/>
       <c r="D654" s="24"/>
       <c r="E654" s="24"/>
     </row>
     <row r="655" ht="24" customHeight="1">
       <c r="A655" s="34"/>
-      <c r="B655" s="34"/>
+      <c r="B655" s="24"/>
       <c r="C655" s="24"/>
       <c r="D655" s="24"/>
       <c r="E655" s="24"/>
     </row>
     <row r="656" ht="24" customHeight="1">
       <c r="A656" s="34"/>
-      <c r="B656" s="34"/>
+      <c r="B656" s="24"/>
       <c r="C656" s="24"/>
       <c r="D656" s="24"/>
       <c r="E656" s="24"/>
     </row>
     <row r="657" ht="24" customHeight="1">
       <c r="A657" s="34"/>
-      <c r="B657" s="34"/>
+      <c r="B657" s="24"/>
       <c r="C657" s="24"/>
       <c r="D657" s="24"/>
       <c r="E657" s="24"/>
     </row>
     <row r="658" ht="24" customHeight="1">
       <c r="A658" s="34"/>
-      <c r="B658" s="34"/>
+      <c r="B658" s="24"/>
       <c r="C658" s="24"/>
       <c r="D658" s="24"/>
       <c r="E658" s="24"/>
     </row>
     <row r="659" ht="24" customHeight="1">
       <c r="A659" s="34"/>
-      <c r="B659" s="34"/>
+      <c r="B659" s="24"/>
       <c r="C659" s="24"/>
       <c r="D659" s="24"/>
       <c r="E659" s="24"/>
     </row>
     <row r="660" ht="24" customHeight="1">
       <c r="A660" s="34"/>
-      <c r="B660" s="34"/>
+      <c r="B660" s="24"/>
       <c r="C660" s="24"/>
       <c r="D660" s="24"/>
       <c r="E660" s="24"/>
     </row>
     <row r="661" ht="24" customHeight="1">
       <c r="A661" s="34"/>
-      <c r="B661" s="34"/>
+      <c r="B661" s="24"/>
       <c r="C661" s="24"/>
       <c r="D661" s="24"/>
       <c r="E661" s="24"/>
     </row>
     <row r="662" ht="24" customHeight="1">
       <c r="A662" s="34"/>
-      <c r="B662" s="34"/>
+      <c r="B662" s="24"/>
       <c r="C662" s="24"/>
       <c r="D662" s="24"/>
       <c r="E662" s="24"/>
     </row>
     <row r="663" ht="24" customHeight="1">
       <c r="A663" s="34"/>
-      <c r="B663" s="34"/>
+      <c r="B663" s="24"/>
       <c r="C663" s="24"/>
       <c r="D663" s="24"/>
       <c r="E663" s="24"/>
     </row>
     <row r="664" ht="24" customHeight="1">
       <c r="A664" s="34"/>
-      <c r="B664" s="34"/>
+      <c r="B664" s="24"/>
       <c r="C664" s="24"/>
       <c r="D664" s="24"/>
       <c r="E664" s="24"/>
     </row>
     <row r="665" ht="24" customHeight="1">
       <c r="A665" s="34"/>
-      <c r="B665" s="34"/>
+      <c r="B665" s="24"/>
       <c r="C665" s="24"/>
       <c r="D665" s="24"/>
       <c r="E665" s="24"/>
     </row>
     <row r="666" ht="24" customHeight="1">
       <c r="A666" s="34"/>
-      <c r="B666" s="34"/>
+      <c r="B666" s="24"/>
       <c r="C666" s="24"/>
       <c r="D666" s="24"/>
       <c r="E666" s="24"/>
     </row>
     <row r="667" ht="24" customHeight="1">
       <c r="A667" s="34"/>
-      <c r="B667" s="34"/>
+      <c r="B667" s="24"/>
       <c r="C667" s="24"/>
       <c r="D667" s="24"/>
       <c r="E667" s="24"/>
     </row>
     <row r="668" ht="24" customHeight="1">
       <c r="A668" s="34"/>
-      <c r="B668" s="34"/>
+      <c r="B668" s="24"/>
       <c r="C668" s="24"/>
       <c r="D668" s="24"/>
       <c r="E668" s="24"/>
     </row>
     <row r="669" ht="24" customHeight="1">
       <c r="A669" s="34"/>
-      <c r="B669" s="34"/>
+      <c r="B669" s="24"/>
       <c r="C669" s="24"/>
       <c r="D669" s="24"/>
       <c r="E669" s="24"/>
     </row>
     <row r="670" ht="24" customHeight="1">
       <c r="A670" s="34"/>
-      <c r="B670" s="34"/>
+      <c r="B670" s="24"/>
       <c r="C670" s="24"/>
       <c r="D670" s="24"/>
       <c r="E670" s="24"/>
     </row>
     <row r="671" ht="24" customHeight="1">
       <c r="A671" s="34"/>
-      <c r="B671" s="34"/>
+      <c r="B671" s="24"/>
       <c r="C671" s="24"/>
       <c r="D671" s="24"/>
       <c r="E671" s="24"/>
     </row>
     <row r="672" ht="24" customHeight="1">
       <c r="A672" s="34"/>
-      <c r="B672" s="34"/>
+      <c r="B672" s="24"/>
       <c r="C672" s="24"/>
       <c r="D672" s="24"/>
       <c r="E672" s="24"/>
     </row>
     <row r="673" ht="24" customHeight="1">
       <c r="A673" s="34"/>
-      <c r="B673" s="34"/>
+      <c r="B673" s="24"/>
       <c r="C673" s="24"/>
       <c r="D673" s="24"/>
       <c r="E673" s="24"/>
     </row>
     <row r="674" ht="24" customHeight="1">
       <c r="A674" s="34"/>
-      <c r="B674" s="34"/>
+      <c r="B674" s="24"/>
       <c r="C674" s="24"/>
       <c r="D674" s="24"/>
       <c r="E674" s="24"/>
     </row>
     <row r="675" ht="24" customHeight="1">
       <c r="A675" s="34"/>
-      <c r="B675" s="34"/>
+      <c r="B675" s="24"/>
       <c r="C675" s="24"/>
       <c r="D675" s="24"/>
       <c r="E675" s="24"/>
     </row>
     <row r="676" ht="24" customHeight="1">
       <c r="A676" s="34"/>
-      <c r="B676" s="34"/>
+      <c r="B676" s="24"/>
       <c r="C676" s="24"/>
       <c r="D676" s="24"/>
       <c r="E676" s="24"/>
     </row>
     <row r="677" ht="24" customHeight="1">
       <c r="A677" s="34"/>
-      <c r="B677" s="34"/>
+      <c r="B677" s="24"/>
       <c r="C677" s="24"/>
       <c r="D677" s="24"/>
       <c r="E677" s="24"/>
     </row>
     <row r="678" ht="24" customHeight="1">
       <c r="A678" s="34"/>
-      <c r="B678" s="34"/>
+      <c r="B678" s="24"/>
       <c r="C678" s="24"/>
       <c r="D678" s="24"/>
       <c r="E678" s="24"/>
     </row>
     <row r="679" ht="24" customHeight="1">
       <c r="A679" s="34"/>
-      <c r="B679" s="34"/>
+      <c r="B679" s="24"/>
       <c r="C679" s="24"/>
       <c r="D679" s="24"/>
       <c r="E679" s="24"/>
     </row>
     <row r="680" ht="24" customHeight="1">
       <c r="A680" s="34"/>
-      <c r="B680" s="34"/>
+      <c r="B680" s="24"/>
       <c r="C680" s="24"/>
       <c r="D680" s="24"/>
       <c r="E680" s="24"/>
     </row>
     <row r="681" ht="24" customHeight="1">
       <c r="A681" s="34"/>
-      <c r="B681" s="34"/>
+      <c r="B681" s="24"/>
       <c r="C681" s="24"/>
       <c r="D681" s="24"/>
       <c r="E681" s="24"/>
     </row>
     <row r="682" ht="24" customHeight="1">
       <c r="A682" s="34"/>
-      <c r="B682" s="34"/>
+      <c r="B682" s="24"/>
       <c r="C682" s="24"/>
       <c r="D682" s="24"/>
       <c r="E682" s="24"/>
     </row>
     <row r="683" ht="24" customHeight="1">
       <c r="A683" s="34"/>
-      <c r="B683" s="34"/>
+      <c r="B683" s="24"/>
       <c r="C683" s="24"/>
       <c r="D683" s="24"/>
       <c r="E683" s="24"/>
     </row>
     <row r="684" ht="24" customHeight="1">
       <c r="A684" s="34"/>
-      <c r="B684" s="34"/>
+      <c r="B684" s="24"/>
       <c r="C684" s="24"/>
       <c r="D684" s="24"/>
       <c r="E684" s="24"/>
     </row>
     <row r="685" ht="24" customHeight="1">
       <c r="A685" s="34"/>
-      <c r="B685" s="34"/>
+      <c r="B685" s="24"/>
       <c r="C685" s="24"/>
       <c r="D685" s="24"/>
       <c r="E685" s="24"/>
     </row>
     <row r="686" ht="24" customHeight="1">
       <c r="A686" s="34"/>
-      <c r="B686" s="34"/>
+      <c r="B686" s="24"/>
       <c r="C686" s="24"/>
       <c r="D686" s="24"/>
       <c r="E686" s="24"/>
     </row>
     <row r="687" ht="24" customHeight="1">
       <c r="A687" s="34"/>
-      <c r="B687" s="34"/>
+      <c r="B687" s="24"/>
       <c r="C687" s="24"/>
       <c r="D687" s="24"/>
       <c r="E687" s="24"/>
     </row>
     <row r="688" ht="24" customHeight="1">
       <c r="A688" s="34"/>
-      <c r="B688" s="34"/>
+      <c r="B688" s="24"/>
       <c r="C688" s="24"/>
       <c r="D688" s="24"/>
       <c r="E688" s="24"/>
     </row>
     <row r="689" ht="24" customHeight="1">
       <c r="A689" s="34"/>
-      <c r="B689" s="34"/>
+      <c r="B689" s="24"/>
       <c r="C689" s="24"/>
       <c r="D689" s="24"/>
       <c r="E689" s="24"/>
     </row>
     <row r="690" ht="24" customHeight="1">
       <c r="A690" s="34"/>
-      <c r="B690" s="34"/>
+      <c r="B690" s="24"/>
       <c r="C690" s="24"/>
       <c r="D690" s="24"/>
       <c r="E690" s="24"/>
     </row>
     <row r="691" ht="24" customHeight="1">
       <c r="A691" s="34"/>
-      <c r="B691" s="34"/>
+      <c r="B691" s="24"/>
       <c r="C691" s="24"/>
       <c r="D691" s="24"/>
       <c r="E691" s="24"/>
     </row>
     <row r="692" ht="24" customHeight="1">
       <c r="A692" s="34"/>
-      <c r="B692" s="34"/>
+      <c r="B692" s="24"/>
       <c r="C692" s="24"/>
       <c r="D692" s="24"/>
       <c r="E692" s="24"/>
     </row>
     <row r="693" ht="24" customHeight="1">
       <c r="A693" s="34"/>
-      <c r="B693" s="34"/>
+      <c r="B693" s="24"/>
       <c r="C693" s="24"/>
       <c r="D693" s="24"/>
       <c r="E693" s="24"/>
     </row>
     <row r="694" ht="24" customHeight="1">
       <c r="A694" s="34"/>
-      <c r="B694" s="34"/>
+      <c r="B694" s="24"/>
       <c r="C694" s="24"/>
       <c r="D694" s="24"/>
       <c r="E694" s="24"/>
     </row>
     <row r="695" ht="24" customHeight="1">
       <c r="A695" s="34"/>
-      <c r="B695" s="34"/>
+      <c r="B695" s="24"/>
       <c r="C695" s="24"/>
       <c r="D695" s="24"/>
       <c r="E695" s="24"/>
     </row>
     <row r="696" ht="24" customHeight="1">
       <c r="A696" s="34"/>
-      <c r="B696" s="34"/>
+      <c r="B696" s="24"/>
       <c r="C696" s="24"/>
       <c r="D696" s="24"/>
       <c r="E696" s="24"/>
     </row>
     <row r="697" ht="24" customHeight="1">
       <c r="A697" s="34"/>
-      <c r="B697" s="34"/>
+      <c r="B697" s="24"/>
       <c r="C697" s="24"/>
       <c r="D697" s="24"/>
       <c r="E697" s="24"/>
     </row>
     <row r="698" ht="24" customHeight="1">
       <c r="A698" s="34"/>
-      <c r="B698" s="34"/>
+      <c r="B698" s="24"/>
       <c r="C698" s="24"/>
       <c r="D698" s="24"/>
       <c r="E698" s="24"/>
     </row>
     <row r="699" ht="24" customHeight="1">
       <c r="A699" s="34"/>
-      <c r="B699" s="34"/>
+      <c r="B699" s="24"/>
       <c r="C699" s="24"/>
       <c r="D699" s="24"/>
       <c r="E699" s="24"/>
     </row>
     <row r="700" ht="24" customHeight="1">
       <c r="A700" s="34"/>
-      <c r="B700" s="34"/>
+      <c r="B700" s="24"/>
       <c r="C700" s="24"/>
       <c r="D700" s="24"/>
       <c r="E700" s="24"/>
     </row>
     <row r="701" ht="24" customHeight="1">
       <c r="A701" s="34"/>
-      <c r="B701" s="34"/>
+      <c r="B701" s="24"/>
       <c r="C701" s="24"/>
       <c r="D701" s="24"/>
       <c r="E701" s="24"/>
     </row>
     <row r="702" ht="24" customHeight="1">
       <c r="A702" s="34"/>
-      <c r="B702" s="34"/>
+      <c r="B702" s="24"/>
       <c r="C702" s="24"/>
       <c r="D702" s="24"/>
       <c r="E702" s="24"/>
     </row>
     <row r="703" ht="24" customHeight="1">
       <c r="A703" s="34"/>
-      <c r="B703" s="34"/>
+      <c r="B703" s="24"/>
       <c r="C703" s="24"/>
       <c r="D703" s="24"/>
       <c r="E703" s="24"/>
     </row>
     <row r="704" ht="24" customHeight="1">
       <c r="A704" s="34"/>
-      <c r="B704" s="34"/>
+      <c r="B704" s="24"/>
       <c r="C704" s="24"/>
       <c r="D704" s="24"/>
       <c r="E704" s="24"/>
     </row>
     <row r="705" ht="24" customHeight="1">
       <c r="A705" s="34"/>
-      <c r="B705" s="34"/>
+      <c r="B705" s="24"/>
       <c r="C705" s="24"/>
       <c r="D705" s="24"/>
       <c r="E705" s="24"/>
     </row>
     <row r="706" ht="24" customHeight="1">
       <c r="A706" s="34"/>
-      <c r="B706" s="34"/>
+      <c r="B706" s="24"/>
       <c r="C706" s="24"/>
       <c r="D706" s="24"/>
       <c r="E706" s="24"/>
     </row>
     <row r="707" ht="24" customHeight="1">
       <c r="A707" s="34"/>
-      <c r="B707" s="34"/>
+      <c r="B707" s="24"/>
       <c r="C707" s="24"/>
       <c r="D707" s="24"/>
       <c r="E707" s="24"/>
     </row>
     <row r="708" ht="24" customHeight="1">
       <c r="A708" s="34"/>
-      <c r="B708" s="34"/>
+      <c r="B708" s="24"/>
       <c r="C708" s="24"/>
       <c r="D708" s="24"/>
       <c r="E708" s="24"/>
     </row>
     <row r="709" ht="24" customHeight="1">
       <c r="A709" s="34"/>
-      <c r="B709" s="34"/>
+      <c r="B709" s="24"/>
       <c r="C709" s="24"/>
       <c r="D709" s="24"/>
       <c r="E709" s="24"/>
     </row>
     <row r="710" ht="24" customHeight="1">
       <c r="A710" s="34"/>
-      <c r="B710" s="34"/>
+      <c r="B710" s="24"/>
       <c r="C710" s="24"/>
       <c r="D710" s="24"/>
       <c r="E710" s="24"/>
     </row>
     <row r="711" ht="24" customHeight="1">
       <c r="A711" s="34"/>
-      <c r="B711" s="34"/>
+      <c r="B711" s="24"/>
       <c r="C711" s="24"/>
       <c r="D711" s="24"/>
       <c r="E711" s="24"/>
     </row>
     <row r="712" ht="24" customHeight="1">
       <c r="A712" s="34"/>
-      <c r="B712" s="34"/>
+      <c r="B712" s="24"/>
       <c r="C712" s="24"/>
       <c r="D712" s="24"/>
       <c r="E712" s="24"/>
     </row>
     <row r="713" ht="24" customHeight="1">
       <c r="A713" s="34"/>
-      <c r="B713" s="34"/>
+      <c r="B713" s="24"/>
       <c r="C713" s="24"/>
       <c r="D713" s="24"/>
       <c r="E713" s="24"/>
     </row>
     <row r="714" ht="24" customHeight="1">
       <c r="A714" s="34"/>
-      <c r="B714" s="34"/>
+      <c r="B714" s="24"/>
       <c r="C714" s="24"/>
       <c r="D714" s="24"/>
       <c r="E714" s="24"/>
     </row>
     <row r="715" ht="24" customHeight="1">
       <c r="A715" s="34"/>
-      <c r="B715" s="34"/>
+      <c r="B715" s="24"/>
       <c r="C715" s="24"/>
       <c r="D715" s="24"/>
       <c r="E715" s="24"/>
     </row>
     <row r="716" ht="24" customHeight="1">
       <c r="A716" s="34"/>
-      <c r="B716" s="34"/>
+      <c r="B716" s="24"/>
       <c r="C716" s="24"/>
       <c r="D716" s="24"/>
       <c r="E716" s="24"/>
     </row>
     <row r="717" ht="24" customHeight="1">
       <c r="A717" s="34"/>
-      <c r="B717" s="34"/>
+      <c r="B717" s="24"/>
       <c r="C717" s="24"/>
       <c r="D717" s="24"/>
       <c r="E717" s="24"/>
     </row>
     <row r="718" ht="24" customHeight="1">
       <c r="A718" s="34"/>
-      <c r="B718" s="34"/>
+      <c r="B718" s="24"/>
       <c r="C718" s="24"/>
       <c r="D718" s="24"/>
       <c r="E718" s="24"/>
     </row>
     <row r="719" ht="24" customHeight="1">
       <c r="A719" s="34"/>
-      <c r="B719" s="34"/>
+      <c r="B719" s="24"/>
       <c r="C719" s="24"/>
       <c r="D719" s="24"/>
       <c r="E719" s="24"/>
     </row>
     <row r="720" ht="24" customHeight="1">
       <c r="A720" s="34"/>
-      <c r="B720" s="34"/>
+      <c r="B720" s="24"/>
       <c r="C720" s="24"/>
       <c r="D720" s="24"/>
       <c r="E720" s="24"/>
     </row>
     <row r="721" ht="24" customHeight="1">
       <c r="A721" s="34"/>
-      <c r="B721" s="34"/>
+      <c r="B721" s="24"/>
       <c r="C721" s="24"/>
       <c r="D721" s="24"/>
       <c r="E721" s="24"/>
     </row>
     <row r="722" ht="24" customHeight="1">
       <c r="A722" s="34"/>
-      <c r="B722" s="34"/>
+      <c r="B722" s="24"/>
       <c r="C722" s="24"/>
       <c r="D722" s="24"/>
       <c r="E722" s="24"/>
     </row>
     <row r="723" ht="24" customHeight="1">
       <c r="A723" s="34"/>
-      <c r="B723" s="34"/>
+      <c r="B723" s="24"/>
       <c r="C723" s="24"/>
       <c r="D723" s="24"/>
       <c r="E723" s="24"/>
     </row>
     <row r="724" ht="24" customHeight="1">
       <c r="A724" s="34"/>
-      <c r="B724" s="34"/>
+      <c r="B724" s="24"/>
       <c r="C724" s="24"/>
       <c r="D724" s="24"/>
       <c r="E724" s="24"/>
     </row>
     <row r="725" ht="24" customHeight="1">
       <c r="A725" s="34"/>
-      <c r="B725" s="34"/>
+      <c r="B725" s="24"/>
       <c r="C725" s="24"/>
       <c r="D725" s="24"/>
       <c r="E725" s="24"/>
     </row>
     <row r="726" ht="24" customHeight="1">
       <c r="A726" s="34"/>
-      <c r="B726" s="34"/>
+      <c r="B726" s="24"/>
       <c r="C726" s="24"/>
       <c r="D726" s="24"/>
       <c r="E726" s="24"/>
     </row>
     <row r="727" ht="24" customHeight="1">
       <c r="A727" s="34"/>
-      <c r="B727" s="34"/>
+      <c r="B727" s="24"/>
       <c r="C727" s="24"/>
       <c r="D727" s="24"/>
       <c r="E727" s="24"/>
     </row>
     <row r="728" ht="24" customHeight="1">
       <c r="A728" s="34"/>
-      <c r="B728" s="34"/>
+      <c r="B728" s="24"/>
       <c r="C728" s="24"/>
       <c r="D728" s="24"/>
       <c r="E728" s="24"/>
     </row>
     <row r="729" ht="24" customHeight="1">
       <c r="A729" s="34"/>
-      <c r="B729" s="34"/>
+      <c r="B729" s="24"/>
       <c r="C729" s="24"/>
       <c r="D729" s="24"/>
       <c r="E729" s="24"/>
     </row>
     <row r="730" ht="24" customHeight="1">
       <c r="A730" s="34"/>
-      <c r="B730" s="34"/>
+      <c r="B730" s="24"/>
       <c r="C730" s="24"/>
       <c r="D730" s="24"/>
       <c r="E730" s="24"/>
     </row>
     <row r="731" ht="24" customHeight="1">
       <c r="A731" s="34"/>
-      <c r="B731" s="34"/>
+      <c r="B731" s="24"/>
       <c r="C731" s="24"/>
       <c r="D731" s="24"/>
       <c r="E731" s="24"/>
     </row>
     <row r="732" ht="24" customHeight="1">
       <c r="A732" s="34"/>
-      <c r="B732" s="34"/>
+      <c r="B732" s="24"/>
       <c r="C732" s="24"/>
       <c r="D732" s="24"/>
       <c r="E732" s="24"/>
     </row>
     <row r="733" ht="24" customHeight="1">
       <c r="A733" s="34"/>
-      <c r="B733" s="34"/>
+      <c r="B733" s="24"/>
       <c r="C733" s="24"/>
       <c r="D733" s="24"/>
       <c r="E733" s="24"/>
     </row>
     <row r="734" ht="24" customHeight="1">
       <c r="A734" s="34"/>
-      <c r="B734" s="34"/>
+      <c r="B734" s="24"/>
       <c r="C734" s="24"/>
       <c r="D734" s="24"/>
       <c r="E734" s="24"/>
     </row>
     <row r="735" ht="24" customHeight="1">
       <c r="A735" s="34"/>
-      <c r="B735" s="34"/>
+      <c r="B735" s="24"/>
       <c r="C735" s="24"/>
       <c r="D735" s="24"/>
       <c r="E735" s="24"/>
     </row>
     <row r="736" ht="24" customHeight="1">
       <c r="A736" s="34"/>
-      <c r="B736" s="34"/>
+      <c r="B736" s="24"/>
       <c r="C736" s="24"/>
       <c r="D736" s="24"/>
       <c r="E736" s="24"/>
     </row>
     <row r="737" ht="24" customHeight="1">
       <c r="A737" s="34"/>
-      <c r="B737" s="34"/>
+      <c r="B737" s="24"/>
       <c r="C737" s="24"/>
       <c r="D737" s="24"/>
       <c r="E737" s="24"/>
     </row>
     <row r="738" ht="24" customHeight="1">
       <c r="A738" s="34"/>
-      <c r="B738" s="34"/>
+      <c r="B738" s="24"/>
       <c r="C738" s="24"/>
       <c r="D738" s="24"/>
       <c r="E738" s="24"/>
     </row>
     <row r="739" ht="24" customHeight="1">
       <c r="A739" s="34"/>
-      <c r="B739" s="34"/>
+      <c r="B739" s="24"/>
       <c r="C739" s="24"/>
       <c r="D739" s="24"/>
       <c r="E739" s="24"/>
     </row>
     <row r="740" ht="24" customHeight="1">
       <c r="A740" s="34"/>
-      <c r="B740" s="34"/>
+      <c r="B740" s="24"/>
       <c r="C740" s="24"/>
       <c r="D740" s="24"/>
       <c r="E740" s="24"/>
     </row>
     <row r="741" ht="24" customHeight="1">
       <c r="A741" s="34"/>
-      <c r="B741" s="34"/>
+      <c r="B741" s="24"/>
       <c r="C741" s="24"/>
       <c r="D741" s="24"/>
       <c r="E741" s="24"/>
     </row>
     <row r="742" ht="24" customHeight="1">
       <c r="A742" s="34"/>
-      <c r="B742" s="34"/>
+      <c r="B742" s="24"/>
       <c r="C742" s="24"/>
       <c r="D742" s="24"/>
       <c r="E742" s="24"/>
     </row>
     <row r="743" ht="24" customHeight="1">
       <c r="A743" s="34"/>
-      <c r="B743" s="34"/>
+      <c r="B743" s="24"/>
       <c r="C743" s="24"/>
       <c r="D743" s="24"/>
       <c r="E743" s="24"/>
     </row>
     <row r="744" ht="24" customHeight="1">
       <c r="A744" s="34"/>
-      <c r="B744" s="34"/>
+      <c r="B744" s="24"/>
       <c r="C744" s="24"/>
       <c r="D744" s="24"/>
       <c r="E744" s="24"/>
     </row>
     <row r="745" ht="24" customHeight="1">
       <c r="A745" s="34"/>
-      <c r="B745" s="34"/>
+      <c r="B745" s="24"/>
       <c r="C745" s="24"/>
       <c r="D745" s="24"/>
       <c r="E745" s="24"/>
     </row>
     <row r="746" ht="24" customHeight="1">
       <c r="A746" s="34"/>
-      <c r="B746" s="34"/>
+      <c r="B746" s="24"/>
       <c r="C746" s="24"/>
       <c r="D746" s="24"/>
       <c r="E746" s="24"/>
     </row>
     <row r="747" ht="24" customHeight="1">
       <c r="A747" s="34"/>
-      <c r="B747" s="34"/>
+      <c r="B747" s="24"/>
       <c r="C747" s="24"/>
       <c r="D747" s="24"/>
       <c r="E747" s="24"/>
     </row>
     <row r="748" ht="24" customHeight="1">
       <c r="A748" s="34"/>
-      <c r="B748" s="34"/>
+      <c r="B748" s="24"/>
       <c r="C748" s="24"/>
       <c r="D748" s="24"/>
       <c r="E748" s="24"/>
     </row>
     <row r="749" ht="24" customHeight="1">
       <c r="A749" s="34"/>
-      <c r="B749" s="34"/>
+      <c r="B749" s="24"/>
       <c r="C749" s="24"/>
       <c r="D749" s="24"/>
       <c r="E749" s="24"/>
     </row>
     <row r="750" ht="24" customHeight="1">
       <c r="A750" s="34"/>
-      <c r="B750" s="34"/>
+      <c r="B750" s="24"/>
       <c r="C750" s="24"/>
       <c r="D750" s="24"/>
       <c r="E750" s="24"/>
     </row>
     <row r="751" ht="24" customHeight="1">
       <c r="A751" s="34"/>
-      <c r="B751" s="34"/>
+      <c r="B751" s="24"/>
       <c r="C751" s="24"/>
       <c r="D751" s="24"/>
       <c r="E751" s="24"/>
     </row>
     <row r="752" ht="24" customHeight="1">
       <c r="A752" s="34"/>
-      <c r="B752" s="34"/>
+      <c r="B752" s="24"/>
       <c r="C752" s="24"/>
       <c r="D752" s="24"/>
       <c r="E752" s="24"/>
     </row>
     <row r="753" ht="24" customHeight="1">
       <c r="A753" s="34"/>
-      <c r="B753" s="34"/>
+      <c r="B753" s="24"/>
       <c r="C753" s="24"/>
       <c r="D753" s="24"/>
       <c r="E753" s="24"/>
     </row>
     <row r="754" ht="24" customHeight="1">
       <c r="A754" s="34"/>
-      <c r="B754" s="34"/>
+      <c r="B754" s="24"/>
       <c r="C754" s="24"/>
       <c r="D754" s="24"/>
       <c r="E754" s="24"/>
     </row>
     <row r="755" ht="24" customHeight="1">
       <c r="A755" s="34"/>
-      <c r="B755" s="34"/>
+      <c r="B755" s="24"/>
       <c r="C755" s="24"/>
       <c r="D755" s="24"/>
       <c r="E755" s="24"/>
     </row>
     <row r="756" ht="24" customHeight="1">
       <c r="A756" s="34"/>
-      <c r="B756" s="34"/>
+      <c r="B756" s="24"/>
       <c r="C756" s="24"/>
       <c r="D756" s="24"/>
       <c r="E756" s="24"/>
     </row>
     <row r="757" ht="24" customHeight="1">
       <c r="A757" s="34"/>
-      <c r="B757" s="34"/>
+      <c r="B757" s="24"/>
       <c r="C757" s="24"/>
       <c r="D757" s="24"/>
       <c r="E757" s="24"/>
     </row>
     <row r="758" ht="24" customHeight="1">
       <c r="A758" s="34"/>
-      <c r="B758" s="34"/>
+      <c r="B758" s="24"/>
       <c r="C758" s="24"/>
       <c r="D758" s="24"/>
       <c r="E758" s="24"/>
     </row>
     <row r="759" ht="24" customHeight="1">
       <c r="A759" s="34"/>
-      <c r="B759" s="34"/>
+      <c r="B759" s="24"/>
       <c r="C759" s="24"/>
       <c r="D759" s="24"/>
       <c r="E759" s="24"/>
     </row>
     <row r="760" ht="24" customHeight="1">
       <c r="A760" s="34"/>
-      <c r="B760" s="34"/>
+      <c r="B760" s="24"/>
       <c r="C760" s="24"/>
       <c r="D760" s="24"/>
       <c r="E760" s="24"/>
     </row>
     <row r="761" ht="24" customHeight="1">
       <c r="A761" s="34"/>
-      <c r="B761" s="34"/>
+      <c r="B761" s="24"/>
       <c r="C761" s="24"/>
       <c r="D761" s="24"/>
       <c r="E761" s="24"/>
     </row>
     <row r="762" ht="24" customHeight="1">
       <c r="A762" s="34"/>
-      <c r="B762" s="34"/>
+      <c r="B762" s="24"/>
       <c r="C762" s="24"/>
       <c r="D762" s="24"/>
       <c r="E762" s="24"/>
     </row>
     <row r="763" ht="24" customHeight="1">
       <c r="A763" s="34"/>
-      <c r="B763" s="34"/>
+      <c r="B763" s="24"/>
       <c r="C763" s="24"/>
       <c r="D763" s="24"/>
       <c r="E763" s="24"/>
     </row>
     <row r="764" ht="24" customHeight="1">
       <c r="A764" s="34"/>
-      <c r="B764" s="34"/>
+      <c r="B764" s="24"/>
       <c r="C764" s="24"/>
       <c r="D764" s="24"/>
       <c r="E764" s="24"/>
     </row>
     <row r="765" ht="24" customHeight="1">
       <c r="A765" s="34"/>
-      <c r="B765" s="34"/>
+      <c r="B765" s="24"/>
       <c r="C765" s="24"/>
       <c r="D765" s="24"/>
       <c r="E765" s="24"/>
     </row>
     <row r="766" ht="24" customHeight="1">
       <c r="A766" s="34"/>
-      <c r="B766" s="34"/>
+      <c r="B766" s="24"/>
       <c r="C766" s="24"/>
       <c r="D766" s="24"/>
       <c r="E766" s="24"/>
     </row>
     <row r="767" ht="24" customHeight="1">
       <c r="A767" s="34"/>
-      <c r="B767" s="34"/>
+      <c r="B767" s="24"/>
       <c r="C767" s="24"/>
       <c r="D767" s="24"/>
       <c r="E767" s="24"/>
     </row>
     <row r="768" ht="24" customHeight="1">
       <c r="A768" s="34"/>
-      <c r="B768" s="34"/>
+      <c r="B768" s="24"/>
       <c r="C768" s="24"/>
       <c r="D768" s="24"/>
       <c r="E768" s="24"/>
     </row>
     <row r="769" ht="24" customHeight="1">
       <c r="A769" s="34"/>
-      <c r="B769" s="34"/>
+      <c r="B769" s="24"/>
       <c r="C769" s="24"/>
       <c r="D769" s="24"/>
       <c r="E769" s="24"/>
     </row>
     <row r="770" ht="24" customHeight="1">
       <c r="A770" s="34"/>
-      <c r="B770" s="34"/>
+      <c r="B770" s="24"/>
       <c r="C770" s="24"/>
       <c r="D770" s="24"/>
       <c r="E770" s="24"/>
     </row>
     <row r="771" ht="24" customHeight="1">
       <c r="A771" s="34"/>
-      <c r="B771" s="34"/>
+      <c r="B771" s="24"/>
       <c r="C771" s="24"/>
       <c r="D771" s="24"/>
       <c r="E771" s="24"/>
     </row>
     <row r="772" ht="24" customHeight="1">
       <c r="A772" s="34"/>
-      <c r="B772" s="34"/>
+      <c r="B772" s="24"/>
       <c r="C772" s="24"/>
       <c r="D772" s="24"/>
       <c r="E772" s="24"/>
     </row>
     <row r="773" ht="24" customHeight="1">
       <c r="A773" s="34"/>
-      <c r="B773" s="34"/>
+      <c r="B773" s="24"/>
       <c r="C773" s="24"/>
       <c r="D773" s="24"/>
       <c r="E773" s="24"/>
     </row>
     <row r="774" ht="24" customHeight="1">
       <c r="A774" s="34"/>
-      <c r="B774" s="34"/>
+      <c r="B774" s="24"/>
       <c r="C774" s="24"/>
       <c r="D774" s="24"/>
       <c r="E774" s="24"/>
     </row>
     <row r="775" ht="24" customHeight="1">
       <c r="A775" s="34"/>
-      <c r="B775" s="34"/>
+      <c r="B775" s="24"/>
       <c r="C775" s="24"/>
       <c r="D775" s="24"/>
       <c r="E775" s="24"/>
     </row>
     <row r="776" ht="24" customHeight="1">
       <c r="A776" s="34"/>
-      <c r="B776" s="34"/>
+      <c r="B776" s="24"/>
       <c r="C776" s="24"/>
       <c r="D776" s="24"/>
       <c r="E776" s="24"/>
     </row>
     <row r="777" ht="24" customHeight="1">
       <c r="A777" s="34"/>
-      <c r="B777" s="34"/>
+      <c r="B777" s="24"/>
       <c r="C777" s="24"/>
       <c r="D777" s="24"/>
       <c r="E777" s="24"/>
     </row>
     <row r="778" ht="24" customHeight="1">
       <c r="A778" s="34"/>
-      <c r="B778" s="34"/>
+      <c r="B778" s="24"/>
       <c r="C778" s="24"/>
       <c r="D778" s="24"/>
       <c r="E778" s="24"/>
     </row>
     <row r="779" ht="24" customHeight="1">
       <c r="A779" s="34"/>
-      <c r="B779" s="34"/>
+      <c r="B779" s="24"/>
       <c r="C779" s="24"/>
       <c r="D779" s="24"/>
       <c r="E779" s="24"/>
     </row>
     <row r="780" ht="24" customHeight="1">
       <c r="A780" s="34"/>
-      <c r="B780" s="34"/>
+      <c r="B780" s="24"/>
       <c r="C780" s="24"/>
       <c r="D780" s="24"/>
       <c r="E780" s="24"/>
     </row>
     <row r="781" ht="24" customHeight="1">
       <c r="A781" s="34"/>
-      <c r="B781" s="34"/>
+      <c r="B781" s="24"/>
       <c r="C781" s="24"/>
       <c r="D781" s="24"/>
       <c r="E781" s="24"/>
     </row>
     <row r="782" ht="24" customHeight="1">
       <c r="A782" s="34"/>
-      <c r="B782" s="34"/>
+      <c r="B782" s="24"/>
       <c r="C782" s="24"/>
       <c r="D782" s="24"/>
       <c r="E782" s="24"/>
     </row>
     <row r="783" ht="24" customHeight="1">
       <c r="A783" s="34"/>
-      <c r="B783" s="34"/>
+      <c r="B783" s="24"/>
       <c r="C783" s="24"/>
       <c r="D783" s="24"/>
       <c r="E783" s="24"/>
     </row>
     <row r="784" ht="24" customHeight="1">
       <c r="A784" s="34"/>
-      <c r="B784" s="34"/>
+      <c r="B784" s="24"/>
       <c r="C784" s="24"/>
       <c r="D784" s="24"/>
       <c r="E784" s="24"/>
     </row>
     <row r="785" ht="24" customHeight="1">
       <c r="A785" s="34"/>
-      <c r="B785" s="34"/>
+      <c r="B785" s="24"/>
       <c r="C785" s="24"/>
       <c r="D785" s="24"/>
       <c r="E785" s="24"/>
     </row>
     <row r="786" ht="24" customHeight="1">
       <c r="A786" s="34"/>
-      <c r="B786" s="34"/>
+      <c r="B786" s="24"/>
       <c r="C786" s="24"/>
       <c r="D786" s="24"/>
       <c r="E786" s="24"/>
     </row>
     <row r="787" ht="24" customHeight="1">
       <c r="A787" s="34"/>
-      <c r="B787" s="34"/>
+      <c r="B787" s="24"/>
       <c r="C787" s="24"/>
       <c r="D787" s="24"/>
       <c r="E787" s="24"/>
     </row>
     <row r="788" ht="24" customHeight="1">
       <c r="A788" s="34"/>
-      <c r="B788" s="34"/>
+      <c r="B788" s="24"/>
       <c r="C788" s="24"/>
       <c r="D788" s="24"/>
       <c r="E788" s="24"/>
     </row>
     <row r="789" ht="24" customHeight="1">
       <c r="A789" s="34"/>
-      <c r="B789" s="34"/>
+      <c r="B789" s="24"/>
       <c r="C789" s="24"/>
       <c r="D789" s="24"/>
       <c r="E789" s="24"/>
     </row>
     <row r="790" ht="24" customHeight="1">
       <c r="A790" s="34"/>
-      <c r="B790" s="34"/>
+      <c r="B790" s="24"/>
       <c r="C790" s="24"/>
       <c r="D790" s="24"/>
       <c r="E790" s="24"/>
     </row>
     <row r="791" ht="24" customHeight="1">
       <c r="A791" s="34"/>
-      <c r="B791" s="34"/>
+      <c r="B791" s="24"/>
       <c r="C791" s="24"/>
       <c r="D791" s="24"/>
       <c r="E791" s="24"/>
     </row>
     <row r="792" ht="24" customHeight="1">
       <c r="A792" s="34"/>
-      <c r="B792" s="34"/>
+      <c r="B792" s="24"/>
       <c r="C792" s="24"/>
       <c r="D792" s="24"/>
       <c r="E792" s="24"/>
     </row>
     <row r="793" ht="24" customHeight="1">
       <c r="A793" s="34"/>
-      <c r="B793" s="34"/>
+      <c r="B793" s="24"/>
       <c r="C793" s="24"/>
       <c r="D793" s="24"/>
       <c r="E793" s="24"/>
     </row>
     <row r="794" ht="24" customHeight="1">
       <c r="A794" s="34"/>
-      <c r="B794" s="34"/>
+      <c r="B794" s="24"/>
       <c r="C794" s="24"/>
       <c r="D794" s="24"/>
       <c r="E794" s="24"/>
     </row>
     <row r="795" ht="24" customHeight="1">
       <c r="A795" s="34"/>
-      <c r="B795" s="34"/>
+      <c r="B795" s="24"/>
       <c r="C795" s="24"/>
       <c r="D795" s="24"/>
       <c r="E795" s="24"/>
     </row>
     <row r="796" ht="24" customHeight="1">
       <c r="A796" s="34"/>
-      <c r="B796" s="34"/>
+      <c r="B796" s="24"/>
       <c r="C796" s="24"/>
       <c r="D796" s="24"/>
       <c r="E796" s="24"/>
     </row>
     <row r="797" ht="24" customHeight="1">
       <c r="A797" s="34"/>
-      <c r="B797" s="34"/>
+      <c r="B797" s="24"/>
       <c r="C797" s="24"/>
       <c r="D797" s="24"/>
       <c r="E797" s="24"/>
     </row>
     <row r="798" ht="24" customHeight="1">
       <c r="A798" s="34"/>
-      <c r="B798" s="34"/>
+      <c r="B798" s="24"/>
       <c r="C798" s="24"/>
       <c r="D798" s="24"/>
       <c r="E798" s="24"/>
     </row>
     <row r="799" ht="24" customHeight="1">
       <c r="A799" s="34"/>
-      <c r="B799" s="34"/>
+      <c r="B799" s="24"/>
       <c r="C799" s="24"/>
       <c r="D799" s="24"/>
       <c r="E799" s="24"/>
     </row>
     <row r="800" ht="24" customHeight="1">
       <c r="A800" s="34"/>
-      <c r="B800" s="34"/>
+      <c r="B800" s="24"/>
       <c r="C800" s="24"/>
       <c r="D800" s="24"/>
       <c r="E800" s="24"/>
     </row>
     <row r="801" ht="24" customHeight="1">
       <c r="A801" s="34"/>
-      <c r="B801" s="34"/>
+      <c r="B801" s="24"/>
       <c r="C801" s="24"/>
       <c r="D801" s="24"/>
       <c r="E801" s="24"/>
     </row>
     <row r="802" ht="24" customHeight="1">
       <c r="A802" s="34"/>
-      <c r="B802" s="34"/>
+      <c r="B802" s="24"/>
       <c r="C802" s="24"/>
       <c r="D802" s="24"/>
       <c r="E802" s="24"/>
     </row>
     <row r="803" ht="24" customHeight="1">
       <c r="A803" s="34"/>
-      <c r="B803" s="34"/>
+      <c r="B803" s="24"/>
       <c r="C803" s="24"/>
       <c r="D803" s="24"/>
       <c r="E803" s="24"/>
     </row>
     <row r="804" ht="24" customHeight="1">
       <c r="A804" s="34"/>
-      <c r="B804" s="34"/>
+      <c r="B804" s="24"/>
       <c r="C804" s="24"/>
       <c r="D804" s="24"/>
       <c r="E804" s="24"/>
     </row>
     <row r="805" ht="24" customHeight="1">
       <c r="A805" s="34"/>
-      <c r="B805" s="34"/>
+      <c r="B805" s="24"/>
       <c r="C805" s="24"/>
       <c r="D805" s="24"/>
       <c r="E805" s="24"/>
     </row>
     <row r="806" ht="24" customHeight="1">
       <c r="A806" s="34"/>
-      <c r="B806" s="34"/>
+      <c r="B806" s="24"/>
       <c r="C806" s="24"/>
       <c r="D806" s="24"/>
       <c r="E806" s="24"/>
     </row>
     <row r="807" ht="24" customHeight="1">
       <c r="A807" s="34"/>
-      <c r="B807" s="34"/>
+      <c r="B807" s="24"/>
       <c r="C807" s="24"/>
       <c r="D807" s="24"/>
       <c r="E807" s="24"/>
     </row>
     <row r="808" ht="24" customHeight="1">
       <c r="A808" s="34"/>
-      <c r="B808" s="34"/>
+      <c r="B808" s="24"/>
       <c r="C808" s="24"/>
       <c r="D808" s="24"/>
       <c r="E808" s="24"/>
     </row>
     <row r="809" ht="24" customHeight="1">
       <c r="A809" s="34"/>
-      <c r="B809" s="34"/>
+      <c r="B809" s="24"/>
       <c r="C809" s="24"/>
       <c r="D809" s="24"/>
       <c r="E809" s="24"/>
     </row>
     <row r="810" ht="24" customHeight="1">
       <c r="A810" s="34"/>
-      <c r="B810" s="34"/>
+      <c r="B810" s="24"/>
       <c r="C810" s="24"/>
       <c r="D810" s="24"/>
       <c r="E810" s="24"/>
     </row>
     <row r="811" ht="24" customHeight="1">
       <c r="A811" s="34"/>
-      <c r="B811" s="34"/>
+      <c r="B811" s="24"/>
       <c r="C811" s="24"/>
       <c r="D811" s="24"/>
       <c r="E811" s="24"/>
     </row>
     <row r="812" ht="24" customHeight="1">
       <c r="A812" s="34"/>
-      <c r="B812" s="34"/>
+      <c r="B812" s="24"/>
       <c r="C812" s="24"/>
       <c r="D812" s="24"/>
       <c r="E812" s="24"/>
     </row>
     <row r="813" ht="24" customHeight="1">
       <c r="A813" s="34"/>
-      <c r="B813" s="34"/>
+      <c r="B813" s="24"/>
       <c r="C813" s="24"/>
       <c r="D813" s="24"/>
       <c r="E813" s="24"/>
     </row>
     <row r="814" ht="24" customHeight="1">
       <c r="A814" s="34"/>
-      <c r="B814" s="34"/>
+      <c r="B814" s="24"/>
       <c r="C814" s="24"/>
       <c r="D814" s="24"/>
       <c r="E814" s="24"/>
     </row>
     <row r="815" ht="24" customHeight="1">
       <c r="A815" s="34"/>
-      <c r="B815" s="34"/>
+      <c r="B815" s="24"/>
       <c r="C815" s="24"/>
       <c r="D815" s="24"/>
       <c r="E815" s="24"/>
     </row>
     <row r="816" ht="24" customHeight="1">
       <c r="A816" s="34"/>
-      <c r="B816" s="34"/>
+      <c r="B816" s="24"/>
       <c r="C816" s="24"/>
       <c r="D816" s="24"/>
       <c r="E816" s="24"/>
     </row>
     <row r="817" ht="24" customHeight="1">
       <c r="A817" s="34"/>
-      <c r="B817" s="34"/>
+      <c r="B817" s="24"/>
       <c r="C817" s="24"/>
       <c r="D817" s="24"/>
       <c r="E817" s="24"/>
     </row>
     <row r="818" ht="24" customHeight="1">
       <c r="A818" s="34"/>
-      <c r="B818" s="34"/>
+      <c r="B818" s="24"/>
       <c r="C818" s="24"/>
       <c r="D818" s="24"/>
       <c r="E818" s="24"/>
     </row>
     <row r="819" ht="24" customHeight="1">
       <c r="A819" s="34"/>
-      <c r="B819" s="34"/>
+      <c r="B819" s="24"/>
       <c r="C819" s="24"/>
       <c r="D819" s="24"/>
       <c r="E819" s="24"/>
     </row>
     <row r="820" ht="24" customHeight="1">
       <c r="A820" s="34"/>
-      <c r="B820" s="34"/>
+      <c r="B820" s="24"/>
       <c r="C820" s="24"/>
       <c r="D820" s="24"/>
       <c r="E820" s="24"/>
     </row>
     <row r="821" ht="24" customHeight="1">
       <c r="A821" s="34"/>
-      <c r="B821" s="34"/>
+      <c r="B821" s="24"/>
       <c r="C821" s="24"/>
       <c r="D821" s="24"/>
       <c r="E821" s="24"/>
     </row>
     <row r="822" ht="24" customHeight="1">
       <c r="A822" s="34"/>
-      <c r="B822" s="34"/>
+      <c r="B822" s="24"/>
       <c r="C822" s="24"/>
       <c r="D822" s="24"/>
       <c r="E822" s="24"/>
     </row>
     <row r="823" ht="24" customHeight="1">
       <c r="A823" s="34"/>
-      <c r="B823" s="34"/>
+      <c r="B823" s="24"/>
       <c r="C823" s="24"/>
       <c r="D823" s="24"/>
       <c r="E823" s="24"/>
     </row>
     <row r="824" ht="24" customHeight="1">
       <c r="A824" s="34"/>
-      <c r="B824" s="34"/>
+      <c r="B824" s="24"/>
       <c r="C824" s="24"/>
       <c r="D824" s="24"/>
       <c r="E824" s="24"/>
     </row>
     <row r="825" ht="24" customHeight="1">
       <c r="A825" s="34"/>
-      <c r="B825" s="34"/>
+      <c r="B825" s="24"/>
       <c r="C825" s="24"/>
       <c r="D825" s="24"/>
       <c r="E825" s="24"/>
     </row>
     <row r="826" ht="24" customHeight="1">
       <c r="A826" s="34"/>
-      <c r="B826" s="34"/>
+      <c r="B826" s="24"/>
       <c r="C826" s="24"/>
       <c r="D826" s="24"/>
       <c r="E826" s="24"/>
     </row>
     <row r="827" ht="24" customHeight="1">
       <c r="A827" s="34"/>
-      <c r="B827" s="34"/>
+      <c r="B827" s="24"/>
       <c r="C827" s="24"/>
       <c r="D827" s="24"/>
       <c r="E827" s="24"/>
     </row>
     <row r="828" ht="24" customHeight="1">
       <c r="A828" s="34"/>
-      <c r="B828" s="34"/>
+      <c r="B828" s="24"/>
       <c r="C828" s="24"/>
       <c r="D828" s="24"/>
       <c r="E828" s="24"/>
     </row>
     <row r="829" ht="24" customHeight="1">
       <c r="A829" s="34"/>
-      <c r="B829" s="34"/>
+      <c r="B829" s="24"/>
       <c r="C829" s="24"/>
       <c r="D829" s="24"/>
       <c r="E829" s="24"/>
     </row>
     <row r="830" ht="24" customHeight="1">
       <c r="A830" s="34"/>
-      <c r="B830" s="34"/>
+      <c r="B830" s="24"/>
       <c r="C830" s="24"/>
       <c r="D830" s="24"/>
       <c r="E830" s="24"/>
     </row>
     <row r="831" ht="24" customHeight="1">
       <c r="A831" s="34"/>
-      <c r="B831" s="34"/>
+      <c r="B831" s="24"/>
       <c r="C831" s="24"/>
       <c r="D831" s="24"/>
       <c r="E831" s="24"/>
     </row>
     <row r="832" ht="24" customHeight="1">
       <c r="A832" s="34"/>
-      <c r="B832" s="34"/>
+      <c r="B832" s="24"/>
       <c r="C832" s="24"/>
       <c r="D832" s="24"/>
       <c r="E832" s="24"/>
     </row>
     <row r="833" ht="24" customHeight="1">
       <c r="A833" s="34"/>
-      <c r="B833" s="34"/>
+      <c r="B833" s="24"/>
       <c r="C833" s="24"/>
       <c r="D833" s="24"/>
       <c r="E833" s="24"/>
     </row>
     <row r="834" ht="24" customHeight="1">
       <c r="A834" s="34"/>
-      <c r="B834" s="34"/>
+      <c r="B834" s="24"/>
       <c r="C834" s="24"/>
       <c r="D834" s="24"/>
       <c r="E834" s="24"/>
     </row>
     <row r="835" ht="24" customHeight="1">
       <c r="A835" s="34"/>
-      <c r="B835" s="34"/>
+      <c r="B835" s="24"/>
       <c r="C835" s="24"/>
       <c r="D835" s="24"/>
       <c r="E835" s="24"/>
     </row>
     <row r="836" ht="24" customHeight="1">
       <c r="A836" s="34"/>
-      <c r="B836" s="34"/>
+      <c r="B836" s="24"/>
       <c r="C836" s="24"/>
       <c r="D836" s="24"/>
       <c r="E836" s="24"/>
     </row>
     <row r="837" ht="24" customHeight="1">
       <c r="A837" s="34"/>
-      <c r="B837" s="34"/>
+      <c r="B837" s="24"/>
       <c r="C837" s="24"/>
       <c r="D837" s="24"/>
       <c r="E837" s="24"/>
     </row>
     <row r="838" ht="24" customHeight="1">
       <c r="A838" s="34"/>
-      <c r="B838" s="34"/>
+      <c r="B838" s="24"/>
       <c r="C838" s="24"/>
       <c r="D838" s="24"/>
       <c r="E838" s="24"/>
     </row>
     <row r="839" ht="24" customHeight="1">
       <c r="A839" s="34"/>
-      <c r="B839" s="34"/>
+      <c r="B839" s="24"/>
       <c r="C839" s="24"/>
       <c r="D839" s="24"/>
       <c r="E839" s="24"/>
     </row>
     <row r="840" ht="24" customHeight="1">
       <c r="A840" s="34"/>
-      <c r="B840" s="34"/>
+      <c r="B840" s="24"/>
       <c r="C840" s="24"/>
       <c r="D840" s="24"/>
       <c r="E840" s="24"/>
     </row>
     <row r="841" ht="24" customHeight="1">
       <c r="A841" s="34"/>
-      <c r="B841" s="34"/>
+      <c r="B841" s="24"/>
       <c r="C841" s="24"/>
       <c r="D841" s="24"/>
       <c r="E841" s="24"/>
     </row>
     <row r="842" ht="24" customHeight="1">
       <c r="A842" s="34"/>
-      <c r="B842" s="34"/>
+      <c r="B842" s="24"/>
       <c r="C842" s="24"/>
       <c r="D842" s="24"/>
       <c r="E842" s="24"/>
     </row>
     <row r="843" ht="24" customHeight="1">
       <c r="A843" s="34"/>
-      <c r="B843" s="34"/>
+      <c r="B843" s="24"/>
       <c r="C843" s="24"/>
       <c r="D843" s="24"/>
       <c r="E843" s="24"/>
     </row>
     <row r="844" ht="24" customHeight="1">
       <c r="A844" s="34"/>
-      <c r="B844" s="34"/>
+      <c r="B844" s="24"/>
       <c r="C844" s="24"/>
       <c r="D844" s="24"/>
       <c r="E844" s="24"/>
     </row>
     <row r="845" ht="24" customHeight="1">
       <c r="A845" s="34"/>
-      <c r="B845" s="34"/>
+      <c r="B845" s="24"/>
       <c r="C845" s="24"/>
       <c r="D845" s="24"/>
       <c r="E845" s="24"/>
     </row>
     <row r="846" ht="24" customHeight="1">
       <c r="A846" s="34"/>
-      <c r="B846" s="34"/>
+      <c r="B846" s="24"/>
       <c r="C846" s="24"/>
       <c r="D846" s="24"/>
       <c r="E846" s="24"/>
     </row>
     <row r="847" ht="24" customHeight="1">
       <c r="A847" s="34"/>
-      <c r="B847" s="34"/>
+      <c r="B847" s="24"/>
       <c r="C847" s="24"/>
       <c r="D847" s="24"/>
       <c r="E847" s="24"/>
     </row>
     <row r="848" ht="24" customHeight="1">
       <c r="A848" s="34"/>
-      <c r="B848" s="34"/>
+      <c r="B848" s="24"/>
       <c r="C848" s="24"/>
       <c r="D848" s="24"/>
       <c r="E848" s="24"/>
     </row>
     <row r="849" ht="24" customHeight="1">
       <c r="A849" s="34"/>
-      <c r="B849" s="34"/>
+      <c r="B849" s="24"/>
       <c r="C849" s="24"/>
       <c r="D849" s="24"/>
       <c r="E849" s="24"/>
     </row>
     <row r="850" ht="24" customHeight="1">
       <c r="A850" s="34"/>
-      <c r="B850" s="34"/>
+      <c r="B850" s="24"/>
       <c r="C850" s="24"/>
       <c r="D850" s="24"/>
       <c r="E850" s="24"/>
     </row>
     <row r="851" ht="24" customHeight="1">
       <c r="A851" s="34"/>
-      <c r="B851" s="34"/>
+      <c r="B851" s="24"/>
       <c r="C851" s="24"/>
       <c r="D851" s="24"/>
       <c r="E851" s="24"/>
     </row>
     <row r="852" ht="24" customHeight="1">
       <c r="A852" s="34"/>
-      <c r="B852" s="34"/>
+      <c r="B852" s="24"/>
       <c r="C852" s="24"/>
       <c r="D852" s="24"/>
       <c r="E852" s="24"/>
     </row>
     <row r="853" ht="24" customHeight="1">
       <c r="A853" s="34"/>
-      <c r="B853" s="34"/>
+      <c r="B853" s="24"/>
       <c r="C853" s="24"/>
       <c r="D853" s="24"/>
       <c r="E853" s="24"/>
     </row>
     <row r="854" ht="24" customHeight="1">
       <c r="A854" s="34"/>
-      <c r="B854" s="34"/>
+      <c r="B854" s="24"/>
       <c r="C854" s="24"/>
       <c r="D854" s="24"/>
       <c r="E854" s="24"/>
     </row>
     <row r="855" ht="24" customHeight="1">
       <c r="A855" s="34"/>
-      <c r="B855" s="34"/>
+      <c r="B855" s="24"/>
       <c r="C855" s="24"/>
       <c r="D855" s="24"/>
       <c r="E855" s="24"/>
     </row>
     <row r="856" ht="24" customHeight="1">
       <c r="A856" s="34"/>
-      <c r="B856" s="34"/>
+      <c r="B856" s="24"/>
       <c r="C856" s="24"/>
       <c r="D856" s="24"/>
       <c r="E856" s="24"/>
     </row>
     <row r="857" ht="24" customHeight="1">
       <c r="A857" s="34"/>
-      <c r="B857" s="34"/>
+      <c r="B857" s="24"/>
       <c r="C857" s="24"/>
       <c r="D857" s="24"/>
       <c r="E857" s="24"/>
     </row>
     <row r="858" ht="24" customHeight="1">
       <c r="A858" s="34"/>
-      <c r="B858" s="34"/>
+      <c r="B858" s="24"/>
       <c r="C858" s="24"/>
       <c r="D858" s="24"/>
       <c r="E858" s="24"/>
     </row>
     <row r="859" ht="24" customHeight="1">
       <c r="A859" s="34"/>
-      <c r="B859" s="34"/>
+      <c r="B859" s="24"/>
       <c r="C859" s="24"/>
       <c r="D859" s="24"/>
       <c r="E859" s="24"/>
     </row>
     <row r="860" ht="24" customHeight="1">
       <c r="A860" s="34"/>
-      <c r="B860" s="34"/>
+      <c r="B860" s="24"/>
       <c r="C860" s="24"/>
       <c r="D860" s="24"/>
       <c r="E860" s="24"/>
     </row>
     <row r="861" ht="24" customHeight="1">
       <c r="A861" s="34"/>
-      <c r="B861" s="34"/>
+      <c r="B861" s="24"/>
       <c r="C861" s="24"/>
       <c r="D861" s="24"/>
       <c r="E861" s="24"/>
     </row>
     <row r="862" ht="24" customHeight="1">
       <c r="A862" s="34"/>
-      <c r="B862" s="34"/>
+      <c r="B862" s="24"/>
       <c r="C862" s="24"/>
       <c r="D862" s="24"/>
       <c r="E862" s="24"/>
     </row>
     <row r="863" ht="24" customHeight="1">
       <c r="A863" s="34"/>
-      <c r="B863" s="34"/>
+      <c r="B863" s="24"/>
       <c r="C863" s="24"/>
       <c r="D863" s="24"/>
       <c r="E863" s="24"/>
     </row>
     <row r="864" ht="24" customHeight="1">
       <c r="A864" s="34"/>
-      <c r="B864" s="34"/>
+      <c r="B864" s="24"/>
       <c r="C864" s="24"/>
       <c r="D864" s="24"/>
       <c r="E864" s="24"/>
     </row>
     <row r="865" ht="24" customHeight="1">
       <c r="A865" s="34"/>
-      <c r="B865" s="34"/>
+      <c r="B865" s="24"/>
       <c r="C865" s="24"/>
       <c r="D865" s="24"/>
       <c r="E865" s="24"/>
     </row>
     <row r="866" ht="24" customHeight="1">
       <c r="A866" s="34"/>
-      <c r="B866" s="34"/>
+      <c r="B866" s="24"/>
       <c r="C866" s="24"/>
       <c r="D866" s="24"/>
       <c r="E866" s="24"/>
     </row>
     <row r="867" ht="24" customHeight="1">
       <c r="A867" s="34"/>
-      <c r="B867" s="34"/>
+      <c r="B867" s="24"/>
       <c r="C867" s="24"/>
       <c r="D867" s="24"/>
       <c r="E867" s="24"/>
     </row>
     <row r="868" ht="24" customHeight="1">
       <c r="A868" s="34"/>
-      <c r="B868" s="34"/>
+      <c r="B868" s="24"/>
       <c r="C868" s="24"/>
       <c r="D868" s="24"/>
       <c r="E868" s="24"/>
     </row>
     <row r="869" ht="24" customHeight="1">
       <c r="A869" s="34"/>
-      <c r="B869" s="34"/>
+      <c r="B869" s="24"/>
       <c r="C869" s="24"/>
       <c r="D869" s="24"/>
       <c r="E869" s="24"/>
     </row>
     <row r="870" ht="24" customHeight="1">
       <c r="A870" s="34"/>
-      <c r="B870" s="34"/>
+      <c r="B870" s="24"/>
       <c r="C870" s="24"/>
       <c r="D870" s="24"/>
       <c r="E870" s="24"/>
     </row>
     <row r="871" ht="24" customHeight="1">
       <c r="A871" s="34"/>
-      <c r="B871" s="34"/>
+      <c r="B871" s="24"/>
       <c r="C871" s="24"/>
       <c r="D871" s="24"/>
       <c r="E871" s="24"/>
     </row>
     <row r="872" ht="24" customHeight="1">
       <c r="A872" s="34"/>
-      <c r="B872" s="34"/>
+      <c r="B872" s="24"/>
       <c r="C872" s="24"/>
       <c r="D872" s="24"/>
       <c r="E872" s="24"/>
     </row>
     <row r="873" ht="24" customHeight="1">
       <c r="A873" s="34"/>
-      <c r="B873" s="34"/>
+      <c r="B873" s="24"/>
       <c r="C873" s="24"/>
       <c r="D873" s="24"/>
       <c r="E873" s="24"/>
     </row>
     <row r="874" ht="24" customHeight="1">
       <c r="A874" s="34"/>
-      <c r="B874" s="34"/>
+      <c r="B874" s="24"/>
       <c r="C874" s="24"/>
       <c r="D874" s="24"/>
       <c r="E874" s="24"/>
     </row>
     <row r="875" ht="24" customHeight="1">
       <c r="A875" s="34"/>
-      <c r="B875" s="34"/>
+      <c r="B875" s="24"/>
       <c r="C875" s="24"/>
       <c r="D875" s="24"/>
       <c r="E875" s="24"/>
     </row>
     <row r="876" ht="24" customHeight="1">
       <c r="A876" s="34"/>
-      <c r="B876" s="34"/>
+      <c r="B876" s="24"/>
       <c r="C876" s="24"/>
       <c r="D876" s="24"/>
       <c r="E876" s="24"/>
     </row>
     <row r="877" ht="24" customHeight="1">
       <c r="A877" s="34"/>
-      <c r="B877" s="34"/>
+      <c r="B877" s="24"/>
       <c r="C877" s="24"/>
       <c r="D877" s="24"/>
       <c r="E877" s="24"/>
     </row>
     <row r="878" ht="24" customHeight="1">
       <c r="A878" s="34"/>
-      <c r="B878" s="34"/>
+      <c r="B878" s="24"/>
       <c r="C878" s="24"/>
       <c r="D878" s="24"/>
       <c r="E878" s="24"/>
     </row>
     <row r="879" ht="24" customHeight="1">
       <c r="A879" s="34"/>
-      <c r="B879" s="34"/>
+      <c r="B879" s="24"/>
       <c r="C879" s="24"/>
       <c r="D879" s="24"/>
       <c r="E879" s="24"/>
     </row>
     <row r="880" ht="24" customHeight="1">
       <c r="A880" s="34"/>
-      <c r="B880" s="34"/>
+      <c r="B880" s="24"/>
       <c r="C880" s="24"/>
       <c r="D880" s="24"/>
       <c r="E880" s="24"/>
     </row>
     <row r="881" ht="24" customHeight="1">
       <c r="A881" s="34"/>
-      <c r="B881" s="34"/>
+      <c r="B881" s="24"/>
       <c r="C881" s="24"/>
       <c r="D881" s="24"/>
       <c r="E881" s="24"/>
     </row>
     <row r="882" ht="24" customHeight="1">
       <c r="A882" s="34"/>
-      <c r="B882" s="34"/>
+      <c r="B882" s="24"/>
       <c r="C882" s="24"/>
       <c r="D882" s="24"/>
       <c r="E882" s="24"/>
     </row>
     <row r="883" ht="24" customHeight="1">
       <c r="A883" s="34"/>
-      <c r="B883" s="34"/>
+      <c r="B883" s="24"/>
       <c r="C883" s="24"/>
       <c r="D883" s="24"/>
       <c r="E883" s="24"/>
     </row>
     <row r="884" ht="24" customHeight="1">
       <c r="A884" s="34"/>
-      <c r="B884" s="34"/>
+      <c r="B884" s="24"/>
       <c r="C884" s="24"/>
       <c r="D884" s="24"/>
       <c r="E884" s="24"/>
     </row>
     <row r="885" ht="24" customHeight="1">
       <c r="A885" s="34"/>
-      <c r="B885" s="34"/>
+      <c r="B885" s="24"/>
       <c r="C885" s="24"/>
       <c r="D885" s="24"/>
       <c r="E885" s="24"/>
     </row>
     <row r="886" ht="24" customHeight="1">
       <c r="A886" s="34"/>
-      <c r="B886" s="34"/>
+      <c r="B886" s="24"/>
       <c r="C886" s="24"/>
       <c r="D886" s="24"/>
       <c r="E886" s="24"/>
     </row>
     <row r="887" ht="24" customHeight="1">
       <c r="A887" s="34"/>
-      <c r="B887" s="34"/>
+      <c r="B887" s="24"/>
       <c r="C887" s="24"/>
       <c r="D887" s="24"/>
       <c r="E887" s="24"/>
     </row>
     <row r="888" ht="24" customHeight="1">
       <c r="A888" s="34"/>
-      <c r="B888" s="34"/>
+      <c r="B888" s="24"/>
       <c r="C888" s="24"/>
       <c r="D888" s="24"/>
       <c r="E888" s="24"/>
     </row>
     <row r="889" ht="24" customHeight="1">
       <c r="A889" s="34"/>
-      <c r="B889" s="34"/>
+      <c r="B889" s="24"/>
       <c r="C889" s="24"/>
       <c r="D889" s="24"/>
       <c r="E889" s="24"/>
     </row>
     <row r="890" ht="24" customHeight="1">
       <c r="A890" s="34"/>
-      <c r="B890" s="34"/>
+      <c r="B890" s="24"/>
       <c r="C890" s="24"/>
       <c r="D890" s="24"/>
       <c r="E890" s="24"/>
     </row>
     <row r="891" ht="24" customHeight="1">
       <c r="A891" s="34"/>
-      <c r="B891" s="34"/>
+      <c r="B891" s="24"/>
       <c r="C891" s="24"/>
       <c r="D891" s="24"/>
       <c r="E891" s="24"/>
     </row>
     <row r="892" ht="24" customHeight="1">
       <c r="A892" s="34"/>
-      <c r="B892" s="34"/>
+      <c r="B892" s="24"/>
       <c r="C892" s="24"/>
       <c r="D892" s="24"/>
       <c r="E892" s="24"/>
     </row>
     <row r="893" ht="24" customHeight="1">
       <c r="A893" s="34"/>
-      <c r="B893" s="34"/>
+      <c r="B893" s="24"/>
       <c r="C893" s="24"/>
       <c r="D893" s="24"/>
       <c r="E893" s="24"/>
     </row>
     <row r="894" ht="24" customHeight="1">
       <c r="A894" s="34"/>
-      <c r="B894" s="34"/>
+      <c r="B894" s="24"/>
       <c r="C894" s="24"/>
       <c r="D894" s="24"/>
       <c r="E894" s="24"/>
     </row>
     <row r="895" ht="24" customHeight="1">
       <c r="A895" s="34"/>
-      <c r="B895" s="34"/>
+      <c r="B895" s="24"/>
       <c r="C895" s="24"/>
       <c r="D895" s="24"/>
       <c r="E895" s="24"/>
     </row>
     <row r="896" ht="24" customHeight="1">
       <c r="A896" s="34"/>
-      <c r="B896" s="34"/>
+      <c r="B896" s="24"/>
       <c r="C896" s="24"/>
       <c r="D896" s="24"/>
       <c r="E896" s="24"/>
     </row>
     <row r="897" ht="24" customHeight="1">
       <c r="A897" s="34"/>
-      <c r="B897" s="34"/>
+      <c r="B897" s="24"/>
       <c r="C897" s="24"/>
       <c r="D897" s="24"/>
       <c r="E897" s="24"/>
     </row>
     <row r="898" ht="24" customHeight="1">
       <c r="A898" s="34"/>
-      <c r="B898" s="34"/>
+      <c r="B898" s="24"/>
       <c r="C898" s="24"/>
       <c r="D898" s="24"/>
       <c r="E898" s="24"/>
     </row>
     <row r="899" ht="24" customHeight="1">
       <c r="A899" s="34"/>
-      <c r="B899" s="34"/>
+      <c r="B899" s="24"/>
       <c r="C899" s="24"/>
       <c r="D899" s="24"/>
       <c r="E899" s="24"/>
     </row>
     <row r="900" ht="24" customHeight="1">
       <c r="A900" s="34"/>
-      <c r="B900" s="34"/>
+      <c r="B900" s="24"/>
       <c r="C900" s="24"/>
       <c r="D900" s="24"/>
       <c r="E900" s="24"/>
     </row>
     <row r="901" ht="24" customHeight="1">
       <c r="A901" s="34"/>
-      <c r="B901" s="34"/>
+      <c r="B901" s="24"/>
       <c r="C901" s="24"/>
       <c r="D901" s="24"/>
       <c r="E901" s="24"/>
     </row>
     <row r="902" ht="24" customHeight="1">
       <c r="A902" s="34"/>
-      <c r="B902" s="34"/>
+      <c r="B902" s="24"/>
       <c r="C902" s="24"/>
       <c r="D902" s="24"/>
       <c r="E902" s="24"/>
     </row>
     <row r="903" ht="24" customHeight="1">
       <c r="A903" s="34"/>
-      <c r="B903" s="34"/>
+      <c r="B903" s="24"/>
       <c r="C903" s="24"/>
       <c r="D903" s="24"/>
       <c r="E903" s="24"/>
     </row>
     <row r="904" ht="24" customHeight="1">
       <c r="A904" s="34"/>
-      <c r="B904" s="34"/>
+      <c r="B904" s="24"/>
       <c r="C904" s="24"/>
       <c r="D904" s="24"/>
       <c r="E904" s="24"/>
     </row>
     <row r="905" ht="24" customHeight="1">
       <c r="A905" s="34"/>
-      <c r="B905" s="34"/>
+      <c r="B905" s="24"/>
       <c r="C905" s="24"/>
       <c r="D905" s="24"/>
       <c r="E905" s="24"/>
     </row>
     <row r="906" ht="24" customHeight="1">
       <c r="A906" s="34"/>
-      <c r="B906" s="34"/>
+      <c r="B906" s="24"/>
       <c r="C906" s="24"/>
       <c r="D906" s="24"/>
       <c r="E906" s="24"/>
     </row>
     <row r="907" ht="24" customHeight="1">
       <c r="A907" s="34"/>
-      <c r="B907" s="34"/>
+      <c r="B907" s="24"/>
       <c r="C907" s="24"/>
       <c r="D907" s="24"/>
       <c r="E907" s="24"/>
     </row>
     <row r="908" ht="24" customHeight="1">
       <c r="A908" s="34"/>
-      <c r="B908" s="34"/>
+      <c r="B908" s="24"/>
       <c r="C908" s="24"/>
       <c r="D908" s="24"/>
       <c r="E908" s="24"/>
     </row>
     <row r="909" ht="24" customHeight="1">
       <c r="A909" s="34"/>
-      <c r="B909" s="34"/>
+      <c r="B909" s="24"/>
       <c r="C909" s="24"/>
       <c r="D909" s="24"/>
       <c r="E909" s="24"/>
     </row>
     <row r="910" ht="24" customHeight="1">
       <c r="A910" s="34"/>
-      <c r="B910" s="34"/>
+      <c r="B910" s="24"/>
       <c r="C910" s="24"/>
       <c r="D910" s="24"/>
       <c r="E910" s="24"/>
     </row>
     <row r="911" ht="24" customHeight="1">
       <c r="A911" s="34"/>
-      <c r="B911" s="34"/>
+      <c r="B911" s="24"/>
       <c r="C911" s="24"/>
       <c r="D911" s="24"/>
       <c r="E911" s="24"/>
     </row>
     <row r="912" ht="24" customHeight="1">
       <c r="A912" s="34"/>
-      <c r="B912" s="34"/>
+      <c r="B912" s="24"/>
       <c r="C912" s="24"/>
       <c r="D912" s="24"/>
       <c r="E912" s="24"/>
     </row>
     <row r="913" ht="24" customHeight="1">
       <c r="A913" s="34"/>
-      <c r="B913" s="34"/>
+      <c r="B913" s="24"/>
       <c r="C913" s="24"/>
       <c r="D913" s="24"/>
       <c r="E913" s="24"/>
     </row>
     <row r="914" ht="24" customHeight="1">
       <c r="A914" s="34"/>
-      <c r="B914" s="34"/>
+      <c r="B914" s="24"/>
       <c r="C914" s="24"/>
       <c r="D914" s="24"/>
       <c r="E914" s="24"/>
     </row>
     <row r="915" ht="24" customHeight="1">
       <c r="A915" s="34"/>
-      <c r="B915" s="34"/>
+      <c r="B915" s="24"/>
       <c r="C915" s="24"/>
       <c r="D915" s="24"/>
       <c r="E915" s="24"/>
     </row>
     <row r="916" ht="24" customHeight="1">
       <c r="A916" s="34"/>
-      <c r="B916" s="34"/>
+      <c r="B916" s="24"/>
       <c r="C916" s="24"/>
       <c r="D916" s="24"/>
       <c r="E916" s="24"/>
     </row>
     <row r="917" ht="24" customHeight="1">
       <c r="A917" s="34"/>
-      <c r="B917" s="34"/>
+      <c r="B917" s="24"/>
       <c r="C917" s="24"/>
       <c r="D917" s="24"/>
       <c r="E917" s="24"/>
     </row>
     <row r="918" ht="24" customHeight="1">
       <c r="A918" s="34"/>
-      <c r="B918" s="34"/>
+      <c r="B918" s="24"/>
       <c r="C918" s="24"/>
       <c r="D918" s="24"/>
       <c r="E918" s="24"/>
     </row>
     <row r="919" ht="24" customHeight="1">
       <c r="A919" s="34"/>
-      <c r="B919" s="34"/>
+      <c r="B919" s="24"/>
       <c r="C919" s="24"/>
       <c r="D919" s="24"/>
       <c r="E919" s="24"/>
     </row>
     <row r="920" ht="24" customHeight="1">
       <c r="A920" s="34"/>
-      <c r="B920" s="34"/>
+      <c r="B920" s="24"/>
       <c r="C920" s="24"/>
       <c r="D920" s="24"/>
       <c r="E920" s="24"/>
     </row>
     <row r="921" ht="24" customHeight="1">
       <c r="A921" s="34"/>
-      <c r="B921" s="34"/>
+      <c r="B921" s="24"/>
       <c r="C921" s="24"/>
       <c r="D921" s="24"/>
       <c r="E921" s="24"/>
     </row>
     <row r="922" ht="24" customHeight="1">
       <c r="A922" s="34"/>
-      <c r="B922" s="34"/>
+      <c r="B922" s="24"/>
       <c r="C922" s="24"/>
       <c r="D922" s="24"/>
       <c r="E922" s="24"/>
     </row>
     <row r="923" ht="24" customHeight="1">
       <c r="A923" s="34"/>
-      <c r="B923" s="34"/>
+      <c r="B923" s="24"/>
       <c r="C923" s="24"/>
       <c r="D923" s="24"/>
       <c r="E923" s="24"/>
     </row>
     <row r="924" ht="24" customHeight="1">
       <c r="A924" s="34"/>
-      <c r="B924" s="34"/>
+      <c r="B924" s="24"/>
       <c r="C924" s="24"/>
       <c r="D924" s="24"/>
       <c r="E924" s="24"/>
     </row>
     <row r="925" ht="24" customHeight="1">
       <c r="A925" s="34"/>
-      <c r="B925" s="34"/>
+      <c r="B925" s="24"/>
       <c r="C925" s="24"/>
       <c r="D925" s="24"/>
       <c r="E925" s="24"/>
     </row>
     <row r="926" ht="24" customHeight="1">
       <c r="A926" s="34"/>
-      <c r="B926" s="34"/>
+      <c r="B926" s="24"/>
       <c r="C926" s="24"/>
       <c r="D926" s="24"/>
       <c r="E926" s="24"/>
     </row>
     <row r="927" ht="24" customHeight="1">
       <c r="A927" s="34"/>
-      <c r="B927" s="34"/>
+      <c r="B927" s="24"/>
       <c r="C927" s="24"/>
       <c r="D927" s="24"/>
       <c r="E927" s="24"/>
     </row>
     <row r="928" ht="24" customHeight="1">
       <c r="A928" s="34"/>
-      <c r="B928" s="34"/>
+      <c r="B928" s="24"/>
       <c r="C928" s="24"/>
       <c r="D928" s="24"/>
       <c r="E928" s="24"/>
     </row>
     <row r="929" ht="24" customHeight="1">
       <c r="A929" s="34"/>
-      <c r="B929" s="34"/>
+      <c r="B929" s="24"/>
       <c r="C929" s="24"/>
       <c r="D929" s="24"/>
       <c r="E929" s="24"/>
     </row>
     <row r="930" ht="24" customHeight="1">
       <c r="A930" s="34"/>
-      <c r="B930" s="34"/>
+      <c r="B930" s="24"/>
       <c r="C930" s="24"/>
       <c r="D930" s="24"/>
       <c r="E930" s="24"/>
     </row>
     <row r="931" ht="24" customHeight="1">
       <c r="A931" s="34"/>
-      <c r="B931" s="34"/>
+      <c r="B931" s="24"/>
       <c r="C931" s="24"/>
       <c r="D931" s="24"/>
       <c r="E931" s="24"/>
     </row>
     <row r="932" ht="24" customHeight="1">
       <c r="A932" s="34"/>
-      <c r="B932" s="34"/>
+      <c r="B932" s="24"/>
       <c r="C932" s="24"/>
       <c r="D932" s="24"/>
       <c r="E932" s="24"/>
     </row>
     <row r="933" ht="24" customHeight="1">
       <c r="A933" s="34"/>
-      <c r="B933" s="34"/>
+      <c r="B933" s="24"/>
       <c r="C933" s="24"/>
       <c r="D933" s="24"/>
       <c r="E933" s="24"/>
     </row>
     <row r="934" ht="24" customHeight="1">
       <c r="A934" s="34"/>
-      <c r="B934" s="34"/>
+      <c r="B934" s="24"/>
       <c r="C934" s="24"/>
       <c r="D934" s="24"/>
       <c r="E934" s="24"/>
     </row>
     <row r="935" ht="24" customHeight="1">
       <c r="A935" s="34"/>
-      <c r="B935" s="34"/>
+      <c r="B935" s="24"/>
       <c r="C935" s="24"/>
       <c r="D935" s="24"/>
       <c r="E935" s="24"/>
     </row>
     <row r="936" ht="24" customHeight="1">
       <c r="A936" s="34"/>
-      <c r="B936" s="34"/>
+      <c r="B936" s="24"/>
       <c r="C936" s="24"/>
       <c r="D936" s="24"/>
       <c r="E936" s="24"/>
     </row>
     <row r="937" ht="24" customHeight="1">
       <c r="A937" s="34"/>
-      <c r="B937" s="34"/>
+      <c r="B937" s="24"/>
       <c r="C937" s="24"/>
       <c r="D937" s="24"/>
       <c r="E937" s="24"/>
     </row>
     <row r="938" ht="24" customHeight="1">
       <c r="A938" s="34"/>
-      <c r="B938" s="34"/>
+      <c r="B938" s="24"/>
       <c r="C938" s="24"/>
       <c r="D938" s="24"/>
       <c r="E938" s="24"/>
     </row>
     <row r="939" ht="24" customHeight="1">
       <c r="A939" s="34"/>
-      <c r="B939" s="34"/>
+      <c r="B939" s="24"/>
       <c r="C939" s="24"/>
       <c r="D939" s="24"/>
       <c r="E939" s="24"/>
     </row>
     <row r="940" ht="24" customHeight="1">
       <c r="A940" s="34"/>
-      <c r="B940" s="34"/>
+      <c r="B940" s="24"/>
       <c r="C940" s="24"/>
       <c r="D940" s="24"/>
       <c r="E940" s="24"/>
     </row>
     <row r="941" ht="24" customHeight="1">
       <c r="A941" s="34"/>
-      <c r="B941" s="34"/>
+      <c r="B941" s="24"/>
       <c r="C941" s="24"/>
       <c r="D941" s="24"/>
       <c r="E941" s="24"/>
     </row>
     <row r="942" ht="24" customHeight="1">
       <c r="A942" s="34"/>
-      <c r="B942" s="34"/>
+      <c r="B942" s="24"/>
       <c r="C942" s="24"/>
       <c r="D942" s="24"/>
       <c r="E942" s="24"/>
     </row>
     <row r="943" ht="24" customHeight="1">
       <c r="A943" s="34"/>
-      <c r="B943" s="34"/>
+      <c r="B943" s="24"/>
       <c r="C943" s="24"/>
       <c r="D943" s="24"/>
       <c r="E943" s="24"/>
     </row>
     <row r="944" ht="24" customHeight="1">
       <c r="A944" s="34"/>
-      <c r="B944" s="34"/>
+      <c r="B944" s="24"/>
       <c r="C944" s="24"/>
       <c r="D944" s="24"/>
       <c r="E944" s="24"/>
     </row>
     <row r="945" ht="24" customHeight="1">
       <c r="A945" s="34"/>
-      <c r="B945" s="34"/>
+      <c r="B945" s="24"/>
       <c r="C945" s="24"/>
       <c r="D945" s="24"/>
       <c r="E945" s="24"/>
     </row>
     <row r="946" ht="24" customHeight="1">
       <c r="A946" s="34"/>
-      <c r="B946" s="34"/>
+      <c r="B946" s="24"/>
       <c r="C946" s="24"/>
       <c r="D946" s="24"/>
       <c r="E946" s="24"/>
     </row>
     <row r="947" ht="24" customHeight="1">
       <c r="A947" s="34"/>
-      <c r="B947" s="34"/>
+      <c r="B947" s="24"/>
       <c r="C947" s="24"/>
       <c r="D947" s="24"/>
       <c r="E947" s="24"/>
     </row>
     <row r="948" ht="24" customHeight="1">
       <c r="A948" s="34"/>
-      <c r="B948" s="34"/>
+      <c r="B948" s="24"/>
       <c r="C948" s="24"/>
       <c r="D948" s="24"/>
       <c r="E948" s="24"/>
     </row>
     <row r="949" ht="24" customHeight="1">
       <c r="A949" s="34"/>
-      <c r="B949" s="34"/>
+      <c r="B949" s="24"/>
       <c r="C949" s="24"/>
       <c r="D949" s="24"/>
       <c r="E949" s="24"/>
     </row>
     <row r="950" ht="24" customHeight="1">
       <c r="A950" s="34"/>
-      <c r="B950" s="34"/>
+      <c r="B950" s="24"/>
       <c r="C950" s="24"/>
       <c r="D950" s="24"/>
       <c r="E950" s="24"/>
     </row>
     <row r="951" ht="24" customHeight="1">
       <c r="A951" s="34"/>
-      <c r="B951" s="34"/>
+      <c r="B951" s="24"/>
       <c r="C951" s="24"/>
       <c r="D951" s="24"/>
       <c r="E951" s="24"/>
     </row>
     <row r="952" ht="24" customHeight="1">
       <c r="A952" s="34"/>
-      <c r="B952" s="34"/>
+      <c r="B952" s="24"/>
       <c r="C952" s="24"/>
       <c r="D952" s="24"/>
       <c r="E952" s="24"/>
     </row>
     <row r="953" ht="24" customHeight="1">
       <c r="A953" s="34"/>
-      <c r="B953" s="34"/>
+      <c r="B953" s="24"/>
       <c r="C953" s="24"/>
       <c r="D953" s="24"/>
       <c r="E953" s="24"/>
     </row>
     <row r="954" ht="24" customHeight="1">
       <c r="A954" s="34"/>
-      <c r="B954" s="34"/>
+      <c r="B954" s="24"/>
       <c r="C954" s="24"/>
       <c r="D954" s="24"/>
       <c r="E954" s="24"/>
     </row>
     <row r="955" ht="24" customHeight="1">
       <c r="A955" s="34"/>
-      <c r="B955" s="34"/>
+      <c r="B955" s="24"/>
       <c r="C955" s="24"/>
       <c r="D955" s="24"/>
       <c r="E955" s="24"/>
     </row>
     <row r="956" ht="24" customHeight="1">
       <c r="A956" s="34"/>
-      <c r="B956" s="34"/>
+      <c r="B956" s="24"/>
       <c r="C956" s="24"/>
       <c r="D956" s="24"/>
       <c r="E956" s="24"/>
     </row>
     <row r="957" ht="24" customHeight="1">
       <c r="A957" s="34"/>
-      <c r="B957" s="34"/>
+      <c r="B957" s="24"/>
       <c r="C957" s="24"/>
       <c r="D957" s="24"/>
       <c r="E957" s="24"/>
     </row>
     <row r="958" ht="24" customHeight="1">
       <c r="A958" s="34"/>
-      <c r="B958" s="34"/>
+      <c r="B958" s="24"/>
       <c r="C958" s="24"/>
       <c r="D958" s="24"/>
       <c r="E958" s="24"/>
     </row>
     <row r="959" ht="24" customHeight="1">
       <c r="A959" s="34"/>
-      <c r="B959" s="34"/>
+      <c r="B959" s="24"/>
       <c r="C959" s="24"/>
       <c r="D959" s="24"/>
       <c r="E959" s="24"/>
     </row>
     <row r="960" ht="24" customHeight="1">
       <c r="A960" s="34"/>
-      <c r="B960" s="34"/>
+      <c r="B960" s="24"/>
       <c r="C960" s="24"/>
       <c r="D960" s="24"/>
       <c r="E960" s="24"/>
     </row>
     <row r="961" ht="24" customHeight="1">
       <c r="A961" s="34"/>
-      <c r="B961" s="34"/>
+      <c r="B961" s="24"/>
       <c r="C961" s="24"/>
       <c r="D961" s="24"/>
       <c r="E961" s="24"/>
     </row>
     <row r="962" ht="24" customHeight="1">
       <c r="A962" s="34"/>
-      <c r="B962" s="34"/>
+      <c r="B962" s="24"/>
       <c r="C962" s="24"/>
       <c r="D962" s="24"/>
       <c r="E962" s="24"/>
     </row>
     <row r="963" ht="24" customHeight="1">
       <c r="A963" s="34"/>
-      <c r="B963" s="34"/>
+      <c r="B963" s="24"/>
       <c r="C963" s="24"/>
       <c r="D963" s="24"/>
       <c r="E963" s="24"/>
     </row>
     <row r="964" ht="24" customHeight="1">
       <c r="A964" s="34"/>
-      <c r="B964" s="34"/>
+      <c r="B964" s="24"/>
       <c r="C964" s="24"/>
       <c r="D964" s="24"/>
       <c r="E964" s="24"/>
     </row>
     <row r="965" ht="24" customHeight="1">
       <c r="A965" s="34"/>
-      <c r="B965" s="34"/>
+      <c r="B965" s="24"/>
       <c r="C965" s="24"/>
       <c r="D965" s="24"/>
       <c r="E965" s="24"/>
     </row>
     <row r="966" ht="24" customHeight="1">
       <c r="A966" s="34"/>
-      <c r="B966" s="34"/>
+      <c r="B966" s="24"/>
       <c r="C966" s="24"/>
       <c r="D966" s="24"/>
       <c r="E966" s="24"/>
     </row>
     <row r="967" ht="24" customHeight="1">
       <c r="A967" s="34"/>
-      <c r="B967" s="34"/>
+      <c r="B967" s="24"/>
       <c r="C967" s="24"/>
       <c r="D967" s="24"/>
       <c r="E967" s="24"/>
     </row>
     <row r="968" ht="24" customHeight="1">
       <c r="A968" s="34"/>
-      <c r="B968" s="34"/>
+      <c r="B968" s="24"/>
       <c r="C968" s="24"/>
       <c r="D968" s="24"/>
       <c r="E968" s="24"/>
     </row>
     <row r="969" ht="24" customHeight="1">
       <c r="A969" s="34"/>
-      <c r="B969" s="34"/>
+      <c r="B969" s="24"/>
       <c r="C969" s="24"/>
       <c r="D969" s="24"/>
       <c r="E969" s="24"/>
     </row>
     <row r="970" ht="24" customHeight="1">
       <c r="A970" s="34"/>
-      <c r="B970" s="34"/>
+      <c r="B970" s="24"/>
       <c r="C970" s="24"/>
       <c r="D970" s="24"/>
       <c r="E970" s="24"/>
     </row>
     <row r="971" ht="24" customHeight="1">
       <c r="A971" s="34"/>
-      <c r="B971" s="34"/>
+      <c r="B971" s="24"/>
       <c r="C971" s="24"/>
       <c r="D971" s="24"/>
       <c r="E971" s="24"/>
     </row>
     <row r="972" ht="24" customHeight="1">
       <c r="A972" s="34"/>
-      <c r="B972" s="34"/>
+      <c r="B972" s="24"/>
       <c r="C972" s="24"/>
       <c r="D972" s="24"/>
       <c r="E972" s="24"/>
     </row>
     <row r="973" ht="24" customHeight="1">
       <c r="A973" s="34"/>
-      <c r="B973" s="34"/>
+      <c r="B973" s="24"/>
       <c r="C973" s="24"/>
       <c r="D973" s="24"/>
       <c r="E973" s="24"/>
     </row>
     <row r="974" ht="24" customHeight="1">
       <c r="A974" s="34"/>
-      <c r="B974" s="34"/>
+      <c r="B974" s="24"/>
       <c r="C974" s="24"/>
       <c r="D974" s="24"/>
       <c r="E974" s="24"/>
     </row>
     <row r="975" ht="24" customHeight="1">
       <c r="A975" s="34"/>
-      <c r="B975" s="34"/>
+      <c r="B975" s="24"/>
       <c r="C975" s="24"/>
       <c r="D975" s="24"/>
       <c r="E975" s="24"/>
     </row>
     <row r="976" ht="24" customHeight="1">
       <c r="A976" s="34"/>
-      <c r="B976" s="34"/>
+      <c r="B976" s="24"/>
       <c r="C976" s="24"/>
       <c r="D976" s="24"/>
       <c r="E976" s="24"/>
     </row>
     <row r="977" ht="24" customHeight="1">
       <c r="A977" s="34"/>
-      <c r="B977" s="34"/>
+      <c r="B977" s="24"/>
       <c r="C977" s="24"/>
       <c r="D977" s="24"/>
       <c r="E977" s="24"/>
     </row>
     <row r="978" ht="24" customHeight="1">
       <c r="A978" s="34"/>
-      <c r="B978" s="34"/>
+      <c r="B978" s="24"/>
       <c r="C978" s="24"/>
       <c r="D978" s="24"/>
       <c r="E978" s="24"/>
     </row>
     <row r="979" ht="24" customHeight="1">
       <c r="A979" s="34"/>
-      <c r="B979" s="34"/>
+      <c r="B979" s="24"/>
       <c r="C979" s="24"/>
       <c r="D979" s="24"/>
       <c r="E979" s="24"/>
     </row>
     <row r="980" ht="24" customHeight="1">
       <c r="A980" s="34"/>
-      <c r="B980" s="34"/>
+      <c r="B980" s="24"/>
       <c r="C980" s="24"/>
       <c r="D980" s="24"/>
       <c r="E980" s="24"/>
     </row>
     <row r="981" ht="24" customHeight="1">
       <c r="A981" s="34"/>
-      <c r="B981" s="34"/>
+      <c r="B981" s="24"/>
       <c r="C981" s="24"/>
       <c r="D981" s="24"/>
       <c r="E981" s="24"/>
     </row>
     <row r="982" ht="24" customHeight="1">
       <c r="A982" s="34"/>
-      <c r="B982" s="34"/>
+      <c r="B982" s="24"/>
       <c r="C982" s="24"/>
       <c r="D982" s="24"/>
       <c r="E982" s="24"/>
     </row>
     <row r="983" ht="24" customHeight="1">
       <c r="A983" s="34"/>
-      <c r="B983" s="34"/>
+      <c r="B983" s="24"/>
       <c r="C983" s="24"/>
       <c r="D983" s="24"/>
       <c r="E983" s="24"/>
     </row>
     <row r="984" ht="24" customHeight="1">
       <c r="A984" s="34"/>
-      <c r="B984" s="34"/>
+      <c r="B984" s="24"/>
       <c r="C984" s="24"/>
       <c r="D984" s="24"/>
       <c r="E984" s="24"/>
     </row>
     <row r="985" ht="24" customHeight="1">
       <c r="A985" s="34"/>
-      <c r="B985" s="34"/>
+      <c r="B985" s="24"/>
       <c r="C985" s="24"/>
       <c r="D985" s="24"/>
       <c r="E985" s="24"/>
     </row>
     <row r="986" ht="24" customHeight="1">
       <c r="A986" s="34"/>
-      <c r="B986" s="34"/>
+      <c r="B986" s="24"/>
       <c r="C986" s="24"/>
       <c r="D986" s="24"/>
       <c r="E986" s="24"/>
     </row>
     <row r="987" ht="24" customHeight="1">
       <c r="A987" s="34"/>
-      <c r="B987" s="34"/>
+      <c r="B987" s="24"/>
       <c r="C987" s="24"/>
       <c r="D987" s="24"/>
       <c r="E987" s="24"/>
     </row>
     <row r="988" ht="24" customHeight="1">
       <c r="A988" s="34"/>
-      <c r="B988" s="34"/>
+      <c r="B988" s="24"/>
       <c r="C988" s="24"/>
       <c r="D988" s="24"/>
       <c r="E988" s="24"/>
     </row>
     <row r="989" ht="24" customHeight="1">
       <c r="A989" s="34"/>
-      <c r="B989" s="34"/>
+      <c r="B989" s="24"/>
       <c r="C989" s="24"/>
       <c r="D989" s="24"/>
       <c r="E989" s="24"/>
     </row>
     <row r="990" ht="24" customHeight="1">
       <c r="A990" s="34"/>
-      <c r="B990" s="34"/>
+      <c r="B990" s="24"/>
       <c r="C990" s="24"/>
       <c r="D990" s="24"/>
       <c r="E990" s="24"/>
     </row>
     <row r="991" ht="24" customHeight="1">
       <c r="A991" s="34"/>
-      <c r="B991" s="34"/>
+      <c r="B991" s="24"/>
       <c r="C991" s="24"/>
       <c r="D991" s="24"/>
       <c r="E991" s="24"/>
     </row>
     <row r="992" ht="24" customHeight="1">
       <c r="A992" s="34"/>
-      <c r="B992" s="34"/>
+      <c r="B992" s="24"/>
       <c r="C992" s="24"/>
       <c r="D992" s="24"/>
       <c r="E992" s="24"/>
     </row>
     <row r="993" ht="24" customHeight="1">
       <c r="A993" s="34"/>
-      <c r="B993" s="34"/>
+      <c r="B993" s="24"/>
       <c r="C993" s="24"/>
       <c r="D993" s="24"/>
       <c r="E993" s="24"/>
     </row>
     <row r="994" ht="24" customHeight="1">
       <c r="A994" s="34"/>
-      <c r="B994" s="34"/>
+      <c r="B994" s="24"/>
       <c r="C994" s="24"/>
       <c r="D994" s="24"/>
       <c r="E994" s="24"/>
     </row>
     <row r="995" ht="24" customHeight="1">
       <c r="A995" s="34"/>
-      <c r="B995" s="34"/>
+      <c r="B995" s="24"/>
       <c r="C995" s="24"/>
       <c r="D995" s="24"/>
       <c r="E995" s="24"/>
     </row>
     <row r="996" ht="24" customHeight="1">
       <c r="A996" s="34"/>
-      <c r="B996" s="34"/>
+      <c r="B996" s="24"/>
       <c r="C996" s="24"/>
       <c r="D996" s="24"/>
       <c r="E996" s="24"/>
     </row>
     <row r="997" ht="24" customHeight="1">
       <c r="A997" s="34"/>
-      <c r="B997" s="34"/>
+      <c r="B997" s="24"/>
       <c r="C997" s="24"/>
       <c r="D997" s="24"/>
       <c r="E997" s="24"/>
     </row>
     <row r="998" ht="24" customHeight="1">
       <c r="A998" s="34"/>
-      <c r="B998" s="34"/>
+      <c r="B998" s="24"/>
       <c r="C998" s="24"/>
       <c r="D998" s="24"/>
       <c r="E998" s="24"/>
     </row>
     <row r="999" ht="24" customHeight="1">
       <c r="A999" s="34"/>
-      <c r="B999" s="34"/>
+      <c r="B999" s="24"/>
       <c r="C999" s="24"/>
       <c r="D999" s="24"/>
       <c r="E999" s="24"/>
     </row>
     <row r="1000" ht="24" customHeight="1">
       <c r="A1000" s="34"/>
-      <c r="B1000" s="34"/>
+      <c r="B1000" s="24"/>
       <c r="C1000" s="24"/>
       <c r="D1000" s="24"/>
       <c r="E1000" s="24"/>
     </row>
     <row r="1001" ht="24" customHeight="1">
       <c r="A1001" s="34"/>
-      <c r="B1001" s="34"/>
+      <c r="B1001" s="24"/>
       <c r="C1001" s="24"/>
       <c r="D1001" s="24"/>
       <c r="E1001" s="24"/>
     </row>
     <row r="1002" ht="24" customHeight="1">
       <c r="A1002" s="34"/>
-      <c r="B1002" s="34"/>
+      <c r="B1002" s="24"/>
       <c r="C1002" s="24"/>
       <c r="D1002" s="24"/>
       <c r="E1002" s="24"/>
     </row>
     <row r="1003" ht="24" customHeight="1">
       <c r="A1003" s="34"/>
-      <c r="B1003" s="34"/>
+      <c r="B1003" s="24"/>
       <c r="C1003" s="24"/>
       <c r="D1003" s="24"/>
       <c r="E1003" s="24"/>
     </row>
     <row r="1004" ht="24" customHeight="1">
       <c r="A1004" s="35"/>
-      <c r="B1004" s="35"/>
+      <c r="B1004" s="25"/>
       <c r="C1004" s="25"/>
       <c r="D1004" s="25"/>
       <c r="E1004" s="25"/>
@@ -20437,7 +20435,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29bf8c0bacfb463b"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23825de4df94a06"/>
   </tableParts>
 </worksheet>
 </file>
@@ -24485,7 +24483,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71b89f8f3b4d4319"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad79013afd7a4dd0"/>
   </tableParts>
 </worksheet>
 </file>
@@ -34578,7 +34576,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ea96d9e34e9495f"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19e3df1fd71f4bad"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45683,7 +45681,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fe9a638dc93436f"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5b0489cd8f24ba3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -49726,7 +49724,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff326025b2514f21"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f449b77dd014086"/>
   </tableParts>
 </worksheet>
 </file>
@@ -53769,7 +53767,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2043f24a556470e"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b6a9ebdd13d4fcb"/>
   </tableParts>
 </worksheet>
 </file>
--- a/public/templates/BOOKENDS_Seed_Template.xlsx
+++ b/public/templates/BOOKENDS_Seed_Template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" r:id="Rb270663088fe4ac0"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOMEs" sheetId="2" r:id="R763cce0d8d63448f"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="3" r:id="R6d15d8762c494235"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="4" r:id="R7771891d26674138"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="5" r:id="R8ff760d1f98f404e"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="6" r:id="R8557a19baef24cf6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagement roles" sheetId="7" r:id="R69c35f41658c4c22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" r:id="R64677503624e4ac5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="9" r:id="R78779d0338b74475"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" r:id="Ra3988a7b6edb400b"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOMEs" sheetId="2" r:id="Re8e02ba489494869"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="3" r:id="R3e4903c44d9e42f9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="4" r:id="Ra7cd01c7d5674967"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="5" r:id="R01eb76db0f014375"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagements" sheetId="6" r:id="R369fa98dfa7d424a"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagement roles" sheetId="7" r:id="R88e383c9734e4e10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" r:id="R488493d6beca4276"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="9" r:id="Rb82e6167246a4fc1"/>
   </sheets>
   <definedNames>
     <definedName name="BookendsHomeCodes">'HOMEs'!$A$5:$A$1004</definedName>
@@ -367,14 +367,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BookendsPeopleInputs" displayName="BookendsPeopleInputs" ref="A4:E1004" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:E1004"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BookendsPeopleInputs" displayName="BookendsPeopleInputs" ref="A4:F1004" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:F1004"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="Person name"/>
     <tableColumn id="2" name="HOME code"/>
     <tableColumn id="3" name="Owner name"/>
     <tableColumn id="4" name="Delivery roles"/>
     <tableColumn id="5" name="Skills"/>
+    <tableColumn id="6" name="Designation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -815,10 +816,10 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="7" t="str">
-        <v>Local setup</v>
+        <v>Workspace setup</v>
       </c>
       <c r="C16" s="18" t="str">
-        <v>Imports configure this browser workspace. They do not create sign-in accounts.</v>
+        <v>Imports update your workspace. They do not create sign-in accounts.</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
@@ -1169,10 +1170,10 @@
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="7" t="str">
-        <v>Optional columns</v>
+        <v>Designation / blanks</v>
       </c>
       <c r="C46" s="18" t="str">
-        <v>Other optional blanks clear values. Omit columns to keep them. Rename in Admin.</v>
+        <v>Impower or Contractor. Optional blanks clear values; omit columns to keep them.</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
@@ -6302,7 +6303,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b7b1caf77ad434f"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0af27d95e01847d4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13366,7 +13367,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b4dff126a946ce"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6da9736f7ec94525"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13383,6 +13384,7 @@
     <col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="43" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="37" customHeight="1">
@@ -13393,15 +13395,17 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="18" t="str">
-        <v>Only name is required. HOME and owner are optional. Separate delivery roles and skills with semicolons.</v>
+        <v>Only name is required. Designation: Impower or Contractor; blank means not set. Separate roles and skills with semicolons.</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" ht="10" customHeight="1">
       <c r="A3" s="3"/>
@@ -13409,6 +13413,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" s="32" t="str">
@@ -13423,8 +13428,11 @@
       <c r="D4" s="30" t="str">
         <v>Delivery roles</v>
       </c>
-      <c r="E4" s="31" t="str">
+      <c r="E4" s="30" t="str">
         <v>Skills</v>
+      </c>
+      <c r="F4" s="31" t="str">
+        <v>Designation</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -13433,6 +13441,7 @@
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="34"/>
@@ -13440,6 +13449,7 @@
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="34"/>
@@ -13447,6 +13457,7 @@
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
       <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="34"/>
@@ -13454,6 +13465,7 @@
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
       <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="34"/>
@@ -13461,6 +13473,7 @@
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
       <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="34"/>
@@ -13468,6 +13481,7 @@
       <c r="C10" s="24"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="34"/>
@@ -13475,6 +13489,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
       <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="34"/>
@@ -13482,6 +13497,7 @@
       <c r="C12" s="24"/>
       <c r="D12" s="24"/>
       <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="34"/>
@@ -13489,6 +13505,7 @@
       <c r="C13" s="24"/>
       <c r="D13" s="24"/>
       <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="34"/>
@@ -13496,6 +13513,7 @@
       <c r="C14" s="24"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="34"/>
@@ -13503,6 +13521,7 @@
       <c r="C15" s="24"/>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="34"/>
@@ -13510,6 +13529,7 @@
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="34"/>
@@ -13517,6 +13537,7 @@
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="34"/>
@@ -13524,6 +13545,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="34"/>
@@ -13531,6 +13553,7 @@
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="34"/>
@@ -13538,6 +13561,7 @@
       <c r="C20" s="24"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="34"/>
@@ -13545,6 +13569,7 @@
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="34"/>
@@ -13552,6 +13577,7 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="34"/>
@@ -13559,6 +13585,7 @@
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
       <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="34"/>
@@ -13566,6 +13593,7 @@
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="34"/>
@@ -13573,6 +13601,7 @@
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="34"/>
@@ -13580,6 +13609,7 @@
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="34"/>
@@ -13587,6 +13617,7 @@
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="34"/>
@@ -13594,6 +13625,7 @@
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="34"/>
@@ -13601,6 +13633,7 @@
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
       <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="34"/>
@@ -13608,6 +13641,7 @@
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
       <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="34"/>
@@ -13615,6 +13649,7 @@
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="34"/>
@@ -13622,6 +13657,7 @@
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="34"/>
@@ -13629,6 +13665,7 @@
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="34"/>
@@ -13636,6 +13673,7 @@
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="34"/>
@@ -13643,6 +13681,7 @@
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="34"/>
@@ -13650,6 +13689,7 @@
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
       <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="34"/>
@@ -13657,6 +13697,7 @@
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="34"/>
@@ -13664,6 +13705,7 @@
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
       <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="34"/>
@@ -13671,6 +13713,7 @@
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="34"/>
@@ -13678,6 +13721,7 @@
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="34"/>
@@ -13685,6 +13729,7 @@
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="34"/>
@@ -13692,6 +13737,7 @@
       <c r="C42" s="24"/>
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="34"/>
@@ -13699,6 +13745,7 @@
       <c r="C43" s="24"/>
       <c r="D43" s="24"/>
       <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="34"/>
@@ -13706,6 +13753,7 @@
       <c r="C44" s="24"/>
       <c r="D44" s="24"/>
       <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="34"/>
@@ -13713,6 +13761,7 @@
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
       <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="34"/>
@@ -13720,6 +13769,7 @@
       <c r="C46" s="24"/>
       <c r="D46" s="24"/>
       <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="34"/>
@@ -13727,6 +13777,7 @@
       <c r="C47" s="24"/>
       <c r="D47" s="24"/>
       <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="34"/>
@@ -13734,6 +13785,7 @@
       <c r="C48" s="24"/>
       <c r="D48" s="24"/>
       <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="34"/>
@@ -13741,6 +13793,7 @@
       <c r="C49" s="24"/>
       <c r="D49" s="24"/>
       <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="34"/>
@@ -13748,6 +13801,7 @@
       <c r="C50" s="24"/>
       <c r="D50" s="24"/>
       <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="34"/>
@@ -13755,6 +13809,7 @@
       <c r="C51" s="24"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="34"/>
@@ -13762,6 +13817,7 @@
       <c r="C52" s="24"/>
       <c r="D52" s="24"/>
       <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="34"/>
@@ -13769,6 +13825,7 @@
       <c r="C53" s="24"/>
       <c r="D53" s="24"/>
       <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="34"/>
@@ -13776,6 +13833,7 @@
       <c r="C54" s="24"/>
       <c r="D54" s="24"/>
       <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="34"/>
@@ -13783,6 +13841,7 @@
       <c r="C55" s="24"/>
       <c r="D55" s="24"/>
       <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="34"/>
@@ -13790,6 +13849,7 @@
       <c r="C56" s="24"/>
       <c r="D56" s="24"/>
       <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="34"/>
@@ -13797,6 +13857,7 @@
       <c r="C57" s="24"/>
       <c r="D57" s="24"/>
       <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="34"/>
@@ -13804,6 +13865,7 @@
       <c r="C58" s="24"/>
       <c r="D58" s="24"/>
       <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="34"/>
@@ -13811,6 +13873,7 @@
       <c r="C59" s="24"/>
       <c r="D59" s="24"/>
       <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="34"/>
@@ -13818,6 +13881,7 @@
       <c r="C60" s="24"/>
       <c r="D60" s="24"/>
       <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="34"/>
@@ -13825,6 +13889,7 @@
       <c r="C61" s="24"/>
       <c r="D61" s="24"/>
       <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="34"/>
@@ -13832,6 +13897,7 @@
       <c r="C62" s="24"/>
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="34"/>
@@ -13839,6 +13905,7 @@
       <c r="C63" s="24"/>
       <c r="D63" s="24"/>
       <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="34"/>
@@ -13846,6 +13913,7 @@
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
       <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="34"/>
@@ -13853,6 +13921,7 @@
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
       <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="34"/>
@@ -13860,6 +13929,7 @@
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
       <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="34"/>
@@ -13867,6 +13937,7 @@
       <c r="C67" s="24"/>
       <c r="D67" s="24"/>
       <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="34"/>
@@ -13874,6 +13945,7 @@
       <c r="C68" s="24"/>
       <c r="D68" s="24"/>
       <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="34"/>
@@ -13881,6 +13953,7 @@
       <c r="C69" s="24"/>
       <c r="D69" s="24"/>
       <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="34"/>
@@ -13888,6 +13961,7 @@
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
       <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="34"/>
@@ -13895,6 +13969,7 @@
       <c r="C71" s="24"/>
       <c r="D71" s="24"/>
       <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="34"/>
@@ -13902,6 +13977,7 @@
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
       <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="34"/>
@@ -13909,6 +13985,7 @@
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
       <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="34"/>
@@ -13916,6 +13993,7 @@
       <c r="C74" s="24"/>
       <c r="D74" s="24"/>
       <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="34"/>
@@ -13923,6 +14001,7 @@
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
       <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="34"/>
@@ -13930,6 +14009,7 @@
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
       <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="34"/>
@@ -13937,6 +14017,7 @@
       <c r="C77" s="24"/>
       <c r="D77" s="24"/>
       <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="34"/>
@@ -13944,6 +14025,7 @@
       <c r="C78" s="24"/>
       <c r="D78" s="24"/>
       <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="34"/>
@@ -13951,6 +14033,7 @@
       <c r="C79" s="24"/>
       <c r="D79" s="24"/>
       <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="34"/>
@@ -13958,6 +14041,7 @@
       <c r="C80" s="24"/>
       <c r="D80" s="24"/>
       <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="34"/>
@@ -13965,6 +14049,7 @@
       <c r="C81" s="24"/>
       <c r="D81" s="24"/>
       <c r="E81" s="24"/>
+      <c r="F81" s="24"/>
     </row>
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="34"/>
@@ -13972,6 +14057,7 @@
       <c r="C82" s="24"/>
       <c r="D82" s="24"/>
       <c r="E82" s="24"/>
+      <c r="F82" s="24"/>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="34"/>
@@ -13979,6 +14065,7 @@
       <c r="C83" s="24"/>
       <c r="D83" s="24"/>
       <c r="E83" s="24"/>
+      <c r="F83" s="24"/>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="34"/>
@@ -13986,6 +14073,7 @@
       <c r="C84" s="24"/>
       <c r="D84" s="24"/>
       <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="34"/>
@@ -13993,6 +14081,7 @@
       <c r="C85" s="24"/>
       <c r="D85" s="24"/>
       <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
     </row>
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="34"/>
@@ -14000,6 +14089,7 @@
       <c r="C86" s="24"/>
       <c r="D86" s="24"/>
       <c r="E86" s="24"/>
+      <c r="F86" s="24"/>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="34"/>
@@ -14007,6 +14097,7 @@
       <c r="C87" s="24"/>
       <c r="D87" s="24"/>
       <c r="E87" s="24"/>
+      <c r="F87" s="24"/>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="34"/>
@@ -14014,6 +14105,7 @@
       <c r="C88" s="24"/>
       <c r="D88" s="24"/>
       <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="34"/>
@@ -14021,6 +14113,7 @@
       <c r="C89" s="24"/>
       <c r="D89" s="24"/>
       <c r="E89" s="24"/>
+      <c r="F89" s="24"/>
     </row>
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="34"/>
@@ -14028,6 +14121,7 @@
       <c r="C90" s="24"/>
       <c r="D90" s="24"/>
       <c r="E90" s="24"/>
+      <c r="F90" s="24"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="34"/>
@@ -14035,6 +14129,7 @@
       <c r="C91" s="24"/>
       <c r="D91" s="24"/>
       <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="34"/>
@@ -14042,6 +14137,7 @@
       <c r="C92" s="24"/>
       <c r="D92" s="24"/>
       <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="34"/>
@@ -14049,6 +14145,7 @@
       <c r="C93" s="24"/>
       <c r="D93" s="24"/>
       <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="34"/>
@@ -14056,6 +14153,7 @@
       <c r="C94" s="24"/>
       <c r="D94" s="24"/>
       <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="34"/>
@@ -14063,6 +14161,7 @@
       <c r="C95" s="24"/>
       <c r="D95" s="24"/>
       <c r="E95" s="24"/>
+      <c r="F95" s="24"/>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="34"/>
@@ -14070,6 +14169,7 @@
       <c r="C96" s="24"/>
       <c r="D96" s="24"/>
       <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="34"/>
@@ -14077,6 +14177,7 @@
       <c r="C97" s="24"/>
       <c r="D97" s="24"/>
       <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="34"/>
@@ -14084,6 +14185,7 @@
       <c r="C98" s="24"/>
       <c r="D98" s="24"/>
       <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="34"/>
@@ -14091,6 +14193,7 @@
       <c r="C99" s="24"/>
       <c r="D99" s="24"/>
       <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="34"/>
@@ -14098,6 +14201,7 @@
       <c r="C100" s="24"/>
       <c r="D100" s="24"/>
       <c r="E100" s="24"/>
+      <c r="F100" s="24"/>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="34"/>
@@ -14105,6 +14209,7 @@
       <c r="C101" s="24"/>
       <c r="D101" s="24"/>
       <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="34"/>
@@ -14112,6 +14217,7 @@
       <c r="C102" s="24"/>
       <c r="D102" s="24"/>
       <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="34"/>
@@ -14119,6 +14225,7 @@
       <c r="C103" s="24"/>
       <c r="D103" s="24"/>
       <c r="E103" s="24"/>
+      <c r="F103" s="24"/>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="34"/>
@@ -14126,6 +14233,7 @@
       <c r="C104" s="24"/>
       <c r="D104" s="24"/>
       <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="34"/>
@@ -14133,6 +14241,7 @@
       <c r="C105" s="24"/>
       <c r="D105" s="24"/>
       <c r="E105" s="24"/>
+      <c r="F105" s="24"/>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="34"/>
@@ -14140,6 +14249,7 @@
       <c r="C106" s="24"/>
       <c r="D106" s="24"/>
       <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="34"/>
@@ -14147,6 +14257,7 @@
       <c r="C107" s="24"/>
       <c r="D107" s="24"/>
       <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="34"/>
@@ -14154,6 +14265,7 @@
       <c r="C108" s="24"/>
       <c r="D108" s="24"/>
       <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="34"/>
@@ -14161,6 +14273,7 @@
       <c r="C109" s="24"/>
       <c r="D109" s="24"/>
       <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="34"/>
@@ -14168,6 +14281,7 @@
       <c r="C110" s="24"/>
       <c r="D110" s="24"/>
       <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="34"/>
@@ -14175,6 +14289,7 @@
       <c r="C111" s="24"/>
       <c r="D111" s="24"/>
       <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="34"/>
@@ -14182,6 +14297,7 @@
       <c r="C112" s="24"/>
       <c r="D112" s="24"/>
       <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="34"/>
@@ -14189,6 +14305,7 @@
       <c r="C113" s="24"/>
       <c r="D113" s="24"/>
       <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="34"/>
@@ -14196,6 +14313,7 @@
       <c r="C114" s="24"/>
       <c r="D114" s="24"/>
       <c r="E114" s="24"/>
+      <c r="F114" s="24"/>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="34"/>
@@ -14203,6 +14321,7 @@
       <c r="C115" s="24"/>
       <c r="D115" s="24"/>
       <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="34"/>
@@ -14210,6 +14329,7 @@
       <c r="C116" s="24"/>
       <c r="D116" s="24"/>
       <c r="E116" s="24"/>
+      <c r="F116" s="24"/>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="34"/>
@@ -14217,6 +14337,7 @@
       <c r="C117" s="24"/>
       <c r="D117" s="24"/>
       <c r="E117" s="24"/>
+      <c r="F117" s="24"/>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="34"/>
@@ -14224,6 +14345,7 @@
       <c r="C118" s="24"/>
       <c r="D118" s="24"/>
       <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="34"/>
@@ -14231,6 +14353,7 @@
       <c r="C119" s="24"/>
       <c r="D119" s="24"/>
       <c r="E119" s="24"/>
+      <c r="F119" s="24"/>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="34"/>
@@ -14238,6 +14361,7 @@
       <c r="C120" s="24"/>
       <c r="D120" s="24"/>
       <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="34"/>
@@ -14245,6 +14369,7 @@
       <c r="C121" s="24"/>
       <c r="D121" s="24"/>
       <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="34"/>
@@ -14252,6 +14377,7 @@
       <c r="C122" s="24"/>
       <c r="D122" s="24"/>
       <c r="E122" s="24"/>
+      <c r="F122" s="24"/>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="34"/>
@@ -14259,6 +14385,7 @@
       <c r="C123" s="24"/>
       <c r="D123" s="24"/>
       <c r="E123" s="24"/>
+      <c r="F123" s="24"/>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="34"/>
@@ -14266,6 +14393,7 @@
       <c r="C124" s="24"/>
       <c r="D124" s="24"/>
       <c r="E124" s="24"/>
+      <c r="F124" s="24"/>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="34"/>
@@ -14273,6 +14401,7 @@
       <c r="C125" s="24"/>
       <c r="D125" s="24"/>
       <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="34"/>
@@ -14280,6 +14409,7 @@
       <c r="C126" s="24"/>
       <c r="D126" s="24"/>
       <c r="E126" s="24"/>
+      <c r="F126" s="24"/>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="34"/>
@@ -14287,6 +14417,7 @@
       <c r="C127" s="24"/>
       <c r="D127" s="24"/>
       <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="34"/>
@@ -14294,6 +14425,7 @@
       <c r="C128" s="24"/>
       <c r="D128" s="24"/>
       <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="34"/>
@@ -14301,6 +14433,7 @@
       <c r="C129" s="24"/>
       <c r="D129" s="24"/>
       <c r="E129" s="24"/>
+      <c r="F129" s="24"/>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="34"/>
@@ -14308,6 +14441,7 @@
       <c r="C130" s="24"/>
       <c r="D130" s="24"/>
       <c r="E130" s="24"/>
+      <c r="F130" s="24"/>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="34"/>
@@ -14315,6 +14449,7 @@
       <c r="C131" s="24"/>
       <c r="D131" s="24"/>
       <c r="E131" s="24"/>
+      <c r="F131" s="24"/>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="34"/>
@@ -14322,6 +14457,7 @@
       <c r="C132" s="24"/>
       <c r="D132" s="24"/>
       <c r="E132" s="24"/>
+      <c r="F132" s="24"/>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="34"/>
@@ -14329,6 +14465,7 @@
       <c r="C133" s="24"/>
       <c r="D133" s="24"/>
       <c r="E133" s="24"/>
+      <c r="F133" s="24"/>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="34"/>
@@ -14336,6 +14473,7 @@
       <c r="C134" s="24"/>
       <c r="D134" s="24"/>
       <c r="E134" s="24"/>
+      <c r="F134" s="24"/>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="34"/>
@@ -14343,6 +14481,7 @@
       <c r="C135" s="24"/>
       <c r="D135" s="24"/>
       <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="34"/>
@@ -14350,6 +14489,7 @@
       <c r="C136" s="24"/>
       <c r="D136" s="24"/>
       <c r="E136" s="24"/>
+      <c r="F136" s="24"/>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="34"/>
@@ -14357,6 +14497,7 @@
       <c r="C137" s="24"/>
       <c r="D137" s="24"/>
       <c r="E137" s="24"/>
+      <c r="F137" s="24"/>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="34"/>
@@ -14364,6 +14505,7 @@
       <c r="C138" s="24"/>
       <c r="D138" s="24"/>
       <c r="E138" s="24"/>
+      <c r="F138" s="24"/>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="34"/>
@@ -14371,6 +14513,7 @@
       <c r="C139" s="24"/>
       <c r="D139" s="24"/>
       <c r="E139" s="24"/>
+      <c r="F139" s="24"/>
     </row>
     <row r="140" ht="24" customHeight="1">
       <c r="A140" s="34"/>
@@ -14378,6 +14521,7 @@
       <c r="C140" s="24"/>
       <c r="D140" s="24"/>
       <c r="E140" s="24"/>
+      <c r="F140" s="24"/>
     </row>
     <row r="141" ht="24" customHeight="1">
       <c r="A141" s="34"/>
@@ -14385,6 +14529,7 @@
       <c r="C141" s="24"/>
       <c r="D141" s="24"/>
       <c r="E141" s="24"/>
+      <c r="F141" s="24"/>
     </row>
     <row r="142" ht="24" customHeight="1">
       <c r="A142" s="34"/>
@@ -14392,6 +14537,7 @@
       <c r="C142" s="24"/>
       <c r="D142" s="24"/>
       <c r="E142" s="24"/>
+      <c r="F142" s="24"/>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="34"/>
@@ -14399,6 +14545,7 @@
       <c r="C143" s="24"/>
       <c r="D143" s="24"/>
       <c r="E143" s="24"/>
+      <c r="F143" s="24"/>
     </row>
     <row r="144" ht="24" customHeight="1">
       <c r="A144" s="34"/>
@@ -14406,6 +14553,7 @@
       <c r="C144" s="24"/>
       <c r="D144" s="24"/>
       <c r="E144" s="24"/>
+      <c r="F144" s="24"/>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="34"/>
@@ -14413,6 +14561,7 @@
       <c r="C145" s="24"/>
       <c r="D145" s="24"/>
       <c r="E145" s="24"/>
+      <c r="F145" s="24"/>
     </row>
     <row r="146" ht="24" customHeight="1">
       <c r="A146" s="34"/>
@@ -14420,6 +14569,7 @@
       <c r="C146" s="24"/>
       <c r="D146" s="24"/>
       <c r="E146" s="24"/>
+      <c r="F146" s="24"/>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="34"/>
@@ -14427,6 +14577,7 @@
       <c r="C147" s="24"/>
       <c r="D147" s="24"/>
       <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
     </row>
     <row r="148" ht="24" customHeight="1">
       <c r="A148" s="34"/>
@@ -14434,6 +14585,7 @@
       <c r="C148" s="24"/>
       <c r="D148" s="24"/>
       <c r="E148" s="24"/>
+      <c r="F148" s="24"/>
     </row>
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="34"/>
@@ -14441,6 +14593,7 @@
       <c r="C149" s="24"/>
       <c r="D149" s="24"/>
       <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
     </row>
     <row r="150" ht="24" customHeight="1">
       <c r="A150" s="34"/>
@@ -14448,6 +14601,7 @@
       <c r="C150" s="24"/>
       <c r="D150" s="24"/>
       <c r="E150" s="24"/>
+      <c r="F150" s="24"/>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="34"/>
@@ -14455,6 +14609,7 @@
       <c r="C151" s="24"/>
       <c r="D151" s="24"/>
       <c r="E151" s="24"/>
+      <c r="F151" s="24"/>
     </row>
     <row r="152" ht="24" customHeight="1">
       <c r="A152" s="34"/>
@@ -14462,6 +14617,7 @@
       <c r="C152" s="24"/>
       <c r="D152" s="24"/>
       <c r="E152" s="24"/>
+      <c r="F152" s="24"/>
     </row>
     <row r="153" ht="24" customHeight="1">
       <c r="A153" s="34"/>
@@ -14469,6 +14625,7 @@
       <c r="C153" s="24"/>
       <c r="D153" s="24"/>
       <c r="E153" s="24"/>
+      <c r="F153" s="24"/>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="34"/>
@@ -14476,6 +14633,7 @@
       <c r="C154" s="24"/>
       <c r="D154" s="24"/>
       <c r="E154" s="24"/>
+      <c r="F154" s="24"/>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="34"/>
@@ -14483,6 +14641,7 @@
       <c r="C155" s="24"/>
       <c r="D155" s="24"/>
       <c r="E155" s="24"/>
+      <c r="F155" s="24"/>
     </row>
     <row r="156" ht="24" customHeight="1">
       <c r="A156" s="34"/>
@@ -14490,6 +14649,7 @@
       <c r="C156" s="24"/>
       <c r="D156" s="24"/>
       <c r="E156" s="24"/>
+      <c r="F156" s="24"/>
     </row>
     <row r="157" ht="24" customHeight="1">
       <c r="A157" s="34"/>
@@ -14497,6 +14657,7 @@
       <c r="C157" s="24"/>
       <c r="D157" s="24"/>
       <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
     </row>
     <row r="158" ht="24" customHeight="1">
       <c r="A158" s="34"/>
@@ -14504,6 +14665,7 @@
       <c r="C158" s="24"/>
       <c r="D158" s="24"/>
       <c r="E158" s="24"/>
+      <c r="F158" s="24"/>
     </row>
     <row r="159" ht="24" customHeight="1">
       <c r="A159" s="34"/>
@@ -14511,6 +14673,7 @@
       <c r="C159" s="24"/>
       <c r="D159" s="24"/>
       <c r="E159" s="24"/>
+      <c r="F159" s="24"/>
     </row>
     <row r="160" ht="24" customHeight="1">
       <c r="A160" s="34"/>
@@ -14518,6 +14681,7 @@
       <c r="C160" s="24"/>
       <c r="D160" s="24"/>
       <c r="E160" s="24"/>
+      <c r="F160" s="24"/>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="34"/>
@@ -14525,6 +14689,7 @@
       <c r="C161" s="24"/>
       <c r="D161" s="24"/>
       <c r="E161" s="24"/>
+      <c r="F161" s="24"/>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="34"/>
@@ -14532,6 +14697,7 @@
       <c r="C162" s="24"/>
       <c r="D162" s="24"/>
       <c r="E162" s="24"/>
+      <c r="F162" s="24"/>
     </row>
     <row r="163" ht="24" customHeight="1">
       <c r="A163" s="34"/>
@@ -14539,6 +14705,7 @@
       <c r="C163" s="24"/>
       <c r="D163" s="24"/>
       <c r="E163" s="24"/>
+      <c r="F163" s="24"/>
     </row>
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="34"/>
@@ -14546,6 +14713,7 @@
       <c r="C164" s="24"/>
       <c r="D164" s="24"/>
       <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="34"/>
@@ -14553,6 +14721,7 @@
       <c r="C165" s="24"/>
       <c r="D165" s="24"/>
       <c r="E165" s="24"/>
+      <c r="F165" s="24"/>
     </row>
     <row r="166" ht="24" customHeight="1">
       <c r="A166" s="34"/>
@@ -14560,6 +14729,7 @@
       <c r="C166" s="24"/>
       <c r="D166" s="24"/>
       <c r="E166" s="24"/>
+      <c r="F166" s="24"/>
     </row>
     <row r="167" ht="24" customHeight="1">
       <c r="A167" s="34"/>
@@ -14567,6 +14737,7 @@
       <c r="C167" s="24"/>
       <c r="D167" s="24"/>
       <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
     </row>
     <row r="168" ht="24" customHeight="1">
       <c r="A168" s="34"/>
@@ -14574,6 +14745,7 @@
       <c r="C168" s="24"/>
       <c r="D168" s="24"/>
       <c r="E168" s="24"/>
+      <c r="F168" s="24"/>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="34"/>
@@ -14581,6 +14753,7 @@
       <c r="C169" s="24"/>
       <c r="D169" s="24"/>
       <c r="E169" s="24"/>
+      <c r="F169" s="24"/>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="34"/>
@@ -14588,6 +14761,7 @@
       <c r="C170" s="24"/>
       <c r="D170" s="24"/>
       <c r="E170" s="24"/>
+      <c r="F170" s="24"/>
     </row>
     <row r="171" ht="24" customHeight="1">
       <c r="A171" s="34"/>
@@ -14595,6 +14769,7 @@
       <c r="C171" s="24"/>
       <c r="D171" s="24"/>
       <c r="E171" s="24"/>
+      <c r="F171" s="24"/>
     </row>
     <row r="172" ht="24" customHeight="1">
       <c r="A172" s="34"/>
@@ -14602,6 +14777,7 @@
       <c r="C172" s="24"/>
       <c r="D172" s="24"/>
       <c r="E172" s="24"/>
+      <c r="F172" s="24"/>
     </row>
     <row r="173" ht="24" customHeight="1">
       <c r="A173" s="34"/>
@@ -14609,6 +14785,7 @@
       <c r="C173" s="24"/>
       <c r="D173" s="24"/>
       <c r="E173" s="24"/>
+      <c r="F173" s="24"/>
     </row>
     <row r="174" ht="24" customHeight="1">
       <c r="A174" s="34"/>
@@ -14616,6 +14793,7 @@
       <c r="C174" s="24"/>
       <c r="D174" s="24"/>
       <c r="E174" s="24"/>
+      <c r="F174" s="24"/>
     </row>
     <row r="175" ht="24" customHeight="1">
       <c r="A175" s="34"/>
@@ -14623,6 +14801,7 @@
       <c r="C175" s="24"/>
       <c r="D175" s="24"/>
       <c r="E175" s="24"/>
+      <c r="F175" s="24"/>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="34"/>
@@ -14630,6 +14809,7 @@
       <c r="C176" s="24"/>
       <c r="D176" s="24"/>
       <c r="E176" s="24"/>
+      <c r="F176" s="24"/>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="34"/>
@@ -14637,6 +14817,7 @@
       <c r="C177" s="24"/>
       <c r="D177" s="24"/>
       <c r="E177" s="24"/>
+      <c r="F177" s="24"/>
     </row>
     <row r="178" ht="24" customHeight="1">
       <c r="A178" s="34"/>
@@ -14644,6 +14825,7 @@
       <c r="C178" s="24"/>
       <c r="D178" s="24"/>
       <c r="E178" s="24"/>
+      <c r="F178" s="24"/>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="34"/>
@@ -14651,6 +14833,7 @@
       <c r="C179" s="24"/>
       <c r="D179" s="24"/>
       <c r="E179" s="24"/>
+      <c r="F179" s="24"/>
     </row>
     <row r="180" ht="24" customHeight="1">
       <c r="A180" s="34"/>
@@ -14658,6 +14841,7 @@
       <c r="C180" s="24"/>
       <c r="D180" s="24"/>
       <c r="E180" s="24"/>
+      <c r="F180" s="24"/>
     </row>
     <row r="181" ht="24" customHeight="1">
       <c r="A181" s="34"/>
@@ -14665,6 +14849,7 @@
       <c r="C181" s="24"/>
       <c r="D181" s="24"/>
       <c r="E181" s="24"/>
+      <c r="F181" s="24"/>
     </row>
     <row r="182" ht="24" customHeight="1">
       <c r="A182" s="34"/>
@@ -14672,6 +14857,7 @@
       <c r="C182" s="24"/>
       <c r="D182" s="24"/>
       <c r="E182" s="24"/>
+      <c r="F182" s="24"/>
     </row>
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="34"/>
@@ -14679,6 +14865,7 @@
       <c r="C183" s="24"/>
       <c r="D183" s="24"/>
       <c r="E183" s="24"/>
+      <c r="F183" s="24"/>
     </row>
     <row r="184" ht="24" customHeight="1">
       <c r="A184" s="34"/>
@@ -14686,6 +14873,7 @@
       <c r="C184" s="24"/>
       <c r="D184" s="24"/>
       <c r="E184" s="24"/>
+      <c r="F184" s="24"/>
     </row>
     <row r="185" ht="24" customHeight="1">
       <c r="A185" s="34"/>
@@ -14693,6 +14881,7 @@
       <c r="C185" s="24"/>
       <c r="D185" s="24"/>
       <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
     </row>
     <row r="186" ht="24" customHeight="1">
       <c r="A186" s="34"/>
@@ -14700,6 +14889,7 @@
       <c r="C186" s="24"/>
       <c r="D186" s="24"/>
       <c r="E186" s="24"/>
+      <c r="F186" s="24"/>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="34"/>
@@ -14707,6 +14897,7 @@
       <c r="C187" s="24"/>
       <c r="D187" s="24"/>
       <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
     </row>
     <row r="188" ht="24" customHeight="1">
       <c r="A188" s="34"/>
@@ -14714,6 +14905,7 @@
       <c r="C188" s="24"/>
       <c r="D188" s="24"/>
       <c r="E188" s="24"/>
+      <c r="F188" s="24"/>
     </row>
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="34"/>
@@ -14721,6 +14913,7 @@
       <c r="C189" s="24"/>
       <c r="D189" s="24"/>
       <c r="E189" s="24"/>
+      <c r="F189" s="24"/>
     </row>
     <row r="190" ht="24" customHeight="1">
       <c r="A190" s="34"/>
@@ -14728,6 +14921,7 @@
       <c r="C190" s="24"/>
       <c r="D190" s="24"/>
       <c r="E190" s="24"/>
+      <c r="F190" s="24"/>
     </row>
     <row r="191" ht="24" customHeight="1">
       <c r="A191" s="34"/>
@@ -14735,6 +14929,7 @@
       <c r="C191" s="24"/>
       <c r="D191" s="24"/>
       <c r="E191" s="24"/>
+      <c r="F191" s="24"/>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="34"/>
@@ -14742,6 +14937,7 @@
       <c r="C192" s="24"/>
       <c r="D192" s="24"/>
       <c r="E192" s="24"/>
+      <c r="F192" s="24"/>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="34"/>
@@ -14749,6 +14945,7 @@
       <c r="C193" s="24"/>
       <c r="D193" s="24"/>
       <c r="E193" s="24"/>
+      <c r="F193" s="24"/>
     </row>
     <row r="194" ht="24" customHeight="1">
       <c r="A194" s="34"/>
@@ -14756,6 +14953,7 @@
       <c r="C194" s="24"/>
       <c r="D194" s="24"/>
       <c r="E194" s="24"/>
+      <c r="F194" s="24"/>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="34"/>
@@ -14763,6 +14961,7 @@
       <c r="C195" s="24"/>
       <c r="D195" s="24"/>
       <c r="E195" s="24"/>
+      <c r="F195" s="24"/>
     </row>
     <row r="196" ht="24" customHeight="1">
       <c r="A196" s="34"/>
@@ -14770,6 +14969,7 @@
       <c r="C196" s="24"/>
       <c r="D196" s="24"/>
       <c r="E196" s="24"/>
+      <c r="F196" s="24"/>
     </row>
     <row r="197" ht="24" customHeight="1">
       <c r="A197" s="34"/>
@@ -14777,6 +14977,7 @@
       <c r="C197" s="24"/>
       <c r="D197" s="24"/>
       <c r="E197" s="24"/>
+      <c r="F197" s="24"/>
     </row>
     <row r="198" ht="24" customHeight="1">
       <c r="A198" s="34"/>
@@ -14784,6 +14985,7 @@
       <c r="C198" s="24"/>
       <c r="D198" s="24"/>
       <c r="E198" s="24"/>
+      <c r="F198" s="24"/>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="34"/>
@@ -14791,6 +14993,7 @@
       <c r="C199" s="24"/>
       <c r="D199" s="24"/>
       <c r="E199" s="24"/>
+      <c r="F199" s="24"/>
     </row>
     <row r="200" ht="24" customHeight="1">
       <c r="A200" s="34"/>
@@ -14798,6 +15001,7 @@
       <c r="C200" s="24"/>
       <c r="D200" s="24"/>
       <c r="E200" s="24"/>
+      <c r="F200" s="24"/>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="34"/>
@@ -14805,6 +15009,7 @@
       <c r="C201" s="24"/>
       <c r="D201" s="24"/>
       <c r="E201" s="24"/>
+      <c r="F201" s="24"/>
     </row>
     <row r="202" ht="24" customHeight="1">
       <c r="A202" s="34"/>
@@ -14812,6 +15017,7 @@
       <c r="C202" s="24"/>
       <c r="D202" s="24"/>
       <c r="E202" s="24"/>
+      <c r="F202" s="24"/>
     </row>
     <row r="203" ht="24" customHeight="1">
       <c r="A203" s="34"/>
@@ -14819,6 +15025,7 @@
       <c r="C203" s="24"/>
       <c r="D203" s="24"/>
       <c r="E203" s="24"/>
+      <c r="F203" s="24"/>
     </row>
     <row r="204" ht="24" customHeight="1">
       <c r="A204" s="34"/>
@@ -14826,6 +15033,7 @@
       <c r="C204" s="24"/>
       <c r="D204" s="24"/>
       <c r="E204" s="24"/>
+      <c r="F204" s="24"/>
     </row>
     <row r="205" ht="24" customHeight="1">
       <c r="A205" s="34"/>
@@ -14833,6 +15041,7 @@
       <c r="C205" s="24"/>
       <c r="D205" s="24"/>
       <c r="E205" s="24"/>
+      <c r="F205" s="24"/>
     </row>
     <row r="206" ht="24" customHeight="1">
       <c r="A206" s="34"/>
@@ -14840,6 +15049,7 @@
       <c r="C206" s="24"/>
       <c r="D206" s="24"/>
       <c r="E206" s="24"/>
+      <c r="F206" s="24"/>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="34"/>
@@ -14847,6 +15057,7 @@
       <c r="C207" s="24"/>
       <c r="D207" s="24"/>
       <c r="E207" s="24"/>
+      <c r="F207" s="24"/>
     </row>
     <row r="208" ht="24" customHeight="1">
       <c r="A208" s="34"/>
@@ -14854,6 +15065,7 @@
       <c r="C208" s="24"/>
       <c r="D208" s="24"/>
       <c r="E208" s="24"/>
+      <c r="F208" s="24"/>
     </row>
     <row r="209" ht="24" customHeight="1">
       <c r="A209" s="34"/>
@@ -14861,6 +15073,7 @@
       <c r="C209" s="24"/>
       <c r="D209" s="24"/>
       <c r="E209" s="24"/>
+      <c r="F209" s="24"/>
     </row>
     <row r="210" ht="24" customHeight="1">
       <c r="A210" s="34"/>
@@ -14868,6 +15081,7 @@
       <c r="C210" s="24"/>
       <c r="D210" s="24"/>
       <c r="E210" s="24"/>
+      <c r="F210" s="24"/>
     </row>
     <row r="211" ht="24" customHeight="1">
       <c r="A211" s="34"/>
@@ -14875,6 +15089,7 @@
       <c r="C211" s="24"/>
       <c r="D211" s="24"/>
       <c r="E211" s="24"/>
+      <c r="F211" s="24"/>
     </row>
     <row r="212" ht="24" customHeight="1">
       <c r="A212" s="34"/>
@@ -14882,6 +15097,7 @@
       <c r="C212" s="24"/>
       <c r="D212" s="24"/>
       <c r="E212" s="24"/>
+      <c r="F212" s="24"/>
     </row>
     <row r="213" ht="24" customHeight="1">
       <c r="A213" s="34"/>
@@ -14889,6 +15105,7 @@
       <c r="C213" s="24"/>
       <c r="D213" s="24"/>
       <c r="E213" s="24"/>
+      <c r="F213" s="24"/>
     </row>
     <row r="214" ht="24" customHeight="1">
       <c r="A214" s="34"/>
@@ -14896,6 +15113,7 @@
       <c r="C214" s="24"/>
       <c r="D214" s="24"/>
       <c r="E214" s="24"/>
+      <c r="F214" s="24"/>
     </row>
     <row r="215" ht="24" customHeight="1">
       <c r="A215" s="34"/>
@@ -14903,6 +15121,7 @@
       <c r="C215" s="24"/>
       <c r="D215" s="24"/>
       <c r="E215" s="24"/>
+      <c r="F215" s="24"/>
     </row>
     <row r="216" ht="24" customHeight="1">
       <c r="A216" s="34"/>
@@ -14910,6 +15129,7 @@
       <c r="C216" s="24"/>
       <c r="D216" s="24"/>
       <c r="E216" s="24"/>
+      <c r="F216" s="24"/>
     </row>
     <row r="217" ht="24" customHeight="1">
       <c r="A217" s="34"/>
@@ -14917,6 +15137,7 @@
       <c r="C217" s="24"/>
       <c r="D217" s="24"/>
       <c r="E217" s="24"/>
+      <c r="F217" s="24"/>
     </row>
     <row r="218" ht="24" customHeight="1">
       <c r="A218" s="34"/>
@@ -14924,6 +15145,7 @@
       <c r="C218" s="24"/>
       <c r="D218" s="24"/>
       <c r="E218" s="24"/>
+      <c r="F218" s="24"/>
     </row>
     <row r="219" ht="24" customHeight="1">
       <c r="A219" s="34"/>
@@ -14931,6 +15153,7 @@
       <c r="C219" s="24"/>
       <c r="D219" s="24"/>
       <c r="E219" s="24"/>
+      <c r="F219" s="24"/>
     </row>
     <row r="220" ht="24" customHeight="1">
       <c r="A220" s="34"/>
@@ -14938,6 +15161,7 @@
       <c r="C220" s="24"/>
       <c r="D220" s="24"/>
       <c r="E220" s="24"/>
+      <c r="F220" s="24"/>
     </row>
     <row r="221" ht="24" customHeight="1">
       <c r="A221" s="34"/>
@@ -14945,6 +15169,7 @@
       <c r="C221" s="24"/>
       <c r="D221" s="24"/>
       <c r="E221" s="24"/>
+      <c r="F221" s="24"/>
     </row>
     <row r="222" ht="24" customHeight="1">
       <c r="A222" s="34"/>
@@ -14952,6 +15177,7 @@
       <c r="C222" s="24"/>
       <c r="D222" s="24"/>
       <c r="E222" s="24"/>
+      <c r="F222" s="24"/>
     </row>
     <row r="223" ht="24" customHeight="1">
       <c r="A223" s="34"/>
@@ -14959,6 +15185,7 @@
       <c r="C223" s="24"/>
       <c r="D223" s="24"/>
       <c r="E223" s="24"/>
+      <c r="F223" s="24"/>
     </row>
     <row r="224" ht="24" customHeight="1">
       <c r="A224" s="34"/>
@@ -14966,6 +15193,7 @@
       <c r="C224" s="24"/>
       <c r="D224" s="24"/>
       <c r="E224" s="24"/>
+      <c r="F224" s="24"/>
     </row>
     <row r="225" ht="24" customHeight="1">
       <c r="A225" s="34"/>
@@ -14973,6 +15201,7 @@
       <c r="C225" s="24"/>
       <c r="D225" s="24"/>
       <c r="E225" s="24"/>
+      <c r="F225" s="24"/>
     </row>
     <row r="226" ht="24" customHeight="1">
       <c r="A226" s="34"/>
@@ -14980,6 +15209,7 @@
       <c r="C226" s="24"/>
       <c r="D226" s="24"/>
       <c r="E226" s="24"/>
+      <c r="F226" s="24"/>
     </row>
     <row r="227" ht="24" customHeight="1">
       <c r="A227" s="34"/>
@@ -14987,6 +15217,7 @@
       <c r="C227" s="24"/>
       <c r="D227" s="24"/>
       <c r="E227" s="24"/>
+      <c r="F227" s="24"/>
     </row>
     <row r="228" ht="24" customHeight="1">
       <c r="A228" s="34"/>
@@ -14994,6 +15225,7 @@
       <c r="C228" s="24"/>
       <c r="D228" s="24"/>
       <c r="E228" s="24"/>
+      <c r="F228" s="24"/>
     </row>
     <row r="229" ht="24" customHeight="1">
       <c r="A229" s="34"/>
@@ -15001,6 +15233,7 @@
       <c r="C229" s="24"/>
       <c r="D229" s="24"/>
       <c r="E229" s="24"/>
+      <c r="F229" s="24"/>
     </row>
     <row r="230" ht="24" customHeight="1">
       <c r="A230" s="34"/>
@@ -15008,6 +15241,7 @@
       <c r="C230" s="24"/>
       <c r="D230" s="24"/>
       <c r="E230" s="24"/>
+      <c r="F230" s="24"/>
     </row>
     <row r="231" ht="24" customHeight="1">
       <c r="A231" s="34"/>
@@ -15015,6 +15249,7 @@
       <c r="C231" s="24"/>
       <c r="D231" s="24"/>
       <c r="E231" s="24"/>
+      <c r="F231" s="24"/>
     </row>
     <row r="232" ht="24" customHeight="1">
       <c r="A232" s="34"/>
@@ -15022,6 +15257,7 @@
       <c r="C232" s="24"/>
       <c r="D232" s="24"/>
       <c r="E232" s="24"/>
+      <c r="F232" s="24"/>
     </row>
     <row r="233" ht="24" customHeight="1">
       <c r="A233" s="34"/>
@@ -15029,6 +15265,7 @@
       <c r="C233" s="24"/>
       <c r="D233" s="24"/>
       <c r="E233" s="24"/>
+      <c r="F233" s="24"/>
     </row>
     <row r="234" ht="24" customHeight="1">
       <c r="A234" s="34"/>
@@ -15036,6 +15273,7 @@
       <c r="C234" s="24"/>
       <c r="D234" s="24"/>
       <c r="E234" s="24"/>
+      <c r="F234" s="24"/>
     </row>
     <row r="235" ht="24" customHeight="1">
       <c r="A235" s="34"/>
@@ -15043,6 +15281,7 @@
       <c r="C235" s="24"/>
       <c r="D235" s="24"/>
       <c r="E235" s="24"/>
+      <c r="F235" s="24"/>
     </row>
     <row r="236" ht="24" customHeight="1">
       <c r="A236" s="34"/>
@@ -15050,6 +15289,7 @@
       <c r="C236" s="24"/>
       <c r="D236" s="24"/>
       <c r="E236" s="24"/>
+      <c r="F236" s="24"/>
     </row>
     <row r="237" ht="24" customHeight="1">
       <c r="A237" s="34"/>
@@ -15057,6 +15297,7 @@
       <c r="C237" s="24"/>
       <c r="D237" s="24"/>
       <c r="E237" s="24"/>
+      <c r="F237" s="24"/>
     </row>
     <row r="238" ht="24" customHeight="1">
       <c r="A238" s="34"/>
@@ -15064,6 +15305,7 @@
       <c r="C238" s="24"/>
       <c r="D238" s="24"/>
       <c r="E238" s="24"/>
+      <c r="F238" s="24"/>
     </row>
     <row r="239" ht="24" customHeight="1">
       <c r="A239" s="34"/>
@@ -15071,6 +15313,7 @@
       <c r="C239" s="24"/>
       <c r="D239" s="24"/>
       <c r="E239" s="24"/>
+      <c r="F239" s="24"/>
     </row>
     <row r="240" ht="24" customHeight="1">
       <c r="A240" s="34"/>
@@ -15078,6 +15321,7 @@
       <c r="C240" s="24"/>
       <c r="D240" s="24"/>
       <c r="E240" s="24"/>
+      <c r="F240" s="24"/>
     </row>
     <row r="241" ht="24" customHeight="1">
       <c r="A241" s="34"/>
@@ -15085,6 +15329,7 @@
       <c r="C241" s="24"/>
       <c r="D241" s="24"/>
       <c r="E241" s="24"/>
+      <c r="F241" s="24"/>
     </row>
     <row r="242" ht="24" customHeight="1">
       <c r="A242" s="34"/>
@@ -15092,6 +15337,7 @@
       <c r="C242" s="24"/>
       <c r="D242" s="24"/>
       <c r="E242" s="24"/>
+      <c r="F242" s="24"/>
     </row>
     <row r="243" ht="24" customHeight="1">
       <c r="A243" s="34"/>
@@ -15099,6 +15345,7 @@
       <c r="C243" s="24"/>
       <c r="D243" s="24"/>
       <c r="E243" s="24"/>
+      <c r="F243" s="24"/>
     </row>
     <row r="244" ht="24" customHeight="1">
       <c r="A244" s="34"/>
@@ -15106,6 +15353,7 @@
       <c r="C244" s="24"/>
       <c r="D244" s="24"/>
       <c r="E244" s="24"/>
+      <c r="F244" s="24"/>
     </row>
     <row r="245" ht="24" customHeight="1">
       <c r="A245" s="34"/>
@@ -15113,6 +15361,7 @@
       <c r="C245" s="24"/>
       <c r="D245" s="24"/>
       <c r="E245" s="24"/>
+      <c r="F245" s="24"/>
     </row>
     <row r="246" ht="24" customHeight="1">
       <c r="A246" s="34"/>
@@ -15120,6 +15369,7 @@
       <c r="C246" s="24"/>
       <c r="D246" s="24"/>
       <c r="E246" s="24"/>
+      <c r="F246" s="24"/>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="34"/>
@@ -15127,6 +15377,7 @@
       <c r="C247" s="24"/>
       <c r="D247" s="24"/>
       <c r="E247" s="24"/>
+      <c r="F247" s="24"/>
     </row>
     <row r="248" ht="24" customHeight="1">
       <c r="A248" s="34"/>
@@ -15134,6 +15385,7 @@
       <c r="C248" s="24"/>
       <c r="D248" s="24"/>
       <c r="E248" s="24"/>
+      <c r="F248" s="24"/>
     </row>
     <row r="249" ht="24" customHeight="1">
       <c r="A249" s="34"/>
@@ -15141,6 +15393,7 @@
       <c r="C249" s="24"/>
       <c r="D249" s="24"/>
       <c r="E249" s="24"/>
+      <c r="F249" s="24"/>
     </row>
     <row r="250" ht="24" customHeight="1">
       <c r="A250" s="34"/>
@@ -15148,6 +15401,7 @@
       <c r="C250" s="24"/>
       <c r="D250" s="24"/>
       <c r="E250" s="24"/>
+      <c r="F250" s="24"/>
     </row>
     <row r="251" ht="24" customHeight="1">
       <c r="A251" s="34"/>
@@ -15155,6 +15409,7 @@
       <c r="C251" s="24"/>
       <c r="D251" s="24"/>
       <c r="E251" s="24"/>
+      <c r="F251" s="24"/>
     </row>
     <row r="252" ht="24" customHeight="1">
       <c r="A252" s="34"/>
@@ -15162,6 +15417,7 @@
       <c r="C252" s="24"/>
       <c r="D252" s="24"/>
       <c r="E252" s="24"/>
+      <c r="F252" s="24"/>
     </row>
     <row r="253" ht="24" customHeight="1">
       <c r="A253" s="34"/>
@@ -15169,6 +15425,7 @@
       <c r="C253" s="24"/>
       <c r="D253" s="24"/>
       <c r="E253" s="24"/>
+      <c r="F253" s="24"/>
     </row>
     <row r="254" ht="24" customHeight="1">
       <c r="A254" s="34"/>
@@ -15176,6 +15433,7 @@
       <c r="C254" s="24"/>
       <c r="D254" s="24"/>
       <c r="E254" s="24"/>
+      <c r="F254" s="24"/>
     </row>
     <row r="255" ht="24" customHeight="1">
       <c r="A255" s="34"/>
@@ -15183,6 +15441,7 @@
       <c r="C255" s="24"/>
       <c r="D255" s="24"/>
       <c r="E255" s="24"/>
+      <c r="F255" s="24"/>
     </row>
     <row r="256" ht="24" customHeight="1">
       <c r="A256" s="34"/>
@@ -15190,6 +15449,7 @@
       <c r="C256" s="24"/>
       <c r="D256" s="24"/>
       <c r="E256" s="24"/>
+      <c r="F256" s="24"/>
     </row>
     <row r="257" ht="24" customHeight="1">
       <c r="A257" s="34"/>
@@ -15197,6 +15457,7 @@
       <c r="C257" s="24"/>
       <c r="D257" s="24"/>
       <c r="E257" s="24"/>
+      <c r="F257" s="24"/>
     </row>
     <row r="258" ht="24" customHeight="1">
       <c r="A258" s="34"/>
@@ -15204,6 +15465,7 @@
       <c r="C258" s="24"/>
       <c r="D258" s="24"/>
       <c r="E258" s="24"/>
+      <c r="F258" s="24"/>
     </row>
     <row r="259" ht="24" customHeight="1">
       <c r="A259" s="34"/>
@@ -15211,6 +15473,7 @@
       <c r="C259" s="24"/>
       <c r="D259" s="24"/>
       <c r="E259" s="24"/>
+      <c r="F259" s="24"/>
     </row>
     <row r="260" ht="24" customHeight="1">
       <c r="A260" s="34"/>
@@ -15218,6 +15481,7 @@
       <c r="C260" s="24"/>
       <c r="D260" s="24"/>
       <c r="E260" s="24"/>
+      <c r="F260" s="24"/>
     </row>
     <row r="261" ht="24" customHeight="1">
       <c r="A261" s="34"/>
@@ -15225,6 +15489,7 @@
       <c r="C261" s="24"/>
       <c r="D261" s="24"/>
       <c r="E261" s="24"/>
+      <c r="F261" s="24"/>
     </row>
     <row r="262" ht="24" customHeight="1">
       <c r="A262" s="34"/>
@@ -15232,6 +15497,7 @@
       <c r="C262" s="24"/>
       <c r="D262" s="24"/>
       <c r="E262" s="24"/>
+      <c r="F262" s="24"/>
     </row>
     <row r="263" ht="24" customHeight="1">
       <c r="A263" s="34"/>
@@ -15239,6 +15505,7 @@
       <c r="C263" s="24"/>
       <c r="D263" s="24"/>
       <c r="E263" s="24"/>
+      <c r="F263" s="24"/>
     </row>
     <row r="264" ht="24" customHeight="1">
       <c r="A264" s="34"/>
@@ -15246,6 +15513,7 @@
       <c r="C264" s="24"/>
       <c r="D264" s="24"/>
       <c r="E264" s="24"/>
+      <c r="F264" s="24"/>
     </row>
     <row r="265" ht="24" customHeight="1">
       <c r="A265" s="34"/>
@@ -15253,6 +15521,7 @@
       <c r="C265" s="24"/>
       <c r="D265" s="24"/>
       <c r="E265" s="24"/>
+      <c r="F265" s="24"/>
     </row>
     <row r="266" ht="24" customHeight="1">
       <c r="A266" s="34"/>
@@ -15260,6 +15529,7 @@
       <c r="C266" s="24"/>
       <c r="D266" s="24"/>
       <c r="E266" s="24"/>
+      <c r="F266" s="24"/>
     </row>
     <row r="267" ht="24" customHeight="1">
       <c r="A267" s="34"/>
@@ -15267,6 +15537,7 @@
       <c r="C267" s="24"/>
       <c r="D267" s="24"/>
       <c r="E267" s="24"/>
+      <c r="F267" s="24"/>
     </row>
     <row r="268" ht="24" customHeight="1">
       <c r="A268" s="34"/>
@@ -15274,6 +15545,7 @@
       <c r="C268" s="24"/>
       <c r="D268" s="24"/>
       <c r="E268" s="24"/>
+      <c r="F268" s="24"/>
     </row>
     <row r="269" ht="24" customHeight="1">
       <c r="A269" s="34"/>
@@ -15281,6 +15553,7 @@
       <c r="C269" s="24"/>
       <c r="D269" s="24"/>
       <c r="E269" s="24"/>
+      <c r="F269" s="24"/>
     </row>
     <row r="270" ht="24" customHeight="1">
       <c r="A270" s="34"/>
@@ -15288,6 +15561,7 @@
       <c r="C270" s="24"/>
       <c r="D270" s="24"/>
       <c r="E270" s="24"/>
+      <c r="F270" s="24"/>
     </row>
     <row r="271" ht="24" customHeight="1">
       <c r="A271" s="34"/>
@@ -15295,6 +15569,7 @@
       <c r="C271" s="24"/>
       <c r="D271" s="24"/>
       <c r="E271" s="24"/>
+      <c r="F271" s="24"/>
     </row>
     <row r="272" ht="24" customHeight="1">
       <c r="A272" s="34"/>
@@ -15302,6 +15577,7 @@
       <c r="C272" s="24"/>
       <c r="D272" s="24"/>
       <c r="E272" s="24"/>
+      <c r="F272" s="24"/>
     </row>
     <row r="273" ht="24" customHeight="1">
       <c r="A273" s="34"/>
@@ -15309,6 +15585,7 @@
       <c r="C273" s="24"/>
       <c r="D273" s="24"/>
       <c r="E273" s="24"/>
+      <c r="F273" s="24"/>
     </row>
     <row r="274" ht="24" customHeight="1">
       <c r="A274" s="34"/>
@@ -15316,6 +15593,7 @@
       <c r="C274" s="24"/>
       <c r="D274" s="24"/>
       <c r="E274" s="24"/>
+      <c r="F274" s="24"/>
     </row>
     <row r="275" ht="24" customHeight="1">
       <c r="A275" s="34"/>
@@ -15323,6 +15601,7 @@
       <c r="C275" s="24"/>
       <c r="D275" s="24"/>
       <c r="E275" s="24"/>
+      <c r="F275" s="24"/>
     </row>
     <row r="276" ht="24" customHeight="1">
       <c r="A276" s="34"/>
@@ -15330,6 +15609,7 @@
       <c r="C276" s="24"/>
       <c r="D276" s="24"/>
       <c r="E276" s="24"/>
+      <c r="F276" s="24"/>
     </row>
     <row r="277" ht="24" customHeight="1">
       <c r="A277" s="34"/>
@@ -15337,6 +15617,7 @@
       <c r="C277" s="24"/>
       <c r="D277" s="24"/>
       <c r="E277" s="24"/>
+      <c r="F277" s="24"/>
     </row>
     <row r="278" ht="24" customHeight="1">
       <c r="A278" s="34"/>
@@ -15344,6 +15625,7 @@
       <c r="C278" s="24"/>
       <c r="D278" s="24"/>
       <c r="E278" s="24"/>
+      <c r="F278" s="24"/>
     </row>
     <row r="279" ht="24" customHeight="1">
       <c r="A279" s="34"/>
@@ -15351,6 +15633,7 @@
       <c r="C279" s="24"/>
       <c r="D279" s="24"/>
       <c r="E279" s="24"/>
+      <c r="F279" s="24"/>
     </row>
     <row r="280" ht="24" customHeight="1">
       <c r="A280" s="34"/>
@@ -15358,6 +15641,7 @@
       <c r="C280" s="24"/>
       <c r="D280" s="24"/>
       <c r="E280" s="24"/>
+      <c r="F280" s="24"/>
     </row>
     <row r="281" ht="24" customHeight="1">
       <c r="A281" s="34"/>
@@ -15365,6 +15649,7 @@
       <c r="C281" s="24"/>
       <c r="D281" s="24"/>
       <c r="E281" s="24"/>
+      <c r="F281" s="24"/>
     </row>
     <row r="282" ht="24" customHeight="1">
       <c r="A282" s="34"/>
@@ -15372,6 +15657,7 @@
       <c r="C282" s="24"/>
       <c r="D282" s="24"/>
       <c r="E282" s="24"/>
+      <c r="F282" s="24"/>
     </row>
     <row r="283" ht="24" customHeight="1">
       <c r="A283" s="34"/>
@@ -15379,6 +15665,7 @@
       <c r="C283" s="24"/>
       <c r="D283" s="24"/>
       <c r="E283" s="24"/>
+      <c r="F283" s="24"/>
     </row>
     <row r="284" ht="24" customHeight="1">
       <c r="A284" s="34"/>
@@ -15386,6 +15673,7 @@
       <c r="C284" s="24"/>
       <c r="D284" s="24"/>
       <c r="E284" s="24"/>
+      <c r="F284" s="24"/>
     </row>
     <row r="285" ht="24" customHeight="1">
       <c r="A285" s="34"/>
@@ -15393,6 +15681,7 @@
       <c r="C285" s="24"/>
       <c r="D285" s="24"/>
       <c r="E285" s="24"/>
+      <c r="F285" s="24"/>
     </row>
     <row r="286" ht="24" customHeight="1">
       <c r="A286" s="34"/>
@@ -15400,6 +15689,7 @@
       <c r="C286" s="24"/>
       <c r="D286" s="24"/>
       <c r="E286" s="24"/>
+      <c r="F286" s="24"/>
     </row>
     <row r="287" ht="24" customHeight="1">
       <c r="A287" s="34"/>
@@ -15407,6 +15697,7 @@
       <c r="C287" s="24"/>
       <c r="D287" s="24"/>
       <c r="E287" s="24"/>
+      <c r="F287" s="24"/>
     </row>
     <row r="288" ht="24" customHeight="1">
       <c r="A288" s="34"/>
@@ -15414,6 +15705,7 @@
       <c r="C288" s="24"/>
       <c r="D288" s="24"/>
       <c r="E288" s="24"/>
+      <c r="F288" s="24"/>
     </row>
     <row r="289" ht="24" customHeight="1">
       <c r="A289" s="34"/>
@@ -15421,6 +15713,7 @@
       <c r="C289" s="24"/>
       <c r="D289" s="24"/>
       <c r="E289" s="24"/>
+      <c r="F289" s="24"/>
     </row>
     <row r="290" ht="24" customHeight="1">
       <c r="A290" s="34"/>
@@ -15428,6 +15721,7 @@
       <c r="C290" s="24"/>
       <c r="D290" s="24"/>
       <c r="E290" s="24"/>
+      <c r="F290" s="24"/>
     </row>
     <row r="291" ht="24" customHeight="1">
       <c r="A291" s="34"/>
@@ -15435,6 +15729,7 @@
       <c r="C291" s="24"/>
       <c r="D291" s="24"/>
       <c r="E291" s="24"/>
+      <c r="F291" s="24"/>
     </row>
     <row r="292" ht="24" customHeight="1">
       <c r="A292" s="34"/>
@@ -15442,6 +15737,7 @@
       <c r="C292" s="24"/>
       <c r="D292" s="24"/>
       <c r="E292" s="24"/>
+      <c r="F292" s="24"/>
     </row>
     <row r="293" ht="24" customHeight="1">
       <c r="A293" s="34"/>
@@ -15449,6 +15745,7 @@
       <c r="C293" s="24"/>
       <c r="D293" s="24"/>
       <c r="E293" s="24"/>
+      <c r="F293" s="24"/>
     </row>
     <row r="294" ht="24" customHeight="1">
       <c r="A294" s="34"/>
@@ -15456,6 +15753,7 @@
       <c r="C294" s="24"/>
       <c r="D294" s="24"/>
       <c r="E294" s="24"/>
+      <c r="F294" s="24"/>
     </row>
     <row r="295" ht="24" customHeight="1">
       <c r="A295" s="34"/>
@@ -15463,6 +15761,7 @@
       <c r="C295" s="24"/>
       <c r="D295" s="24"/>
       <c r="E295" s="24"/>
+      <c r="F295" s="24"/>
     </row>
     <row r="296" ht="24" customHeight="1">
       <c r="A296" s="34"/>
@@ -15470,6 +15769,7 @@
       <c r="C296" s="24"/>
       <c r="D296" s="24"/>
       <c r="E296" s="24"/>
+      <c r="F296" s="24"/>
     </row>
     <row r="297" ht="24" customHeight="1">
       <c r="A297" s="34"/>
@@ -15477,6 +15777,7 @@
       <c r="C297" s="24"/>
       <c r="D297" s="24"/>
       <c r="E297" s="24"/>
+      <c r="F297" s="24"/>
     </row>
     <row r="298" ht="24" customHeight="1">
       <c r="A298" s="34"/>
@@ -15484,6 +15785,7 @@
       <c r="C298" s="24"/>
       <c r="D298" s="24"/>
       <c r="E298" s="24"/>
+      <c r="F298" s="24"/>
     </row>
     <row r="299" ht="24" customHeight="1">
       <c r="A299" s="34"/>
@@ -15491,6 +15793,7 @@
       <c r="C299" s="24"/>
       <c r="D299" s="24"/>
       <c r="E299" s="24"/>
+      <c r="F299" s="24"/>
     </row>
     <row r="300" ht="24" customHeight="1">
       <c r="A300" s="34"/>
@@ -15498,6 +15801,7 @@
       <c r="C300" s="24"/>
       <c r="D300" s="24"/>
       <c r="E300" s="24"/>
+      <c r="F300" s="24"/>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="34"/>
@@ -15505,6 +15809,7 @@
       <c r="C301" s="24"/>
       <c r="D301" s="24"/>
       <c r="E301" s="24"/>
+      <c r="F301" s="24"/>
     </row>
     <row r="302" ht="24" customHeight="1">
       <c r="A302" s="34"/>
@@ -15512,6 +15817,7 @@
       <c r="C302" s="24"/>
       <c r="D302" s="24"/>
       <c r="E302" s="24"/>
+      <c r="F302" s="24"/>
     </row>
     <row r="303" ht="24" customHeight="1">
       <c r="A303" s="34"/>
@@ -15519,6 +15825,7 @@
       <c r="C303" s="24"/>
       <c r="D303" s="24"/>
       <c r="E303" s="24"/>
+      <c r="F303" s="24"/>
     </row>
     <row r="304" ht="24" customHeight="1">
       <c r="A304" s="34"/>
@@ -15526,6 +15833,7 @@
       <c r="C304" s="24"/>
       <c r="D304" s="24"/>
       <c r="E304" s="24"/>
+      <c r="F304" s="24"/>
     </row>
     <row r="305" ht="24" customHeight="1">
       <c r="A305" s="34"/>
@@ -15533,6 +15841,7 @@
       <c r="C305" s="24"/>
       <c r="D305" s="24"/>
       <c r="E305" s="24"/>
+      <c r="F305" s="24"/>
     </row>
     <row r="306" ht="24" customHeight="1">
       <c r="A306" s="34"/>
@@ -15540,6 +15849,7 @@
       <c r="C306" s="24"/>
       <c r="D306" s="24"/>
       <c r="E306" s="24"/>
+      <c r="F306" s="24"/>
     </row>
     <row r="307" ht="24" customHeight="1">
       <c r="A307" s="34"/>
@@ -15547,6 +15857,7 @@
       <c r="C307" s="24"/>
       <c r="D307" s="24"/>
       <c r="E307" s="24"/>
+      <c r="F307" s="24"/>
     </row>
     <row r="308" ht="24" customHeight="1">
       <c r="A308" s="34"/>
@@ -15554,6 +15865,7 @@
       <c r="C308" s="24"/>
       <c r="D308" s="24"/>
       <c r="E308" s="24"/>
+      <c r="F308" s="24"/>
     </row>
     <row r="309" ht="24" customHeight="1">
       <c r="A309" s="34"/>
@@ -15561,6 +15873,7 @@
       <c r="C309" s="24"/>
       <c r="D309" s="24"/>
       <c r="E309" s="24"/>
+      <c r="F309" s="24"/>
     </row>
     <row r="310" ht="24" customHeight="1">
       <c r="A310" s="34"/>
@@ -15568,6 +15881,7 @@
       <c r="C310" s="24"/>
       <c r="D310" s="24"/>
       <c r="E310" s="24"/>
+      <c r="F310" s="24"/>
     </row>
     <row r="311" ht="24" customHeight="1">
       <c r="A311" s="34"/>
@@ -15575,6 +15889,7 @@
       <c r="C311" s="24"/>
       <c r="D311" s="24"/>
       <c r="E311" s="24"/>
+      <c r="F311" s="24"/>
     </row>
     <row r="312" ht="24" customHeight="1">
       <c r="A312" s="34"/>
@@ -15582,6 +15897,7 @@
       <c r="C312" s="24"/>
       <c r="D312" s="24"/>
       <c r="E312" s="24"/>
+      <c r="F312" s="24"/>
     </row>
     <row r="313" ht="24" customHeight="1">
       <c r="A313" s="34"/>
@@ -15589,6 +15905,7 @@
       <c r="C313" s="24"/>
       <c r="D313" s="24"/>
       <c r="E313" s="24"/>
+      <c r="F313" s="24"/>
     </row>
     <row r="314" ht="24" customHeight="1">
       <c r="A314" s="34"/>
@@ -15596,6 +15913,7 @@
       <c r="C314" s="24"/>
       <c r="D314" s="24"/>
       <c r="E314" s="24"/>
+      <c r="F314" s="24"/>
     </row>
     <row r="315" ht="24" customHeight="1">
       <c r="A315" s="34"/>
@@ -15603,6 +15921,7 @@
       <c r="C315" s="24"/>
       <c r="D315" s="24"/>
       <c r="E315" s="24"/>
+      <c r="F315" s="24"/>
     </row>
     <row r="316" ht="24" customHeight="1">
       <c r="A316" s="34"/>
@@ -15610,6 +15929,7 @@
       <c r="C316" s="24"/>
       <c r="D316" s="24"/>
       <c r="E316" s="24"/>
+      <c r="F316" s="24"/>
     </row>
     <row r="317" ht="24" customHeight="1">
       <c r="A317" s="34"/>
@@ -15617,6 +15937,7 @@
       <c r="C317" s="24"/>
       <c r="D317" s="24"/>
       <c r="E317" s="24"/>
+      <c r="F317" s="24"/>
     </row>
     <row r="318" ht="24" customHeight="1">
       <c r="A318" s="34"/>
@@ -15624,6 +15945,7 @@
       <c r="C318" s="24"/>
       <c r="D318" s="24"/>
       <c r="E318" s="24"/>
+      <c r="F318" s="24"/>
     </row>
     <row r="319" ht="24" customHeight="1">
       <c r="A319" s="34"/>
@@ -15631,6 +15953,7 @@
       <c r="C319" s="24"/>
       <c r="D319" s="24"/>
       <c r="E319" s="24"/>
+      <c r="F319" s="24"/>
     </row>
     <row r="320" ht="24" customHeight="1">
       <c r="A320" s="34"/>
@@ -15638,6 +15961,7 @@
       <c r="C320" s="24"/>
       <c r="D320" s="24"/>
       <c r="E320" s="24"/>
+      <c r="F320" s="24"/>
     </row>
     <row r="321" ht="24" customHeight="1">
       <c r="A321" s="34"/>
@@ -15645,6 +15969,7 @@
       <c r="C321" s="24"/>
       <c r="D321" s="24"/>
       <c r="E321" s="24"/>
+      <c r="F321" s="24"/>
     </row>
     <row r="322" ht="24" customHeight="1">
       <c r="A322" s="34"/>
@@ -15652,6 +15977,7 @@
       <c r="C322" s="24"/>
       <c r="D322" s="24"/>
       <c r="E322" s="24"/>
+      <c r="F322" s="24"/>
     </row>
     <row r="323" ht="24" customHeight="1">
       <c r="A323" s="34"/>
@@ -15659,6 +15985,7 @@
       <c r="C323" s="24"/>
       <c r="D323" s="24"/>
       <c r="E323" s="24"/>
+      <c r="F323" s="24"/>
     </row>
     <row r="324" ht="24" customHeight="1">
       <c r="A324" s="34"/>
@@ -15666,6 +15993,7 @@
       <c r="C324" s="24"/>
       <c r="D324" s="24"/>
       <c r="E324" s="24"/>
+      <c r="F324" s="24"/>
     </row>
     <row r="325" ht="24" customHeight="1">
       <c r="A325" s="34"/>
@@ -15673,6 +16001,7 @@
       <c r="C325" s="24"/>
       <c r="D325" s="24"/>
       <c r="E325" s="24"/>
+      <c r="F325" s="24"/>
     </row>
     <row r="326" ht="24" customHeight="1">
       <c r="A326" s="34"/>
@@ -15680,6 +16009,7 @@
       <c r="C326" s="24"/>
       <c r="D326" s="24"/>
       <c r="E326" s="24"/>
+      <c r="F326" s="24"/>
     </row>
     <row r="327" ht="24" customHeight="1">
       <c r="A327" s="34"/>
@@ -15687,6 +16017,7 @@
       <c r="C327" s="24"/>
       <c r="D327" s="24"/>
       <c r="E327" s="24"/>
+      <c r="F327" s="24"/>
     </row>
     <row r="328" ht="24" customHeight="1">
       <c r="A328" s="34"/>
@@ -15694,6 +16025,7 @@
       <c r="C328" s="24"/>
       <c r="D328" s="24"/>
       <c r="E328" s="24"/>
+      <c r="F328" s="24"/>
     </row>
     <row r="329" ht="24" customHeight="1">
       <c r="A329" s="34"/>
@@ -15701,6 +16033,7 @@
       <c r="C329" s="24"/>
       <c r="D329" s="24"/>
       <c r="E329" s="24"/>
+      <c r="F329" s="24"/>
     </row>
     <row r="330" ht="24" customHeight="1">
       <c r="A330" s="34"/>
@@ -15708,6 +16041,7 @@
       <c r="C330" s="24"/>
       <c r="D330" s="24"/>
       <c r="E330" s="24"/>
+      <c r="F330" s="24"/>
     </row>
     <row r="331" ht="24" customHeight="1">
       <c r="A331" s="34"/>
@@ -15715,6 +16049,7 @@
       <c r="C331" s="24"/>
       <c r="D331" s="24"/>
       <c r="E331" s="24"/>
+      <c r="F331" s="24"/>
     </row>
     <row r="332" ht="24" customHeight="1">
       <c r="A332" s="34"/>
@@ -15722,6 +16057,7 @@
       <c r="C332" s="24"/>
       <c r="D332" s="24"/>
       <c r="E332" s="24"/>
+      <c r="F332" s="24"/>
     </row>
     <row r="333" ht="24" customHeight="1">
       <c r="A333" s="34"/>
@@ -15729,6 +16065,7 @@
       <c r="C333" s="24"/>
       <c r="D333" s="24"/>
       <c r="E333" s="24"/>
+      <c r="F333" s="24"/>
     </row>
     <row r="334" ht="24" customHeight="1">
       <c r="A334" s="34"/>
@@ -15736,6 +16073,7 @@
       <c r="C334" s="24"/>
       <c r="D334" s="24"/>
       <c r="E334" s="24"/>
+      <c r="F334" s="24"/>
     </row>
     <row r="335" ht="24" customHeight="1">
       <c r="A335" s="34"/>
@@ -15743,6 +16081,7 @@
       <c r="C335" s="24"/>
       <c r="D335" s="24"/>
       <c r="E335" s="24"/>
+      <c r="F335" s="24"/>
     </row>
     <row r="336" ht="24" customHeight="1">
       <c r="A336" s="34"/>
@@ -15750,6 +16089,7 @@
       <c r="C336" s="24"/>
       <c r="D336" s="24"/>
       <c r="E336" s="24"/>
+      <c r="F336" s="24"/>
     </row>
     <row r="337" ht="24" customHeight="1">
       <c r="A337" s="34"/>
@@ -15757,6 +16097,7 @@
       <c r="C337" s="24"/>
       <c r="D337" s="24"/>
       <c r="E337" s="24"/>
+      <c r="F337" s="24"/>
     </row>
     <row r="338" ht="24" customHeight="1">
       <c r="A338" s="34"/>
@@ -15764,6 +16105,7 @@
       <c r="C338" s="24"/>
       <c r="D338" s="24"/>
       <c r="E338" s="24"/>
+      <c r="F338" s="24"/>
     </row>
     <row r="339" ht="24" customHeight="1">
       <c r="A339" s="34"/>
@@ -15771,6 +16113,7 @@
       <c r="C339" s="24"/>
       <c r="D339" s="24"/>
       <c r="E339" s="24"/>
+      <c r="F339" s="24"/>
     </row>
     <row r="340" ht="24" customHeight="1">
       <c r="A340" s="34"/>
@@ -15778,6 +16121,7 @@
       <c r="C340" s="24"/>
       <c r="D340" s="24"/>
       <c r="E340" s="24"/>
+      <c r="F340" s="24"/>
     </row>
     <row r="341" ht="24" customHeight="1">
       <c r="A341" s="34"/>
@@ -15785,6 +16129,7 @@
       <c r="C341" s="24"/>
       <c r="D341" s="24"/>
       <c r="E341" s="24"/>
+      <c r="F341" s="24"/>
     </row>
     <row r="342" ht="24" customHeight="1">
       <c r="A342" s="34"/>
@@ -15792,6 +16137,7 @@
       <c r="C342" s="24"/>
       <c r="D342" s="24"/>
       <c r="E342" s="24"/>
+      <c r="F342" s="24"/>
     </row>
     <row r="343" ht="24" customHeight="1">
       <c r="A343" s="34"/>
@@ -15799,6 +16145,7 @@
       <c r="C343" s="24"/>
       <c r="D343" s="24"/>
       <c r="E343" s="24"/>
+      <c r="F343" s="24"/>
     </row>
     <row r="344" ht="24" customHeight="1">
       <c r="A344" s="34"/>
@@ -15806,6 +16153,7 @@
       <c r="C344" s="24"/>
       <c r="D344" s="24"/>
       <c r="E344" s="24"/>
+      <c r="F344" s="24"/>
     </row>
     <row r="345" ht="24" customHeight="1">
       <c r="A345" s="34"/>
@@ -15813,6 +16161,7 @@
       <c r="C345" s="24"/>
       <c r="D345" s="24"/>
       <c r="E345" s="24"/>
+      <c r="F345" s="24"/>
     </row>
     <row r="346" ht="24" customHeight="1">
       <c r="A346" s="34"/>
@@ -15820,6 +16169,7 @@
       <c r="C346" s="24"/>
       <c r="D346" s="24"/>
       <c r="E346" s="24"/>
+      <c r="F346" s="24"/>
     </row>
     <row r="347" ht="24" customHeight="1">
       <c r="A347" s="34"/>
@@ -15827,6 +16177,7 @@
       <c r="C347" s="24"/>
       <c r="D347" s="24"/>
       <c r="E347" s="24"/>
+      <c r="F347" s="24"/>
     </row>
     <row r="348" ht="24" customHeight="1">
       <c r="A348" s="34"/>
@@ -15834,6 +16185,7 @@
       <c r="C348" s="24"/>
       <c r="D348" s="24"/>
       <c r="E348" s="24"/>
+      <c r="F348" s="24"/>
     </row>
     <row r="349" ht="24" customHeight="1">
       <c r="A349" s="34"/>
@@ -15841,6 +16193,7 @@
       <c r="C349" s="24"/>
       <c r="D349" s="24"/>
       <c r="E349" s="24"/>
+      <c r="F349" s="24"/>
     </row>
     <row r="350" ht="24" customHeight="1">
       <c r="A350" s="34"/>
@@ -15848,6 +16201,7 @@
       <c r="C350" s="24"/>
       <c r="D350" s="24"/>
       <c r="E350" s="24"/>
+      <c r="F350" s="24"/>
     </row>
     <row r="351" ht="24" customHeight="1">
       <c r="A351" s="34"/>
@@ -15855,6 +16209,7 @@
       <c r="C351" s="24"/>
       <c r="D351" s="24"/>
       <c r="E351" s="24"/>
+      <c r="F351" s="24"/>
     </row>
     <row r="352" ht="24" customHeight="1">
       <c r="A352" s="34"/>
@@ -15862,6 +16217,7 @@
       <c r="C352" s="24"/>
       <c r="D352" s="24"/>
       <c r="E352" s="24"/>
+      <c r="F352" s="24"/>
     </row>
     <row r="353" ht="24" customHeight="1">
       <c r="A353" s="34"/>
@@ -15869,6 +16225,7 @@
       <c r="C353" s="24"/>
       <c r="D353" s="24"/>
       <c r="E353" s="24"/>
+      <c r="F353" s="24"/>
     </row>
     <row r="354" ht="24" customHeight="1">
       <c r="A354" s="34"/>
@@ -15876,6 +16233,7 @@
       <c r="C354" s="24"/>
       <c r="D354" s="24"/>
       <c r="E354" s="24"/>
+      <c r="F354" s="24"/>
     </row>
     <row r="355" ht="24" customHeight="1">
       <c r="A355" s="34"/>
@@ -15883,6 +16241,7 @@
       <c r="C355" s="24"/>
       <c r="D355" s="24"/>
       <c r="E355" s="24"/>
+      <c r="F355" s="24"/>
     </row>
     <row r="356" ht="24" customHeight="1">
       <c r="A356" s="34"/>
@@ -15890,6 +16249,7 @@
       <c r="C356" s="24"/>
       <c r="D356" s="24"/>
       <c r="E356" s="24"/>
+      <c r="F356" s="24"/>
     </row>
     <row r="357" ht="24" customHeight="1">
       <c r="A357" s="34"/>
@@ -15897,6 +16257,7 @@
       <c r="C357" s="24"/>
       <c r="D357" s="24"/>
       <c r="E357" s="24"/>
+      <c r="F357" s="24"/>
     </row>
     <row r="358" ht="24" customHeight="1">
       <c r="A358" s="34"/>
@@ -15904,6 +16265,7 @@
       <c r="C358" s="24"/>
       <c r="D358" s="24"/>
       <c r="E358" s="24"/>
+      <c r="F358" s="24"/>
     </row>
     <row r="359" ht="24" customHeight="1">
       <c r="A359" s="34"/>
@@ -15911,6 +16273,7 @@
       <c r="C359" s="24"/>
       <c r="D359" s="24"/>
       <c r="E359" s="24"/>
+      <c r="F359" s="24"/>
     </row>
     <row r="360" ht="24" customHeight="1">
       <c r="A360" s="34"/>
@@ -15918,6 +16281,7 @@
       <c r="C360" s="24"/>
       <c r="D360" s="24"/>
       <c r="E360" s="24"/>
+      <c r="F360" s="24"/>
     </row>
     <row r="361" ht="24" customHeight="1">
       <c r="A361" s="34"/>
@@ -15925,6 +16289,7 @@
       <c r="C361" s="24"/>
       <c r="D361" s="24"/>
       <c r="E361" s="24"/>
+      <c r="F361" s="24"/>
     </row>
     <row r="362" ht="24" customHeight="1">
       <c r="A362" s="34"/>
@@ -15932,6 +16297,7 @@
       <c r="C362" s="24"/>
       <c r="D362" s="24"/>
       <c r="E362" s="24"/>
+      <c r="F362" s="24"/>
     </row>
     <row r="363" ht="24" customHeight="1">
       <c r="A363" s="34"/>
@@ -15939,6 +16305,7 @@
       <c r="C363" s="24"/>
       <c r="D363" s="24"/>
       <c r="E363" s="24"/>
+      <c r="F363" s="24"/>
     </row>
     <row r="364" ht="24" customHeight="1">
       <c r="A364" s="34"/>
@@ -15946,6 +16313,7 @@
       <c r="C364" s="24"/>
       <c r="D364" s="24"/>
       <c r="E364" s="24"/>
+      <c r="F364" s="24"/>
     </row>
     <row r="365" ht="24" customHeight="1">
       <c r="A365" s="34"/>
@@ -15953,6 +16321,7 @@
       <c r="C365" s="24"/>
       <c r="D365" s="24"/>
       <c r="E365" s="24"/>
+      <c r="F365" s="24"/>
     </row>
     <row r="366" ht="24" customHeight="1">
       <c r="A366" s="34"/>
@@ -15960,6 +16329,7 @@
       <c r="C366" s="24"/>
       <c r="D366" s="24"/>
       <c r="E366" s="24"/>
+      <c r="F366" s="24"/>
     </row>
     <row r="367" ht="24" customHeight="1">
       <c r="A367" s="34"/>
@@ -15967,6 +16337,7 @@
       <c r="C367" s="24"/>
       <c r="D367" s="24"/>
       <c r="E367" s="24"/>
+      <c r="F367" s="24"/>
     </row>
     <row r="368" ht="24" customHeight="1">
       <c r="A368" s="34"/>
@@ -15974,6 +16345,7 @@
       <c r="C368" s="24"/>
       <c r="D368" s="24"/>
       <c r="E368" s="24"/>
+      <c r="F368" s="24"/>
     </row>
     <row r="369" ht="24" customHeight="1">
       <c r="A369" s="34"/>
@@ -15981,6 +16353,7 @@
       <c r="C369" s="24"/>
       <c r="D369" s="24"/>
       <c r="E369" s="24"/>
+      <c r="F369" s="24"/>
     </row>
     <row r="370" ht="24" customHeight="1">
       <c r="A370" s="34"/>
@@ -15988,6 +16361,7 @@
       <c r="C370" s="24"/>
       <c r="D370" s="24"/>
       <c r="E370" s="24"/>
+      <c r="F370" s="24"/>
     </row>
     <row r="371" ht="24" customHeight="1">
       <c r="A371" s="34"/>
@@ -15995,6 +16369,7 @@
       <c r="C371" s="24"/>
       <c r="D371" s="24"/>
       <c r="E371" s="24"/>
+      <c r="F371" s="24"/>
     </row>
     <row r="372" ht="24" customHeight="1">
       <c r="A372" s="34"/>
@@ -16002,6 +16377,7 @@
       <c r="C372" s="24"/>
       <c r="D372" s="24"/>
       <c r="E372" s="24"/>
+      <c r="F372" s="24"/>
     </row>
     <row r="373" ht="24" customHeight="1">
       <c r="A373" s="34"/>
@@ -16009,6 +16385,7 @@
       <c r="C373" s="24"/>
       <c r="D373" s="24"/>
       <c r="E373" s="24"/>
+      <c r="F373" s="24"/>
     </row>
     <row r="374" ht="24" customHeight="1">
       <c r="A374" s="34"/>
@@ -16016,6 +16393,7 @@
       <c r="C374" s="24"/>
       <c r="D374" s="24"/>
       <c r="E374" s="24"/>
+      <c r="F374" s="24"/>
     </row>
     <row r="375" ht="24" customHeight="1">
       <c r="A375" s="34"/>
@@ -16023,6 +16401,7 @@
       <c r="C375" s="24"/>
       <c r="D375" s="24"/>
       <c r="E375" s="24"/>
+      <c r="F375" s="24"/>
     </row>
     <row r="376" ht="24" customHeight="1">
       <c r="A376" s="34"/>
@@ -16030,6 +16409,7 @@
       <c r="C376" s="24"/>
       <c r="D376" s="24"/>
       <c r="E376" s="24"/>
+      <c r="F376" s="24"/>
     </row>
     <row r="377" ht="24" customHeight="1">
       <c r="A377" s="34"/>
@@ -16037,6 +16417,7 @@
       <c r="C377" s="24"/>
       <c r="D377" s="24"/>
       <c r="E377" s="24"/>
+      <c r="F377" s="24"/>
     </row>
     <row r="378" ht="24" customHeight="1">
       <c r="A378" s="34"/>
@@ -16044,6 +16425,7 @@
       <c r="C378" s="24"/>
       <c r="D378" s="24"/>
       <c r="E378" s="24"/>
+      <c r="F378" s="24"/>
     </row>
     <row r="379" ht="24" customHeight="1">
       <c r="A379" s="34"/>
@@ -16051,6 +16433,7 @@
       <c r="C379" s="24"/>
       <c r="D379" s="24"/>
       <c r="E379" s="24"/>
+      <c r="F379" s="24"/>
     </row>
     <row r="380" ht="24" customHeight="1">
       <c r="A380" s="34"/>
@@ -16058,6 +16441,7 @@
       <c r="C380" s="24"/>
       <c r="D380" s="24"/>
       <c r="E380" s="24"/>
+      <c r="F380" s="24"/>
     </row>
     <row r="381" ht="24" customHeight="1">
       <c r="A381" s="34"/>
@@ -16065,6 +16449,7 @@
       <c r="C381" s="24"/>
       <c r="D381" s="24"/>
       <c r="E381" s="24"/>
+      <c r="F381" s="24"/>
     </row>
     <row r="382" ht="24" customHeight="1">
       <c r="A382" s="34"/>
@@ -16072,6 +16457,7 @@
       <c r="C382" s="24"/>
       <c r="D382" s="24"/>
       <c r="E382" s="24"/>
+      <c r="F382" s="24"/>
     </row>
     <row r="383" ht="24" customHeight="1">
       <c r="A383" s="34"/>
@@ -16079,6 +16465,7 @@
       <c r="C383" s="24"/>
       <c r="D383" s="24"/>
       <c r="E383" s="24"/>
+      <c r="F383" s="24"/>
     </row>
     <row r="384" ht="24" customHeight="1">
       <c r="A384" s="34"/>
@@ -16086,6 +16473,7 @@
       <c r="C384" s="24"/>
       <c r="D384" s="24"/>
       <c r="E384" s="24"/>
+      <c r="F384" s="24"/>
     </row>
     <row r="385" ht="24" customHeight="1">
       <c r="A385" s="34"/>
@@ -16093,6 +16481,7 @@
       <c r="C385" s="24"/>
       <c r="D385" s="24"/>
       <c r="E385" s="24"/>
+      <c r="F385" s="24"/>
     </row>
     <row r="386" ht="24" customHeight="1">
       <c r="A386" s="34"/>
@@ -16100,6 +16489,7 @@
       <c r="C386" s="24"/>
       <c r="D386" s="24"/>
       <c r="E386" s="24"/>
+      <c r="F386" s="24"/>
     </row>
     <row r="387" ht="24" customHeight="1">
       <c r="A387" s="34"/>
@@ -16107,6 +16497,7 @@
       <c r="C387" s="24"/>
       <c r="D387" s="24"/>
       <c r="E387" s="24"/>
+      <c r="F387" s="24"/>
     </row>
     <row r="388" ht="24" customHeight="1">
       <c r="A388" s="34"/>
@@ -16114,6 +16505,7 @@
       <c r="C388" s="24"/>
       <c r="D388" s="24"/>
       <c r="E388" s="24"/>
+      <c r="F388" s="24"/>
     </row>
     <row r="389" ht="24" customHeight="1">
       <c r="A389" s="34"/>
@@ -16121,6 +16513,7 @@
       <c r="C389" s="24"/>
       <c r="D389" s="24"/>
       <c r="E389" s="24"/>
+      <c r="F389" s="24"/>
     </row>
     <row r="390" ht="24" customHeight="1">
       <c r="A390" s="34"/>
@@ -16128,6 +16521,7 @@
       <c r="C390" s="24"/>
       <c r="D390" s="24"/>
       <c r="E390" s="24"/>
+      <c r="F390" s="24"/>
     </row>
     <row r="391" ht="24" customHeight="1">
       <c r="A391" s="34"/>
@@ -16135,6 +16529,7 @@
       <c r="C391" s="24"/>
       <c r="D391" s="24"/>
       <c r="E391" s="24"/>
+      <c r="F391" s="24"/>
     </row>
     <row r="392" ht="24" customHeight="1">
       <c r="A392" s="34"/>
@@ -16142,6 +16537,7 @@
       <c r="C392" s="24"/>
       <c r="D392" s="24"/>
       <c r="E392" s="24"/>
+      <c r="F392" s="24"/>
     </row>
     <row r="393" ht="24" customHeight="1">
       <c r="A393" s="34"/>
@@ -16149,6 +16545,7 @@
       <c r="C393" s="24"/>
       <c r="D393" s="24"/>
       <c r="E393" s="24"/>
+      <c r="F393" s="24"/>
     </row>
     <row r="394" ht="24" customHeight="1">
       <c r="A394" s="34"/>
@@ -16156,6 +16553,7 @@
       <c r="C394" s="24"/>
       <c r="D394" s="24"/>
       <c r="E394" s="24"/>
+      <c r="F394" s="24"/>
     </row>
     <row r="395" ht="24" customHeight="1">
       <c r="A395" s="34"/>
@@ -16163,6 +16561,7 @@
       <c r="C395" s="24"/>
       <c r="D395" s="24"/>
       <c r="E395" s="24"/>
+      <c r="F395" s="24"/>
     </row>
     <row r="396" ht="24" customHeight="1">
       <c r="A396" s="34"/>
@@ -16170,6 +16569,7 @@
       <c r="C396" s="24"/>
       <c r="D396" s="24"/>
       <c r="E396" s="24"/>
+      <c r="F396" s="24"/>
     </row>
     <row r="397" ht="24" customHeight="1">
       <c r="A397" s="34"/>
@@ -16177,6 +16577,7 @@
       <c r="C397" s="24"/>
       <c r="D397" s="24"/>
       <c r="E397" s="24"/>
+      <c r="F397" s="24"/>
     </row>
     <row r="398" ht="24" customHeight="1">
       <c r="A398" s="34"/>
@@ -16184,6 +16585,7 @@
       <c r="C398" s="24"/>
       <c r="D398" s="24"/>
       <c r="E398" s="24"/>
+      <c r="F398" s="24"/>
     </row>
     <row r="399" ht="24" customHeight="1">
       <c r="A399" s="34"/>
@@ -16191,6 +16593,7 @@
       <c r="C399" s="24"/>
       <c r="D399" s="24"/>
       <c r="E399" s="24"/>
+      <c r="F399" s="24"/>
     </row>
     <row r="400" ht="24" customHeight="1">
       <c r="A400" s="34"/>
@@ -16198,6 +16601,7 @@
       <c r="C400" s="24"/>
       <c r="D400" s="24"/>
       <c r="E400" s="24"/>
+      <c r="F400" s="24"/>
     </row>
     <row r="401" ht="24" customHeight="1">
       <c r="A401" s="34"/>
@@ -16205,6 +16609,7 @@
       <c r="C401" s="24"/>
       <c r="D401" s="24"/>
       <c r="E401" s="24"/>
+      <c r="F401" s="24"/>
     </row>
     <row r="402" ht="24" customHeight="1">
       <c r="A402" s="34"/>
@@ -16212,6 +16617,7 @@
       <c r="C402" s="24"/>
       <c r="D402" s="24"/>
       <c r="E402" s="24"/>
+      <c r="F402" s="24"/>
     </row>
     <row r="403" ht="24" customHeight="1">
       <c r="A403" s="34"/>
@@ -16219,6 +16625,7 @@
       <c r="C403" s="24"/>
       <c r="D403" s="24"/>
       <c r="E403" s="24"/>
+      <c r="F403" s="24"/>
     </row>
     <row r="404" ht="24" customHeight="1">
       <c r="A404" s="34"/>
@@ -16226,6 +16633,7 @@
       <c r="C404" s="24"/>
       <c r="D404" s="24"/>
       <c r="E404" s="24"/>
+      <c r="F404" s="24"/>
     </row>
     <row r="405" ht="24" customHeight="1">
       <c r="A405" s="34"/>
@@ -16233,6 +16641,7 @@
       <c r="C405" s="24"/>
       <c r="D405" s="24"/>
       <c r="E405" s="24"/>
+      <c r="F405" s="24"/>
     </row>
     <row r="406" ht="24" customHeight="1">
       <c r="A406" s="34"/>
@@ -16240,6 +16649,7 @@
       <c r="C406" s="24"/>
       <c r="D406" s="24"/>
       <c r="E406" s="24"/>
+      <c r="F406" s="24"/>
     </row>
     <row r="407" ht="24" customHeight="1">
       <c r="A407" s="34"/>
@@ -16247,6 +16657,7 @@
       <c r="C407" s="24"/>
       <c r="D407" s="24"/>
       <c r="E407" s="24"/>
+      <c r="F407" s="24"/>
     </row>
     <row r="408" ht="24" customHeight="1">
       <c r="A408" s="34"/>
@@ -16254,6 +16665,7 @@
       <c r="C408" s="24"/>
       <c r="D408" s="24"/>
       <c r="E408" s="24"/>
+      <c r="F408" s="24"/>
     </row>
     <row r="409" ht="24" customHeight="1">
       <c r="A409" s="34"/>
@@ -16261,6 +16673,7 @@
       <c r="C409" s="24"/>
       <c r="D409" s="24"/>
       <c r="E409" s="24"/>
+      <c r="F409" s="24"/>
     </row>
     <row r="410" ht="24" customHeight="1">
       <c r="A410" s="34"/>
@@ -16268,6 +16681,7 @@
       <c r="C410" s="24"/>
       <c r="D410" s="24"/>
       <c r="E410" s="24"/>
+      <c r="F410" s="24"/>
     </row>
     <row r="411" ht="24" customHeight="1">
       <c r="A411" s="34"/>
@@ -16275,6 +16689,7 @@
       <c r="C411" s="24"/>
       <c r="D411" s="24"/>
       <c r="E411" s="24"/>
+      <c r="F411" s="24"/>
     </row>
     <row r="412" ht="24" customHeight="1">
       <c r="A412" s="34"/>
@@ -16282,6 +16697,7 @@
       <c r="C412" s="24"/>
       <c r="D412" s="24"/>
       <c r="E412" s="24"/>
+      <c r="F412" s="24"/>
     </row>
     <row r="413" ht="24" customHeight="1">
       <c r="A413" s="34"/>
@@ -16289,6 +16705,7 @@
       <c r="C413" s="24"/>
       <c r="D413" s="24"/>
       <c r="E413" s="24"/>
+      <c r="F413" s="24"/>
     </row>
     <row r="414" ht="24" customHeight="1">
       <c r="A414" s="34"/>
@@ -16296,6 +16713,7 @@
       <c r="C414" s="24"/>
       <c r="D414" s="24"/>
       <c r="E414" s="24"/>
+      <c r="F414" s="24"/>
     </row>
     <row r="415" ht="24" customHeight="1">
       <c r="A415" s="34"/>
@@ -16303,6 +16721,7 @@
       <c r="C415" s="24"/>
       <c r="D415" s="24"/>
       <c r="E415" s="24"/>
+      <c r="F415" s="24"/>
     </row>
     <row r="416" ht="24" customHeight="1">
       <c r="A416" s="34"/>
@@ -16310,6 +16729,7 @@
       <c r="C416" s="24"/>
       <c r="D416" s="24"/>
       <c r="E416" s="24"/>
+      <c r="F416" s="24"/>
     </row>
     <row r="417" ht="24" customHeight="1">
       <c r="A417" s="34"/>
@@ -16317,6 +16737,7 @@
       <c r="C417" s="24"/>
       <c r="D417" s="24"/>
       <c r="E417" s="24"/>
+      <c r="F417" s="24"/>
     </row>
     <row r="418" ht="24" customHeight="1">
       <c r="A418" s="34"/>
@@ -16324,6 +16745,7 @@
       <c r="C418" s="24"/>
       <c r="D418" s="24"/>
       <c r="E418" s="24"/>
+      <c r="F418" s="24"/>
     </row>
     <row r="419" ht="24" customHeight="1">
       <c r="A419" s="34"/>
@@ -16331,6 +16753,7 @@
       <c r="C419" s="24"/>
       <c r="D419" s="24"/>
       <c r="E419" s="24"/>
+      <c r="F419" s="24"/>
     </row>
     <row r="420" ht="24" customHeight="1">
       <c r="A420" s="34"/>
@@ -16338,6 +16761,7 @@
       <c r="C420" s="24"/>
       <c r="D420" s="24"/>
       <c r="E420" s="24"/>
+      <c r="F420" s="24"/>
     </row>
     <row r="421" ht="24" customHeight="1">
       <c r="A421" s="34"/>
@@ -16345,6 +16769,7 @@
       <c r="C421" s="24"/>
       <c r="D421" s="24"/>
       <c r="E421" s="24"/>
+      <c r="F421" s="24"/>
     </row>
     <row r="422" ht="24" customHeight="1">
       <c r="A422" s="34"/>
@@ -16352,6 +16777,7 @@
       <c r="C422" s="24"/>
       <c r="D422" s="24"/>
       <c r="E422" s="24"/>
+      <c r="F422" s="24"/>
     </row>
     <row r="423" ht="24" customHeight="1">
       <c r="A423" s="34"/>
@@ -16359,6 +16785,7 @@
       <c r="C423" s="24"/>
       <c r="D423" s="24"/>
       <c r="E423" s="24"/>
+      <c r="F423" s="24"/>
     </row>
     <row r="424" ht="24" customHeight="1">
       <c r="A424" s="34"/>
@@ -16366,6 +16793,7 @@
       <c r="C424" s="24"/>
       <c r="D424" s="24"/>
       <c r="E424" s="24"/>
+      <c r="F424" s="24"/>
     </row>
     <row r="425" ht="24" customHeight="1">
       <c r="A425" s="34"/>
@@ -16373,6 +16801,7 @@
       <c r="C425" s="24"/>
       <c r="D425" s="24"/>
       <c r="E425" s="24"/>
+      <c r="F425" s="24"/>
     </row>
     <row r="426" ht="24" customHeight="1">
       <c r="A426" s="34"/>
@@ -16380,6 +16809,7 @@
       <c r="C426" s="24"/>
       <c r="D426" s="24"/>
       <c r="E426" s="24"/>
+      <c r="F426" s="24"/>
     </row>
     <row r="427" ht="24" customHeight="1">
       <c r="A427" s="34"/>
@@ -16387,6 +16817,7 @@
       <c r="C427" s="24"/>
       <c r="D427" s="24"/>
       <c r="E427" s="24"/>
+      <c r="F427" s="24"/>
     </row>
     <row r="428" ht="24" customHeight="1">
       <c r="A428" s="34"/>
@@ -16394,6 +16825,7 @@
       <c r="C428" s="24"/>
       <c r="D428" s="24"/>
       <c r="E428" s="24"/>
+      <c r="F428" s="24"/>
     </row>
     <row r="429" ht="24" customHeight="1">
       <c r="A429" s="34"/>
@@ -16401,6 +16833,7 @@
       <c r="C429" s="24"/>
       <c r="D429" s="24"/>
       <c r="E429" s="24"/>
+      <c r="F429" s="24"/>
     </row>
     <row r="430" ht="24" customHeight="1">
       <c r="A430" s="34"/>
@@ -16408,6 +16841,7 @@
       <c r="C430" s="24"/>
       <c r="D430" s="24"/>
       <c r="E430" s="24"/>
+      <c r="F430" s="24"/>
     </row>
     <row r="431" ht="24" customHeight="1">
       <c r="A431" s="34"/>
@@ -16415,6 +16849,7 @@
       <c r="C431" s="24"/>
       <c r="D431" s="24"/>
       <c r="E431" s="24"/>
+      <c r="F431" s="24"/>
     </row>
     <row r="432" ht="24" customHeight="1">
       <c r="A432" s="34"/>
@@ -16422,6 +16857,7 @@
       <c r="C432" s="24"/>
       <c r="D432" s="24"/>
       <c r="E432" s="24"/>
+      <c r="F432" s="24"/>
     </row>
     <row r="433" ht="24" customHeight="1">
       <c r="A433" s="34"/>
@@ -16429,6 +16865,7 @@
       <c r="C433" s="24"/>
       <c r="D433" s="24"/>
       <c r="E433" s="24"/>
+      <c r="F433" s="24"/>
     </row>
     <row r="434" ht="24" customHeight="1">
       <c r="A434" s="34"/>
@@ -16436,6 +16873,7 @@
       <c r="C434" s="24"/>
       <c r="D434" s="24"/>
       <c r="E434" s="24"/>
+      <c r="F434" s="24"/>
     </row>
     <row r="435" ht="24" customHeight="1">
       <c r="A435" s="34"/>
@@ -16443,6 +16881,7 @@
       <c r="C435" s="24"/>
       <c r="D435" s="24"/>
       <c r="E435" s="24"/>
+      <c r="F435" s="24"/>
     </row>
     <row r="436" ht="24" customHeight="1">
       <c r="A436" s="34"/>
@@ -16450,6 +16889,7 @@
       <c r="C436" s="24"/>
       <c r="D436" s="24"/>
       <c r="E436" s="24"/>
+      <c r="F436" s="24"/>
     </row>
     <row r="437" ht="24" customHeight="1">
       <c r="A437" s="34"/>
@@ -16457,6 +16897,7 @@
       <c r="C437" s="24"/>
       <c r="D437" s="24"/>
       <c r="E437" s="24"/>
+      <c r="F437" s="24"/>
     </row>
     <row r="438" ht="24" customHeight="1">
       <c r="A438" s="34"/>
@@ -16464,6 +16905,7 @@
       <c r="C438" s="24"/>
       <c r="D438" s="24"/>
       <c r="E438" s="24"/>
+      <c r="F438" s="24"/>
     </row>
     <row r="439" ht="24" customHeight="1">
       <c r="A439" s="34"/>
@@ -16471,6 +16913,7 @@
       <c r="C439" s="24"/>
       <c r="D439" s="24"/>
       <c r="E439" s="24"/>
+      <c r="F439" s="24"/>
     </row>
     <row r="440" ht="24" customHeight="1">
       <c r="A440" s="34"/>
@@ -16478,6 +16921,7 @@
       <c r="C440" s="24"/>
       <c r="D440" s="24"/>
       <c r="E440" s="24"/>
+      <c r="F440" s="24"/>
     </row>
     <row r="441" ht="24" customHeight="1">
       <c r="A441" s="34"/>
@@ -16485,6 +16929,7 @@
       <c r="C441" s="24"/>
       <c r="D441" s="24"/>
       <c r="E441" s="24"/>
+      <c r="F441" s="24"/>
     </row>
     <row r="442" ht="24" customHeight="1">
       <c r="A442" s="34"/>
@@ -16492,6 +16937,7 @@
       <c r="C442" s="24"/>
       <c r="D442" s="24"/>
       <c r="E442" s="24"/>
+      <c r="F442" s="24"/>
     </row>
     <row r="443" ht="24" customHeight="1">
       <c r="A443" s="34"/>
@@ -16499,6 +16945,7 @@
       <c r="C443" s="24"/>
       <c r="D443" s="24"/>
       <c r="E443" s="24"/>
+      <c r="F443" s="24"/>
     </row>
     <row r="444" ht="24" customHeight="1">
       <c r="A444" s="34"/>
@@ -16506,6 +16953,7 @@
       <c r="C444" s="24"/>
       <c r="D444" s="24"/>
       <c r="E444" s="24"/>
+      <c r="F444" s="24"/>
     </row>
     <row r="445" ht="24" customHeight="1">
       <c r="A445" s="34"/>
@@ -16513,6 +16961,7 @@
       <c r="C445" s="24"/>
       <c r="D445" s="24"/>
       <c r="E445" s="24"/>
+      <c r="F445" s="24"/>
     </row>
     <row r="446" ht="24" customHeight="1">
       <c r="A446" s="34"/>
@@ -16520,6 +16969,7 @@
       <c r="C446" s="24"/>
       <c r="D446" s="24"/>
       <c r="E446" s="24"/>
+      <c r="F446" s="24"/>
     </row>
     <row r="447" ht="24" customHeight="1">
       <c r="A447" s="34"/>
@@ -16527,6 +16977,7 @@
       <c r="C447" s="24"/>
       <c r="D447" s="24"/>
       <c r="E447" s="24"/>
+      <c r="F447" s="24"/>
     </row>
     <row r="448" ht="24" customHeight="1">
       <c r="A448" s="34"/>
@@ -16534,6 +16985,7 @@
       <c r="C448" s="24"/>
       <c r="D448" s="24"/>
       <c r="E448" s="24"/>
+      <c r="F448" s="24"/>
     </row>
     <row r="449" ht="24" customHeight="1">
       <c r="A449" s="34"/>
@@ -16541,6 +16993,7 @@
       <c r="C449" s="24"/>
       <c r="D449" s="24"/>
       <c r="E449" s="24"/>
+      <c r="F449" s="24"/>
     </row>
     <row r="450" ht="24" customHeight="1">
       <c r="A450" s="34"/>
@@ -16548,6 +17001,7 @@
       <c r="C450" s="24"/>
       <c r="D450" s="24"/>
       <c r="E450" s="24"/>
+      <c r="F450" s="24"/>
     </row>
     <row r="451" ht="24" customHeight="1">
       <c r="A451" s="34"/>
@@ -16555,6 +17009,7 @@
       <c r="C451" s="24"/>
       <c r="D451" s="24"/>
       <c r="E451" s="24"/>
+      <c r="F451" s="24"/>
     </row>
     <row r="452" ht="24" customHeight="1">
       <c r="A452" s="34"/>
@@ -16562,6 +17017,7 @@
       <c r="C452" s="24"/>
       <c r="D452" s="24"/>
       <c r="E452" s="24"/>
+      <c r="F452" s="24"/>
     </row>
     <row r="453" ht="24" customHeight="1">
       <c r="A453" s="34"/>
@@ -16569,6 +17025,7 @@
       <c r="C453" s="24"/>
       <c r="D453" s="24"/>
       <c r="E453" s="24"/>
+      <c r="F453" s="24"/>
     </row>
     <row r="454" ht="24" customHeight="1">
       <c r="A454" s="34"/>
@@ -16576,6 +17033,7 @@
       <c r="C454" s="24"/>
       <c r="D454" s="24"/>
       <c r="E454" s="24"/>
+      <c r="F454" s="24"/>
     </row>
     <row r="455" ht="24" customHeight="1">
       <c r="A455" s="34"/>
@@ -16583,6 +17041,7 @@
       <c r="C455" s="24"/>
       <c r="D455" s="24"/>
       <c r="E455" s="24"/>
+      <c r="F455" s="24"/>
     </row>
     <row r="456" ht="24" customHeight="1">
       <c r="A456" s="34"/>
@@ -16590,6 +17049,7 @@
       <c r="C456" s="24"/>
       <c r="D456" s="24"/>
       <c r="E456" s="24"/>
+      <c r="F456" s="24"/>
     </row>
     <row r="457" ht="24" customHeight="1">
       <c r="A457" s="34"/>
@@ -16597,6 +17057,7 @@
       <c r="C457" s="24"/>
       <c r="D457" s="24"/>
       <c r="E457" s="24"/>
+      <c r="F457" s="24"/>
     </row>
     <row r="458" ht="24" customHeight="1">
       <c r="A458" s="34"/>
@@ -16604,6 +17065,7 @@
       <c r="C458" s="24"/>
       <c r="D458" s="24"/>
       <c r="E458" s="24"/>
+      <c r="F458" s="24"/>
     </row>
     <row r="459" ht="24" customHeight="1">
       <c r="A459" s="34"/>
@@ -16611,6 +17073,7 @@
       <c r="C459" s="24"/>
       <c r="D459" s="24"/>
       <c r="E459" s="24"/>
+      <c r="F459" s="24"/>
     </row>
     <row r="460" ht="24" customHeight="1">
       <c r="A460" s="34"/>
@@ -16618,6 +17081,7 @@
       <c r="C460" s="24"/>
       <c r="D460" s="24"/>
       <c r="E460" s="24"/>
+      <c r="F460" s="24"/>
     </row>
     <row r="461" ht="24" customHeight="1">
       <c r="A461" s="34"/>
@@ -16625,6 +17089,7 @@
       <c r="C461" s="24"/>
       <c r="D461" s="24"/>
       <c r="E461" s="24"/>
+      <c r="F461" s="24"/>
     </row>
     <row r="462" ht="24" customHeight="1">
       <c r="A462" s="34"/>
@@ -16632,6 +17097,7 @@
       <c r="C462" s="24"/>
       <c r="D462" s="24"/>
       <c r="E462" s="24"/>
+      <c r="F462" s="24"/>
     </row>
     <row r="463" ht="24" customHeight="1">
       <c r="A463" s="34"/>
@@ -16639,6 +17105,7 @@
       <c r="C463" s="24"/>
       <c r="D463" s="24"/>
       <c r="E463" s="24"/>
+      <c r="F463" s="24"/>
     </row>
     <row r="464" ht="24" customHeight="1">
       <c r="A464" s="34"/>
@@ -16646,6 +17113,7 @@
       <c r="C464" s="24"/>
       <c r="D464" s="24"/>
       <c r="E464" s="24"/>
+      <c r="F464" s="24"/>
     </row>
     <row r="465" ht="24" customHeight="1">
       <c r="A465" s="34"/>
@@ -16653,6 +17121,7 @@
       <c r="C465" s="24"/>
       <c r="D465" s="24"/>
       <c r="E465" s="24"/>
+      <c r="F465" s="24"/>
     </row>
     <row r="466" ht="24" customHeight="1">
       <c r="A466" s="34"/>
@@ -16660,6 +17129,7 @@
       <c r="C466" s="24"/>
       <c r="D466" s="24"/>
       <c r="E466" s="24"/>
+      <c r="F466" s="24"/>
     </row>
     <row r="467" ht="24" customHeight="1">
       <c r="A467" s="34"/>
@@ -16667,6 +17137,7 @@
       <c r="C467" s="24"/>
       <c r="D467" s="24"/>
       <c r="E467" s="24"/>
+      <c r="F467" s="24"/>
     </row>
     <row r="468" ht="24" customHeight="1">
       <c r="A468" s="34"/>
@@ -16674,6 +17145,7 @@
       <c r="C468" s="24"/>
       <c r="D468" s="24"/>
       <c r="E468" s="24"/>
+      <c r="F468" s="24"/>
     </row>
     <row r="469" ht="24" customHeight="1">
       <c r="A469" s="34"/>
@@ -16681,6 +17153,7 @@
       <c r="C469" s="24"/>
       <c r="D469" s="24"/>
       <c r="E469" s="24"/>
+      <c r="F469" s="24"/>
     </row>
     <row r="470" ht="24" customHeight="1">
       <c r="A470" s="34"/>
@@ -16688,6 +17161,7 @@
       <c r="C470" s="24"/>
       <c r="D470" s="24"/>
       <c r="E470" s="24"/>
+      <c r="F470" s="24"/>
     </row>
     <row r="471" ht="24" customHeight="1">
       <c r="A471" s="34"/>
@@ -16695,6 +17169,7 @@
       <c r="C471" s="24"/>
       <c r="D471" s="24"/>
       <c r="E471" s="24"/>
+      <c r="F471" s="24"/>
     </row>
     <row r="472" ht="24" customHeight="1">
       <c r="A472" s="34"/>
@@ -16702,6 +17177,7 @@
       <c r="C472" s="24"/>
       <c r="D472" s="24"/>
       <c r="E472" s="24"/>
+      <c r="F472" s="24"/>
     </row>
     <row r="473" ht="24" customHeight="1">
       <c r="A473" s="34"/>
@@ -16709,6 +17185,7 @@
       <c r="C473" s="24"/>
       <c r="D473" s="24"/>
       <c r="E473" s="24"/>
+      <c r="F473" s="24"/>
     </row>
     <row r="474" ht="24" customHeight="1">
       <c r="A474" s="34"/>
@@ -16716,6 +17193,7 @@
       <c r="C474" s="24"/>
       <c r="D474" s="24"/>
       <c r="E474" s="24"/>
+      <c r="F474" s="24"/>
     </row>
     <row r="475" ht="24" customHeight="1">
       <c r="A475" s="34"/>
@@ -16723,6 +17201,7 @@
       <c r="C475" s="24"/>
       <c r="D475" s="24"/>
       <c r="E475" s="24"/>
+      <c r="F475" s="24"/>
     </row>
     <row r="476" ht="24" customHeight="1">
       <c r="A476" s="34"/>
@@ -16730,6 +17209,7 @@
       <c r="C476" s="24"/>
       <c r="D476" s="24"/>
       <c r="E476" s="24"/>
+      <c r="F476" s="24"/>
     </row>
     <row r="477" ht="24" customHeight="1">
       <c r="A477" s="34"/>
@@ -16737,6 +17217,7 @@
       <c r="C477" s="24"/>
       <c r="D477" s="24"/>
       <c r="E477" s="24"/>
+      <c r="F477" s="24"/>
     </row>
     <row r="478" ht="24" customHeight="1">
       <c r="A478" s="34"/>
@@ -16744,6 +17225,7 @@
       <c r="C478" s="24"/>
       <c r="D478" s="24"/>
       <c r="E478" s="24"/>
+      <c r="F478" s="24"/>
     </row>
     <row r="479" ht="24" customHeight="1">
       <c r="A479" s="34"/>
@@ -16751,6 +17233,7 @@
       <c r="C479" s="24"/>
       <c r="D479" s="24"/>
       <c r="E479" s="24"/>
+      <c r="F479" s="24"/>
     </row>
     <row r="480" ht="24" customHeight="1">
       <c r="A480" s="34"/>
@@ -16758,6 +17241,7 @@
       <c r="C480" s="24"/>
       <c r="D480" s="24"/>
       <c r="E480" s="24"/>
+      <c r="F480" s="24"/>
     </row>
     <row r="481" ht="24" customHeight="1">
       <c r="A481" s="34"/>
@@ -16765,6 +17249,7 @@
       <c r="C481" s="24"/>
       <c r="D481" s="24"/>
       <c r="E481" s="24"/>
+      <c r="F481" s="24"/>
     </row>
     <row r="482" ht="24" customHeight="1">
       <c r="A482" s="34"/>
@@ -16772,6 +17257,7 @@
       <c r="C482" s="24"/>
       <c r="D482" s="24"/>
       <c r="E482" s="24"/>
+      <c r="F482" s="24"/>
     </row>
     <row r="483" ht="24" customHeight="1">
       <c r="A483" s="34"/>
@@ -16779,6 +17265,7 @@
       <c r="C483" s="24"/>
       <c r="D483" s="24"/>
       <c r="E483" s="24"/>
+      <c r="F483" s="24"/>
     </row>
     <row r="484" ht="24" customHeight="1">
       <c r="A484" s="34"/>
@@ -16786,6 +17273,7 @@
       <c r="C484" s="24"/>
       <c r="D484" s="24"/>
       <c r="E484" s="24"/>
+      <c r="F484" s="24"/>
     </row>
     <row r="485" ht="24" customHeight="1">
       <c r="A485" s="34"/>
@@ -16793,6 +17281,7 @@
       <c r="C485" s="24"/>
       <c r="D485" s="24"/>
       <c r="E485" s="24"/>
+      <c r="F485" s="24"/>
     </row>
     <row r="486" ht="24" customHeight="1">
       <c r="A486" s="34"/>
@@ -16800,6 +17289,7 @@
       <c r="C486" s="24"/>
       <c r="D486" s="24"/>
       <c r="E486" s="24"/>
+      <c r="F486" s="24"/>
     </row>
     <row r="487" ht="24" customHeight="1">
       <c r="A487" s="34"/>
@@ -16807,6 +17297,7 @@
       <c r="C487" s="24"/>
       <c r="D487" s="24"/>
       <c r="E487" s="24"/>
+      <c r="F487" s="24"/>
     </row>
     <row r="488" ht="24" customHeight="1">
       <c r="A488" s="34"/>
@@ -16814,6 +17305,7 @@
       <c r="C488" s="24"/>
       <c r="D488" s="24"/>
       <c r="E488" s="24"/>
+      <c r="F488" s="24"/>
     </row>
     <row r="489" ht="24" customHeight="1">
       <c r="A489" s="34"/>
@@ -16821,6 +17313,7 @@
       <c r="C489" s="24"/>
       <c r="D489" s="24"/>
       <c r="E489" s="24"/>
+      <c r="F489" s="24"/>
     </row>
     <row r="490" ht="24" customHeight="1">
       <c r="A490" s="34"/>
@@ -16828,6 +17321,7 @@
       <c r="C490" s="24"/>
       <c r="D490" s="24"/>
       <c r="E490" s="24"/>
+      <c r="F490" s="24"/>
     </row>
     <row r="491" ht="24" customHeight="1">
       <c r="A491" s="34"/>
@@ -16835,6 +17329,7 @@
       <c r="C491" s="24"/>
       <c r="D491" s="24"/>
       <c r="E491" s="24"/>
+      <c r="F491" s="24"/>
     </row>
     <row r="492" ht="24" customHeight="1">
       <c r="A492" s="34"/>
@@ -16842,6 +17337,7 @@
       <c r="C492" s="24"/>
       <c r="D492" s="24"/>
       <c r="E492" s="24"/>
+      <c r="F492" s="24"/>
     </row>
     <row r="493" ht="24" customHeight="1">
       <c r="A493" s="34"/>
@@ -16849,6 +17345,7 @@
       <c r="C493" s="24"/>
       <c r="D493" s="24"/>
       <c r="E493" s="24"/>
+      <c r="F493" s="24"/>
     </row>
     <row r="494" ht="24" customHeight="1">
       <c r="A494" s="34"/>
@@ -16856,6 +17353,7 @@
       <c r="C494" s="24"/>
       <c r="D494" s="24"/>
       <c r="E494" s="24"/>
+      <c r="F494" s="24"/>
     </row>
     <row r="495" ht="24" customHeight="1">
       <c r="A495" s="34"/>
@@ -16863,6 +17361,7 @@
       <c r="C495" s="24"/>
       <c r="D495" s="24"/>
       <c r="E495" s="24"/>
+      <c r="F495" s="24"/>
     </row>
     <row r="496" ht="24" customHeight="1">
       <c r="A496" s="34"/>
@@ -16870,6 +17369,7 @@
       <c r="C496" s="24"/>
       <c r="D496" s="24"/>
       <c r="E496" s="24"/>
+      <c r="F496" s="24"/>
     </row>
     <row r="497" ht="24" customHeight="1">
       <c r="A497" s="34"/>
@@ -16877,6 +17377,7 @@
       <c r="C497" s="24"/>
       <c r="D497" s="24"/>
       <c r="E497" s="24"/>
+      <c r="F497" s="24"/>
     </row>
     <row r="498" ht="24" customHeight="1">
       <c r="A498" s="34"/>
@@ -16884,6 +17385,7 @@
       <c r="C498" s="24"/>
       <c r="D498" s="24"/>
       <c r="E498" s="24"/>
+      <c r="F498" s="24"/>
     </row>
     <row r="499" ht="24" customHeight="1">
       <c r="A499" s="34"/>
@@ -16891,6 +17393,7 @@
       <c r="C499" s="24"/>
       <c r="D499" s="24"/>
       <c r="E499" s="24"/>
+      <c r="F499" s="24"/>
     </row>
     <row r="500" ht="24" customHeight="1">
       <c r="A500" s="34"/>
@@ -16898,6 +17401,7 @@
       <c r="C500" s="24"/>
       <c r="D500" s="24"/>
       <c r="E500" s="24"/>
+      <c r="F500" s="24"/>
     </row>
     <row r="501" ht="24" customHeight="1">
       <c r="A501" s="34"/>
@@ -16905,6 +17409,7 @@
       <c r="C501" s="24"/>
       <c r="D501" s="24"/>
       <c r="E501" s="24"/>
+      <c r="F501" s="24"/>
     </row>
     <row r="502" ht="24" customHeight="1">
       <c r="A502" s="34"/>
@@ -16912,6 +17417,7 @@
       <c r="C502" s="24"/>
       <c r="D502" s="24"/>
       <c r="E502" s="24"/>
+      <c r="F502" s="24"/>
     </row>
     <row r="503" ht="24" customHeight="1">
       <c r="A503" s="34"/>
@@ -16919,6 +17425,7 @@
       <c r="C503" s="24"/>
       <c r="D503" s="24"/>
       <c r="E503" s="24"/>
+      <c r="F503" s="24"/>
     </row>
     <row r="504" ht="24" customHeight="1">
       <c r="A504" s="34"/>
@@ -16926,6 +17433,7 @@
       <c r="C504" s="24"/>
       <c r="D504" s="24"/>
       <c r="E504" s="24"/>
+      <c r="F504" s="24"/>
     </row>
     <row r="505" ht="24" customHeight="1">
       <c r="A505" s="34"/>
@@ -16933,6 +17441,7 @@
       <c r="C505" s="24"/>
       <c r="D505" s="24"/>
       <c r="E505" s="24"/>
+      <c r="F505" s="24"/>
     </row>
     <row r="506" ht="24" customHeight="1">
       <c r="A506" s="34"/>
@@ -16940,6 +17449,7 @@
       <c r="C506" s="24"/>
       <c r="D506" s="24"/>
       <c r="E506" s="24"/>
+      <c r="F506" s="24"/>
     </row>
     <row r="507" ht="24" customHeight="1">
       <c r="A507" s="34"/>
@@ -16947,6 +17457,7 @@
       <c r="C507" s="24"/>
       <c r="D507" s="24"/>
       <c r="E507" s="24"/>
+      <c r="F507" s="24"/>
     </row>
     <row r="508" ht="24" customHeight="1">
       <c r="A508" s="34"/>
@@ -16954,6 +17465,7 @@
       <c r="C508" s="24"/>
       <c r="D508" s="24"/>
       <c r="E508" s="24"/>
+      <c r="F508" s="24"/>
     </row>
     <row r="509" ht="24" customHeight="1">
       <c r="A509" s="34"/>
@@ -16961,6 +17473,7 @@
       <c r="C509" s="24"/>
       <c r="D509" s="24"/>
       <c r="E509" s="24"/>
+      <c r="F509" s="24"/>
     </row>
     <row r="510" ht="24" customHeight="1">
       <c r="A510" s="34"/>
@@ -16968,6 +17481,7 @@
       <c r="C510" s="24"/>
       <c r="D510" s="24"/>
       <c r="E510" s="24"/>
+      <c r="F510" s="24"/>
     </row>
     <row r="511" ht="24" customHeight="1">
       <c r="A511" s="34"/>
@@ -16975,6 +17489,7 @@
       <c r="C511" s="24"/>
       <c r="D511" s="24"/>
       <c r="E511" s="24"/>
+      <c r="F511" s="24"/>
     </row>
     <row r="512" ht="24" customHeight="1">
       <c r="A512" s="34"/>
@@ -16982,6 +17497,7 @@
       <c r="C512" s="24"/>
       <c r="D512" s="24"/>
       <c r="E512" s="24"/>
+      <c r="F512" s="24"/>
     </row>
     <row r="513" ht="24" customHeight="1">
       <c r="A513" s="34"/>
@@ -16989,6 +17505,7 @@
       <c r="C513" s="24"/>
       <c r="D513" s="24"/>
       <c r="E513" s="24"/>
+      <c r="F513" s="24"/>
     </row>
     <row r="514" ht="24" customHeight="1">
       <c r="A514" s="34"/>
@@ -16996,6 +17513,7 @@
       <c r="C514" s="24"/>
       <c r="D514" s="24"/>
       <c r="E514" s="24"/>
+      <c r="F514" s="24"/>
     </row>
     <row r="515" ht="24" customHeight="1">
       <c r="A515" s="34"/>
@@ -17003,6 +17521,7 @@
       <c r="C515" s="24"/>
       <c r="D515" s="24"/>
       <c r="E515" s="24"/>
+      <c r="F515" s="24"/>
     </row>
     <row r="516" ht="24" customHeight="1">
       <c r="A516" s="34"/>
@@ -17010,6 +17529,7 @@
       <c r="C516" s="24"/>
       <c r="D516" s="24"/>
       <c r="E516" s="24"/>
+      <c r="F516" s="24"/>
     </row>
     <row r="517" ht="24" customHeight="1">
       <c r="A517" s="34"/>
@@ -17017,6 +17537,7 @@
       <c r="C517" s="24"/>
       <c r="D517" s="24"/>
       <c r="E517" s="24"/>
+      <c r="F517" s="24"/>
     </row>
     <row r="518" ht="24" customHeight="1">
       <c r="A518" s="34"/>
@@ -17024,6 +17545,7 @@
       <c r="C518" s="24"/>
       <c r="D518" s="24"/>
       <c r="E518" s="24"/>
+      <c r="F518" s="24"/>
     </row>
     <row r="519" ht="24" customHeight="1">
       <c r="A519" s="34"/>
@@ -17031,6 +17553,7 @@
       <c r="C519" s="24"/>
       <c r="D519" s="24"/>
       <c r="E519" s="24"/>
+      <c r="F519" s="24"/>
     </row>
     <row r="520" ht="24" customHeight="1">
       <c r="A520" s="34"/>
@@ -17038,6 +17561,7 @@
       <c r="C520" s="24"/>
       <c r="D520" s="24"/>
       <c r="E520" s="24"/>
+      <c r="F520" s="24"/>
     </row>
     <row r="521" ht="24" customHeight="1">
       <c r="A521" s="34"/>
@@ -17045,6 +17569,7 @@
       <c r="C521" s="24"/>
       <c r="D521" s="24"/>
       <c r="E521" s="24"/>
+      <c r="F521" s="24"/>
     </row>
     <row r="522" ht="24" customHeight="1">
       <c r="A522" s="34"/>
@@ -17052,6 +17577,7 @@
       <c r="C522" s="24"/>
       <c r="D522" s="24"/>
       <c r="E522" s="24"/>
+      <c r="F522" s="24"/>
     </row>
     <row r="523" ht="24" customHeight="1">
       <c r="A523" s="34"/>
@@ -17059,6 +17585,7 @@
       <c r="C523" s="24"/>
       <c r="D523" s="24"/>
       <c r="E523" s="24"/>
+      <c r="F523" s="24"/>
     </row>
     <row r="524" ht="24" customHeight="1">
       <c r="A524" s="34"/>
@@ -17066,6 +17593,7 @@
       <c r="C524" s="24"/>
       <c r="D524" s="24"/>
       <c r="E524" s="24"/>
+      <c r="F524" s="24"/>
     </row>
     <row r="525" ht="24" customHeight="1">
       <c r="A525" s="34"/>
@@ -17073,6 +17601,7 @@
       <c r="C525" s="24"/>
       <c r="D525" s="24"/>
       <c r="E525" s="24"/>
+      <c r="F525" s="24"/>
     </row>
     <row r="526" ht="24" customHeight="1">
       <c r="A526" s="34"/>
@@ -17080,6 +17609,7 @@
       <c r="C526" s="24"/>
       <c r="D526" s="24"/>
       <c r="E526" s="24"/>
+      <c r="F526" s="24"/>
     </row>
     <row r="527" ht="24" customHeight="1">
       <c r="A527" s="34"/>
@@ -17087,6 +17617,7 @@
       <c r="C527" s="24"/>
       <c r="D527" s="24"/>
       <c r="E527" s="24"/>
+      <c r="F527" s="24"/>
     </row>
     <row r="528" ht="24" customHeight="1">
       <c r="A528" s="34"/>
@@ -17094,6 +17625,7 @@
       <c r="C528" s="24"/>
       <c r="D528" s="24"/>
       <c r="E528" s="24"/>
+      <c r="F528" s="24"/>
     </row>
     <row r="529" ht="24" customHeight="1">
       <c r="A529" s="34"/>
@@ -17101,6 +17633,7 @@
       <c r="C529" s="24"/>
       <c r="D529" s="24"/>
       <c r="E529" s="24"/>
+      <c r="F529" s="24"/>
     </row>
     <row r="530" ht="24" customHeight="1">
       <c r="A530" s="34"/>
@@ -17108,6 +17641,7 @@
       <c r="C530" s="24"/>
       <c r="D530" s="24"/>
       <c r="E530" s="24"/>
+      <c r="F530" s="24"/>
     </row>
     <row r="531" ht="24" customHeight="1">
       <c r="A531" s="34"/>
@@ -17115,6 +17649,7 @@
       <c r="C531" s="24"/>
       <c r="D531" s="24"/>
       <c r="E531" s="24"/>
+      <c r="F531" s="24"/>
     </row>
     <row r="532" ht="24" customHeight="1">
       <c r="A532" s="34"/>
@@ -17122,6 +17657,7 @@
       <c r="C532" s="24"/>
       <c r="D532" s="24"/>
       <c r="E532" s="24"/>
+      <c r="F532" s="24"/>
     </row>
     <row r="533" ht="24" customHeight="1">
       <c r="A533" s="34"/>
@@ -17129,6 +17665,7 @@
       <c r="C533" s="24"/>
       <c r="D533" s="24"/>
       <c r="E533" s="24"/>
+      <c r="F533" s="24"/>
     </row>
     <row r="534" ht="24" customHeight="1">
       <c r="A534" s="34"/>
@@ -17136,6 +17673,7 @@
       <c r="C534" s="24"/>
       <c r="D534" s="24"/>
       <c r="E534" s="24"/>
+      <c r="F534" s="24"/>
     </row>
     <row r="535" ht="24" customHeight="1">
       <c r="A535" s="34"/>
@@ -17143,6 +17681,7 @@
       <c r="C535" s="24"/>
       <c r="D535" s="24"/>
       <c r="E535" s="24"/>
+      <c r="F535" s="24"/>
     </row>
     <row r="536" ht="24" customHeight="1">
       <c r="A536" s="34"/>
@@ -17150,6 +17689,7 @@
       <c r="C536" s="24"/>
       <c r="D536" s="24"/>
       <c r="E536" s="24"/>
+      <c r="F536" s="24"/>
     </row>
     <row r="537" ht="24" customHeight="1">
       <c r="A537" s="34"/>
@@ -17157,6 +17697,7 @@
       <c r="C537" s="24"/>
       <c r="D537" s="24"/>
       <c r="E537" s="24"/>
+      <c r="F537" s="24"/>
     </row>
     <row r="538" ht="24" customHeight="1">
       <c r="A538" s="34"/>
@@ -17164,6 +17705,7 @@
       <c r="C538" s="24"/>
       <c r="D538" s="24"/>
       <c r="E538" s="24"/>
+      <c r="F538" s="24"/>
     </row>
     <row r="539" ht="24" customHeight="1">
       <c r="A539" s="34"/>
@@ -17171,6 +17713,7 @@
       <c r="C539" s="24"/>
       <c r="D539" s="24"/>
       <c r="E539" s="24"/>
+      <c r="F539" s="24"/>
     </row>
     <row r="540" ht="24" customHeight="1">
       <c r="A540" s="34"/>
@@ -17178,6 +17721,7 @@
       <c r="C540" s="24"/>
       <c r="D540" s="24"/>
       <c r="E540" s="24"/>
+      <c r="F540" s="24"/>
     </row>
     <row r="541" ht="24" customHeight="1">
       <c r="A541" s="34"/>
@@ -17185,6 +17729,7 @@
       <c r="C541" s="24"/>
       <c r="D541" s="24"/>
       <c r="E541" s="24"/>
+      <c r="F541" s="24"/>
     </row>
     <row r="542" ht="24" customHeight="1">
       <c r="A542" s="34"/>
@@ -17192,6 +17737,7 @@
       <c r="C542" s="24"/>
       <c r="D542" s="24"/>
       <c r="E542" s="24"/>
+      <c r="F542" s="24"/>
     </row>
     <row r="543" ht="24" customHeight="1">
       <c r="A543" s="34"/>
@@ -17199,6 +17745,7 @@
       <c r="C543" s="24"/>
       <c r="D543" s="24"/>
       <c r="E543" s="24"/>
+      <c r="F543" s="24"/>
     </row>
     <row r="544" ht="24" customHeight="1">
       <c r="A544" s="34"/>
@@ -17206,6 +17753,7 @@
       <c r="C544" s="24"/>
       <c r="D544" s="24"/>
       <c r="E544" s="24"/>
+      <c r="F544" s="24"/>
     </row>
     <row r="545" ht="24" customHeight="1">
       <c r="A545" s="34"/>
@@ -17213,6 +17761,7 @@
       <c r="C545" s="24"/>
       <c r="D545" s="24"/>
       <c r="E545" s="24"/>
+      <c r="F545" s="24"/>
     </row>
     <row r="546" ht="24" customHeight="1">
       <c r="A546" s="34"/>
@@ -17220,6 +17769,7 @@
       <c r="C546" s="24"/>
       <c r="D546" s="24"/>
       <c r="E546" s="24"/>
+      <c r="F546" s="24"/>
     </row>
     <row r="547" ht="24" customHeight="1">
       <c r="A547" s="34"/>
@@ -17227,6 +17777,7 @@
       <c r="C547" s="24"/>
       <c r="D547" s="24"/>
       <c r="E547" s="24"/>
+      <c r="F547" s="24"/>
     </row>
     <row r="548" ht="24" customHeight="1">
       <c r="A548" s="34"/>
@@ -17234,6 +17785,7 @@
       <c r="C548" s="24"/>
       <c r="D548" s="24"/>
       <c r="E548" s="24"/>
+      <c r="F548" s="24"/>
     </row>
     <row r="549" ht="24" customHeight="1">
       <c r="A549" s="34"/>
@@ -17241,6 +17793,7 @@
       <c r="C549" s="24"/>
       <c r="D549" s="24"/>
       <c r="E549" s="24"/>
+      <c r="F549" s="24"/>
     </row>
     <row r="550" ht="24" customHeight="1">
       <c r="A550" s="34"/>
@@ -17248,6 +17801,7 @@
       <c r="C550" s="24"/>
       <c r="D550" s="24"/>
       <c r="E550" s="24"/>
+      <c r="F550" s="24"/>
     </row>
     <row r="551" ht="24" customHeight="1">
       <c r="A551" s="34"/>
@@ -17255,6 +17809,7 @@
       <c r="C551" s="24"/>
       <c r="D551" s="24"/>
       <c r="E551" s="24"/>
+      <c r="F551" s="24"/>
     </row>
     <row r="552" ht="24" customHeight="1">
       <c r="A552" s="34"/>
@@ -17262,6 +17817,7 @@
       <c r="C552" s="24"/>
       <c r="D552" s="24"/>
       <c r="E552" s="24"/>
+      <c r="F552" s="24"/>
     </row>
     <row r="553" ht="24" customHeight="1">
       <c r="A553" s="34"/>
@@ -17269,6 +17825,7 @@
       <c r="C553" s="24"/>
       <c r="D553" s="24"/>
       <c r="E553" s="24"/>
+      <c r="F553" s="24"/>
     </row>
     <row r="554" ht="24" customHeight="1">
       <c r="A554" s="34"/>
@@ -17276,6 +17833,7 @@
       <c r="C554" s="24"/>
       <c r="D554" s="24"/>
       <c r="E554" s="24"/>
+      <c r="F554" s="24"/>
     </row>
     <row r="555" ht="24" customHeight="1">
       <c r="A555" s="34"/>
@@ -17283,6 +17841,7 @@
       <c r="C555" s="24"/>
       <c r="D555" s="24"/>
       <c r="E555" s="24"/>
+      <c r="F555" s="24"/>
     </row>
     <row r="556" ht="24" customHeight="1">
       <c r="A556" s="34"/>
@@ -17290,6 +17849,7 @@
       <c r="C556" s="24"/>
       <c r="D556" s="24"/>
       <c r="E556" s="24"/>
+      <c r="F556" s="24"/>
     </row>
     <row r="557" ht="24" customHeight="1">
       <c r="A557" s="34"/>
@@ -17297,6 +17857,7 @@
       <c r="C557" s="24"/>
       <c r="D557" s="24"/>
       <c r="E557" s="24"/>
+      <c r="F557" s="24"/>
     </row>
     <row r="558" ht="24" customHeight="1">
       <c r="A558" s="34"/>
@@ -17304,6 +17865,7 @@
       <c r="C558" s="24"/>
       <c r="D558" s="24"/>
       <c r="E558" s="24"/>
+      <c r="F558" s="24"/>
     </row>
     <row r="559" ht="24" customHeight="1">
       <c r="A559" s="34"/>
@@ -17311,6 +17873,7 @@
       <c r="C559" s="24"/>
       <c r="D559" s="24"/>
       <c r="E559" s="24"/>
+      <c r="F559" s="24"/>
     </row>
     <row r="560" ht="24" customHeight="1">
       <c r="A560" s="34"/>
@@ -17318,6 +17881,7 @@
       <c r="C560" s="24"/>
       <c r="D560" s="24"/>
       <c r="E560" s="24"/>
+      <c r="F560" s="24"/>
     </row>
     <row r="561" ht="24" customHeight="1">
       <c r="A561" s="34"/>
@@ -17325,6 +17889,7 @@
       <c r="C561" s="24"/>
       <c r="D561" s="24"/>
       <c r="E561" s="24"/>
+      <c r="F561" s="24"/>
     </row>
     <row r="562" ht="24" customHeight="1">
       <c r="A562" s="34"/>
@@ -17332,6 +17897,7 @@
       <c r="C562" s="24"/>
       <c r="D562" s="24"/>
       <c r="E562" s="24"/>
+      <c r="F562" s="24"/>
     </row>
     <row r="563" ht="24" customHeight="1">
       <c r="A563" s="34"/>
@@ -17339,6 +17905,7 @@
       <c r="C563" s="24"/>
       <c r="D563" s="24"/>
       <c r="E563" s="24"/>
+      <c r="F563" s="24"/>
     </row>
     <row r="564" ht="24" customHeight="1">
       <c r="A564" s="34"/>
@@ -17346,6 +17913,7 @@
       <c r="C564" s="24"/>
       <c r="D564" s="24"/>
       <c r="E564" s="24"/>
+      <c r="F564" s="24"/>
     </row>
     <row r="565" ht="24" customHeight="1">
       <c r="A565" s="34"/>
@@ -17353,6 +17921,7 @@
       <c r="C565" s="24"/>
       <c r="D565" s="24"/>
       <c r="E565" s="24"/>
+      <c r="F565" s="24"/>
     </row>
     <row r="566" ht="24" customHeight="1">
       <c r="A566" s="34"/>
@@ -17360,6 +17929,7 @@
       <c r="C566" s="24"/>
       <c r="D566" s="24"/>
       <c r="E566" s="24"/>
+      <c r="F566" s="24"/>
     </row>
     <row r="567" ht="24" customHeight="1">
       <c r="A567" s="34"/>
@@ -17367,6 +17937,7 @@
       <c r="C567" s="24"/>
       <c r="D567" s="24"/>
       <c r="E567" s="24"/>
+      <c r="F567" s="24"/>
     </row>
     <row r="568" ht="24" customHeight="1">
       <c r="A568" s="34"/>
@@ -17374,6 +17945,7 @@
       <c r="C568" s="24"/>
       <c r="D568" s="24"/>
       <c r="E568" s="24"/>
+      <c r="F568" s="24"/>
     </row>
     <row r="569" ht="24" customHeight="1">
       <c r="A569" s="34"/>
@@ -17381,6 +17953,7 @@
       <c r="C569" s="24"/>
       <c r="D569" s="24"/>
       <c r="E569" s="24"/>
+      <c r="F569" s="24"/>
     </row>
     <row r="570" ht="24" customHeight="1">
       <c r="A570" s="34"/>
@@ -17388,6 +17961,7 @@
       <c r="C570" s="24"/>
       <c r="D570" s="24"/>
       <c r="E570" s="24"/>
+      <c r="F570" s="24"/>
     </row>
     <row r="571" ht="24" customHeight="1">
       <c r="A571" s="34"/>
@@ -17395,6 +17969,7 @@
       <c r="C571" s="24"/>
       <c r="D571" s="24"/>
       <c r="E571" s="24"/>
+      <c r="F571" s="24"/>
     </row>
     <row r="572" ht="24" customHeight="1">
       <c r="A572" s="34"/>
@@ -17402,6 +17977,7 @@
       <c r="C572" s="24"/>
       <c r="D572" s="24"/>
       <c r="E572" s="24"/>
+      <c r="F572" s="24"/>
     </row>
     <row r="573" ht="24" customHeight="1">
       <c r="A573" s="34"/>
@@ -17409,6 +17985,7 @@
       <c r="C573" s="24"/>
       <c r="D573" s="24"/>
       <c r="E573" s="24"/>
+      <c r="F573" s="24"/>
     </row>
     <row r="574" ht="24" customHeight="1">
       <c r="A574" s="34"/>
@@ -17416,6 +17993,7 @@
       <c r="C574" s="24"/>
       <c r="D574" s="24"/>
       <c r="E574" s="24"/>
+      <c r="F574" s="24"/>
     </row>
     <row r="575" ht="24" customHeight="1">
       <c r="A575" s="34"/>
@@ -17423,6 +18001,7 @@
       <c r="C575" s="24"/>
       <c r="D575" s="24"/>
       <c r="E575" s="24"/>
+      <c r="F575" s="24"/>
     </row>
     <row r="576" ht="24" customHeight="1">
       <c r="A576" s="34"/>
@@ -17430,6 +18009,7 @@
       <c r="C576" s="24"/>
       <c r="D576" s="24"/>
       <c r="E576" s="24"/>
+      <c r="F576" s="24"/>
     </row>
     <row r="577" ht="24" customHeight="1">
       <c r="A577" s="34"/>
@@ -17437,6 +18017,7 @@
       <c r="C577" s="24"/>
       <c r="D577" s="24"/>
       <c r="E577" s="24"/>
+      <c r="F577" s="24"/>
     </row>
     <row r="578" ht="24" customHeight="1">
       <c r="A578" s="34"/>
@@ -17444,6 +18025,7 @@
       <c r="C578" s="24"/>
       <c r="D578" s="24"/>
       <c r="E578" s="24"/>
+      <c r="F578" s="24"/>
     </row>
     <row r="579" ht="24" customHeight="1">
       <c r="A579" s="34"/>
@@ -17451,6 +18033,7 @@
       <c r="C579" s="24"/>
       <c r="D579" s="24"/>
       <c r="E579" s="24"/>
+      <c r="F579" s="24"/>
     </row>
     <row r="580" ht="24" customHeight="1">
       <c r="A580" s="34"/>
@@ -17458,6 +18041,7 @@
       <c r="C580" s="24"/>
       <c r="D580" s="24"/>
       <c r="E580" s="24"/>
+      <c r="F580" s="24"/>
     </row>
     <row r="581" ht="24" customHeight="1">
       <c r="A581" s="34"/>
@@ -17465,6 +18049,7 @@
       <c r="C581" s="24"/>
       <c r="D581" s="24"/>
       <c r="E581" s="24"/>
+      <c r="F581" s="24"/>
     </row>
     <row r="582" ht="24" customHeight="1">
       <c r="A582" s="34"/>
@@ -17472,6 +18057,7 @@
       <c r="C582" s="24"/>
       <c r="D582" s="24"/>
       <c r="E582" s="24"/>
+      <c r="F582" s="24"/>
     </row>
     <row r="583" ht="24" customHeight="1">
       <c r="A583" s="34"/>
@@ -17479,6 +18065,7 @@
       <c r="C583" s="24"/>
       <c r="D583" s="24"/>
       <c r="E583" s="24"/>
+      <c r="F583" s="24"/>
     </row>
     <row r="584" ht="24" customHeight="1">
       <c r="A584" s="34"/>
@@ -17486,6 +18073,7 @@
       <c r="C584" s="24"/>
       <c r="D584" s="24"/>
       <c r="E584" s="24"/>
+      <c r="F584" s="24"/>
     </row>
     <row r="585" ht="24" customHeight="1">
       <c r="A585" s="34"/>
@@ -17493,6 +18081,7 @@
       <c r="C585" s="24"/>
       <c r="D585" s="24"/>
       <c r="E585" s="24"/>
+      <c r="F585" s="24"/>
     </row>
     <row r="586" ht="24" customHeight="1">
       <c r="A586" s="34"/>
@@ -17500,6 +18089,7 @@
       <c r="C586" s="24"/>
       <c r="D586" s="24"/>
       <c r="E586" s="24"/>
+      <c r="F586" s="24"/>
     </row>
     <row r="587" ht="24" customHeight="1">
       <c r="A587" s="34"/>
@@ -17507,6 +18097,7 @@
       <c r="C587" s="24"/>
       <c r="D587" s="24"/>
       <c r="E587" s="24"/>
+      <c r="F587" s="24"/>
     </row>
     <row r="588" ht="24" customHeight="1">
       <c r="A588" s="34"/>
@@ -17514,6 +18105,7 @@
       <c r="C588" s="24"/>
       <c r="D588" s="24"/>
       <c r="E588" s="24"/>
+      <c r="F588" s="24"/>
     </row>
     <row r="589" ht="24" customHeight="1">
       <c r="A589" s="34"/>
@@ -17521,6 +18113,7 @@
       <c r="C589" s="24"/>
       <c r="D589" s="24"/>
       <c r="E589" s="24"/>
+      <c r="F589" s="24"/>
     </row>
     <row r="590" ht="24" customHeight="1">
       <c r="A590" s="34"/>
@@ -17528,6 +18121,7 @@
       <c r="C590" s="24"/>
       <c r="D590" s="24"/>
       <c r="E590" s="24"/>
+      <c r="F590" s="24"/>
     </row>
     <row r="591" ht="24" customHeight="1">
       <c r="A591" s="34"/>
@@ -17535,6 +18129,7 @@
       <c r="C591" s="24"/>
       <c r="D591" s="24"/>
       <c r="E591" s="24"/>
+      <c r="F591" s="24"/>
     </row>
     <row r="592" ht="24" customHeight="1">
       <c r="A592" s="34"/>
@@ -17542,6 +18137,7 @@
       <c r="C592" s="24"/>
       <c r="D592" s="24"/>
       <c r="E592" s="24"/>
+      <c r="F592" s="24"/>
     </row>
     <row r="593" ht="24" customHeight="1">
       <c r="A593" s="34"/>
@@ -17549,6 +18145,7 @@
       <c r="C593" s="24"/>
       <c r="D593" s="24"/>
       <c r="E593" s="24"/>
+      <c r="F593" s="24"/>
     </row>
     <row r="594" ht="24" customHeight="1">
       <c r="A594" s="34"/>
@@ -17556,6 +18153,7 @@
       <c r="C594" s="24"/>
       <c r="D594" s="24"/>
       <c r="E594" s="24"/>
+      <c r="F594" s="24"/>
     </row>
     <row r="595" ht="24" customHeight="1">
       <c r="A595" s="34"/>
@@ -17563,6 +18161,7 @@
       <c r="C595" s="24"/>
       <c r="D595" s="24"/>
       <c r="E595" s="24"/>
+      <c r="F595" s="24"/>
     </row>
     <row r="596" ht="24" customHeight="1">
       <c r="A596" s="34"/>
@@ -17570,6 +18169,7 @@
       <c r="C596" s="24"/>
       <c r="D596" s="24"/>
       <c r="E596" s="24"/>
+      <c r="F596" s="24"/>
     </row>
     <row r="597" ht="24" customHeight="1">
       <c r="A597" s="34"/>
@@ -17577,6 +18177,7 @@
       <c r="C597" s="24"/>
       <c r="D597" s="24"/>
       <c r="E597" s="24"/>
+      <c r="F597" s="24"/>
     </row>
     <row r="598" ht="24" customHeight="1">
       <c r="A598" s="34"/>
@@ -17584,6 +18185,7 @@
       <c r="C598" s="24"/>
       <c r="D598" s="24"/>
       <c r="E598" s="24"/>
+      <c r="F598" s="24"/>
     </row>
     <row r="599" ht="24" customHeight="1">
       <c r="A599" s="34"/>
@@ -17591,6 +18193,7 @@
       <c r="C599" s="24"/>
       <c r="D599" s="24"/>
       <c r="E599" s="24"/>
+      <c r="F599" s="24"/>
     </row>
     <row r="600" ht="24" customHeight="1">
       <c r="A600" s="34"/>
@@ -17598,6 +18201,7 @@
       <c r="C600" s="24"/>
       <c r="D600" s="24"/>
       <c r="E600" s="24"/>
+      <c r="F600" s="24"/>
     </row>
     <row r="601" ht="24" customHeight="1">
       <c r="A601" s="34"/>
@@ -17605,6 +18209,7 @@
       <c r="C601" s="24"/>
       <c r="D601" s="24"/>
       <c r="E601" s="24"/>
+      <c r="F601" s="24"/>
     </row>
     <row r="602" ht="24" customHeight="1">
       <c r="A602" s="34"/>
@@ -17612,6 +18217,7 @@
       <c r="C602" s="24"/>
       <c r="D602" s="24"/>
       <c r="E602" s="24"/>
+      <c r="F602" s="24"/>
     </row>
     <row r="603" ht="24" customHeight="1">
       <c r="A603" s="34"/>
@@ -17619,6 +18225,7 @@
       <c r="C603" s="24"/>
       <c r="D603" s="24"/>
       <c r="E603" s="24"/>
+      <c r="F603" s="24"/>
     </row>
     <row r="604" ht="24" customHeight="1">
       <c r="A604" s="34"/>
@@ -17626,6 +18233,7 @@
       <c r="C604" s="24"/>
       <c r="D604" s="24"/>
       <c r="E604" s="24"/>
+      <c r="F604" s="24"/>
     </row>
     <row r="605" ht="24" customHeight="1">
       <c r="A605" s="34"/>
@@ -17633,6 +18241,7 @@
       <c r="C605" s="24"/>
       <c r="D605" s="24"/>
       <c r="E605" s="24"/>
+      <c r="F605" s="24"/>
     </row>
     <row r="606" ht="24" customHeight="1">
       <c r="A606" s="34"/>
@@ -17640,6 +18249,7 @@
       <c r="C606" s="24"/>
       <c r="D606" s="24"/>
       <c r="E606" s="24"/>
+      <c r="F606" s="24"/>
     </row>
     <row r="607" ht="24" customHeight="1">
       <c r="A607" s="34"/>
@@ -17647,6 +18257,7 @@
       <c r="C607" s="24"/>
       <c r="D607" s="24"/>
       <c r="E607" s="24"/>
+      <c r="F607" s="24"/>
     </row>
     <row r="608" ht="24" customHeight="1">
       <c r="A608" s="34"/>
@@ -17654,6 +18265,7 @@
       <c r="C608" s="24"/>
       <c r="D608" s="24"/>
       <c r="E608" s="24"/>
+      <c r="F608" s="24"/>
     </row>
     <row r="609" ht="24" customHeight="1">
       <c r="A609" s="34"/>
@@ -17661,6 +18273,7 @@
       <c r="C609" s="24"/>
       <c r="D609" s="24"/>
       <c r="E609" s="24"/>
+      <c r="F609" s="24"/>
     </row>
     <row r="610" ht="24" customHeight="1">
       <c r="A610" s="34"/>
@@ -17668,6 +18281,7 @@
       <c r="C610" s="24"/>
       <c r="D610" s="24"/>
       <c r="E610" s="24"/>
+      <c r="F610" s="24"/>
     </row>
     <row r="611" ht="24" customHeight="1">
       <c r="A611" s="34"/>
@@ -17675,6 +18289,7 @@
       <c r="C611" s="24"/>
       <c r="D611" s="24"/>
       <c r="E611" s="24"/>
+      <c r="F611" s="24"/>
     </row>
     <row r="612" ht="24" customHeight="1">
       <c r="A612" s="34"/>
@@ -17682,6 +18297,7 @@
       <c r="C612" s="24"/>
       <c r="D612" s="24"/>
       <c r="E612" s="24"/>
+      <c r="F612" s="24"/>
     </row>
     <row r="613" ht="24" customHeight="1">
       <c r="A613" s="34"/>
@@ -17689,6 +18305,7 @@
       <c r="C613" s="24"/>
       <c r="D613" s="24"/>
       <c r="E613" s="24"/>
+      <c r="F613" s="24"/>
     </row>
     <row r="614" ht="24" customHeight="1">
       <c r="A614" s="34"/>
@@ -17696,6 +18313,7 @@
       <c r="C614" s="24"/>
       <c r="D614" s="24"/>
       <c r="E614" s="24"/>
+      <c r="F614" s="24"/>
     </row>
     <row r="615" ht="24" customHeight="1">
       <c r="A615" s="34"/>
@@ -17703,6 +18321,7 @@
       <c r="C615" s="24"/>
       <c r="D615" s="24"/>
       <c r="E615" s="24"/>
+      <c r="F615" s="24"/>
     </row>
     <row r="616" ht="24" customHeight="1">
       <c r="A616" s="34"/>
@@ -17710,6 +18329,7 @@
       <c r="C616" s="24"/>
       <c r="D616" s="24"/>
       <c r="E616" s="24"/>
+      <c r="F616" s="24"/>
     </row>
     <row r="617" ht="24" customHeight="1">
       <c r="A617" s="34"/>
@@ -17717,6 +18337,7 @@
       <c r="C617" s="24"/>
       <c r="D617" s="24"/>
       <c r="E617" s="24"/>
+      <c r="F617" s="24"/>
     </row>
     <row r="618" ht="24" customHeight="1">
       <c r="A618" s="34"/>
@@ -17724,6 +18345,7 @@
       <c r="C618" s="24"/>
       <c r="D618" s="24"/>
       <c r="E618" s="24"/>
+      <c r="F618" s="24"/>
     </row>
     <row r="619" ht="24" customHeight="1">
       <c r="A619" s="34"/>
@@ -17731,6 +18353,7 @@
       <c r="C619" s="24"/>
       <c r="D619" s="24"/>
       <c r="E619" s="24"/>
+      <c r="F619" s="24"/>
     </row>
     <row r="620" ht="24" customHeight="1">
       <c r="A620" s="34"/>
@@ -17738,6 +18361,7 @@
       <c r="C620" s="24"/>
       <c r="D620" s="24"/>
       <c r="E620" s="24"/>
+      <c r="F620" s="24"/>
     </row>
     <row r="621" ht="24" customHeight="1">
       <c r="A621" s="34"/>
@@ -17745,6 +18369,7 @@
       <c r="C621" s="24"/>
       <c r="D621" s="24"/>
       <c r="E621" s="24"/>
+      <c r="F621" s="24"/>
     </row>
     <row r="622" ht="24" customHeight="1">
       <c r="A622" s="34"/>
@@ -17752,6 +18377,7 @@
       <c r="C622" s="24"/>
       <c r="D622" s="24"/>
       <c r="E622" s="24"/>
+      <c r="F622" s="24"/>
     </row>
     <row r="623" ht="24" customHeight="1">
       <c r="A623" s="34"/>
@@ -17759,6 +18385,7 @@
       <c r="C623" s="24"/>
       <c r="D623" s="24"/>
       <c r="E623" s="24"/>
+      <c r="F623" s="24"/>
     </row>
     <row r="624" ht="24" customHeight="1">
       <c r="A624" s="34"/>
@@ -17766,6 +18393,7 @@
       <c r="C624" s="24"/>
       <c r="D624" s="24"/>
       <c r="E624" s="24"/>
+      <c r="F624" s="24"/>
     </row>
     <row r="625" ht="24" customHeight="1">
       <c r="A625" s="34"/>
@@ -17773,6 +18401,7 @@
       <c r="C625" s="24"/>
       <c r="D625" s="24"/>
       <c r="E625" s="24"/>
+      <c r="F625" s="24"/>
     </row>
     <row r="626" ht="24" customHeight="1">
       <c r="A626" s="34"/>
@@ -17780,6 +18409,7 @@
       <c r="C626" s="24"/>
       <c r="D626" s="24"/>
       <c r="E626" s="24"/>
+      <c r="F626" s="24"/>
     </row>
     <row r="627" ht="24" customHeight="1">
       <c r="A627" s="34"/>
@@ -17787,6 +18417,7 @@
       <c r="C627" s="24"/>
       <c r="D627" s="24"/>
       <c r="E627" s="24"/>
+      <c r="F627" s="24"/>
     </row>
     <row r="628" ht="24" customHeight="1">
       <c r="A628" s="34"/>
@@ -17794,6 +18425,7 @@
       <c r="C628" s="24"/>
       <c r="D628" s="24"/>
       <c r="E628" s="24"/>
+      <c r="F628" s="24"/>
     </row>
     <row r="629" ht="24" customHeight="1">
       <c r="A629" s="34"/>
@@ -17801,6 +18433,7 @@
       <c r="C629" s="24"/>
       <c r="D629" s="24"/>
       <c r="E629" s="24"/>
+      <c r="F629" s="24"/>
     </row>
     <row r="630" ht="24" customHeight="1">
       <c r="A630" s="34"/>
@@ -17808,6 +18441,7 @@
       <c r="C630" s="24"/>
       <c r="D630" s="24"/>
       <c r="E630" s="24"/>
+      <c r="F630" s="24"/>
     </row>
     <row r="631" ht="24" customHeight="1">
       <c r="A631" s="34"/>
@@ -17815,6 +18449,7 @@
       <c r="C631" s="24"/>
       <c r="D631" s="24"/>
       <c r="E631" s="24"/>
+      <c r="F631" s="24"/>
     </row>
     <row r="632" ht="24" customHeight="1">
       <c r="A632" s="34"/>
@@ -17822,6 +18457,7 @@
       <c r="C632" s="24"/>
       <c r="D632" s="24"/>
       <c r="E632" s="24"/>
+      <c r="F632" s="24"/>
     </row>
     <row r="633" ht="24" customHeight="1">
       <c r="A633" s="34"/>
@@ -17829,6 +18465,7 @@
       <c r="C633" s="24"/>
       <c r="D633" s="24"/>
       <c r="E633" s="24"/>
+      <c r="F633" s="24"/>
     </row>
     <row r="634" ht="24" customHeight="1">
       <c r="A634" s="34"/>
@@ -17836,6 +18473,7 @@
       <c r="C634" s="24"/>
       <c r="D634" s="24"/>
       <c r="E634" s="24"/>
+      <c r="F634" s="24"/>
     </row>
     <row r="635" ht="24" customHeight="1">
       <c r="A635" s="34"/>
@@ -17843,6 +18481,7 @@
       <c r="C635" s="24"/>
       <c r="D635" s="24"/>
       <c r="E635" s="24"/>
+      <c r="F635" s="24"/>
     </row>
     <row r="636" ht="24" customHeight="1">
       <c r="A636" s="34"/>
@@ -17850,6 +18489,7 @@
       <c r="C636" s="24"/>
       <c r="D636" s="24"/>
       <c r="E636" s="24"/>
+      <c r="F636" s="24"/>
     </row>
     <row r="637" ht="24" customHeight="1">
       <c r="A637" s="34"/>
@@ -17857,6 +18497,7 @@
       <c r="C637" s="24"/>
       <c r="D637" s="24"/>
       <c r="E637" s="24"/>
+      <c r="F637" s="24"/>
     </row>
     <row r="638" ht="24" customHeight="1">
       <c r="A638" s="34"/>
@@ -17864,6 +18505,7 @@
       <c r="C638" s="24"/>
       <c r="D638" s="24"/>
       <c r="E638" s="24"/>
+      <c r="F638" s="24"/>
     </row>
     <row r="639" ht="24" customHeight="1">
       <c r="A639" s="34"/>
@@ -17871,6 +18513,7 @@
       <c r="C639" s="24"/>
       <c r="D639" s="24"/>
       <c r="E639" s="24"/>
+      <c r="F639" s="24"/>
     </row>
     <row r="640" ht="24" customHeight="1">
       <c r="A640" s="34"/>
@@ -17878,6 +18521,7 @@
       <c r="C640" s="24"/>
       <c r="D640" s="24"/>
       <c r="E640" s="24"/>
+      <c r="F640" s="24"/>
     </row>
     <row r="641" ht="24" customHeight="1">
       <c r="A641" s="34"/>
@@ -17885,6 +18529,7 @@
       <c r="C641" s="24"/>
       <c r="D641" s="24"/>
       <c r="E641" s="24"/>
+      <c r="F641" s="24"/>
     </row>
     <row r="642" ht="24" customHeight="1">
       <c r="A642" s="34"/>
@@ -17892,6 +18537,7 @@
       <c r="C642" s="24"/>
       <c r="D642" s="24"/>
       <c r="E642" s="24"/>
+      <c r="F642" s="24"/>
     </row>
     <row r="643" ht="24" customHeight="1">
       <c r="A643" s="34"/>
@@ -17899,6 +18545,7 @@
       <c r="C643" s="24"/>
       <c r="D643" s="24"/>
       <c r="E643" s="24"/>
+      <c r="F643" s="24"/>
     </row>
     <row r="644" ht="24" customHeight="1">
       <c r="A644" s="34"/>
@@ -17906,6 +18553,7 @@
       <c r="C644" s="24"/>
       <c r="D644" s="24"/>
       <c r="E644" s="24"/>
+      <c r="F644" s="24"/>
     </row>
     <row r="645" ht="24" customHeight="1">
       <c r="A645" s="34"/>
@@ -17913,6 +18561,7 @@
       <c r="C645" s="24"/>
       <c r="D645" s="24"/>
       <c r="E645" s="24"/>
+      <c r="F645" s="24"/>
     </row>
     <row r="646" ht="24" customHeight="1">
       <c r="A646" s="34"/>
@@ -17920,6 +18569,7 @@
       <c r="C646" s="24"/>
       <c r="D646" s="24"/>
       <c r="E646" s="24"/>
+      <c r="F646" s="24"/>
     </row>
     <row r="647" ht="24" customHeight="1">
       <c r="A647" s="34"/>
@@ -17927,6 +18577,7 @@
       <c r="C647" s="24"/>
       <c r="D647" s="24"/>
       <c r="E647" s="24"/>
+      <c r="F647" s="24"/>
     </row>
     <row r="648" ht="24" customHeight="1">
       <c r="A648" s="34"/>
@@ -17934,6 +18585,7 @@
       <c r="C648" s="24"/>
       <c r="D648" s="24"/>
       <c r="E648" s="24"/>
+      <c r="F648" s="24"/>
     </row>
     <row r="649" ht="24" customHeight="1">
       <c r="A649" s="34"/>
@@ -17941,6 +18593,7 @@
       <c r="C649" s="24"/>
       <c r="D649" s="24"/>
       <c r="E649" s="24"/>
+      <c r="F649" s="24"/>
     </row>
     <row r="650" ht="24" customHeight="1">
       <c r="A650" s="34"/>
@@ -17948,6 +18601,7 @@
       <c r="C650" s="24"/>
       <c r="D650" s="24"/>
       <c r="E650" s="24"/>
+      <c r="F650" s="24"/>
     </row>
     <row r="651" ht="24" customHeight="1">
       <c r="A651" s="34"/>
@@ -17955,6 +18609,7 @@
       <c r="C651" s="24"/>
       <c r="D651" s="24"/>
       <c r="E651" s="24"/>
+      <c r="F651" s="24"/>
     </row>
     <row r="652" ht="24" customHeight="1">
       <c r="A652" s="34"/>
@@ -17962,6 +18617,7 @@
       <c r="C652" s="24"/>
       <c r="D652" s="24"/>
       <c r="E652" s="24"/>
+      <c r="F652" s="24"/>
     </row>
     <row r="653" ht="24" customHeight="1">
       <c r="A653" s="34"/>
@@ -17969,6 +18625,7 @@
       <c r="C653" s="24"/>
       <c r="D653" s="24"/>
       <c r="E653" s="24"/>
+      <c r="F653" s="24"/>
     </row>
     <row r="654" ht="24" customHeight="1">
       <c r="A654" s="34"/>
@@ -17976,6 +18633,7 @@
       <c r="C654" s="24"/>
       <c r="D654" s="24"/>
       <c r="E654" s="24"/>
+      <c r="F654" s="24"/>
     </row>
     <row r="655" ht="24" customHeight="1">
       <c r="A655" s="34"/>
@@ -17983,6 +18641,7 @@
       <c r="C655" s="24"/>
       <c r="D655" s="24"/>
       <c r="E655" s="24"/>
+      <c r="F655" s="24"/>
     </row>
     <row r="656" ht="24" customHeight="1">
       <c r="A656" s="34"/>
@@ -17990,6 +18649,7 @@
       <c r="C656" s="24"/>
       <c r="D656" s="24"/>
       <c r="E656" s="24"/>
+      <c r="F656" s="24"/>
     </row>
     <row r="657" ht="24" customHeight="1">
       <c r="A657" s="34"/>
@@ -17997,6 +18657,7 @@
       <c r="C657" s="24"/>
       <c r="D657" s="24"/>
       <c r="E657" s="24"/>
+      <c r="F657" s="24"/>
     </row>
     <row r="658" ht="24" customHeight="1">
       <c r="A658" s="34"/>
@@ -18004,6 +18665,7 @@
       <c r="C658" s="24"/>
       <c r="D658" s="24"/>
       <c r="E658" s="24"/>
+      <c r="F658" s="24"/>
     </row>
     <row r="659" ht="24" customHeight="1">
       <c r="A659" s="34"/>
@@ -18011,6 +18673,7 @@
       <c r="C659" s="24"/>
       <c r="D659" s="24"/>
       <c r="E659" s="24"/>
+      <c r="F659" s="24"/>
     </row>
     <row r="660" ht="24" customHeight="1">
       <c r="A660" s="34"/>
@@ -18018,6 +18681,7 @@
       <c r="C660" s="24"/>
       <c r="D660" s="24"/>
       <c r="E660" s="24"/>
+      <c r="F660" s="24"/>
     </row>
     <row r="661" ht="24" customHeight="1">
       <c r="A661" s="34"/>
@@ -18025,6 +18689,7 @@
       <c r="C661" s="24"/>
       <c r="D661" s="24"/>
       <c r="E661" s="24"/>
+      <c r="F661" s="24"/>
     </row>
     <row r="662" ht="24" customHeight="1">
       <c r="A662" s="34"/>
@@ -18032,6 +18697,7 @@
       <c r="C662" s="24"/>
       <c r="D662" s="24"/>
       <c r="E662" s="24"/>
+      <c r="F662" s="24"/>
     </row>
     <row r="663" ht="24" customHeight="1">
       <c r="A663" s="34"/>
@@ -18039,6 +18705,7 @@
       <c r="C663" s="24"/>
       <c r="D663" s="24"/>
       <c r="E663" s="24"/>
+      <c r="F663" s="24"/>
     </row>
     <row r="664" ht="24" customHeight="1">
       <c r="A664" s="34"/>
@@ -18046,6 +18713,7 @@
       <c r="C664" s="24"/>
       <c r="D664" s="24"/>
       <c r="E664" s="24"/>
+      <c r="F664" s="24"/>
     </row>
     <row r="665" ht="24" customHeight="1">
       <c r="A665" s="34"/>
@@ -18053,6 +18721,7 @@
       <c r="C665" s="24"/>
       <c r="D665" s="24"/>
       <c r="E665" s="24"/>
+      <c r="F665" s="24"/>
     </row>
     <row r="666" ht="24" customHeight="1">
       <c r="A666" s="34"/>
@@ -18060,6 +18729,7 @@
       <c r="C666" s="24"/>
       <c r="D666" s="24"/>
       <c r="E666" s="24"/>
+      <c r="F666" s="24"/>
     </row>
     <row r="667" ht="24" customHeight="1">
       <c r="A667" s="34"/>
@@ -18067,6 +18737,7 @@
       <c r="C667" s="24"/>
       <c r="D667" s="24"/>
       <c r="E667" s="24"/>
+      <c r="F667" s="24"/>
     </row>
     <row r="668" ht="24" customHeight="1">
       <c r="A668" s="34"/>
@@ -18074,6 +18745,7 @@
       <c r="C668" s="24"/>
       <c r="D668" s="24"/>
       <c r="E668" s="24"/>
+      <c r="F668" s="24"/>
     </row>
     <row r="669" ht="24" customHeight="1">
       <c r="A669" s="34"/>
@@ -18081,6 +18753,7 @@
       <c r="C669" s="24"/>
       <c r="D669" s="24"/>
       <c r="E669" s="24"/>
+      <c r="F669" s="24"/>
     </row>
     <row r="670" ht="24" customHeight="1">
       <c r="A670" s="34"/>
@@ -18088,6 +18761,7 @@
       <c r="C670" s="24"/>
       <c r="D670" s="24"/>
       <c r="E670" s="24"/>
+      <c r="F670" s="24"/>
     </row>
     <row r="671" ht="24" customHeight="1">
       <c r="A671" s="34"/>
@@ -18095,6 +18769,7 @@
       <c r="C671" s="24"/>
       <c r="D671" s="24"/>
       <c r="E671" s="24"/>
+      <c r="F671" s="24"/>
     </row>
     <row r="672" ht="24" customHeight="1">
       <c r="A672" s="34"/>
@@ -18102,6 +18777,7 @@
       <c r="C672" s="24"/>
       <c r="D672" s="24"/>
       <c r="E672" s="24"/>
+      <c r="F672" s="24"/>
     </row>
     <row r="673" ht="24" customHeight="1">
       <c r="A673" s="34"/>
@@ -18109,6 +18785,7 @@
       <c r="C673" s="24"/>
       <c r="D673" s="24"/>
       <c r="E673" s="24"/>
+      <c r="F673" s="24"/>
     </row>
     <row r="674" ht="24" customHeight="1">
       <c r="A674" s="34"/>
@@ -18116,6 +18793,7 @@
       <c r="C674" s="24"/>
       <c r="D674" s="24"/>
       <c r="E674" s="24"/>
+      <c r="F674" s="24"/>
     </row>
     <row r="675" ht="24" customHeight="1">
       <c r="A675" s="34"/>
@@ -18123,6 +18801,7 @@
       <c r="C675" s="24"/>
       <c r="D675" s="24"/>
       <c r="E675" s="24"/>
+      <c r="F675" s="24"/>
     </row>
     <row r="676" ht="24" customHeight="1">
       <c r="A676" s="34"/>
@@ -18130,6 +18809,7 @@
       <c r="C676" s="24"/>
       <c r="D676" s="24"/>
       <c r="E676" s="24"/>
+      <c r="F676" s="24"/>
     </row>
     <row r="677" ht="24" customHeight="1">
       <c r="A677" s="34"/>
@@ -18137,6 +18817,7 @@
       <c r="C677" s="24"/>
       <c r="D677" s="24"/>
       <c r="E677" s="24"/>
+      <c r="F677" s="24"/>
     </row>
     <row r="678" ht="24" customHeight="1">
       <c r="A678" s="34"/>
@@ -18144,6 +18825,7 @@
       <c r="C678" s="24"/>
       <c r="D678" s="24"/>
       <c r="E678" s="24"/>
+      <c r="F678" s="24"/>
     </row>
     <row r="679" ht="24" customHeight="1">
       <c r="A679" s="34"/>
@@ -18151,6 +18833,7 @@
       <c r="C679" s="24"/>
       <c r="D679" s="24"/>
       <c r="E679" s="24"/>
+      <c r="F679" s="24"/>
     </row>
     <row r="680" ht="24" customHeight="1">
       <c r="A680" s="34"/>
@@ -18158,6 +18841,7 @@
       <c r="C680" s="24"/>
       <c r="D680" s="24"/>
       <c r="E680" s="24"/>
+      <c r="F680" s="24"/>
     </row>
     <row r="681" ht="24" customHeight="1">
       <c r="A681" s="34"/>
@@ -18165,6 +18849,7 @@
       <c r="C681" s="24"/>
       <c r="D681" s="24"/>
       <c r="E681" s="24"/>
+      <c r="F681" s="24"/>
     </row>
     <row r="682" ht="24" customHeight="1">
       <c r="A682" s="34"/>
@@ -18172,6 +18857,7 @@
       <c r="C682" s="24"/>
       <c r="D682" s="24"/>
       <c r="E682" s="24"/>
+      <c r="F682" s="24"/>
     </row>
     <row r="683" ht="24" customHeight="1">
       <c r="A683" s="34"/>
@@ -18179,6 +18865,7 @@
       <c r="C683" s="24"/>
       <c r="D683" s="24"/>
       <c r="E683" s="24"/>
+      <c r="F683" s="24"/>
     </row>
     <row r="684" ht="24" customHeight="1">
       <c r="A684" s="34"/>
@@ -18186,6 +18873,7 @@
       <c r="C684" s="24"/>
       <c r="D684" s="24"/>
       <c r="E684" s="24"/>
+      <c r="F684" s="24"/>
     </row>
     <row r="685" ht="24" customHeight="1">
       <c r="A685" s="34"/>
@@ -18193,6 +18881,7 @@
       <c r="C685" s="24"/>
       <c r="D685" s="24"/>
       <c r="E685" s="24"/>
+      <c r="F685" s="24"/>
     </row>
     <row r="686" ht="24" customHeight="1">
       <c r="A686" s="34"/>
@@ -18200,6 +18889,7 @@
       <c r="C686" s="24"/>
       <c r="D686" s="24"/>
       <c r="E686" s="24"/>
+      <c r="F686" s="24"/>
     </row>
     <row r="687" ht="24" customHeight="1">
       <c r="A687" s="34"/>
@@ -18207,6 +18897,7 @@
       <c r="C687" s="24"/>
       <c r="D687" s="24"/>
       <c r="E687" s="24"/>
+      <c r="F687" s="24"/>
     </row>
     <row r="688" ht="24" customHeight="1">
       <c r="A688" s="34"/>
@@ -18214,6 +18905,7 @@
       <c r="C688" s="24"/>
       <c r="D688" s="24"/>
       <c r="E688" s="24"/>
+      <c r="F688" s="24"/>
     </row>
     <row r="689" ht="24" customHeight="1">
       <c r="A689" s="34"/>
@@ -18221,6 +18913,7 @@
       <c r="C689" s="24"/>
       <c r="D689" s="24"/>
       <c r="E689" s="24"/>
+      <c r="F689" s="24"/>
     </row>
     <row r="690" ht="24" customHeight="1">
       <c r="A690" s="34"/>
@@ -18228,6 +18921,7 @@
       <c r="C690" s="24"/>
       <c r="D690" s="24"/>
       <c r="E690" s="24"/>
+      <c r="F690" s="24"/>
     </row>
     <row r="691" ht="24" customHeight="1">
       <c r="A691" s="34"/>
@@ -18235,6 +18929,7 @@
       <c r="C691" s="24"/>
       <c r="D691" s="24"/>
       <c r="E691" s="24"/>
+      <c r="F691" s="24"/>
     </row>
     <row r="692" ht="24" customHeight="1">
       <c r="A692" s="34"/>
@@ -18242,6 +18937,7 @@
       <c r="C692" s="24"/>
       <c r="D692" s="24"/>
       <c r="E692" s="24"/>
+      <c r="F692" s="24"/>
     </row>
     <row r="693" ht="24" customHeight="1">
       <c r="A693" s="34"/>
@@ -18249,6 +18945,7 @@
       <c r="C693" s="24"/>
       <c r="D693" s="24"/>
       <c r="E693" s="24"/>
+      <c r="F693" s="24"/>
     </row>
     <row r="694" ht="24" customHeight="1">
       <c r="A694" s="34"/>
@@ -18256,6 +18953,7 @@
       <c r="C694" s="24"/>
       <c r="D694" s="24"/>
       <c r="E694" s="24"/>
+      <c r="F694" s="24"/>
     </row>
     <row r="695" ht="24" customHeight="1">
       <c r="A695" s="34"/>
@@ -18263,6 +18961,7 @@
       <c r="C695" s="24"/>
       <c r="D695" s="24"/>
       <c r="E695" s="24"/>
+      <c r="F695" s="24"/>
     </row>
     <row r="696" ht="24" customHeight="1">
       <c r="A696" s="34"/>
@@ -18270,6 +18969,7 @@
       <c r="C696" s="24"/>
       <c r="D696" s="24"/>
       <c r="E696" s="24"/>
+      <c r="F696" s="24"/>
     </row>
     <row r="697" ht="24" customHeight="1">
       <c r="A697" s="34"/>
@@ -18277,6 +18977,7 @@
       <c r="C697" s="24"/>
       <c r="D697" s="24"/>
       <c r="E697" s="24"/>
+      <c r="F697" s="24"/>
     </row>
     <row r="698" ht="24" customHeight="1">
       <c r="A698" s="34"/>
@@ -18284,6 +18985,7 @@
       <c r="C698" s="24"/>
       <c r="D698" s="24"/>
       <c r="E698" s="24"/>
+      <c r="F698" s="24"/>
     </row>
     <row r="699" ht="24" customHeight="1">
       <c r="A699" s="34"/>
@@ -18291,6 +18993,7 @@
       <c r="C699" s="24"/>
       <c r="D699" s="24"/>
       <c r="E699" s="24"/>
+      <c r="F699" s="24"/>
     </row>
     <row r="700" ht="24" customHeight="1">
       <c r="A700" s="34"/>
@@ -18298,6 +19001,7 @@
       <c r="C700" s="24"/>
       <c r="D700" s="24"/>
       <c r="E700" s="24"/>
+      <c r="F700" s="24"/>
     </row>
     <row r="701" ht="24" customHeight="1">
       <c r="A701" s="34"/>
@@ -18305,6 +19009,7 @@
       <c r="C701" s="24"/>
       <c r="D701" s="24"/>
       <c r="E701" s="24"/>
+      <c r="F701" s="24"/>
     </row>
     <row r="702" ht="24" customHeight="1">
       <c r="A702" s="34"/>
@@ -18312,6 +19017,7 @@
       <c r="C702" s="24"/>
       <c r="D702" s="24"/>
       <c r="E702" s="24"/>
+      <c r="F702" s="24"/>
     </row>
     <row r="703" ht="24" customHeight="1">
       <c r="A703" s="34"/>
@@ -18319,6 +19025,7 @@
       <c r="C703" s="24"/>
       <c r="D703" s="24"/>
       <c r="E703" s="24"/>
+      <c r="F703" s="24"/>
     </row>
     <row r="704" ht="24" customHeight="1">
       <c r="A704" s="34"/>
@@ -18326,6 +19033,7 @@
       <c r="C704" s="24"/>
       <c r="D704" s="24"/>
       <c r="E704" s="24"/>
+      <c r="F704" s="24"/>
     </row>
     <row r="705" ht="24" customHeight="1">
       <c r="A705" s="34"/>
@@ -18333,6 +19041,7 @@
       <c r="C705" s="24"/>
       <c r="D705" s="24"/>
       <c r="E705" s="24"/>
+      <c r="F705" s="24"/>
     </row>
     <row r="706" ht="24" customHeight="1">
       <c r="A706" s="34"/>
@@ -18340,6 +19049,7 @@
       <c r="C706" s="24"/>
       <c r="D706" s="24"/>
       <c r="E706" s="24"/>
+      <c r="F706" s="24"/>
     </row>
     <row r="707" ht="24" customHeight="1">
       <c r="A707" s="34"/>
@@ -18347,6 +19057,7 @@
       <c r="C707" s="24"/>
       <c r="D707" s="24"/>
       <c r="E707" s="24"/>
+      <c r="F707" s="24"/>
     </row>
     <row r="708" ht="24" customHeight="1">
       <c r="A708" s="34"/>
@@ -18354,6 +19065,7 @@
       <c r="C708" s="24"/>
       <c r="D708" s="24"/>
       <c r="E708" s="24"/>
+      <c r="F708" s="24"/>
     </row>
     <row r="709" ht="24" customHeight="1">
       <c r="A709" s="34"/>
@@ -18361,6 +19073,7 @@
       <c r="C709" s="24"/>
       <c r="D709" s="24"/>
       <c r="E709" s="24"/>
+      <c r="F709" s="24"/>
     </row>
     <row r="710" ht="24" customHeight="1">
       <c r="A710" s="34"/>
@@ -18368,6 +19081,7 @@
       <c r="C710" s="24"/>
       <c r="D710" s="24"/>
       <c r="E710" s="24"/>
+      <c r="F710" s="24"/>
     </row>
     <row r="711" ht="24" customHeight="1">
       <c r="A711" s="34"/>
@@ -18375,6 +19089,7 @@
       <c r="C711" s="24"/>
       <c r="D711" s="24"/>
       <c r="E711" s="24"/>
+      <c r="F711" s="24"/>
     </row>
     <row r="712" ht="24" customHeight="1">
       <c r="A712" s="34"/>
@@ -18382,6 +19097,7 @@
       <c r="C712" s="24"/>
       <c r="D712" s="24"/>
       <c r="E712" s="24"/>
+      <c r="F712" s="24"/>
     </row>
     <row r="713" ht="24" customHeight="1">
       <c r="A713" s="34"/>
@@ -18389,6 +19105,7 @@
       <c r="C713" s="24"/>
       <c r="D713" s="24"/>
       <c r="E713" s="24"/>
+      <c r="F713" s="24"/>
     </row>
     <row r="714" ht="24" customHeight="1">
       <c r="A714" s="34"/>
@@ -18396,6 +19113,7 @@
       <c r="C714" s="24"/>
       <c r="D714" s="24"/>
       <c r="E714" s="24"/>
+      <c r="F714" s="24"/>
     </row>
     <row r="715" ht="24" customHeight="1">
       <c r="A715" s="34"/>
@@ -18403,6 +19121,7 @@
       <c r="C715" s="24"/>
       <c r="D715" s="24"/>
       <c r="E715" s="24"/>
+      <c r="F715" s="24"/>
     </row>
     <row r="716" ht="24" customHeight="1">
       <c r="A716" s="34"/>
@@ -18410,6 +19129,7 @@
       <c r="C716" s="24"/>
       <c r="D716" s="24"/>
       <c r="E716" s="24"/>
+      <c r="F716" s="24"/>
     </row>
     <row r="717" ht="24" customHeight="1">
       <c r="A717" s="34"/>
@@ -18417,6 +19137,7 @@
       <c r="C717" s="24"/>
       <c r="D717" s="24"/>
       <c r="E717" s="24"/>
+      <c r="F717" s="24"/>
     </row>
     <row r="718" ht="24" customHeight="1">
       <c r="A718" s="34"/>
@@ -18424,6 +19145,7 @@
       <c r="C718" s="24"/>
       <c r="D718" s="24"/>
       <c r="E718" s="24"/>
+      <c r="F718" s="24"/>
     </row>
     <row r="719" ht="24" customHeight="1">
       <c r="A719" s="34"/>
@@ -18431,6 +19153,7 @@
       <c r="C719" s="24"/>
       <c r="D719" s="24"/>
       <c r="E719" s="24"/>
+      <c r="F719" s="24"/>
     </row>
     <row r="720" ht="24" customHeight="1">
       <c r="A720" s="34"/>
@@ -18438,6 +19161,7 @@
       <c r="C720" s="24"/>
       <c r="D720" s="24"/>
       <c r="E720" s="24"/>
+      <c r="F720" s="24"/>
     </row>
     <row r="721" ht="24" customHeight="1">
       <c r="A721" s="34"/>
@@ -18445,6 +19169,7 @@
       <c r="C721" s="24"/>
       <c r="D721" s="24"/>
       <c r="E721" s="24"/>
+      <c r="F721" s="24"/>
     </row>
     <row r="722" ht="24" customHeight="1">
       <c r="A722" s="34"/>
@@ -18452,6 +19177,7 @@
       <c r="C722" s="24"/>
       <c r="D722" s="24"/>
       <c r="E722" s="24"/>
+      <c r="F722" s="24"/>
     </row>
     <row r="723" ht="24" customHeight="1">
       <c r="A723" s="34"/>
@@ -18459,6 +19185,7 @@
       <c r="C723" s="24"/>
       <c r="D723" s="24"/>
       <c r="E723" s="24"/>
+      <c r="F723" s="24"/>
     </row>
     <row r="724" ht="24" customHeight="1">
       <c r="A724" s="34"/>
@@ -18466,6 +19193,7 @@
       <c r="C724" s="24"/>
       <c r="D724" s="24"/>
       <c r="E724" s="24"/>
+      <c r="F724" s="24"/>
     </row>
     <row r="725" ht="24" customHeight="1">
       <c r="A725" s="34"/>
@@ -18473,6 +19201,7 @@
       <c r="C725" s="24"/>
       <c r="D725" s="24"/>
       <c r="E725" s="24"/>
+      <c r="F725" s="24"/>
     </row>
     <row r="726" ht="24" customHeight="1">
       <c r="A726" s="34"/>
@@ -18480,6 +19209,7 @@
       <c r="C726" s="24"/>
       <c r="D726" s="24"/>
       <c r="E726" s="24"/>
+      <c r="F726" s="24"/>
     </row>
     <row r="727" ht="24" customHeight="1">
       <c r="A727" s="34"/>
@@ -18487,6 +19217,7 @@
       <c r="C727" s="24"/>
       <c r="D727" s="24"/>
       <c r="E727" s="24"/>
+      <c r="F727" s="24"/>
     </row>
     <row r="728" ht="24" customHeight="1">
       <c r="A728" s="34"/>
@@ -18494,6 +19225,7 @@
       <c r="C728" s="24"/>
       <c r="D728" s="24"/>
       <c r="E728" s="24"/>
+      <c r="F728" s="24"/>
     </row>
     <row r="729" ht="24" customHeight="1">
       <c r="A729" s="34"/>
@@ -18501,6 +19233,7 @@
       <c r="C729" s="24"/>
       <c r="D729" s="24"/>
       <c r="E729" s="24"/>
+      <c r="F729" s="24"/>
     </row>
     <row r="730" ht="24" customHeight="1">
       <c r="A730" s="34"/>
@@ -18508,6 +19241,7 @@
       <c r="C730" s="24"/>
       <c r="D730" s="24"/>
       <c r="E730" s="24"/>
+      <c r="F730" s="24"/>
     </row>
     <row r="731" ht="24" customHeight="1">
       <c r="A731" s="34"/>
@@ -18515,6 +19249,7 @@
       <c r="C731" s="24"/>
       <c r="D731" s="24"/>
       <c r="E731" s="24"/>
+      <c r="F731" s="24"/>
     </row>
     <row r="732" ht="24" customHeight="1">
       <c r="A732" s="34"/>
@@ -18522,6 +19257,7 @@
       <c r="C732" s="24"/>
       <c r="D732" s="24"/>
       <c r="E732" s="24"/>
+      <c r="F732" s="24"/>
     </row>
     <row r="733" ht="24" customHeight="1">
       <c r="A733" s="34"/>
@@ -18529,6 +19265,7 @@
       <c r="C733" s="24"/>
       <c r="D733" s="24"/>
       <c r="E733" s="24"/>
+      <c r="F733" s="24"/>
     </row>
     <row r="734" ht="24" customHeight="1">
       <c r="A734" s="34"/>
@@ -18536,6 +19273,7 @@
       <c r="C734" s="24"/>
       <c r="D734" s="24"/>
       <c r="E734" s="24"/>
+      <c r="F734" s="24"/>
     </row>
     <row r="735" ht="24" customHeight="1">
       <c r="A735" s="34"/>
@@ -18543,6 +19281,7 @@
       <c r="C735" s="24"/>
       <c r="D735" s="24"/>
       <c r="E735" s="24"/>
+      <c r="F735" s="24"/>
     </row>
     <row r="736" ht="24" customHeight="1">
       <c r="A736" s="34"/>
@@ -18550,6 +19289,7 @@
       <c r="C736" s="24"/>
       <c r="D736" s="24"/>
       <c r="E736" s="24"/>
+      <c r="F736" s="24"/>
     </row>
     <row r="737" ht="24" customHeight="1">
       <c r="A737" s="34"/>
@@ -18557,6 +19297,7 @@
       <c r="C737" s="24"/>
       <c r="D737" s="24"/>
       <c r="E737" s="24"/>
+      <c r="F737" s="24"/>
     </row>
     <row r="738" ht="24" customHeight="1">
       <c r="A738" s="34"/>
@@ -18564,6 +19305,7 @@
       <c r="C738" s="24"/>
       <c r="D738" s="24"/>
       <c r="E738" s="24"/>
+      <c r="F738" s="24"/>
     </row>
     <row r="739" ht="24" customHeight="1">
       <c r="A739" s="34"/>
@@ -18571,6 +19313,7 @@
       <c r="C739" s="24"/>
       <c r="D739" s="24"/>
       <c r="E739" s="24"/>
+      <c r="F739" s="24"/>
     </row>
     <row r="740" ht="24" customHeight="1">
       <c r="A740" s="34"/>
@@ -18578,6 +19321,7 @@
       <c r="C740" s="24"/>
       <c r="D740" s="24"/>
       <c r="E740" s="24"/>
+      <c r="F740" s="24"/>
     </row>
     <row r="741" ht="24" customHeight="1">
       <c r="A741" s="34"/>
@@ -18585,6 +19329,7 @@
       <c r="C741" s="24"/>
       <c r="D741" s="24"/>
       <c r="E741" s="24"/>
+      <c r="F741" s="24"/>
     </row>
     <row r="742" ht="24" customHeight="1">
       <c r="A742" s="34"/>
@@ -18592,6 +19337,7 @@
       <c r="C742" s="24"/>
       <c r="D742" s="24"/>
       <c r="E742" s="24"/>
+      <c r="F742" s="24"/>
     </row>
     <row r="743" ht="24" customHeight="1">
       <c r="A743" s="34"/>
@@ -18599,6 +19345,7 @@
       <c r="C743" s="24"/>
       <c r="D743" s="24"/>
       <c r="E743" s="24"/>
+      <c r="F743" s="24"/>
     </row>
     <row r="744" ht="24" customHeight="1">
       <c r="A744" s="34"/>
@@ -18606,6 +19353,7 @@
       <c r="C744" s="24"/>
       <c r="D744" s="24"/>
       <c r="E744" s="24"/>
+      <c r="F744" s="24"/>
     </row>
     <row r="745" ht="24" customHeight="1">
       <c r="A745" s="34"/>
@@ -18613,6 +19361,7 @@
       <c r="C745" s="24"/>
       <c r="D745" s="24"/>
       <c r="E745" s="24"/>
+      <c r="F745" s="24"/>
     </row>
     <row r="746" ht="24" customHeight="1">
       <c r="A746" s="34"/>
@@ -18620,6 +19369,7 @@
       <c r="C746" s="24"/>
       <c r="D746" s="24"/>
       <c r="E746" s="24"/>
+      <c r="F746" s="24"/>
     </row>
     <row r="747" ht="24" customHeight="1">
       <c r="A747" s="34"/>
@@ -18627,6 +19377,7 @@
       <c r="C747" s="24"/>
       <c r="D747" s="24"/>
       <c r="E747" s="24"/>
+      <c r="F747" s="24"/>
     </row>
     <row r="748" ht="24" customHeight="1">
       <c r="A748" s="34"/>
@@ -18634,6 +19385,7 @@
       <c r="C748" s="24"/>
       <c r="D748" s="24"/>
       <c r="E748" s="24"/>
+      <c r="F748" s="24"/>
     </row>
     <row r="749" ht="24" customHeight="1">
       <c r="A749" s="34"/>
@@ -18641,6 +19393,7 @@
       <c r="C749" s="24"/>
       <c r="D749" s="24"/>
       <c r="E749" s="24"/>
+      <c r="F749" s="24"/>
     </row>
     <row r="750" ht="24" customHeight="1">
       <c r="A750" s="34"/>
@@ -18648,6 +19401,7 @@
       <c r="C750" s="24"/>
       <c r="D750" s="24"/>
       <c r="E750" s="24"/>
+      <c r="F750" s="24"/>
     </row>
     <row r="751" ht="24" customHeight="1">
       <c r="A751" s="34"/>
@@ -18655,6 +19409,7 @@
       <c r="C751" s="24"/>
       <c r="D751" s="24"/>
       <c r="E751" s="24"/>
+      <c r="F751" s="24"/>
     </row>
     <row r="752" ht="24" customHeight="1">
       <c r="A752" s="34"/>
@@ -18662,6 +19417,7 @@
       <c r="C752" s="24"/>
       <c r="D752" s="24"/>
       <c r="E752" s="24"/>
+      <c r="F752" s="24"/>
     </row>
     <row r="753" ht="24" customHeight="1">
       <c r="A753" s="34"/>
@@ -18669,6 +19425,7 @@
       <c r="C753" s="24"/>
       <c r="D753" s="24"/>
       <c r="E753" s="24"/>
+      <c r="F753" s="24"/>
     </row>
     <row r="754" ht="24" customHeight="1">
       <c r="A754" s="34"/>
@@ -18676,6 +19433,7 @@
       <c r="C754" s="24"/>
       <c r="D754" s="24"/>
       <c r="E754" s="24"/>
+      <c r="F754" s="24"/>
     </row>
     <row r="755" ht="24" customHeight="1">
       <c r="A755" s="34"/>
@@ -18683,6 +19441,7 @@
       <c r="C755" s="24"/>
       <c r="D755" s="24"/>
       <c r="E755" s="24"/>
+      <c r="F755" s="24"/>
     </row>
     <row r="756" ht="24" customHeight="1">
       <c r="A756" s="34"/>
@@ -18690,6 +19449,7 @@
       <c r="C756" s="24"/>
       <c r="D756" s="24"/>
       <c r="E756" s="24"/>
+      <c r="F756" s="24"/>
     </row>
     <row r="757" ht="24" customHeight="1">
       <c r="A757" s="34"/>
@@ -18697,6 +19457,7 @@
       <c r="C757" s="24"/>
       <c r="D757" s="24"/>
       <c r="E757" s="24"/>
+      <c r="F757" s="24"/>
     </row>
     <row r="758" ht="24" customHeight="1">
       <c r="A758" s="34"/>
@@ -18704,6 +19465,7 @@
       <c r="C758" s="24"/>
       <c r="D758" s="24"/>
       <c r="E758" s="24"/>
+      <c r="F758" s="24"/>
     </row>
     <row r="759" ht="24" customHeight="1">
       <c r="A759" s="34"/>
@@ -18711,6 +19473,7 @@
       <c r="C759" s="24"/>
       <c r="D759" s="24"/>
       <c r="E759" s="24"/>
+      <c r="F759" s="24"/>
     </row>
     <row r="760" ht="24" customHeight="1">
       <c r="A760" s="34"/>
@@ -18718,6 +19481,7 @@
       <c r="C760" s="24"/>
       <c r="D760" s="24"/>
       <c r="E760" s="24"/>
+      <c r="F760" s="24"/>
     </row>
     <row r="761" ht="24" customHeight="1">
       <c r="A761" s="34"/>
@@ -18725,6 +19489,7 @@
       <c r="C761" s="24"/>
       <c r="D761" s="24"/>
       <c r="E761" s="24"/>
+      <c r="F761" s="24"/>
     </row>
     <row r="762" ht="24" customHeight="1">
       <c r="A762" s="34"/>
@@ -18732,6 +19497,7 @@
       <c r="C762" s="24"/>
       <c r="D762" s="24"/>
       <c r="E762" s="24"/>
+      <c r="F762" s="24"/>
     </row>
     <row r="763" ht="24" customHeight="1">
       <c r="A763" s="34"/>
@@ -18739,6 +19505,7 @@
       <c r="C763" s="24"/>
       <c r="D763" s="24"/>
       <c r="E763" s="24"/>
+      <c r="F763" s="24"/>
     </row>
     <row r="764" ht="24" customHeight="1">
       <c r="A764" s="34"/>
@@ -18746,6 +19513,7 @@
       <c r="C764" s="24"/>
       <c r="D764" s="24"/>
       <c r="E764" s="24"/>
+      <c r="F764" s="24"/>
     </row>
     <row r="765" ht="24" customHeight="1">
       <c r="A765" s="34"/>
@@ -18753,6 +19521,7 @@
       <c r="C765" s="24"/>
       <c r="D765" s="24"/>
       <c r="E765" s="24"/>
+      <c r="F765" s="24"/>
     </row>
     <row r="766" ht="24" customHeight="1">
       <c r="A766" s="34"/>
@@ -18760,6 +19529,7 @@
       <c r="C766" s="24"/>
       <c r="D766" s="24"/>
       <c r="E766" s="24"/>
+      <c r="F766" s="24"/>
     </row>
     <row r="767" ht="24" customHeight="1">
       <c r="A767" s="34"/>
@@ -18767,6 +19537,7 @@
       <c r="C767" s="24"/>
       <c r="D767" s="24"/>
       <c r="E767" s="24"/>
+      <c r="F767" s="24"/>
     </row>
     <row r="768" ht="24" customHeight="1">
       <c r="A768" s="34"/>
@@ -18774,6 +19545,7 @@
       <c r="C768" s="24"/>
       <c r="D768" s="24"/>
       <c r="E768" s="24"/>
+      <c r="F768" s="24"/>
     </row>
     <row r="769" ht="24" customHeight="1">
       <c r="A769" s="34"/>
@@ -18781,6 +19553,7 @@
       <c r="C769" s="24"/>
       <c r="D769" s="24"/>
       <c r="E769" s="24"/>
+      <c r="F769" s="24"/>
     </row>
     <row r="770" ht="24" customHeight="1">
       <c r="A770" s="34"/>
@@ -18788,6 +19561,7 @@
       <c r="C770" s="24"/>
       <c r="D770" s="24"/>
       <c r="E770" s="24"/>
+      <c r="F770" s="24"/>
     </row>
     <row r="771" ht="24" customHeight="1">
       <c r="A771" s="34"/>
@@ -18795,6 +19569,7 @@
       <c r="C771" s="24"/>
       <c r="D771" s="24"/>
       <c r="E771" s="24"/>
+      <c r="F771" s="24"/>
     </row>
     <row r="772" ht="24" customHeight="1">
       <c r="A772" s="34"/>
@@ -18802,6 +19577,7 @@
       <c r="C772" s="24"/>
       <c r="D772" s="24"/>
       <c r="E772" s="24"/>
+      <c r="F772" s="24"/>
     </row>
     <row r="773" ht="24" customHeight="1">
       <c r="A773" s="34"/>
@@ -18809,6 +19585,7 @@
       <c r="C773" s="24"/>
       <c r="D773" s="24"/>
       <c r="E773" s="24"/>
+      <c r="F773" s="24"/>
     </row>
     <row r="774" ht="24" customHeight="1">
       <c r="A774" s="34"/>
@@ -18816,6 +19593,7 @@
       <c r="C774" s="24"/>
       <c r="D774" s="24"/>
       <c r="E774" s="24"/>
+      <c r="F774" s="24"/>
     </row>
     <row r="775" ht="24" customHeight="1">
       <c r="A775" s="34"/>
@@ -18823,6 +19601,7 @@
       <c r="C775" s="24"/>
       <c r="D775" s="24"/>
       <c r="E775" s="24"/>
+      <c r="F775" s="24"/>
     </row>
     <row r="776" ht="24" customHeight="1">
       <c r="A776" s="34"/>
@@ -18830,6 +19609,7 @@
       <c r="C776" s="24"/>
       <c r="D776" s="24"/>
       <c r="E776" s="24"/>
+      <c r="F776" s="24"/>
     </row>
     <row r="777" ht="24" customHeight="1">
       <c r="A777" s="34"/>
@@ -18837,6 +19617,7 @@
       <c r="C777" s="24"/>
       <c r="D777" s="24"/>
       <c r="E777" s="24"/>
+      <c r="F777" s="24"/>
     </row>
     <row r="778" ht="24" customHeight="1">
       <c r="A778" s="34"/>
@@ -18844,6 +19625,7 @@
       <c r="C778" s="24"/>
       <c r="D778" s="24"/>
       <c r="E778" s="24"/>
+      <c r="F778" s="24"/>
     </row>
     <row r="779" ht="24" customHeight="1">
       <c r="A779" s="34"/>
@@ -18851,6 +19633,7 @@
       <c r="C779" s="24"/>
       <c r="D779" s="24"/>
       <c r="E779" s="24"/>
+      <c r="F779" s="24"/>
     </row>
     <row r="780" ht="24" customHeight="1">
       <c r="A780" s="34"/>
@@ -18858,6 +19641,7 @@
       <c r="C780" s="24"/>
       <c r="D780" s="24"/>
       <c r="E780" s="24"/>
+      <c r="F780" s="24"/>
     </row>
     <row r="781" ht="24" customHeight="1">
       <c r="A781" s="34"/>
@@ -18865,6 +19649,7 @@
       <c r="C781" s="24"/>
       <c r="D781" s="24"/>
       <c r="E781" s="24"/>
+      <c r="F781" s="24"/>
     </row>
     <row r="782" ht="24" customHeight="1">
       <c r="A782" s="34"/>
@@ -18872,6 +19657,7 @@
       <c r="C782" s="24"/>
       <c r="D782" s="24"/>
       <c r="E782" s="24"/>
+      <c r="F782" s="24"/>
     </row>
     <row r="783" ht="24" customHeight="1">
       <c r="A783" s="34"/>
@@ -18879,6 +19665,7 @@
       <c r="C783" s="24"/>
       <c r="D783" s="24"/>
       <c r="E783" s="24"/>
+      <c r="F783" s="24"/>
     </row>
     <row r="784" ht="24" customHeight="1">
       <c r="A784" s="34"/>
@@ -18886,6 +19673,7 @@
       <c r="C784" s="24"/>
       <c r="D784" s="24"/>
       <c r="E784" s="24"/>
+      <c r="F784" s="24"/>
     </row>
     <row r="785" ht="24" customHeight="1">
       <c r="A785" s="34"/>
@@ -18893,6 +19681,7 @@
       <c r="C785" s="24"/>
       <c r="D785" s="24"/>
       <c r="E785" s="24"/>
+      <c r="F785" s="24"/>
     </row>
     <row r="786" ht="24" customHeight="1">
       <c r="A786" s="34"/>
@@ -18900,6 +19689,7 @@
       <c r="C786" s="24"/>
       <c r="D786" s="24"/>
       <c r="E786" s="24"/>
+      <c r="F786" s="24"/>
     </row>
     <row r="787" ht="24" customHeight="1">
       <c r="A787" s="34"/>
@@ -18907,6 +19697,7 @@
       <c r="C787" s="24"/>
       <c r="D787" s="24"/>
       <c r="E787" s="24"/>
+      <c r="F787" s="24"/>
     </row>
     <row r="788" ht="24" customHeight="1">
       <c r="A788" s="34"/>
@@ -18914,6 +19705,7 @@
       <c r="C788" s="24"/>
       <c r="D788" s="24"/>
       <c r="E788" s="24"/>
+      <c r="F788" s="24"/>
     </row>
     <row r="789" ht="24" customHeight="1">
       <c r="A789" s="34"/>
@@ -18921,6 +19713,7 @@
       <c r="C789" s="24"/>
       <c r="D789" s="24"/>
       <c r="E789" s="24"/>
+      <c r="F789" s="24"/>
     </row>
     <row r="790" ht="24" customHeight="1">
       <c r="A790" s="34"/>
@@ -18928,6 +19721,7 @@
       <c r="C790" s="24"/>
       <c r="D790" s="24"/>
       <c r="E790" s="24"/>
+      <c r="F790" s="24"/>
     </row>
     <row r="791" ht="24" customHeight="1">
       <c r="A791" s="34"/>
@@ -18935,6 +19729,7 @@
       <c r="C791" s="24"/>
       <c r="D791" s="24"/>
       <c r="E791" s="24"/>
+      <c r="F791" s="24"/>
     </row>
     <row r="792" ht="24" customHeight="1">
       <c r="A792" s="34"/>
@@ -18942,6 +19737,7 @@
       <c r="C792" s="24"/>
       <c r="D792" s="24"/>
       <c r="E792" s="24"/>
+      <c r="F792" s="24"/>
     </row>
     <row r="793" ht="24" customHeight="1">
       <c r="A793" s="34"/>
@@ -18949,6 +19745,7 @@
       <c r="C793" s="24"/>
       <c r="D793" s="24"/>
       <c r="E793" s="24"/>
+      <c r="F793" s="24"/>
     </row>
     <row r="794" ht="24" customHeight="1">
       <c r="A794" s="34"/>
@@ -18956,6 +19753,7 @@
       <c r="C794" s="24"/>
       <c r="D794" s="24"/>
       <c r="E794" s="24"/>
+      <c r="F794" s="24"/>
     </row>
     <row r="795" ht="24" customHeight="1">
       <c r="A795" s="34"/>
@@ -18963,6 +19761,7 @@
       <c r="C795" s="24"/>
       <c r="D795" s="24"/>
       <c r="E795" s="24"/>
+      <c r="F795" s="24"/>
     </row>
     <row r="796" ht="24" customHeight="1">
       <c r="A796" s="34"/>
@@ -18970,6 +19769,7 @@
       <c r="C796" s="24"/>
       <c r="D796" s="24"/>
       <c r="E796" s="24"/>
+      <c r="F796" s="24"/>
     </row>
     <row r="797" ht="24" customHeight="1">
       <c r="A797" s="34"/>
@@ -18977,6 +19777,7 @@
       <c r="C797" s="24"/>
       <c r="D797" s="24"/>
       <c r="E797" s="24"/>
+      <c r="F797" s="24"/>
     </row>
     <row r="798" ht="24" customHeight="1">
       <c r="A798" s="34"/>
@@ -18984,6 +19785,7 @@
       <c r="C798" s="24"/>
       <c r="D798" s="24"/>
       <c r="E798" s="24"/>
+      <c r="F798" s="24"/>
     </row>
     <row r="799" ht="24" customHeight="1">
       <c r="A799" s="34"/>
@@ -18991,6 +19793,7 @@
       <c r="C799" s="24"/>
       <c r="D799" s="24"/>
       <c r="E799" s="24"/>
+      <c r="F799" s="24"/>
     </row>
     <row r="800" ht="24" customHeight="1">
       <c r="A800" s="34"/>
@@ -18998,6 +19801,7 @@
       <c r="C800" s="24"/>
       <c r="D800" s="24"/>
       <c r="E800" s="24"/>
+      <c r="F800" s="24"/>
     </row>
     <row r="801" ht="24" customHeight="1">
       <c r="A801" s="34"/>
@@ -19005,6 +19809,7 @@
       <c r="C801" s="24"/>
       <c r="D801" s="24"/>
       <c r="E801" s="24"/>
+      <c r="F801" s="24"/>
     </row>
     <row r="802" ht="24" customHeight="1">
       <c r="A802" s="34"/>
@@ -19012,6 +19817,7 @@
       <c r="C802" s="24"/>
       <c r="D802" s="24"/>
       <c r="E802" s="24"/>
+      <c r="F802" s="24"/>
     </row>
     <row r="803" ht="24" customHeight="1">
       <c r="A803" s="34"/>
@@ -19019,6 +19825,7 @@
       <c r="C803" s="24"/>
       <c r="D803" s="24"/>
       <c r="E803" s="24"/>
+      <c r="F803" s="24"/>
     </row>
     <row r="804" ht="24" customHeight="1">
       <c r="A804" s="34"/>
@@ -19026,6 +19833,7 @@
       <c r="C804" s="24"/>
       <c r="D804" s="24"/>
       <c r="E804" s="24"/>
+      <c r="F804" s="24"/>
     </row>
     <row r="805" ht="24" customHeight="1">
       <c r="A805" s="34"/>
@@ -19033,6 +19841,7 @@
       <c r="C805" s="24"/>
       <c r="D805" s="24"/>
       <c r="E805" s="24"/>
+      <c r="F805" s="24"/>
     </row>
     <row r="806" ht="24" customHeight="1">
       <c r="A806" s="34"/>
@@ -19040,6 +19849,7 @@
       <c r="C806" s="24"/>
       <c r="D806" s="24"/>
       <c r="E806" s="24"/>
+      <c r="F806" s="24"/>
     </row>
     <row r="807" ht="24" customHeight="1">
       <c r="A807" s="34"/>
@@ -19047,6 +19857,7 @@
       <c r="C807" s="24"/>
       <c r="D807" s="24"/>
       <c r="E807" s="24"/>
+      <c r="F807" s="24"/>
     </row>
     <row r="808" ht="24" customHeight="1">
       <c r="A808" s="34"/>
@@ -19054,6 +19865,7 @@
       <c r="C808" s="24"/>
       <c r="D808" s="24"/>
       <c r="E808" s="24"/>
+      <c r="F808" s="24"/>
     </row>
     <row r="809" ht="24" customHeight="1">
       <c r="A809" s="34"/>
@@ -19061,6 +19873,7 @@
       <c r="C809" s="24"/>
       <c r="D809" s="24"/>
       <c r="E809" s="24"/>
+      <c r="F809" s="24"/>
     </row>
     <row r="810" ht="24" customHeight="1">
       <c r="A810" s="34"/>
@@ -19068,6 +19881,7 @@
       <c r="C810" s="24"/>
       <c r="D810" s="24"/>
       <c r="E810" s="24"/>
+      <c r="F810" s="24"/>
     </row>
     <row r="811" ht="24" customHeight="1">
       <c r="A811" s="34"/>
@@ -19075,6 +19889,7 @@
       <c r="C811" s="24"/>
       <c r="D811" s="24"/>
       <c r="E811" s="24"/>
+      <c r="F811" s="24"/>
     </row>
     <row r="812" ht="24" customHeight="1">
       <c r="A812" s="34"/>
@@ -19082,6 +19897,7 @@
       <c r="C812" s="24"/>
       <c r="D812" s="24"/>
       <c r="E812" s="24"/>
+      <c r="F812" s="24"/>
     </row>
     <row r="813" ht="24" customHeight="1">
       <c r="A813" s="34"/>
@@ -19089,6 +19905,7 @@
       <c r="C813" s="24"/>
       <c r="D813" s="24"/>
       <c r="E813" s="24"/>
+      <c r="F813" s="24"/>
     </row>
     <row r="814" ht="24" customHeight="1">
       <c r="A814" s="34"/>
@@ -19096,6 +19913,7 @@
       <c r="C814" s="24"/>
       <c r="D814" s="24"/>
       <c r="E814" s="24"/>
+      <c r="F814" s="24"/>
     </row>
     <row r="815" ht="24" customHeight="1">
       <c r="A815" s="34"/>
@@ -19103,6 +19921,7 @@
       <c r="C815" s="24"/>
       <c r="D815" s="24"/>
       <c r="E815" s="24"/>
+      <c r="F815" s="24"/>
     </row>
     <row r="816" ht="24" customHeight="1">
       <c r="A816" s="34"/>
@@ -19110,6 +19929,7 @@
       <c r="C816" s="24"/>
       <c r="D816" s="24"/>
       <c r="E816" s="24"/>
+      <c r="F816" s="24"/>
     </row>
     <row r="817" ht="24" customHeight="1">
       <c r="A817" s="34"/>
@@ -19117,6 +19937,7 @@
       <c r="C817" s="24"/>
       <c r="D817" s="24"/>
       <c r="E817" s="24"/>
+      <c r="F817" s="24"/>
     </row>
     <row r="818" ht="24" customHeight="1">
       <c r="A818" s="34"/>
@@ -19124,6 +19945,7 @@
       <c r="C818" s="24"/>
       <c r="D818" s="24"/>
       <c r="E818" s="24"/>
+      <c r="F818" s="24"/>
     </row>
     <row r="819" ht="24" customHeight="1">
       <c r="A819" s="34"/>
@@ -19131,6 +19953,7 @@
       <c r="C819" s="24"/>
       <c r="D819" s="24"/>
       <c r="E819" s="24"/>
+      <c r="F819" s="24"/>
     </row>
     <row r="820" ht="24" customHeight="1">
       <c r="A820" s="34"/>
@@ -19138,6 +19961,7 @@
       <c r="C820" s="24"/>
       <c r="D820" s="24"/>
       <c r="E820" s="24"/>
+      <c r="F820" s="24"/>
     </row>
     <row r="821" ht="24" customHeight="1">
       <c r="A821" s="34"/>
@@ -19145,6 +19969,7 @@
       <c r="C821" s="24"/>
       <c r="D821" s="24"/>
       <c r="E821" s="24"/>
+      <c r="F821" s="24"/>
     </row>
     <row r="822" ht="24" customHeight="1">
       <c r="A822" s="34"/>
@@ -19152,6 +19977,7 @@
       <c r="C822" s="24"/>
       <c r="D822" s="24"/>
       <c r="E822" s="24"/>
+      <c r="F822" s="24"/>
     </row>
     <row r="823" ht="24" customHeight="1">
       <c r="A823" s="34"/>
@@ -19159,6 +19985,7 @@
       <c r="C823" s="24"/>
       <c r="D823" s="24"/>
       <c r="E823" s="24"/>
+      <c r="F823" s="24"/>
     </row>
     <row r="824" ht="24" customHeight="1">
       <c r="A824" s="34"/>
@@ -19166,6 +19993,7 @@
       <c r="C824" s="24"/>
       <c r="D824" s="24"/>
       <c r="E824" s="24"/>
+      <c r="F824" s="24"/>
     </row>
     <row r="825" ht="24" customHeight="1">
       <c r="A825" s="34"/>
@@ -19173,6 +20001,7 @@
       <c r="C825" s="24"/>
       <c r="D825" s="24"/>
       <c r="E825" s="24"/>
+      <c r="F825" s="24"/>
     </row>
     <row r="826" ht="24" customHeight="1">
       <c r="A826" s="34"/>
@@ -19180,6 +20009,7 @@
       <c r="C826" s="24"/>
       <c r="D826" s="24"/>
       <c r="E826" s="24"/>
+      <c r="F826" s="24"/>
     </row>
     <row r="827" ht="24" customHeight="1">
       <c r="A827" s="34"/>
@@ -19187,6 +20017,7 @@
       <c r="C827" s="24"/>
       <c r="D827" s="24"/>
       <c r="E827" s="24"/>
+      <c r="F827" s="24"/>
     </row>
     <row r="828" ht="24" customHeight="1">
       <c r="A828" s="34"/>
@@ -19194,6 +20025,7 @@
       <c r="C828" s="24"/>
       <c r="D828" s="24"/>
       <c r="E828" s="24"/>
+      <c r="F828" s="24"/>
     </row>
     <row r="829" ht="24" customHeight="1">
       <c r="A829" s="34"/>
@@ -19201,6 +20033,7 @@
       <c r="C829" s="24"/>
       <c r="D829" s="24"/>
       <c r="E829" s="24"/>
+      <c r="F829" s="24"/>
     </row>
     <row r="830" ht="24" customHeight="1">
       <c r="A830" s="34"/>
@@ -19208,6 +20041,7 @@
       <c r="C830" s="24"/>
       <c r="D830" s="24"/>
       <c r="E830" s="24"/>
+      <c r="F830" s="24"/>
     </row>
     <row r="831" ht="24" customHeight="1">
       <c r="A831" s="34"/>
@@ -19215,6 +20049,7 @@
       <c r="C831" s="24"/>
       <c r="D831" s="24"/>
       <c r="E831" s="24"/>
+      <c r="F831" s="24"/>
     </row>
     <row r="832" ht="24" customHeight="1">
       <c r="A832" s="34"/>
@@ -19222,6 +20057,7 @@
       <c r="C832" s="24"/>
       <c r="D832" s="24"/>
       <c r="E832" s="24"/>
+      <c r="F832" s="24"/>
     </row>
     <row r="833" ht="24" customHeight="1">
       <c r="A833" s="34"/>
@@ -19229,6 +20065,7 @@
       <c r="C833" s="24"/>
       <c r="D833" s="24"/>
       <c r="E833" s="24"/>
+      <c r="F833" s="24"/>
     </row>
     <row r="834" ht="24" customHeight="1">
       <c r="A834" s="34"/>
@@ -19236,6 +20073,7 @@
       <c r="C834" s="24"/>
       <c r="D834" s="24"/>
       <c r="E834" s="24"/>
+      <c r="F834" s="24"/>
     </row>
     <row r="835" ht="24" customHeight="1">
       <c r="A835" s="34"/>
@@ -19243,6 +20081,7 @@
       <c r="C835" s="24"/>
       <c r="D835" s="24"/>
       <c r="E835" s="24"/>
+      <c r="F835" s="24"/>
     </row>
     <row r="836" ht="24" customHeight="1">
       <c r="A836" s="34"/>
@@ -19250,6 +20089,7 @@
       <c r="C836" s="24"/>
       <c r="D836" s="24"/>
       <c r="E836" s="24"/>
+      <c r="F836" s="24"/>
     </row>
     <row r="837" ht="24" customHeight="1">
       <c r="A837" s="34"/>
@@ -19257,6 +20097,7 @@
       <c r="C837" s="24"/>
       <c r="D837" s="24"/>
       <c r="E837" s="24"/>
+      <c r="F837" s="24"/>
     </row>
     <row r="838" ht="24" customHeight="1">
       <c r="A838" s="34"/>
@@ -19264,6 +20105,7 @@
       <c r="C838" s="24"/>
       <c r="D838" s="24"/>
       <c r="E838" s="24"/>
+      <c r="F838" s="24"/>
     </row>
     <row r="839" ht="24" customHeight="1">
       <c r="A839" s="34"/>
@@ -19271,6 +20113,7 @@
       <c r="C839" s="24"/>
       <c r="D839" s="24"/>
       <c r="E839" s="24"/>
+      <c r="F839" s="24"/>
     </row>
     <row r="840" ht="24" customHeight="1">
       <c r="A840" s="34"/>
@@ -19278,6 +20121,7 @@
       <c r="C840" s="24"/>
       <c r="D840" s="24"/>
       <c r="E840" s="24"/>
+      <c r="F840" s="24"/>
     </row>
     <row r="841" ht="24" customHeight="1">
       <c r="A841" s="34"/>
@@ -19285,6 +20129,7 @@
       <c r="C841" s="24"/>
       <c r="D841" s="24"/>
       <c r="E841" s="24"/>
+      <c r="F841" s="24"/>
     </row>
     <row r="842" ht="24" customHeight="1">
       <c r="A842" s="34"/>
@@ -19292,6 +20137,7 @@
       <c r="C842" s="24"/>
       <c r="D842" s="24"/>
       <c r="E842" s="24"/>
+      <c r="F842" s="24"/>
     </row>
     <row r="843" ht="24" customHeight="1">
       <c r="A843" s="34"/>
@@ -19299,6 +20145,7 @@
       <c r="C843" s="24"/>
       <c r="D843" s="24"/>
       <c r="E843" s="24"/>
+      <c r="F843" s="24"/>
     </row>
     <row r="844" ht="24" customHeight="1">
       <c r="A844" s="34"/>
@@ -19306,6 +20153,7 @@
       <c r="C844" s="24"/>
       <c r="D844" s="24"/>
       <c r="E844" s="24"/>
+      <c r="F844" s="24"/>
     </row>
     <row r="845" ht="24" customHeight="1">
       <c r="A845" s="34"/>
@@ -19313,6 +20161,7 @@
       <c r="C845" s="24"/>
       <c r="D845" s="24"/>
       <c r="E845" s="24"/>
+      <c r="F845" s="24"/>
     </row>
     <row r="846" ht="24" customHeight="1">
       <c r="A846" s="34"/>
@@ -19320,6 +20169,7 @@
       <c r="C846" s="24"/>
       <c r="D846" s="24"/>
       <c r="E846" s="24"/>
+      <c r="F846" s="24"/>
     </row>
     <row r="847" ht="24" customHeight="1">
       <c r="A847" s="34"/>
@@ -19327,6 +20177,7 @@
       <c r="C847" s="24"/>
       <c r="D847" s="24"/>
       <c r="E847" s="24"/>
+      <c r="F847" s="24"/>
     </row>
     <row r="848" ht="24" customHeight="1">
       <c r="A848" s="34"/>
@@ -19334,6 +20185,7 @@
       <c r="C848" s="24"/>
       <c r="D848" s="24"/>
       <c r="E848" s="24"/>
+      <c r="F848" s="24"/>
     </row>
     <row r="849" ht="24" customHeight="1">
       <c r="A849" s="34"/>
@@ -19341,6 +20193,7 @@
       <c r="C849" s="24"/>
       <c r="D849" s="24"/>
       <c r="E849" s="24"/>
+      <c r="F849" s="24"/>
     </row>
     <row r="850" ht="24" customHeight="1">
       <c r="A850" s="34"/>
@@ -19348,6 +20201,7 @@
       <c r="C850" s="24"/>
       <c r="D850" s="24"/>
       <c r="E850" s="24"/>
+      <c r="F850" s="24"/>
     </row>
     <row r="851" ht="24" customHeight="1">
       <c r="A851" s="34"/>
@@ -19355,6 +20209,7 @@
       <c r="C851" s="24"/>
       <c r="D851" s="24"/>
       <c r="E851" s="24"/>
+      <c r="F851" s="24"/>
     </row>
     <row r="852" ht="24" customHeight="1">
       <c r="A852" s="34"/>
@@ -19362,6 +20217,7 @@
       <c r="C852" s="24"/>
       <c r="D852" s="24"/>
       <c r="E852" s="24"/>
+      <c r="F852" s="24"/>
     </row>
     <row r="853" ht="24" customHeight="1">
       <c r="A853" s="34"/>
@@ -19369,6 +20225,7 @@
       <c r="C853" s="24"/>
       <c r="D853" s="24"/>
       <c r="E853" s="24"/>
+      <c r="F853" s="24"/>
     </row>
     <row r="854" ht="24" customHeight="1">
       <c r="A854" s="34"/>
@@ -19376,6 +20233,7 @@
       <c r="C854" s="24"/>
       <c r="D854" s="24"/>
       <c r="E854" s="24"/>
+      <c r="F854" s="24"/>
     </row>
     <row r="855" ht="24" customHeight="1">
       <c r="A855" s="34"/>
@@ -19383,6 +20241,7 @@
       <c r="C855" s="24"/>
       <c r="D855" s="24"/>
       <c r="E855" s="24"/>
+      <c r="F855" s="24"/>
     </row>
     <row r="856" ht="24" customHeight="1">
       <c r="A856" s="34"/>
@@ -19390,6 +20249,7 @@
       <c r="C856" s="24"/>
       <c r="D856" s="24"/>
       <c r="E856" s="24"/>
+      <c r="F856" s="24"/>
     </row>
     <row r="857" ht="24" customHeight="1">
       <c r="A857" s="34"/>
@@ -19397,6 +20257,7 @@
       <c r="C857" s="24"/>
       <c r="D857" s="24"/>
       <c r="E857" s="24"/>
+      <c r="F857" s="24"/>
     </row>
     <row r="858" ht="24" customHeight="1">
       <c r="A858" s="34"/>
@@ -19404,6 +20265,7 @@
       <c r="C858" s="24"/>
       <c r="D858" s="24"/>
       <c r="E858" s="24"/>
+      <c r="F858" s="24"/>
     </row>
     <row r="859" ht="24" customHeight="1">
       <c r="A859" s="34"/>
@@ -19411,6 +20273,7 @@
       <c r="C859" s="24"/>
       <c r="D859" s="24"/>
       <c r="E859" s="24"/>
+      <c r="F859" s="24"/>
     </row>
     <row r="860" ht="24" customHeight="1">
       <c r="A860" s="34"/>
@@ -19418,6 +20281,7 @@
       <c r="C860" s="24"/>
       <c r="D860" s="24"/>
       <c r="E860" s="24"/>
+      <c r="F860" s="24"/>
     </row>
     <row r="861" ht="24" customHeight="1">
       <c r="A861" s="34"/>
@@ -19425,6 +20289,7 @@
       <c r="C861" s="24"/>
       <c r="D861" s="24"/>
       <c r="E861" s="24"/>
+      <c r="F861" s="24"/>
     </row>
     <row r="862" ht="24" customHeight="1">
       <c r="A862" s="34"/>
@@ -19432,6 +20297,7 @@
       <c r="C862" s="24"/>
       <c r="D862" s="24"/>
       <c r="E862" s="24"/>
+      <c r="F862" s="24"/>
     </row>
     <row r="863" ht="24" customHeight="1">
       <c r="A863" s="34"/>
@@ -19439,6 +20305,7 @@
       <c r="C863" s="24"/>
       <c r="D863" s="24"/>
       <c r="E863" s="24"/>
+      <c r="F863" s="24"/>
     </row>
     <row r="864" ht="24" customHeight="1">
       <c r="A864" s="34"/>
@@ -19446,6 +20313,7 @@
       <c r="C864" s="24"/>
       <c r="D864" s="24"/>
       <c r="E864" s="24"/>
+      <c r="F864" s="24"/>
     </row>
     <row r="865" ht="24" customHeight="1">
       <c r="A865" s="34"/>
@@ -19453,6 +20321,7 @@
       <c r="C865" s="24"/>
       <c r="D865" s="24"/>
       <c r="E865" s="24"/>
+      <c r="F865" s="24"/>
     </row>
     <row r="866" ht="24" customHeight="1">
       <c r="A866" s="34"/>
@@ -19460,6 +20329,7 @@
       <c r="C866" s="24"/>
       <c r="D866" s="24"/>
       <c r="E866" s="24"/>
+      <c r="F866" s="24"/>
     </row>
     <row r="867" ht="24" customHeight="1">
       <c r="A867" s="34"/>
@@ -19467,6 +20337,7 @@
       <c r="C867" s="24"/>
       <c r="D867" s="24"/>
       <c r="E867" s="24"/>
+      <c r="F867" s="24"/>
     </row>
     <row r="868" ht="24" customHeight="1">
       <c r="A868" s="34"/>
@@ -19474,6 +20345,7 @@
       <c r="C868" s="24"/>
       <c r="D868" s="24"/>
       <c r="E868" s="24"/>
+      <c r="F868" s="24"/>
     </row>
     <row r="869" ht="24" customHeight="1">
       <c r="A869" s="34"/>
@@ -19481,6 +20353,7 @@
       <c r="C869" s="24"/>
       <c r="D869" s="24"/>
       <c r="E869" s="24"/>
+      <c r="F869" s="24"/>
     </row>
     <row r="870" ht="24" customHeight="1">
       <c r="A870" s="34"/>
@@ -19488,6 +20361,7 @@
       <c r="C870" s="24"/>
       <c r="D870" s="24"/>
       <c r="E870" s="24"/>
+      <c r="F870" s="24"/>
     </row>
     <row r="871" ht="24" customHeight="1">
       <c r="A871" s="34"/>
@@ -19495,6 +20369,7 @@
       <c r="C871" s="24"/>
       <c r="D871" s="24"/>
       <c r="E871" s="24"/>
+      <c r="F871" s="24"/>
     </row>
     <row r="872" ht="24" customHeight="1">
       <c r="A872" s="34"/>
@@ -19502,6 +20377,7 @@
       <c r="C872" s="24"/>
       <c r="D872" s="24"/>
       <c r="E872" s="24"/>
+      <c r="F872" s="24"/>
     </row>
     <row r="873" ht="24" customHeight="1">
       <c r="A873" s="34"/>
@@ -19509,6 +20385,7 @@
       <c r="C873" s="24"/>
       <c r="D873" s="24"/>
       <c r="E873" s="24"/>
+      <c r="F873" s="24"/>
     </row>
     <row r="874" ht="24" customHeight="1">
       <c r="A874" s="34"/>
@@ -19516,6 +20393,7 @@
       <c r="C874" s="24"/>
       <c r="D874" s="24"/>
       <c r="E874" s="24"/>
+      <c r="F874" s="24"/>
     </row>
     <row r="875" ht="24" customHeight="1">
       <c r="A875" s="34"/>
@@ -19523,6 +20401,7 @@
       <c r="C875" s="24"/>
       <c r="D875" s="24"/>
       <c r="E875" s="24"/>
+      <c r="F875" s="24"/>
     </row>
     <row r="876" ht="24" customHeight="1">
       <c r="A876" s="34"/>
@@ -19530,6 +20409,7 @@
       <c r="C876" s="24"/>
       <c r="D876" s="24"/>
       <c r="E876" s="24"/>
+      <c r="F876" s="24"/>
     </row>
     <row r="877" ht="24" customHeight="1">
       <c r="A877" s="34"/>
@@ -19537,6 +20417,7 @@
       <c r="C877" s="24"/>
       <c r="D877" s="24"/>
       <c r="E877" s="24"/>
+      <c r="F877" s="24"/>
     </row>
     <row r="878" ht="24" customHeight="1">
       <c r="A878" s="34"/>
@@ -19544,6 +20425,7 @@
       <c r="C878" s="24"/>
       <c r="D878" s="24"/>
       <c r="E878" s="24"/>
+      <c r="F878" s="24"/>
     </row>
     <row r="879" ht="24" customHeight="1">
       <c r="A879" s="34"/>
@@ -19551,6 +20433,7 @@
       <c r="C879" s="24"/>
       <c r="D879" s="24"/>
       <c r="E879" s="24"/>
+      <c r="F879" s="24"/>
     </row>
     <row r="880" ht="24" customHeight="1">
       <c r="A880" s="34"/>
@@ -19558,6 +20441,7 @@
       <c r="C880" s="24"/>
       <c r="D880" s="24"/>
       <c r="E880" s="24"/>
+      <c r="F880" s="24"/>
     </row>
     <row r="881" ht="24" customHeight="1">
       <c r="A881" s="34"/>
@@ -19565,6 +20449,7 @@
       <c r="C881" s="24"/>
       <c r="D881" s="24"/>
       <c r="E881" s="24"/>
+      <c r="F881" s="24"/>
     </row>
     <row r="882" ht="24" customHeight="1">
       <c r="A882" s="34"/>
@@ -19572,6 +20457,7 @@
       <c r="C882" s="24"/>
       <c r="D882" s="24"/>
       <c r="E882" s="24"/>
+      <c r="F882" s="24"/>
     </row>
     <row r="883" ht="24" customHeight="1">
       <c r="A883" s="34"/>
@@ -19579,6 +20465,7 @@
       <c r="C883" s="24"/>
       <c r="D883" s="24"/>
       <c r="E883" s="24"/>
+      <c r="F883" s="24"/>
     </row>
     <row r="884" ht="24" customHeight="1">
       <c r="A884" s="34"/>
@@ -19586,6 +20473,7 @@
       <c r="C884" s="24"/>
       <c r="D884" s="24"/>
       <c r="E884" s="24"/>
+      <c r="F884" s="24"/>
     </row>
     <row r="885" ht="24" customHeight="1">
       <c r="A885" s="34"/>
@@ -19593,6 +20481,7 @@
       <c r="C885" s="24"/>
       <c r="D885" s="24"/>
       <c r="E885" s="24"/>
+      <c r="F885" s="24"/>
     </row>
     <row r="886" ht="24" customHeight="1">
       <c r="A886" s="34"/>
@@ -19600,6 +20489,7 @@
       <c r="C886" s="24"/>
       <c r="D886" s="24"/>
       <c r="E886" s="24"/>
+      <c r="F886" s="24"/>
     </row>
     <row r="887" ht="24" customHeight="1">
       <c r="A887" s="34"/>
@@ -19607,6 +20497,7 @@
       <c r="C887" s="24"/>
       <c r="D887" s="24"/>
       <c r="E887" s="24"/>
+      <c r="F887" s="24"/>
     </row>
     <row r="888" ht="24" customHeight="1">
       <c r="A888" s="34"/>
@@ -19614,6 +20505,7 @@
       <c r="C888" s="24"/>
       <c r="D888" s="24"/>
       <c r="E888" s="24"/>
+      <c r="F888" s="24"/>
     </row>
     <row r="889" ht="24" customHeight="1">
       <c r="A889" s="34"/>
@@ -19621,6 +20513,7 @@
       <c r="C889" s="24"/>
       <c r="D889" s="24"/>
       <c r="E889" s="24"/>
+      <c r="F889" s="24"/>
     </row>
     <row r="890" ht="24" customHeight="1">
       <c r="A890" s="34"/>
@@ -19628,6 +20521,7 @@
       <c r="C890" s="24"/>
       <c r="D890" s="24"/>
       <c r="E890" s="24"/>
+      <c r="F890" s="24"/>
     </row>
     <row r="891" ht="24" customHeight="1">
       <c r="A891" s="34"/>
@@ -19635,6 +20529,7 @@
       <c r="C891" s="24"/>
       <c r="D891" s="24"/>
       <c r="E891" s="24"/>
+      <c r="F891" s="24"/>
     </row>
     <row r="892" ht="24" customHeight="1">
       <c r="A892" s="34"/>
@@ -19642,6 +20537,7 @@
       <c r="C892" s="24"/>
       <c r="D892" s="24"/>
       <c r="E892" s="24"/>
+      <c r="F892" s="24"/>
     </row>
     <row r="893" ht="24" customHeight="1">
       <c r="A893" s="34"/>
@@ -19649,6 +20545,7 @@
       <c r="C893" s="24"/>
       <c r="D893" s="24"/>
       <c r="E893" s="24"/>
+      <c r="F893" s="24"/>
     </row>
     <row r="894" ht="24" customHeight="1">
       <c r="A894" s="34"/>
@@ -19656,6 +20553,7 @@
       <c r="C894" s="24"/>
       <c r="D894" s="24"/>
       <c r="E894" s="24"/>
+      <c r="F894" s="24"/>
     </row>
     <row r="895" ht="24" customHeight="1">
       <c r="A895" s="34"/>
@@ -19663,6 +20561,7 @@
       <c r="C895" s="24"/>
       <c r="D895" s="24"/>
       <c r="E895" s="24"/>
+      <c r="F895" s="24"/>
     </row>
     <row r="896" ht="24" customHeight="1">
       <c r="A896" s="34"/>
@@ -19670,6 +20569,7 @@
       <c r="C896" s="24"/>
       <c r="D896" s="24"/>
       <c r="E896" s="24"/>
+      <c r="F896" s="24"/>
     </row>
     <row r="897" ht="24" customHeight="1">
       <c r="A897" s="34"/>
@@ -19677,6 +20577,7 @@
       <c r="C897" s="24"/>
       <c r="D897" s="24"/>
       <c r="E897" s="24"/>
+      <c r="F897" s="24"/>
     </row>
     <row r="898" ht="24" customHeight="1">
       <c r="A898" s="34"/>
@@ -19684,6 +20585,7 @@
       <c r="C898" s="24"/>
       <c r="D898" s="24"/>
       <c r="E898" s="24"/>
+      <c r="F898" s="24"/>
     </row>
     <row r="899" ht="24" customHeight="1">
       <c r="A899" s="34"/>
@@ -19691,6 +20593,7 @@
       <c r="C899" s="24"/>
       <c r="D899" s="24"/>
       <c r="E899" s="24"/>
+      <c r="F899" s="24"/>
     </row>
     <row r="900" ht="24" customHeight="1">
       <c r="A900" s="34"/>
@@ -19698,6 +20601,7 @@
       <c r="C900" s="24"/>
       <c r="D900" s="24"/>
       <c r="E900" s="24"/>
+      <c r="F900" s="24"/>
     </row>
     <row r="901" ht="24" customHeight="1">
       <c r="A901" s="34"/>
@@ -19705,6 +20609,7 @@
       <c r="C901" s="24"/>
       <c r="D901" s="24"/>
       <c r="E901" s="24"/>
+      <c r="F901" s="24"/>
     </row>
     <row r="902" ht="24" customHeight="1">
       <c r="A902" s="34"/>
@@ -19712,6 +20617,7 @@
       <c r="C902" s="24"/>
       <c r="D902" s="24"/>
       <c r="E902" s="24"/>
+      <c r="F902" s="24"/>
     </row>
     <row r="903" ht="24" customHeight="1">
       <c r="A903" s="34"/>
@@ -19719,6 +20625,7 @@
       <c r="C903" s="24"/>
       <c r="D903" s="24"/>
       <c r="E903" s="24"/>
+      <c r="F903" s="24"/>
     </row>
     <row r="904" ht="24" customHeight="1">
       <c r="A904" s="34"/>
@@ -19726,6 +20633,7 @@
       <c r="C904" s="24"/>
       <c r="D904" s="24"/>
       <c r="E904" s="24"/>
+      <c r="F904" s="24"/>
     </row>
     <row r="905" ht="24" customHeight="1">
       <c r="A905" s="34"/>
@@ -19733,6 +20641,7 @@
       <c r="C905" s="24"/>
       <c r="D905" s="24"/>
       <c r="E905" s="24"/>
+      <c r="F905" s="24"/>
     </row>
     <row r="906" ht="24" customHeight="1">
       <c r="A906" s="34"/>
@@ -19740,6 +20649,7 @@
       <c r="C906" s="24"/>
       <c r="D906" s="24"/>
       <c r="E906" s="24"/>
+      <c r="F906" s="24"/>
     </row>
     <row r="907" ht="24" customHeight="1">
       <c r="A907" s="34"/>
@@ -19747,6 +20657,7 @@
       <c r="C907" s="24"/>
       <c r="D907" s="24"/>
       <c r="E907" s="24"/>
+      <c r="F907" s="24"/>
     </row>
     <row r="908" ht="24" customHeight="1">
       <c r="A908" s="34"/>
@@ -19754,6 +20665,7 @@
       <c r="C908" s="24"/>
       <c r="D908" s="24"/>
       <c r="E908" s="24"/>
+      <c r="F908" s="24"/>
     </row>
     <row r="909" ht="24" customHeight="1">
       <c r="A909" s="34"/>
@@ -19761,6 +20673,7 @@
       <c r="C909" s="24"/>
       <c r="D909" s="24"/>
       <c r="E909" s="24"/>
+      <c r="F909" s="24"/>
     </row>
     <row r="910" ht="24" customHeight="1">
       <c r="A910" s="34"/>
@@ -19768,6 +20681,7 @@
       <c r="C910" s="24"/>
       <c r="D910" s="24"/>
       <c r="E910" s="24"/>
+      <c r="F910" s="24"/>
     </row>
     <row r="911" ht="24" customHeight="1">
       <c r="A911" s="34"/>
@@ -19775,6 +20689,7 @@
       <c r="C911" s="24"/>
       <c r="D911" s="24"/>
       <c r="E911" s="24"/>
+      <c r="F911" s="24"/>
     </row>
     <row r="912" ht="24" customHeight="1">
       <c r="A912" s="34"/>
@@ -19782,6 +20697,7 @@
       <c r="C912" s="24"/>
       <c r="D912" s="24"/>
       <c r="E912" s="24"/>
+      <c r="F912" s="24"/>
     </row>
     <row r="913" ht="24" customHeight="1">
       <c r="A913" s="34"/>
@@ -19789,6 +20705,7 @@
       <c r="C913" s="24"/>
       <c r="D913" s="24"/>
       <c r="E913" s="24"/>
+      <c r="F913" s="24"/>
     </row>
     <row r="914" ht="24" customHeight="1">
       <c r="A914" s="34"/>
@@ -19796,6 +20713,7 @@
       <c r="C914" s="24"/>
       <c r="D914" s="24"/>
       <c r="E914" s="24"/>
+      <c r="F914" s="24"/>
     </row>
     <row r="915" ht="24" customHeight="1">
       <c r="A915" s="34"/>
@@ -19803,6 +20721,7 @@
       <c r="C915" s="24"/>
       <c r="D915" s="24"/>
       <c r="E915" s="24"/>
+      <c r="F915" s="24"/>
     </row>
     <row r="916" ht="24" customHeight="1">
       <c r="A916" s="34"/>
@@ -19810,6 +20729,7 @@
       <c r="C916" s="24"/>
       <c r="D916" s="24"/>
       <c r="E916" s="24"/>
+      <c r="F916" s="24"/>
     </row>
     <row r="917" ht="24" customHeight="1">
       <c r="A917" s="34"/>
@@ -19817,6 +20737,7 @@
       <c r="C917" s="24"/>
       <c r="D917" s="24"/>
       <c r="E917" s="24"/>
+      <c r="F917" s="24"/>
     </row>
     <row r="918" ht="24" customHeight="1">
       <c r="A918" s="34"/>
@@ -19824,6 +20745,7 @@
       <c r="C918" s="24"/>
       <c r="D918" s="24"/>
       <c r="E918" s="24"/>
+      <c r="F918" s="24"/>
     </row>
     <row r="919" ht="24" customHeight="1">
       <c r="A919" s="34"/>
@@ -19831,6 +20753,7 @@
       <c r="C919" s="24"/>
       <c r="D919" s="24"/>
       <c r="E919" s="24"/>
+      <c r="F919" s="24"/>
     </row>
     <row r="920" ht="24" customHeight="1">
       <c r="A920" s="34"/>
@@ -19838,6 +20761,7 @@
       <c r="C920" s="24"/>
       <c r="D920" s="24"/>
       <c r="E920" s="24"/>
+      <c r="F920" s="24"/>
     </row>
     <row r="921" ht="24" customHeight="1">
       <c r="A921" s="34"/>
@@ -19845,6 +20769,7 @@
       <c r="C921" s="24"/>
       <c r="D921" s="24"/>
       <c r="E921" s="24"/>
+      <c r="F921" s="24"/>
     </row>
     <row r="922" ht="24" customHeight="1">
       <c r="A922" s="34"/>
@@ -19852,6 +20777,7 @@
       <c r="C922" s="24"/>
       <c r="D922" s="24"/>
       <c r="E922" s="24"/>
+      <c r="F922" s="24"/>
     </row>
     <row r="923" ht="24" customHeight="1">
       <c r="A923" s="34"/>
@@ -19859,6 +20785,7 @@
       <c r="C923" s="24"/>
       <c r="D923" s="24"/>
       <c r="E923" s="24"/>
+      <c r="F923" s="24"/>
     </row>
     <row r="924" ht="24" customHeight="1">
       <c r="A924" s="34"/>
@@ -19866,6 +20793,7 @@
       <c r="C924" s="24"/>
       <c r="D924" s="24"/>
       <c r="E924" s="24"/>
+      <c r="F924" s="24"/>
     </row>
     <row r="925" ht="24" customHeight="1">
       <c r="A925" s="34"/>
@@ -19873,6 +20801,7 @@
       <c r="C925" s="24"/>
       <c r="D925" s="24"/>
       <c r="E925" s="24"/>
+      <c r="F925" s="24"/>
     </row>
     <row r="926" ht="24" customHeight="1">
       <c r="A926" s="34"/>
@@ -19880,6 +20809,7 @@
       <c r="C926" s="24"/>
       <c r="D926" s="24"/>
       <c r="E926" s="24"/>
+      <c r="F926" s="24"/>
     </row>
     <row r="927" ht="24" customHeight="1">
       <c r="A927" s="34"/>
@@ -19887,6 +20817,7 @@
       <c r="C927" s="24"/>
       <c r="D927" s="24"/>
       <c r="E927" s="24"/>
+      <c r="F927" s="24"/>
     </row>
     <row r="928" ht="24" customHeight="1">
       <c r="A928" s="34"/>
@@ -19894,6 +20825,7 @@
       <c r="C928" s="24"/>
       <c r="D928" s="24"/>
       <c r="E928" s="24"/>
+      <c r="F928" s="24"/>
     </row>
     <row r="929" ht="24" customHeight="1">
       <c r="A929" s="34"/>
@@ -19901,6 +20833,7 @@
       <c r="C929" s="24"/>
       <c r="D929" s="24"/>
       <c r="E929" s="24"/>
+      <c r="F929" s="24"/>
     </row>
     <row r="930" ht="24" customHeight="1">
       <c r="A930" s="34"/>
@@ -19908,6 +20841,7 @@
       <c r="C930" s="24"/>
       <c r="D930" s="24"/>
       <c r="E930" s="24"/>
+      <c r="F930" s="24"/>
     </row>
     <row r="931" ht="24" customHeight="1">
       <c r="A931" s="34"/>
@@ -19915,6 +20849,7 @@
       <c r="C931" s="24"/>
       <c r="D931" s="24"/>
       <c r="E931" s="24"/>
+      <c r="F931" s="24"/>
     </row>
     <row r="932" ht="24" customHeight="1">
       <c r="A932" s="34"/>
@@ -19922,6 +20857,7 @@
       <c r="C932" s="24"/>
       <c r="D932" s="24"/>
       <c r="E932" s="24"/>
+      <c r="F932" s="24"/>
     </row>
     <row r="933" ht="24" customHeight="1">
       <c r="A933" s="34"/>
@@ -19929,6 +20865,7 @@
       <c r="C933" s="24"/>
       <c r="D933" s="24"/>
       <c r="E933" s="24"/>
+      <c r="F933" s="24"/>
     </row>
     <row r="934" ht="24" customHeight="1">
       <c r="A934" s="34"/>
@@ -19936,6 +20873,7 @@
       <c r="C934" s="24"/>
       <c r="D934" s="24"/>
       <c r="E934" s="24"/>
+      <c r="F934" s="24"/>
     </row>
     <row r="935" ht="24" customHeight="1">
       <c r="A935" s="34"/>
@@ -19943,6 +20881,7 @@
       <c r="C935" s="24"/>
       <c r="D935" s="24"/>
       <c r="E935" s="24"/>
+      <c r="F935" s="24"/>
     </row>
     <row r="936" ht="24" customHeight="1">
       <c r="A936" s="34"/>
@@ -19950,6 +20889,7 @@
       <c r="C936" s="24"/>
       <c r="D936" s="24"/>
       <c r="E936" s="24"/>
+      <c r="F936" s="24"/>
     </row>
     <row r="937" ht="24" customHeight="1">
       <c r="A937" s="34"/>
@@ -19957,6 +20897,7 @@
       <c r="C937" s="24"/>
       <c r="D937" s="24"/>
       <c r="E937" s="24"/>
+      <c r="F937" s="24"/>
     </row>
     <row r="938" ht="24" customHeight="1">
       <c r="A938" s="34"/>
@@ -19964,6 +20905,7 @@
       <c r="C938" s="24"/>
       <c r="D938" s="24"/>
       <c r="E938" s="24"/>
+      <c r="F938" s="24"/>
     </row>
     <row r="939" ht="24" customHeight="1">
       <c r="A939" s="34"/>
@@ -19971,6 +20913,7 @@
       <c r="C939" s="24"/>
       <c r="D939" s="24"/>
       <c r="E939" s="24"/>
+      <c r="F939" s="24"/>
     </row>
     <row r="940" ht="24" customHeight="1">
       <c r="A940" s="34"/>
@@ -19978,6 +20921,7 @@
       <c r="C940" s="24"/>
       <c r="D940" s="24"/>
       <c r="E940" s="24"/>
+      <c r="F940" s="24"/>
     </row>
     <row r="941" ht="24" customHeight="1">
       <c r="A941" s="34"/>
@@ -19985,6 +20929,7 @@
       <c r="C941" s="24"/>
       <c r="D941" s="24"/>
       <c r="E941" s="24"/>
+      <c r="F941" s="24"/>
     </row>
     <row r="942" ht="24" customHeight="1">
       <c r="A942" s="34"/>
@@ -19992,6 +20937,7 @@
       <c r="C942" s="24"/>
       <c r="D942" s="24"/>
       <c r="E942" s="24"/>
+      <c r="F942" s="24"/>
     </row>
     <row r="943" ht="24" customHeight="1">
       <c r="A943" s="34"/>
@@ -19999,6 +20945,7 @@
       <c r="C943" s="24"/>
       <c r="D943" s="24"/>
       <c r="E943" s="24"/>
+      <c r="F943" s="24"/>
     </row>
     <row r="944" ht="24" customHeight="1">
       <c r="A944" s="34"/>
@@ -20006,6 +20953,7 @@
       <c r="C944" s="24"/>
       <c r="D944" s="24"/>
       <c r="E944" s="24"/>
+      <c r="F944" s="24"/>
     </row>
     <row r="945" ht="24" customHeight="1">
       <c r="A945" s="34"/>
@@ -20013,6 +20961,7 @@
       <c r="C945" s="24"/>
       <c r="D945" s="24"/>
       <c r="E945" s="24"/>
+      <c r="F945" s="24"/>
     </row>
     <row r="946" ht="24" customHeight="1">
       <c r="A946" s="34"/>
@@ -20020,6 +20969,7 @@
       <c r="C946" s="24"/>
       <c r="D946" s="24"/>
       <c r="E946" s="24"/>
+      <c r="F946" s="24"/>
     </row>
     <row r="947" ht="24" customHeight="1">
       <c r="A947" s="34"/>
@@ -20027,6 +20977,7 @@
       <c r="C947" s="24"/>
       <c r="D947" s="24"/>
       <c r="E947" s="24"/>
+      <c r="F947" s="24"/>
     </row>
     <row r="948" ht="24" customHeight="1">
       <c r="A948" s="34"/>
@@ -20034,6 +20985,7 @@
       <c r="C948" s="24"/>
       <c r="D948" s="24"/>
       <c r="E948" s="24"/>
+      <c r="F948" s="24"/>
     </row>
     <row r="949" ht="24" customHeight="1">
       <c r="A949" s="34"/>
@@ -20041,6 +20993,7 @@
       <c r="C949" s="24"/>
       <c r="D949" s="24"/>
       <c r="E949" s="24"/>
+      <c r="F949" s="24"/>
     </row>
     <row r="950" ht="24" customHeight="1">
       <c r="A950" s="34"/>
@@ -20048,6 +21001,7 @@
       <c r="C950" s="24"/>
       <c r="D950" s="24"/>
       <c r="E950" s="24"/>
+      <c r="F950" s="24"/>
     </row>
     <row r="951" ht="24" customHeight="1">
       <c r="A951" s="34"/>
@@ -20055,6 +21009,7 @@
       <c r="C951" s="24"/>
       <c r="D951" s="24"/>
       <c r="E951" s="24"/>
+      <c r="F951" s="24"/>
     </row>
     <row r="952" ht="24" customHeight="1">
       <c r="A952" s="34"/>
@@ -20062,6 +21017,7 @@
       <c r="C952" s="24"/>
       <c r="D952" s="24"/>
       <c r="E952" s="24"/>
+      <c r="F952" s="24"/>
     </row>
     <row r="953" ht="24" customHeight="1">
       <c r="A953" s="34"/>
@@ -20069,6 +21025,7 @@
       <c r="C953" s="24"/>
       <c r="D953" s="24"/>
       <c r="E953" s="24"/>
+      <c r="F953" s="24"/>
     </row>
     <row r="954" ht="24" customHeight="1">
       <c r="A954" s="34"/>
@@ -20076,6 +21033,7 @@
       <c r="C954" s="24"/>
       <c r="D954" s="24"/>
       <c r="E954" s="24"/>
+      <c r="F954" s="24"/>
     </row>
     <row r="955" ht="24" customHeight="1">
       <c r="A955" s="34"/>
@@ -20083,6 +21041,7 @@
       <c r="C955" s="24"/>
       <c r="D955" s="24"/>
       <c r="E955" s="24"/>
+      <c r="F955" s="24"/>
     </row>
     <row r="956" ht="24" customHeight="1">
       <c r="A956" s="34"/>
@@ -20090,6 +21049,7 @@
       <c r="C956" s="24"/>
       <c r="D956" s="24"/>
       <c r="E956" s="24"/>
+      <c r="F956" s="24"/>
     </row>
     <row r="957" ht="24" customHeight="1">
       <c r="A957" s="34"/>
@@ -20097,6 +21057,7 @@
       <c r="C957" s="24"/>
       <c r="D957" s="24"/>
       <c r="E957" s="24"/>
+      <c r="F957" s="24"/>
     </row>
     <row r="958" ht="24" customHeight="1">
       <c r="A958" s="34"/>
@@ -20104,6 +21065,7 @@
       <c r="C958" s="24"/>
       <c r="D958" s="24"/>
       <c r="E958" s="24"/>
+      <c r="F958" s="24"/>
     </row>
     <row r="959" ht="24" customHeight="1">
       <c r="A959" s="34"/>
@@ -20111,6 +21073,7 @@
       <c r="C959" s="24"/>
       <c r="D959" s="24"/>
       <c r="E959" s="24"/>
+      <c r="F959" s="24"/>
     </row>
     <row r="960" ht="24" customHeight="1">
       <c r="A960" s="34"/>
@@ -20118,6 +21081,7 @@
       <c r="C960" s="24"/>
       <c r="D960" s="24"/>
       <c r="E960" s="24"/>
+      <c r="F960" s="24"/>
     </row>
     <row r="961" ht="24" customHeight="1">
       <c r="A961" s="34"/>
@@ -20125,6 +21089,7 @@
       <c r="C961" s="24"/>
       <c r="D961" s="24"/>
       <c r="E961" s="24"/>
+      <c r="F961" s="24"/>
     </row>
     <row r="962" ht="24" customHeight="1">
       <c r="A962" s="34"/>
@@ -20132,6 +21097,7 @@
       <c r="C962" s="24"/>
       <c r="D962" s="24"/>
       <c r="E962" s="24"/>
+      <c r="F962" s="24"/>
     </row>
     <row r="963" ht="24" customHeight="1">
       <c r="A963" s="34"/>
@@ -20139,6 +21105,7 @@
       <c r="C963" s="24"/>
       <c r="D963" s="24"/>
       <c r="E963" s="24"/>
+      <c r="F963" s="24"/>
     </row>
     <row r="964" ht="24" customHeight="1">
       <c r="A964" s="34"/>
@@ -20146,6 +21113,7 @@
       <c r="C964" s="24"/>
       <c r="D964" s="24"/>
       <c r="E964" s="24"/>
+      <c r="F964" s="24"/>
     </row>
     <row r="965" ht="24" customHeight="1">
       <c r="A965" s="34"/>
@@ -20153,6 +21121,7 @@
       <c r="C965" s="24"/>
       <c r="D965" s="24"/>
       <c r="E965" s="24"/>
+      <c r="F965" s="24"/>
     </row>
     <row r="966" ht="24" customHeight="1">
       <c r="A966" s="34"/>
@@ -20160,6 +21129,7 @@
       <c r="C966" s="24"/>
       <c r="D966" s="24"/>
       <c r="E966" s="24"/>
+      <c r="F966" s="24"/>
     </row>
     <row r="967" ht="24" customHeight="1">
       <c r="A967" s="34"/>
@@ -20167,6 +21137,7 @@
       <c r="C967" s="24"/>
       <c r="D967" s="24"/>
       <c r="E967" s="24"/>
+      <c r="F967" s="24"/>
     </row>
     <row r="968" ht="24" customHeight="1">
       <c r="A968" s="34"/>
@@ -20174,6 +21145,7 @@
       <c r="C968" s="24"/>
       <c r="D968" s="24"/>
       <c r="E968" s="24"/>
+      <c r="F968" s="24"/>
     </row>
     <row r="969" ht="24" customHeight="1">
       <c r="A969" s="34"/>
@@ -20181,6 +21153,7 @@
       <c r="C969" s="24"/>
       <c r="D969" s="24"/>
       <c r="E969" s="24"/>
+      <c r="F969" s="24"/>
     </row>
     <row r="970" ht="24" customHeight="1">
       <c r="A970" s="34"/>
@@ -20188,6 +21161,7 @@
       <c r="C970" s="24"/>
       <c r="D970" s="24"/>
       <c r="E970" s="24"/>
+      <c r="F970" s="24"/>
     </row>
     <row r="971" ht="24" customHeight="1">
       <c r="A971" s="34"/>
@@ -20195,6 +21169,7 @@
       <c r="C971" s="24"/>
       <c r="D971" s="24"/>
       <c r="E971" s="24"/>
+      <c r="F971" s="24"/>
     </row>
     <row r="972" ht="24" customHeight="1">
       <c r="A972" s="34"/>
@@ -20202,6 +21177,7 @@
       <c r="C972" s="24"/>
       <c r="D972" s="24"/>
       <c r="E972" s="24"/>
+      <c r="F972" s="24"/>
     </row>
     <row r="973" ht="24" customHeight="1">
       <c r="A973" s="34"/>
@@ -20209,6 +21185,7 @@
       <c r="C973" s="24"/>
       <c r="D973" s="24"/>
       <c r="E973" s="24"/>
+      <c r="F973" s="24"/>
     </row>
     <row r="974" ht="24" customHeight="1">
       <c r="A974" s="34"/>
@@ -20216,6 +21193,7 @@
       <c r="C974" s="24"/>
       <c r="D974" s="24"/>
       <c r="E974" s="24"/>
+      <c r="F974" s="24"/>
     </row>
     <row r="975" ht="24" customHeight="1">
       <c r="A975" s="34"/>
@@ -20223,6 +21201,7 @@
       <c r="C975" s="24"/>
       <c r="D975" s="24"/>
       <c r="E975" s="24"/>
+      <c r="F975" s="24"/>
     </row>
     <row r="976" ht="24" customHeight="1">
       <c r="A976" s="34"/>
@@ -20230,6 +21209,7 @@
       <c r="C976" s="24"/>
       <c r="D976" s="24"/>
       <c r="E976" s="24"/>
+      <c r="F976" s="24"/>
     </row>
     <row r="977" ht="24" customHeight="1">
       <c r="A977" s="34"/>
@@ -20237,6 +21217,7 @@
       <c r="C977" s="24"/>
       <c r="D977" s="24"/>
       <c r="E977" s="24"/>
+      <c r="F977" s="24"/>
     </row>
     <row r="978" ht="24" customHeight="1">
       <c r="A978" s="34"/>
@@ -20244,6 +21225,7 @@
       <c r="C978" s="24"/>
       <c r="D978" s="24"/>
       <c r="E978" s="24"/>
+      <c r="F978" s="24"/>
     </row>
     <row r="979" ht="24" customHeight="1">
       <c r="A979" s="34"/>
@@ -20251,6 +21233,7 @@
       <c r="C979" s="24"/>
       <c r="D979" s="24"/>
       <c r="E979" s="24"/>
+      <c r="F979" s="24"/>
     </row>
     <row r="980" ht="24" customHeight="1">
       <c r="A980" s="34"/>
@@ -20258,6 +21241,7 @@
       <c r="C980" s="24"/>
       <c r="D980" s="24"/>
       <c r="E980" s="24"/>
+      <c r="F980" s="24"/>
     </row>
     <row r="981" ht="24" customHeight="1">
       <c r="A981" s="34"/>
@@ -20265,6 +21249,7 @@
       <c r="C981" s="24"/>
       <c r="D981" s="24"/>
       <c r="E981" s="24"/>
+      <c r="F981" s="24"/>
     </row>
     <row r="982" ht="24" customHeight="1">
       <c r="A982" s="34"/>
@@ -20272,6 +21257,7 @@
       <c r="C982" s="24"/>
       <c r="D982" s="24"/>
       <c r="E982" s="24"/>
+      <c r="F982" s="24"/>
     </row>
     <row r="983" ht="24" customHeight="1">
       <c r="A983" s="34"/>
@@ -20279,6 +21265,7 @@
       <c r="C983" s="24"/>
       <c r="D983" s="24"/>
       <c r="E983" s="24"/>
+      <c r="F983" s="24"/>
     </row>
     <row r="984" ht="24" customHeight="1">
       <c r="A984" s="34"/>
@@ -20286,6 +21273,7 @@
       <c r="C984" s="24"/>
       <c r="D984" s="24"/>
       <c r="E984" s="24"/>
+      <c r="F984" s="24"/>
     </row>
     <row r="985" ht="24" customHeight="1">
       <c r="A985" s="34"/>
@@ -20293,6 +21281,7 @@
       <c r="C985" s="24"/>
       <c r="D985" s="24"/>
       <c r="E985" s="24"/>
+      <c r="F985" s="24"/>
     </row>
     <row r="986" ht="24" customHeight="1">
       <c r="A986" s="34"/>
@@ -20300,6 +21289,7 @@
       <c r="C986" s="24"/>
       <c r="D986" s="24"/>
       <c r="E986" s="24"/>
+      <c r="F986" s="24"/>
     </row>
     <row r="987" ht="24" customHeight="1">
       <c r="A987" s="34"/>
@@ -20307,6 +21297,7 @@
       <c r="C987" s="24"/>
       <c r="D987" s="24"/>
       <c r="E987" s="24"/>
+      <c r="F987" s="24"/>
     </row>
     <row r="988" ht="24" customHeight="1">
       <c r="A988" s="34"/>
@@ -20314,6 +21305,7 @@
       <c r="C988" s="24"/>
       <c r="D988" s="24"/>
       <c r="E988" s="24"/>
+      <c r="F988" s="24"/>
     </row>
     <row r="989" ht="24" customHeight="1">
       <c r="A989" s="34"/>
@@ -20321,6 +21313,7 @@
       <c r="C989" s="24"/>
       <c r="D989" s="24"/>
       <c r="E989" s="24"/>
+      <c r="F989" s="24"/>
     </row>
     <row r="990" ht="24" customHeight="1">
       <c r="A990" s="34"/>
@@ -20328,6 +21321,7 @@
       <c r="C990" s="24"/>
       <c r="D990" s="24"/>
       <c r="E990" s="24"/>
+      <c r="F990" s="24"/>
     </row>
     <row r="991" ht="24" customHeight="1">
       <c r="A991" s="34"/>
@@ -20335,6 +21329,7 @@
       <c r="C991" s="24"/>
       <c r="D991" s="24"/>
       <c r="E991" s="24"/>
+      <c r="F991" s="24"/>
     </row>
     <row r="992" ht="24" customHeight="1">
       <c r="A992" s="34"/>
@@ -20342,6 +21337,7 @@
       <c r="C992" s="24"/>
       <c r="D992" s="24"/>
       <c r="E992" s="24"/>
+      <c r="F992" s="24"/>
     </row>
     <row r="993" ht="24" customHeight="1">
       <c r="A993" s="34"/>
@@ -20349,6 +21345,7 @@
       <c r="C993" s="24"/>
       <c r="D993" s="24"/>
       <c r="E993" s="24"/>
+      <c r="F993" s="24"/>
     </row>
     <row r="994" ht="24" customHeight="1">
       <c r="A994" s="34"/>
@@ -20356,6 +21353,7 @@
       <c r="C994" s="24"/>
       <c r="D994" s="24"/>
       <c r="E994" s="24"/>
+      <c r="F994" s="24"/>
     </row>
     <row r="995" ht="24" customHeight="1">
       <c r="A995" s="34"/>
@@ -20363,6 +21361,7 @@
       <c r="C995" s="24"/>
       <c r="D995" s="24"/>
       <c r="E995" s="24"/>
+      <c r="F995" s="24"/>
     </row>
     <row r="996" ht="24" customHeight="1">
       <c r="A996" s="34"/>
@@ -20370,6 +21369,7 @@
       <c r="C996" s="24"/>
       <c r="D996" s="24"/>
       <c r="E996" s="24"/>
+      <c r="F996" s="24"/>
     </row>
     <row r="997" ht="24" customHeight="1">
       <c r="A997" s="34"/>
@@ -20377,6 +21377,7 @@
       <c r="C997" s="24"/>
       <c r="D997" s="24"/>
       <c r="E997" s="24"/>
+      <c r="F997" s="24"/>
     </row>
     <row r="998" ht="24" customHeight="1">
       <c r="A998" s="34"/>
@@ -20384,6 +21385,7 @@
       <c r="C998" s="24"/>
       <c r="D998" s="24"/>
       <c r="E998" s="24"/>
+      <c r="F998" s="24"/>
     </row>
     <row r="999" ht="24" customHeight="1">
       <c r="A999" s="34"/>
@@ -20391,6 +21393,7 @@
       <c r="C999" s="24"/>
       <c r="D999" s="24"/>
       <c r="E999" s="24"/>
+      <c r="F999" s="24"/>
     </row>
     <row r="1000" ht="24" customHeight="1">
       <c r="A1000" s="34"/>
@@ -20398,6 +21401,7 @@
       <c r="C1000" s="24"/>
       <c r="D1000" s="24"/>
       <c r="E1000" s="24"/>
+      <c r="F1000" s="24"/>
     </row>
     <row r="1001" ht="24" customHeight="1">
       <c r="A1001" s="34"/>
@@ -20405,6 +21409,7 @@
       <c r="C1001" s="24"/>
       <c r="D1001" s="24"/>
       <c r="E1001" s="24"/>
+      <c r="F1001" s="24"/>
     </row>
     <row r="1002" ht="24" customHeight="1">
       <c r="A1002" s="34"/>
@@ -20412,6 +21417,7 @@
       <c r="C1002" s="24"/>
       <c r="D1002" s="24"/>
       <c r="E1002" s="24"/>
+      <c r="F1002" s="24"/>
     </row>
     <row r="1003" ht="24" customHeight="1">
       <c r="A1003" s="34"/>
@@ -20419,6 +21425,7 @@
       <c r="C1003" s="24"/>
       <c r="D1003" s="24"/>
       <c r="E1003" s="24"/>
+      <c r="F1003" s="24"/>
     </row>
     <row r="1004" ht="24" customHeight="1">
       <c r="A1004" s="35"/>
@@ -20426,16 +21433,20 @@
       <c r="C1004" s="25"/>
       <c r="D1004" s="25"/>
       <c r="E1004" s="25"/>
+      <c r="F1004" s="25"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" sqref="B5:B1004">
       <formula1>BookendsHomeCodes</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F5:F1004">
+      <formula1>"Impower,Contractor"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23825de4df94a06"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b349e581d9d4251"/>
   </tableParts>
 </worksheet>
 </file>
@@ -24483,7 +25494,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad79013afd7a4dd0"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbd1f608d2864326"/>
   </tableParts>
 </worksheet>
 </file>
@@ -34576,7 +35587,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19e3df1fd71f4bad"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb91ebfdbafb44212"/>
   </tableParts>
 </worksheet>
 </file>
@@ -45681,7 +46692,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5b0489cd8f24ba3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3042b1e356704bbe"/>
   </tableParts>
 </worksheet>
 </file>
@@ -49724,7 +50735,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f449b77dd014086"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R539f19342de247e2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -53767,7 +54778,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b6a9ebdd13d4fcb"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe95d4f204304f93"/>
   </tableParts>
 </worksheet>
 </file>